--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baray020\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A738344F-A7AC-4A26-AC33-208E3DFBA1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46528205-A4FD-4828-8841-6F7BB72A2BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="1740" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1890" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dotaci" sheetId="1" r:id="rId1"/>
@@ -9699,17 +9699,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -41844,35 +41844,35 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" s="25"/>
-      <c r="C2" s="44">
+      <c r="C2" s="46">
         <v>2026</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
     </row>
     <row r="3" spans="2:14" ht="15.5">
       <c r="B3" s="26"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
     </row>
     <row r="4" spans="2:14" ht="15.5">
       <c r="B4" s="27"/>
@@ -42110,14 +42110,14 @@
         <v>3066</v>
       </c>
       <c r="C14" s="42">
-        <v>4.4000000000000003E-3</v>
+        <v>4.8999999999999998E-3</v>
       </c>
       <c r="D14" s="42">
-        <v>6.9999999999999999E-4</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="E14" s="41">
         <f>SUM(C14:D14)</f>
-        <v>5.1000000000000004E-3</v>
+        <v>5.7999999999999996E-3</v>
       </c>
     </row>
     <row r="15" spans="2:14">
@@ -42125,14 +42125,14 @@
         <v>1843</v>
       </c>
       <c r="C15" s="42">
-        <v>4.4000000000000003E-3</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="D15" s="42">
         <v>1E-4</v>
       </c>
       <c r="E15" s="41">
         <f t="shared" ref="E15:E17" si="0">SUM(C15:D15)</f>
-        <v>4.5000000000000005E-3</v>
+        <v>3.8E-3</v>
       </c>
     </row>
     <row r="16" spans="2:14">
@@ -42140,14 +42140,14 @@
         <v>3067</v>
       </c>
       <c r="C16" s="42">
-        <v>1.9800000000000002E-2</v>
+        <v>1.9300000000000001E-2</v>
       </c>
       <c r="D16" s="42">
-        <v>2.3E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="E16" s="41">
         <f t="shared" si="0"/>
-        <v>2.2100000000000002E-2</v>
+        <v>2.3200000000000002E-2</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -42155,28 +42155,28 @@
         <v>3068</v>
       </c>
       <c r="C17" s="42">
-        <v>6.9999999999999999E-4</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="D17" s="42">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="E17" s="41">
         <f t="shared" si="0"/>
-        <v>2E-3</v>
+        <v>2.8999999999999998E-3</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="C18" s="41">
         <f>SUM(C14:C17)</f>
-        <v>2.93E-2</v>
+        <v>2.9500000000000002E-2</v>
       </c>
       <c r="D18" s="41">
         <f>SUM(D14:D17)</f>
-        <v>4.3999999999999994E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="E18" s="41">
         <f>SUM(E14:E17)</f>
-        <v>3.3700000000000008E-2</v>
+        <v>3.5700000000000003E-2</v>
       </c>
     </row>
     <row r="21" spans="2:5">
@@ -42189,7 +42189,7 @@
         <v>3066</v>
       </c>
       <c r="C22" s="42">
-        <v>0</v>
+        <v>9.1999999999999998E-3</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -42197,7 +42197,7 @@
         <v>1843</v>
       </c>
       <c r="C23" s="42">
-        <v>1.6999999999999999E-3</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="24" spans="2:5">
@@ -42205,7 +42205,7 @@
         <v>3067</v>
       </c>
       <c r="C24" s="42">
-        <v>1.5900000000000001E-2</v>
+        <v>1.55E-2</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -42213,13 +42213,13 @@
         <v>3068</v>
       </c>
       <c r="C25" s="42">
-        <v>5.0000000000000001E-4</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="26" spans="2:5">
       <c r="C26" s="41">
         <f>SUM(C22:C25)</f>
-        <v>1.8100000000000002E-2</v>
+        <v>2.8700000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="2:5">
@@ -42227,7 +42227,7 @@
         <v>3069</v>
       </c>
       <c r="C28" s="42">
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="29" spans="2:5">
@@ -42235,7 +42235,7 @@
         <v>3070</v>
       </c>
       <c r="C29" s="42">
-        <v>1.8100000000000002E-2</v>
+        <v>2.8199999999999999E-2</v>
       </c>
     </row>
   </sheetData>
@@ -42258,32 +42258,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9">
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="47" t="s">
         <v>3083</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="E1" s="45" t="s">
+      <c r="C1" s="47"/>
+      <c r="E1" s="47" t="s">
         <v>3084</v>
       </c>
-      <c r="F1" s="45"/>
-      <c r="H1" s="46" t="s">
+      <c r="F1" s="47"/>
+      <c r="H1" s="44" t="s">
         <v>3090</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="I1" s="44" t="s">
         <v>3091</v>
       </c>
     </row>
     <row r="2" spans="2:9">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="44" t="s">
         <v>3075</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="44" t="s">
         <v>3076</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="44" t="s">
         <v>3075</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="F2" s="44" t="s">
         <v>3076</v>
       </c>
       <c r="H2" s="41">
@@ -42298,7 +42298,7 @@
         <v>3077</v>
       </c>
       <c r="C3" s="39"/>
-      <c r="E3" s="47" t="s">
+      <c r="E3" s="45" t="s">
         <v>3089</v>
       </c>
       <c r="F3" s="39">
@@ -42310,7 +42310,7 @@
         <v>3078</v>
       </c>
       <c r="C4" s="39"/>
-      <c r="E4" s="47" t="s">
+      <c r="E4" s="45" t="s">
         <v>3085</v>
       </c>
       <c r="F4" s="39"/>
@@ -42322,7 +42322,7 @@
       <c r="C5" s="39">
         <v>1</v>
       </c>
-      <c r="E5" s="47" t="s">
+      <c r="E5" s="45" t="s">
         <v>3086</v>
       </c>
       <c r="F5" s="39"/>
@@ -42332,7 +42332,7 @@
         <v>3080</v>
       </c>
       <c r="C6" s="39"/>
-      <c r="E6" s="47" t="s">
+      <c r="E6" s="45" t="s">
         <v>3087</v>
       </c>
       <c r="F6" s="39"/>
@@ -42344,7 +42344,7 @@
       <c r="C7" s="39">
         <v>3</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="45" t="s">
         <v>3088</v>
       </c>
       <c r="F7" s="39"/>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baray020\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46528205-A4FD-4828-8841-6F7BB72A2BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6942051-055F-44F6-9FC6-592198C7A7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1890" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="1740" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dotaci" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6225" uniqueCount="3092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6209" uniqueCount="3089">
   <si>
     <t>HENRIQUEZ POOL FELIPE ALBERTO</t>
   </si>
@@ -9159,18 +9159,9 @@
     <t>SILVA VALDIVIA CRISTIAN LEONAR</t>
   </si>
   <si>
-    <t>VILLALON LOPEZ RODRIGO ALEJAND</t>
-  </si>
-  <si>
     <t>Nueva</t>
   </si>
   <si>
-    <t>IBACACHE PIZARRO IDECIO ENRIQU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urología </t>
-  </si>
-  <si>
     <t>VILLALON CISTERNAS RICARDO ANT</t>
   </si>
   <si>
@@ -9255,18 +9246,12 @@
     <t>Interrupcion de descanso</t>
   </si>
   <si>
-    <t xml:space="preserve">Continuación </t>
-  </si>
-  <si>
     <t>Traumatología</t>
   </si>
   <si>
     <t xml:space="preserve">Medicina General </t>
   </si>
   <si>
-    <t xml:space="preserve">Nueva </t>
-  </si>
-  <si>
     <t>Etapa</t>
   </si>
   <si>
@@ -9316,6 +9301,12 @@
   </si>
   <si>
     <t>% Actual</t>
+  </si>
+  <si>
+    <t>Acum.</t>
+  </si>
+  <si>
+    <t>CACERES RODRIGUEZ CLAUDIA ELIS</t>
   </si>
 </sst>
 </file>
@@ -40911,7 +40902,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D3B0B5-E7CA-41F3-B584-8BB10868D96B}">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.54296875" customWidth="1"/>
@@ -40922,14 +40913,15 @@
     <col min="6" max="7" width="7.36328125" customWidth="1"/>
     <col min="8" max="9" width="12.6328125" customWidth="1"/>
     <col min="10" max="10" width="6.7265625" customWidth="1"/>
-    <col min="11" max="11" width="20.26953125" customWidth="1"/>
-    <col min="12" max="12" width="14.7265625" customWidth="1"/>
-    <col min="13" max="13" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13.6328125" customWidth="1"/>
-    <col min="16" max="16" width="38.6328125" customWidth="1"/>
+    <col min="11" max="11" width="9.36328125" customWidth="1"/>
+    <col min="12" max="12" width="20.26953125" customWidth="1"/>
+    <col min="13" max="13" width="14.7265625" customWidth="1"/>
+    <col min="14" max="14" width="21.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13.6328125" customWidth="1"/>
+    <col min="17" max="17" width="38.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="58">
+    <row r="1" spans="1:17" ht="58">
       <c r="A1" s="18" t="s">
         <v>2543</v>
       </c>
@@ -40961,25 +40953,28 @@
         <v>3028</v>
       </c>
       <c r="K1" s="18" t="s">
+        <v>3087</v>
+      </c>
+      <c r="L1" s="18" t="s">
         <v>3029</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="M1" s="18" t="s">
         <v>3030</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="N1" s="18" t="s">
         <v>3031</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="O1" s="18" t="s">
         <v>3032</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="P1" s="18" t="s">
         <v>3033</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="Q1" s="18" t="s">
         <v>3034</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" s="20">
         <v>39653</v>
       </c>
@@ -41010,84 +41005,90 @@
       <c r="J2" s="20">
         <v>30</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="20">
+        <v>716</v>
+      </c>
+      <c r="L2" s="22" t="s">
         <v>3036</v>
       </c>
-      <c r="L2" s="22" t="s">
-        <v>3071</v>
-      </c>
       <c r="M2" s="22" t="s">
-        <v>3072</v>
-      </c>
-      <c r="N2" s="23">
+        <v>3030</v>
+      </c>
+      <c r="N2" s="22" t="s">
+        <v>3068</v>
+      </c>
+      <c r="O2" s="23">
         <v>359</v>
       </c>
-      <c r="O2" s="23">
+      <c r="P2" s="23">
         <v>716</v>
       </c>
-      <c r="P2" s="22" t="s">
+      <c r="Q2" s="22" t="s">
         <v>2572</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17">
       <c r="A3" s="20">
+        <v>39667</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>3088</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>3020</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>2565</v>
+      </c>
+      <c r="H3" s="24">
+        <v>46195</v>
+      </c>
+      <c r="I3" s="24">
+        <v>46205</v>
+      </c>
+      <c r="J3" s="20">
+        <v>11</v>
+      </c>
+      <c r="K3" s="20">
+        <v>11</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>3036</v>
+      </c>
+      <c r="M3" s="22" t="s">
+        <v>3039</v>
+      </c>
+      <c r="N3" s="22" t="s">
+        <v>3043</v>
+      </c>
+      <c r="O3" s="23">
+        <v>92</v>
+      </c>
+      <c r="P3" s="23">
+        <v>136</v>
+      </c>
+      <c r="Q3" s="22" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="20">
         <v>51900</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B4" s="21" t="s">
         <v>682</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C4" s="21" t="s">
         <v>681</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>3022</v>
-      </c>
-      <c r="G3" s="23">
-        <v>1</v>
-      </c>
-      <c r="H3" s="24">
-        <v>46189</v>
-      </c>
-      <c r="I3" s="24">
-        <v>46190</v>
-      </c>
-      <c r="J3" s="20">
-        <v>2</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>3036</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>3040</v>
-      </c>
-      <c r="M3" s="22" t="s">
-        <v>3072</v>
-      </c>
-      <c r="N3" s="23">
-        <v>2</v>
-      </c>
-      <c r="O3" s="23">
-        <v>41</v>
-      </c>
-      <c r="P3" s="22" t="s">
-        <v>2572</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="20">
-        <v>51906</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>704</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>3037</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>92</v>
@@ -41099,45 +41100,48 @@
         <v>3022</v>
       </c>
       <c r="G4" s="23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H4" s="24">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="I4" s="24">
-        <v>46219</v>
+        <v>46196</v>
       </c>
       <c r="J4" s="20">
-        <v>30</v>
-      </c>
-      <c r="K4" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="20">
+        <v>8</v>
+      </c>
+      <c r="L4" s="22" t="s">
         <v>3036</v>
       </c>
-      <c r="L4" s="22" t="s">
-        <v>3071</v>
-      </c>
       <c r="M4" s="22" t="s">
-        <v>3072</v>
-      </c>
-      <c r="N4" s="23">
-        <v>390</v>
+        <v>3030</v>
+      </c>
+      <c r="N4" s="22" t="s">
+        <v>3068</v>
       </c>
       <c r="O4" s="23">
-        <v>750</v>
-      </c>
-      <c r="P4" s="22" t="s">
-        <v>2570</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>8</v>
+      </c>
+      <c r="P4" s="23">
+        <v>47</v>
+      </c>
+      <c r="Q4" s="22" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="20">
-        <v>51908</v>
+        <v>51906</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="D5" s="22" t="s">
         <v>92</v>
@@ -41149,45 +41153,48 @@
         <v>3022</v>
       </c>
       <c r="G5" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" s="24">
-        <v>46161</v>
+        <v>46190</v>
       </c>
       <c r="I5" s="24">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="J5" s="20">
-        <v>60</v>
-      </c>
-      <c r="K5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="20">
+        <v>912</v>
+      </c>
+      <c r="L5" s="22" t="s">
         <v>3036</v>
       </c>
-      <c r="L5" s="22" t="s">
-        <v>3071</v>
-      </c>
       <c r="M5" s="22" t="s">
-        <v>3072</v>
-      </c>
-      <c r="N5" s="23">
-        <v>390</v>
+        <v>3030</v>
+      </c>
+      <c r="N5" s="22" t="s">
+        <v>3068</v>
       </c>
       <c r="O5" s="23">
-        <v>735</v>
-      </c>
-      <c r="P5" s="22" t="s">
-        <v>2572</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>360</v>
+      </c>
+      <c r="P5" s="23">
+        <v>750</v>
+      </c>
+      <c r="Q5" s="22" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="20">
-        <v>51915</v>
+        <v>51908</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>745</v>
+        <v>715</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="D6" s="22" t="s">
         <v>92</v>
@@ -41199,48 +41206,51 @@
         <v>3022</v>
       </c>
       <c r="G6" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="24">
-        <v>46181</v>
+        <v>46161</v>
       </c>
       <c r="I6" s="24">
-        <v>46187</v>
+        <v>46220</v>
       </c>
       <c r="J6" s="20">
-        <v>7</v>
-      </c>
-      <c r="K6" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="20">
+        <v>1145</v>
+      </c>
+      <c r="L6" s="22" t="s">
         <v>3036</v>
       </c>
-      <c r="L6" s="22" t="s">
-        <v>3071</v>
-      </c>
       <c r="M6" s="22" t="s">
-        <v>3073</v>
-      </c>
-      <c r="N6" s="23">
-        <v>7</v>
+        <v>3030</v>
+      </c>
+      <c r="N6" s="22" t="s">
+        <v>3068</v>
       </c>
       <c r="O6" s="23">
-        <v>7</v>
-      </c>
-      <c r="P6" s="22" t="s">
-        <v>2570</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>345</v>
+      </c>
+      <c r="P6" s="23">
+        <v>735</v>
+      </c>
+      <c r="Q6" s="22" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="20">
-        <v>51968</v>
+        <v>53451</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>797</v>
+        <v>1121</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>585</v>
+        <v>130</v>
       </c>
       <c r="E7" s="22" t="s">
         <v>37</v>
@@ -41252,45 +41262,48 @@
         <v>4</v>
       </c>
       <c r="H7" s="24">
-        <v>46169</v>
+        <v>46189</v>
       </c>
       <c r="I7" s="24">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="J7" s="20">
-        <v>21</v>
-      </c>
-      <c r="K7" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="20">
+        <v>22</v>
+      </c>
+      <c r="L7" s="22" t="s">
         <v>3036</v>
       </c>
-      <c r="L7" s="22" t="s">
-        <v>3071</v>
-      </c>
       <c r="M7" s="22" t="s">
-        <v>3042</v>
-      </c>
-      <c r="N7" s="23">
-        <v>21</v>
+        <v>3030</v>
+      </c>
+      <c r="N7" s="22" t="s">
+        <v>3069</v>
       </c>
       <c r="O7" s="23">
-        <v>21</v>
-      </c>
-      <c r="P7" s="22" t="s">
-        <v>2570</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>22</v>
+      </c>
+      <c r="P7" s="23">
+        <v>166</v>
+      </c>
+      <c r="Q7" s="22" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="20">
-        <v>51973</v>
+        <v>53848</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>807</v>
+        <v>1202</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>806</v>
+        <v>3041</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="E8" s="22" t="s">
         <v>37</v>
@@ -41302,45 +41315,48 @@
         <v>2</v>
       </c>
       <c r="H8" s="24">
-        <v>46177</v>
+        <v>46170</v>
       </c>
       <c r="I8" s="24">
-        <v>46184</v>
+        <v>46199</v>
       </c>
       <c r="J8" s="20">
-        <v>8</v>
-      </c>
-      <c r="K8" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="20">
+        <v>60</v>
+      </c>
+      <c r="L8" s="22" t="s">
         <v>3036</v>
       </c>
-      <c r="L8" s="22" t="s">
-        <v>3074</v>
-      </c>
       <c r="M8" s="22" t="s">
-        <v>3073</v>
-      </c>
-      <c r="N8" s="23">
-        <v>21</v>
+        <v>3030</v>
+      </c>
+      <c r="N8" s="22" t="s">
+        <v>3068</v>
       </c>
       <c r="O8" s="23">
-        <v>29</v>
-      </c>
-      <c r="P8" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="P8" s="23">
+        <v>145</v>
+      </c>
+      <c r="Q8" s="22" t="s">
         <v>2570</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:17">
       <c r="A9" s="20">
-        <v>53451</v>
+        <v>56288</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>1121</v>
+        <v>1437</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="E9" s="22" t="s">
         <v>37</v>
@@ -41349,98 +41365,104 @@
         <v>3022</v>
       </c>
       <c r="G9" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9" s="24">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="I9" s="24">
-        <v>46199</v>
+        <v>46204</v>
       </c>
       <c r="J9" s="20">
-        <v>11</v>
-      </c>
-      <c r="K9" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="20">
+        <v>110</v>
+      </c>
+      <c r="L9" s="22" t="s">
         <v>3036</v>
       </c>
-      <c r="L9" s="22" t="s">
-        <v>3071</v>
-      </c>
       <c r="M9" s="22" t="s">
-        <v>3073</v>
-      </c>
-      <c r="N9" s="23">
-        <v>22</v>
+        <v>3030</v>
+      </c>
+      <c r="N9" s="22" t="s">
+        <v>3068</v>
       </c>
       <c r="O9" s="23">
-        <v>166</v>
-      </c>
-      <c r="P9" s="22" t="s">
-        <v>2572</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>130</v>
+      </c>
+      <c r="P9" s="23">
+        <v>229</v>
+      </c>
+      <c r="Q9" s="22" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="20">
-        <v>53848</v>
+        <v>56561</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>1202</v>
+        <v>1461</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>3044</v>
+        <v>1460</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F10" s="23" t="s">
         <v>3022</v>
       </c>
       <c r="G10" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="24">
-        <v>46170</v>
+        <v>46189</v>
       </c>
       <c r="I10" s="24">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="J10" s="20">
-        <v>30</v>
-      </c>
-      <c r="K10" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="20">
+        <v>15</v>
+      </c>
+      <c r="L10" s="22" t="s">
         <v>3036</v>
       </c>
-      <c r="L10" s="22" t="s">
-        <v>3071</v>
-      </c>
       <c r="M10" s="22" t="s">
-        <v>3072</v>
-      </c>
-      <c r="N10" s="23">
-        <v>90</v>
+        <v>3039</v>
+      </c>
+      <c r="N10" s="22" t="s">
+        <v>3069</v>
       </c>
       <c r="O10" s="23">
-        <v>145</v>
-      </c>
-      <c r="P10" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="P10" s="23">
+        <v>44</v>
+      </c>
+      <c r="Q10" s="22" t="s">
         <v>2570</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:17">
       <c r="A11" s="20">
-        <v>56288</v>
+        <v>59381</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>1437</v>
+        <v>1547</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="E11" s="22" t="s">
         <v>37</v>
@@ -41449,98 +41471,104 @@
         <v>3022</v>
       </c>
       <c r="G11" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="24">
-        <v>46191</v>
+        <v>46178</v>
       </c>
       <c r="I11" s="24">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="J11" s="20">
-        <v>14</v>
-      </c>
-      <c r="K11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="20">
+        <v>261</v>
+      </c>
+      <c r="L11" s="22" t="s">
         <v>3036</v>
       </c>
-      <c r="L11" s="22" t="s">
-        <v>3071</v>
-      </c>
       <c r="M11" s="22" t="s">
-        <v>3046</v>
-      </c>
-      <c r="N11" s="23">
-        <v>130</v>
+        <v>3030</v>
+      </c>
+      <c r="N11" s="22" t="s">
+        <v>3068</v>
       </c>
       <c r="O11" s="23">
-        <v>229</v>
-      </c>
-      <c r="P11" s="22" t="s">
-        <v>2570</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>261</v>
+      </c>
+      <c r="P11" s="23">
+        <v>264</v>
+      </c>
+      <c r="Q11" s="22" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="20">
-        <v>56561</v>
+        <v>59385</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>1461</v>
+        <v>1568</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>1460</v>
+        <v>3045</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="F12" s="23" t="s">
         <v>3022</v>
       </c>
       <c r="G12" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" s="24">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="I12" s="24">
-        <v>46203</v>
+        <v>46216</v>
       </c>
       <c r="J12" s="20">
-        <v>15</v>
-      </c>
-      <c r="K12" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="20">
+        <v>76</v>
+      </c>
+      <c r="L12" s="22" t="s">
         <v>3036</v>
       </c>
-      <c r="L12" s="22" t="s">
-        <v>3040</v>
-      </c>
       <c r="M12" s="22" t="s">
-        <v>3073</v>
-      </c>
-      <c r="N12" s="23">
-        <v>40</v>
+        <v>3030</v>
+      </c>
+      <c r="N12" s="22" t="s">
+        <v>3068</v>
       </c>
       <c r="O12" s="23">
-        <v>44</v>
-      </c>
-      <c r="P12" s="22" t="s">
-        <v>2570</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>76</v>
+      </c>
+      <c r="P12" s="23">
+        <v>76</v>
+      </c>
+      <c r="Q12" s="22" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="20">
-        <v>59381</v>
+        <v>59387</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>1547</v>
+        <v>1579</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>3047</v>
+        <v>1578</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="E13" s="22" t="s">
         <v>37</v>
@@ -41552,280 +41580,192 @@
         <v>1</v>
       </c>
       <c r="H13" s="24">
-        <v>46178</v>
+        <v>46163</v>
       </c>
       <c r="I13" s="24">
-        <v>46207</v>
+        <v>46192</v>
       </c>
       <c r="J13" s="20">
         <v>30</v>
       </c>
-      <c r="K13" s="22" t="s">
+      <c r="K13" s="20">
+        <v>204</v>
+      </c>
+      <c r="L13" s="22" t="s">
         <v>3036</v>
       </c>
-      <c r="L13" s="22" t="s">
-        <v>3071</v>
-      </c>
       <c r="M13" s="22" t="s">
-        <v>3072</v>
-      </c>
-      <c r="N13" s="23">
-        <v>261</v>
+        <v>3030</v>
+      </c>
+      <c r="N13" s="22" t="s">
+        <v>3068</v>
       </c>
       <c r="O13" s="23">
-        <v>264</v>
-      </c>
-      <c r="P13" s="22" t="s">
-        <v>2572</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>211</v>
+      </c>
+      <c r="P13" s="23">
+        <v>236</v>
+      </c>
+      <c r="Q13" s="22" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="20">
-        <v>59385</v>
+        <v>59401</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>1568</v>
+        <v>1605</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>3048</v>
+        <v>1604</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F14" s="23" t="s">
         <v>3022</v>
       </c>
       <c r="G14" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" s="24">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="I14" s="24">
-        <v>46216</v>
+        <v>46209</v>
       </c>
       <c r="J14" s="20">
-        <v>26</v>
-      </c>
-      <c r="K14" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="20">
+        <v>21</v>
+      </c>
+      <c r="L14" s="22" t="s">
         <v>3036</v>
       </c>
-      <c r="L14" s="22" t="s">
-        <v>3071</v>
-      </c>
       <c r="M14" s="22" t="s">
-        <v>3072</v>
-      </c>
-      <c r="N14" s="23">
-        <v>76</v>
+        <v>3039</v>
+      </c>
+      <c r="N14" s="22" t="s">
+        <v>3068</v>
       </c>
       <c r="O14" s="23">
-        <v>76</v>
-      </c>
-      <c r="P14" s="22" t="s">
-        <v>2572</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <v>21</v>
+      </c>
+      <c r="P14" s="23">
+        <v>35</v>
+      </c>
+      <c r="Q14" s="22" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="20">
-        <v>59387</v>
+        <v>70535</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>1579</v>
+        <v>1958</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>1578</v>
+        <v>1957</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="F15" s="23" t="s">
         <v>3022</v>
       </c>
       <c r="G15" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="24">
-        <v>46163</v>
+        <v>46184</v>
       </c>
       <c r="I15" s="24">
-        <v>46192</v>
+        <v>46213</v>
       </c>
       <c r="J15" s="20">
         <v>30</v>
       </c>
-      <c r="K15" s="22" t="s">
+      <c r="K15" s="20">
+        <v>60</v>
+      </c>
+      <c r="L15" s="22" t="s">
         <v>3036</v>
       </c>
-      <c r="L15" s="22" t="s">
-        <v>3071</v>
-      </c>
       <c r="M15" s="22" t="s">
-        <v>3072</v>
-      </c>
-      <c r="N15" s="23">
-        <v>211</v>
+        <v>3030</v>
+      </c>
+      <c r="N15" s="22" t="s">
+        <v>3068</v>
       </c>
       <c r="O15" s="23">
-        <v>236</v>
-      </c>
-      <c r="P15" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="P15" s="23">
+        <v>60</v>
+      </c>
+      <c r="Q15" s="22" t="s">
         <v>2570</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:17">
       <c r="A16" s="20">
-        <v>59401</v>
+        <v>74084</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>1605</v>
+        <v>2035</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>1604</v>
+        <v>2034</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>55</v>
+        <v>585</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F16" s="23" t="s">
         <v>3022</v>
       </c>
       <c r="G16" s="23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="24">
-        <v>46189</v>
+        <v>46172</v>
       </c>
       <c r="I16" s="24">
-        <v>46209</v>
+        <v>46201</v>
       </c>
       <c r="J16" s="20">
-        <v>21</v>
-      </c>
-      <c r="K16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="K16" s="20">
+        <v>90</v>
+      </c>
+      <c r="L16" s="22" t="s">
         <v>3036</v>
       </c>
-      <c r="L16" s="22" t="s">
-        <v>3040</v>
-      </c>
       <c r="M16" s="22" t="s">
-        <v>3072</v>
-      </c>
-      <c r="N16" s="23">
-        <v>21</v>
+        <v>3030</v>
+      </c>
+      <c r="N16" s="22" t="s">
+        <v>3068</v>
       </c>
       <c r="O16" s="23">
-        <v>35</v>
-      </c>
-      <c r="P16" s="22" t="s">
-        <v>2570</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="20">
-        <v>70535</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>1958</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>1957</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>3022</v>
-      </c>
-      <c r="G17" s="23">
-        <v>2</v>
-      </c>
-      <c r="H17" s="24">
-        <v>46184</v>
-      </c>
-      <c r="I17" s="24">
-        <v>46213</v>
-      </c>
-      <c r="J17" s="20">
-        <v>30</v>
-      </c>
-      <c r="K17" s="22" t="s">
-        <v>3036</v>
-      </c>
-      <c r="L17" s="22" t="s">
-        <v>3071</v>
-      </c>
-      <c r="M17" s="22" t="s">
-        <v>3072</v>
-      </c>
-      <c r="N17" s="23">
-        <v>60</v>
-      </c>
-      <c r="O17" s="23">
-        <v>60</v>
-      </c>
-      <c r="P17" s="22" t="s">
-        <v>2570</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="20">
-        <v>74084</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>2035</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>2034</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>585</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="23" t="s">
-        <v>3022</v>
-      </c>
-      <c r="G18" s="23">
-        <v>2</v>
-      </c>
-      <c r="H18" s="24">
-        <v>46172</v>
-      </c>
-      <c r="I18" s="24">
-        <v>46201</v>
-      </c>
-      <c r="J18" s="20">
-        <v>30</v>
-      </c>
-      <c r="K18" s="22" t="s">
-        <v>3036</v>
-      </c>
-      <c r="L18" s="22" t="s">
-        <v>3071</v>
-      </c>
-      <c r="M18" s="22" t="s">
-        <v>3072</v>
-      </c>
-      <c r="N18" s="23">
         <v>90</v>
       </c>
-      <c r="O18" s="23">
+      <c r="P16" s="23">
         <v>240</v>
       </c>
-      <c r="P18" s="22" t="s">
+      <c r="Q16" s="22" t="s">
         <v>2572</v>
       </c>
     </row>
@@ -41877,45 +41817,45 @@
     <row r="4" spans="2:14" ht="15.5">
       <c r="B4" s="27"/>
       <c r="C4" s="28" t="s">
+        <v>3046</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>3047</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>3048</v>
+      </c>
+      <c r="F4" s="28" t="s">
         <v>3049</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="G4" s="28" t="s">
         <v>3050</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>3051</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="I4" s="29" t="s">
         <v>3052</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="J4" s="29" t="s">
         <v>3053</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="K4" s="29" t="s">
         <v>3054</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="L4" s="29" t="s">
         <v>3055</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="M4" s="29" t="s">
         <v>3056</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="N4" s="29" t="s">
         <v>3057</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>3058</v>
-      </c>
-      <c r="M4" s="29" t="s">
-        <v>3059</v>
-      </c>
-      <c r="N4" s="29" t="s">
-        <v>3060</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="15.5">
       <c r="B5" s="30" t="s">
-        <v>3061</v>
+        <v>3058</v>
       </c>
       <c r="C5" s="31">
         <v>4.2900000000000001E-2</v>
@@ -41956,7 +41896,7 @@
     </row>
     <row r="6" spans="2:14" ht="15.5">
       <c r="B6" s="33" t="s">
-        <v>3062</v>
+        <v>3059</v>
       </c>
       <c r="C6" s="31">
         <v>9.7999999999999997E-3</v>
@@ -41997,7 +41937,7 @@
     </row>
     <row r="7" spans="2:14" ht="15.5">
       <c r="B7" s="33" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
       <c r="C7" s="34">
         <v>5.2699999999999997E-2</v>
@@ -42068,7 +42008,7 @@
     </row>
     <row r="10" spans="2:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="B10" s="36" t="s">
-        <v>3064</v>
+        <v>3061</v>
       </c>
       <c r="C10" s="37">
         <v>5.8400000000000001E-2</v>
@@ -42096,18 +42036,18 @@
     <row r="11" spans="2:14" ht="15" thickTop="1"/>
     <row r="13" spans="2:14">
       <c r="C13" s="39" t="s">
-        <v>3061</v>
+        <v>3058</v>
       </c>
       <c r="D13" s="39" t="s">
+        <v>3059</v>
+      </c>
+      <c r="E13" s="39" t="s">
         <v>3062</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>3065</v>
       </c>
     </row>
     <row r="14" spans="2:14">
       <c r="B14" s="40" t="s">
-        <v>3066</v>
+        <v>3063</v>
       </c>
       <c r="C14" s="42">
         <v>4.8999999999999998E-3</v>
@@ -42137,7 +42077,7 @@
     </row>
     <row r="16" spans="2:14">
       <c r="B16" s="40" t="s">
-        <v>3067</v>
+        <v>3064</v>
       </c>
       <c r="C16" s="42">
         <v>1.9300000000000001E-2</v>
@@ -42152,7 +42092,7 @@
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="40" t="s">
-        <v>3068</v>
+        <v>3065</v>
       </c>
       <c r="C17" s="42">
         <v>1.6000000000000001E-3</v>
@@ -42181,12 +42121,12 @@
     </row>
     <row r="21" spans="2:5">
       <c r="C21" s="40" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="43" t="s">
-        <v>3066</v>
+        <v>3063</v>
       </c>
       <c r="C22" s="42">
         <v>9.1999999999999998E-3</v>
@@ -42202,7 +42142,7 @@
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="43" t="s">
-        <v>3067</v>
+        <v>3064</v>
       </c>
       <c r="C24" s="42">
         <v>1.55E-2</v>
@@ -42210,7 +42150,7 @@
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="43" t="s">
-        <v>3068</v>
+        <v>3065</v>
       </c>
       <c r="C25" s="42">
         <v>2E-3</v>
@@ -42224,7 +42164,7 @@
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="40" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="C28" s="42">
         <v>5.0000000000000001E-4</v>
@@ -42232,7 +42172,7 @@
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="40" t="s">
-        <v>3070</v>
+        <v>3067</v>
       </c>
       <c r="C29" s="42">
         <v>2.8199999999999999E-2</v>
@@ -42259,32 +42199,32 @@
   <sheetData>
     <row r="1" spans="2:9">
       <c r="B1" s="47" t="s">
-        <v>3083</v>
+        <v>3078</v>
       </c>
       <c r="C1" s="47"/>
       <c r="E1" s="47" t="s">
-        <v>3084</v>
+        <v>3079</v>
       </c>
       <c r="F1" s="47"/>
       <c r="H1" s="44" t="s">
-        <v>3090</v>
+        <v>3085</v>
       </c>
       <c r="I1" s="44" t="s">
-        <v>3091</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="2" spans="2:9">
       <c r="B2" s="44" t="s">
-        <v>3075</v>
+        <v>3070</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>3076</v>
+        <v>3071</v>
       </c>
       <c r="E2" s="44" t="s">
-        <v>3075</v>
+        <v>3070</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>3076</v>
+        <v>3071</v>
       </c>
       <c r="H2" s="41">
         <v>0.01</v>
@@ -42295,11 +42235,11 @@
     </row>
     <row r="3" spans="2:9">
       <c r="B3" s="40" t="s">
-        <v>3077</v>
+        <v>3072</v>
       </c>
       <c r="C3" s="39"/>
       <c r="E3" s="45" t="s">
-        <v>3089</v>
+        <v>3084</v>
       </c>
       <c r="F3" s="39">
         <v>1</v>
@@ -42307,51 +42247,51 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="40" t="s">
-        <v>3078</v>
+        <v>3073</v>
       </c>
       <c r="C4" s="39"/>
       <c r="E4" s="45" t="s">
-        <v>3085</v>
+        <v>3080</v>
       </c>
       <c r="F4" s="39"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="40" t="s">
-        <v>3079</v>
+        <v>3074</v>
       </c>
       <c r="C5" s="39">
         <v>1</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>3086</v>
+        <v>3081</v>
       </c>
       <c r="F5" s="39"/>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" s="40" t="s">
-        <v>3080</v>
+        <v>3075</v>
       </c>
       <c r="C6" s="39"/>
       <c r="E6" s="45" t="s">
-        <v>3087</v>
+        <v>3082</v>
       </c>
       <c r="F6" s="39"/>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" s="40" t="s">
-        <v>3081</v>
+        <v>3076</v>
       </c>
       <c r="C7" s="39">
         <v>3</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>3088</v>
+        <v>3083</v>
       </c>
       <c r="F7" s="39"/>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="40" t="s">
-        <v>3082</v>
+        <v>3077</v>
       </c>
       <c r="C8" s="39"/>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baray020\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB1EC90-3095-4E5A-9148-6732B3D534CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8022D2F1-DC2F-49AA-9DC5-D3B06E6DE2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1890" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1890" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dotaci" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6612" uniqueCount="1680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6594" uniqueCount="1679">
   <si>
     <t>HENRIQUEZ POOL FELIPE ALBERTO</t>
   </si>
@@ -4896,18 +4896,9 @@
     <t>SILVA VALDIVIA CRISTIAN LEONAR</t>
   </si>
   <si>
-    <t>Nueva</t>
-  </si>
-  <si>
-    <t>VILLALON CISTERNAS RICARDO ANT</t>
-  </si>
-  <si>
     <t>AGUILERA VIDELA EFRAIN DEL CAR</t>
   </si>
   <si>
-    <t>ASTUDILLO CORDERO SERVANDO DEL</t>
-  </si>
-  <si>
     <t xml:space="preserve">Psiquiatría </t>
   </si>
   <si>
@@ -4983,9 +4974,6 @@
     <t>Interrupcion de descanso</t>
   </si>
   <si>
-    <t xml:space="preserve">Medicina General </t>
-  </si>
-  <si>
     <t>Etapa</t>
   </si>
   <si>
@@ -5079,7 +5067,16 @@
     <t>febrero</t>
   </si>
   <si>
-    <t xml:space="preserve">Traumatología </t>
+    <t xml:space="preserve">Continua </t>
+  </si>
+  <si>
+    <t>Traumatología</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueva </t>
+  </si>
+  <si>
+    <t>Medicina General</t>
   </si>
 </sst>
 </file>
@@ -5863,7 +5860,7 @@
         <v>57</v>
       </c>
       <c r="P435" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q435" s="34">
         <v>45789</v>
@@ -5929,7 +5926,7 @@
         <v>65</v>
       </c>
       <c r="P436" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q436" s="34">
         <v>33119</v>
@@ -5995,7 +5992,7 @@
         <v>65</v>
       </c>
       <c r="P437" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q437" s="34">
         <v>43235</v>
@@ -6061,7 +6058,7 @@
         <v>63</v>
       </c>
       <c r="P438" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q438" s="34">
         <v>34731</v>
@@ -6127,7 +6124,7 @@
         <v>56</v>
       </c>
       <c r="P439" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q439" s="34">
         <v>36923</v>
@@ -6193,7 +6190,7 @@
         <v>61</v>
       </c>
       <c r="P440" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q440" s="34">
         <v>31199</v>
@@ -6259,7 +6256,7 @@
         <v>58</v>
       </c>
       <c r="P441" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q441" s="34">
         <v>32629</v>
@@ -6325,7 +6322,7 @@
         <v>58</v>
       </c>
       <c r="P442" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q442" s="34">
         <v>37501</v>
@@ -6391,7 +6388,7 @@
         <v>59</v>
       </c>
       <c r="P443" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q443" s="34">
         <v>33091</v>
@@ -6457,7 +6454,7 @@
         <v>62</v>
       </c>
       <c r="P444" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q444" s="34">
         <v>32752</v>
@@ -6523,7 +6520,7 @@
         <v>61</v>
       </c>
       <c r="P445" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q445" s="34">
         <v>30817</v>
@@ -6589,7 +6586,7 @@
         <v>57</v>
       </c>
       <c r="P446" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q446" s="34">
         <v>33091</v>
@@ -6655,7 +6652,7 @@
         <v>59</v>
       </c>
       <c r="P447" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q447" s="34">
         <v>32157</v>
@@ -6721,7 +6718,7 @@
         <v>56</v>
       </c>
       <c r="P448" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q448" s="34">
         <v>38462</v>
@@ -6787,7 +6784,7 @@
         <v>57</v>
       </c>
       <c r="P449" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q449" s="34">
         <v>32782</v>
@@ -6853,7 +6850,7 @@
         <v>57</v>
       </c>
       <c r="P450" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q450" s="34">
         <v>33939</v>
@@ -6919,7 +6916,7 @@
         <v>60</v>
       </c>
       <c r="P451" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q451" s="34">
         <v>32660</v>
@@ -6985,7 +6982,7 @@
         <v>61</v>
       </c>
       <c r="P452" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q452" s="34">
         <v>32157</v>
@@ -7051,7 +7048,7 @@
         <v>57</v>
       </c>
       <c r="P453" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q453" s="34">
         <v>32629</v>
@@ -7117,7 +7114,7 @@
         <v>60</v>
       </c>
       <c r="P454" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q454" s="34">
         <v>38078</v>
@@ -7183,7 +7180,7 @@
         <v>59</v>
       </c>
       <c r="P455" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q455" s="34">
         <v>33263</v>
@@ -7249,7 +7246,7 @@
         <v>55</v>
       </c>
       <c r="P456" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q456" s="34">
         <v>33091</v>
@@ -7315,7 +7312,7 @@
         <v>57</v>
       </c>
       <c r="P457" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q457" s="34">
         <v>37015</v>
@@ -7381,7 +7378,7 @@
         <v>59</v>
       </c>
       <c r="P458" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q458" s="34">
         <v>33378</v>
@@ -7447,7 +7444,7 @@
         <v>57</v>
       </c>
       <c r="P459" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q459" s="34">
         <v>33179</v>
@@ -7513,7 +7510,7 @@
         <v>57</v>
       </c>
       <c r="P460" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q460" s="34">
         <v>37501</v>
@@ -7579,7 +7576,7 @@
         <v>58</v>
       </c>
       <c r="P461" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q461" s="34">
         <v>38322</v>
@@ -7645,7 +7642,7 @@
         <v>57</v>
       </c>
       <c r="P462" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q462" s="34">
         <v>33939</v>
@@ -7711,7 +7708,7 @@
         <v>56</v>
       </c>
       <c r="P463" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q463" s="34">
         <v>32752</v>
@@ -7777,7 +7774,7 @@
         <v>56</v>
       </c>
       <c r="P464" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q464" s="34">
         <v>37501</v>
@@ -7843,7 +7840,7 @@
         <v>56</v>
       </c>
       <c r="P465" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q465" s="34">
         <v>33165</v>
@@ -7909,7 +7906,7 @@
         <v>56</v>
       </c>
       <c r="P466" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q466" s="34">
         <v>33170</v>
@@ -7975,7 +7972,7 @@
         <v>55</v>
       </c>
       <c r="P467" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q467" s="34">
         <v>38078</v>
@@ -8041,7 +8038,7 @@
         <v>55</v>
       </c>
       <c r="P468" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q468" s="34">
         <v>37501</v>
@@ -8107,7 +8104,7 @@
         <v>54</v>
       </c>
       <c r="P469" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q469" s="34">
         <v>37012</v>
@@ -8173,7 +8170,7 @@
         <v>55</v>
       </c>
       <c r="P470" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q470" s="34">
         <v>38462</v>
@@ -8239,7 +8236,7 @@
         <v>54</v>
       </c>
       <c r="P471" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q471" s="34">
         <v>38322</v>
@@ -8305,7 +8302,7 @@
         <v>53</v>
       </c>
       <c r="P472" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q472" s="34">
         <v>37501</v>
@@ -8371,7 +8368,7 @@
         <v>57</v>
       </c>
       <c r="P473" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q473" s="34">
         <v>33165</v>
@@ -8437,7 +8434,7 @@
         <v>56</v>
       </c>
       <c r="P474" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q474" s="34">
         <v>33210</v>
@@ -8503,7 +8500,7 @@
         <v>57</v>
       </c>
       <c r="P475" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q475" s="34">
         <v>32752</v>
@@ -8569,7 +8566,7 @@
         <v>57</v>
       </c>
       <c r="P476" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q476" s="34">
         <v>33101</v>
@@ -8635,7 +8632,7 @@
         <v>55</v>
       </c>
       <c r="P477" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q477" s="34">
         <v>37501</v>
@@ -8701,7 +8698,7 @@
         <v>52</v>
       </c>
       <c r="P478" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q478" s="34">
         <v>38034</v>
@@ -8767,7 +8764,7 @@
         <v>53</v>
       </c>
       <c r="P479" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q479" s="34">
         <v>37012</v>
@@ -8833,7 +8830,7 @@
         <v>54</v>
       </c>
       <c r="P480" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q480" s="34">
         <v>37012</v>
@@ -8899,7 +8896,7 @@
         <v>53</v>
       </c>
       <c r="P481" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q481" s="34">
         <v>37501</v>
@@ -8965,7 +8962,7 @@
         <v>53</v>
       </c>
       <c r="P482" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q482" s="34">
         <v>37501</v>
@@ -9031,7 +9028,7 @@
         <v>54</v>
       </c>
       <c r="P483" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q483" s="34">
         <v>37625</v>
@@ -9097,7 +9094,7 @@
         <v>53</v>
       </c>
       <c r="P484" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q484" s="34">
         <v>33504</v>
@@ -9163,7 +9160,7 @@
         <v>52</v>
       </c>
       <c r="P485" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q485" s="34">
         <v>37935</v>
@@ -9229,7 +9226,7 @@
         <v>53</v>
       </c>
       <c r="P486" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q486" s="34">
         <v>37501</v>
@@ -9295,7 +9292,7 @@
         <v>53</v>
       </c>
       <c r="P487" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q487" s="34">
         <v>37501</v>
@@ -9361,7 +9358,7 @@
         <v>52</v>
       </c>
       <c r="P488" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q488" s="34">
         <v>37012</v>
@@ -9427,7 +9424,7 @@
         <v>51</v>
       </c>
       <c r="P489" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q489" s="34">
         <v>38005</v>
@@ -9493,7 +9490,7 @@
         <v>52</v>
       </c>
       <c r="P490" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q490" s="34">
         <v>37012</v>
@@ -9559,7 +9556,7 @@
         <v>50</v>
       </c>
       <c r="P491" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q491" s="34">
         <v>37021</v>
@@ -9625,7 +9622,7 @@
         <v>50</v>
       </c>
       <c r="P492" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q492" s="34">
         <v>37501</v>
@@ -9691,7 +9688,7 @@
         <v>49</v>
       </c>
       <c r="P493" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q493" s="34">
         <v>37502</v>
@@ -9757,7 +9754,7 @@
         <v>49</v>
       </c>
       <c r="P494" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q494" s="34">
         <v>37712</v>
@@ -9823,7 +9820,7 @@
         <v>47</v>
       </c>
       <c r="P495" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q495" s="34">
         <v>37501</v>
@@ -9889,7 +9886,7 @@
         <v>47</v>
       </c>
       <c r="P496" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q496" s="34">
         <v>38173</v>
@@ -9955,7 +9952,7 @@
         <v>48</v>
       </c>
       <c r="P497" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q497" s="34">
         <v>37561</v>
@@ -10021,7 +10018,7 @@
         <v>48</v>
       </c>
       <c r="P498" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q498" s="34">
         <v>37501</v>
@@ -10087,7 +10084,7 @@
         <v>46</v>
       </c>
       <c r="P499" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q499" s="34">
         <v>37935</v>
@@ -10153,7 +10150,7 @@
         <v>46</v>
       </c>
       <c r="P500" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q500" s="34">
         <v>38261</v>
@@ -10219,7 +10216,7 @@
         <v>46</v>
       </c>
       <c r="P501" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q501" s="34">
         <v>37622</v>
@@ -10285,7 +10282,7 @@
         <v>52</v>
       </c>
       <c r="P502" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q502" s="34">
         <v>37165</v>
@@ -10351,7 +10348,7 @@
         <v>57</v>
       </c>
       <c r="P503" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q503" s="34">
         <v>37501</v>
@@ -10417,7 +10414,7 @@
         <v>52</v>
       </c>
       <c r="P504" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q504" s="34">
         <v>37469</v>
@@ -10483,7 +10480,7 @@
         <v>53</v>
       </c>
       <c r="P505" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q505" s="34">
         <v>38462</v>
@@ -10549,7 +10546,7 @@
         <v>52</v>
       </c>
       <c r="P506" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q506" s="34">
         <v>38231</v>
@@ -10615,7 +10612,7 @@
         <v>51</v>
       </c>
       <c r="P507" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q507" s="34">
         <v>37973</v>
@@ -10681,7 +10678,7 @@
         <v>42</v>
       </c>
       <c r="P508" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q508" s="34">
         <v>38231</v>
@@ -10747,7 +10744,7 @@
         <v>42</v>
       </c>
       <c r="P509" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q509" s="34">
         <v>38322</v>
@@ -10813,7 +10810,7 @@
         <v>40</v>
       </c>
       <c r="P510" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q510" s="34">
         <v>38322</v>
@@ -10879,7 +10876,7 @@
         <v>57</v>
       </c>
       <c r="P511" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q511" s="34">
         <v>37622</v>
@@ -10945,7 +10942,7 @@
         <v>65</v>
       </c>
       <c r="P512" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q512" s="34">
         <v>33057</v>
@@ -11011,7 +11008,7 @@
         <v>61</v>
       </c>
       <c r="P513" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q513" s="34">
         <v>32752</v>
@@ -11077,7 +11074,7 @@
         <v>65</v>
       </c>
       <c r="P514" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q514" s="34">
         <v>32629</v>
@@ -11143,7 +11140,7 @@
         <v>63</v>
       </c>
       <c r="P515" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q515" s="34">
         <v>33939</v>
@@ -11209,7 +11206,7 @@
         <v>64</v>
       </c>
       <c r="P516" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q516" s="34">
         <v>30834</v>
@@ -11275,7 +11272,7 @@
         <v>65</v>
       </c>
       <c r="P517" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q517" s="34">
         <v>31731</v>
@@ -11341,7 +11338,7 @@
         <v>47</v>
       </c>
       <c r="P518" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q518" s="34">
         <v>38443</v>
@@ -11407,7 +11404,7 @@
         <v>64</v>
       </c>
       <c r="P519" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q519" s="34">
         <v>38462</v>
@@ -11473,7 +11470,7 @@
         <v>59</v>
       </c>
       <c r="P520" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q520" s="34">
         <v>38322</v>
@@ -11539,7 +11536,7 @@
         <v>59</v>
       </c>
       <c r="P521" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q521" s="34">
         <v>33064</v>
@@ -11605,7 +11602,7 @@
         <v>42</v>
       </c>
       <c r="P522" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q522" s="34">
         <v>40910</v>
@@ -11671,7 +11668,7 @@
         <v>49</v>
       </c>
       <c r="P523" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q523" s="34">
         <v>39114</v>
@@ -11737,7 +11734,7 @@
         <v>48</v>
       </c>
       <c r="P524" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q524" s="34">
         <v>38839</v>
@@ -11803,7 +11800,7 @@
         <v>55</v>
       </c>
       <c r="P525" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q525" s="34">
         <v>39734</v>
@@ -11869,7 +11866,7 @@
         <v>44</v>
       </c>
       <c r="P526" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q526" s="34">
         <v>39694</v>
@@ -11935,7 +11932,7 @@
         <v>54</v>
       </c>
       <c r="P527" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q527" s="34">
         <v>39098</v>
@@ -12001,7 +11998,7 @@
         <v>45</v>
       </c>
       <c r="P528" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q528" s="34">
         <v>39097</v>
@@ -12067,7 +12064,7 @@
         <v>44</v>
       </c>
       <c r="P529" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q529" s="34">
         <v>40301</v>
@@ -12133,7 +12130,7 @@
         <v>50</v>
       </c>
       <c r="P530" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q530" s="34">
         <v>39083</v>
@@ -12199,7 +12196,7 @@
         <v>37</v>
       </c>
       <c r="P531" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q531" s="34">
         <v>39234</v>
@@ -12265,7 +12262,7 @@
         <v>45</v>
       </c>
       <c r="P532" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q532" s="34">
         <v>39234</v>
@@ -12331,7 +12328,7 @@
         <v>50</v>
       </c>
       <c r="P533" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q533" s="34">
         <v>39234</v>
@@ -12397,7 +12394,7 @@
         <v>43</v>
       </c>
       <c r="P534" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q534" s="34">
         <v>39234</v>
@@ -12463,7 +12460,7 @@
         <v>41</v>
       </c>
       <c r="P535" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q535" s="34">
         <v>39234</v>
@@ -12529,7 +12526,7 @@
         <v>40</v>
       </c>
       <c r="P536" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q536" s="34">
         <v>39234</v>
@@ -12595,7 +12592,7 @@
         <v>40</v>
       </c>
       <c r="P537" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q537" s="34">
         <v>39234</v>
@@ -12661,7 +12658,7 @@
         <v>40</v>
       </c>
       <c r="P538" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q538" s="34">
         <v>39234</v>
@@ -12727,7 +12724,7 @@
         <v>52</v>
       </c>
       <c r="P539" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q539" s="34">
         <v>42064</v>
@@ -12793,7 +12790,7 @@
         <v>50</v>
       </c>
       <c r="P540" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q540" s="34">
         <v>39340</v>
@@ -12859,7 +12856,7 @@
         <v>51</v>
       </c>
       <c r="P541" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q541" s="34">
         <v>39340</v>
@@ -12925,7 +12922,7 @@
         <v>50</v>
       </c>
       <c r="P542" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q542" s="34">
         <v>39340</v>
@@ -12991,7 +12988,7 @@
         <v>49</v>
       </c>
       <c r="P543" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q543" s="34">
         <v>39340</v>
@@ -13057,7 +13054,7 @@
         <v>49</v>
       </c>
       <c r="P544" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q544" s="34">
         <v>39340</v>
@@ -13123,7 +13120,7 @@
         <v>54</v>
       </c>
       <c r="P545" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q545" s="34">
         <v>39340</v>
@@ -13189,7 +13186,7 @@
         <v>58</v>
       </c>
       <c r="P546" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q546" s="34">
         <v>39340</v>
@@ -13255,7 +13252,7 @@
         <v>51</v>
       </c>
       <c r="P547" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q547" s="34">
         <v>39340</v>
@@ -13321,7 +13318,7 @@
         <v>57</v>
       </c>
       <c r="P548" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q548" s="34">
         <v>39340</v>
@@ -13387,7 +13384,7 @@
         <v>54</v>
       </c>
       <c r="P549" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q549" s="34">
         <v>39340</v>
@@ -13453,7 +13450,7 @@
         <v>48</v>
       </c>
       <c r="P550" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q550" s="34">
         <v>39340</v>
@@ -13519,7 +13516,7 @@
         <v>53</v>
       </c>
       <c r="P551" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q551" s="34">
         <v>39340</v>
@@ -13585,7 +13582,7 @@
         <v>52</v>
       </c>
       <c r="P552" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q552" s="34">
         <v>39340</v>
@@ -13651,7 +13648,7 @@
         <v>49</v>
       </c>
       <c r="P553" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q553" s="34">
         <v>39340</v>
@@ -13717,7 +13714,7 @@
         <v>63</v>
       </c>
       <c r="P554" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q554" s="34">
         <v>39340</v>
@@ -13783,7 +13780,7 @@
         <v>50</v>
       </c>
       <c r="P555" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q555" s="34">
         <v>39340</v>
@@ -13849,7 +13846,7 @@
         <v>52</v>
       </c>
       <c r="P556" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q556" s="34">
         <v>39340</v>
@@ -13915,7 +13912,7 @@
         <v>53</v>
       </c>
       <c r="P557" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q557" s="34">
         <v>39340</v>
@@ -13981,7 +13978,7 @@
         <v>47</v>
       </c>
       <c r="P558" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q558" s="34">
         <v>39340</v>
@@ -14047,7 +14044,7 @@
         <v>59</v>
       </c>
       <c r="P559" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q559" s="34">
         <v>39340</v>
@@ -14113,7 +14110,7 @@
         <v>45</v>
       </c>
       <c r="P560" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q560" s="34">
         <v>39340</v>
@@ -14179,7 +14176,7 @@
         <v>56</v>
       </c>
       <c r="P561" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q561" s="34">
         <v>39340</v>
@@ -14245,7 +14242,7 @@
         <v>54</v>
       </c>
       <c r="P562" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q562" s="34">
         <v>39340</v>
@@ -14311,7 +14308,7 @@
         <v>60</v>
       </c>
       <c r="P563" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q563" s="34">
         <v>39340</v>
@@ -14377,7 +14374,7 @@
         <v>48</v>
       </c>
       <c r="P564" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q564" s="34">
         <v>39340</v>
@@ -14443,7 +14440,7 @@
         <v>56</v>
       </c>
       <c r="P565" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q565" s="34">
         <v>39340</v>
@@ -14509,7 +14506,7 @@
         <v>57</v>
       </c>
       <c r="P566" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q566" s="34">
         <v>39340</v>
@@ -14575,7 +14572,7 @@
         <v>53</v>
       </c>
       <c r="P567" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q567" s="34">
         <v>39356</v>
@@ -14641,7 +14638,7 @@
         <v>50</v>
       </c>
       <c r="P568" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q568" s="34">
         <v>39356</v>
@@ -14707,7 +14704,7 @@
         <v>53</v>
       </c>
       <c r="P569" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q569" s="34">
         <v>39356</v>
@@ -14773,7 +14770,7 @@
         <v>54</v>
       </c>
       <c r="P570" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q570" s="34">
         <v>39356</v>
@@ -14839,7 +14836,7 @@
         <v>54</v>
       </c>
       <c r="P571" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q571" s="34">
         <v>39356</v>
@@ -14905,7 +14902,7 @@
         <v>52</v>
       </c>
       <c r="P572" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q572" s="34">
         <v>40049</v>
@@ -14971,7 +14968,7 @@
         <v>53</v>
       </c>
       <c r="P573" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q573" s="34">
         <v>39356</v>
@@ -15037,7 +15034,7 @@
         <v>48</v>
       </c>
       <c r="P574" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q574" s="34">
         <v>39356</v>
@@ -15103,7 +15100,7 @@
         <v>49</v>
       </c>
       <c r="P575" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q575" s="34">
         <v>39356</v>
@@ -15169,7 +15166,7 @@
         <v>52</v>
       </c>
       <c r="P576" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q576" s="34">
         <v>39356</v>
@@ -15235,7 +15232,7 @@
         <v>51</v>
       </c>
       <c r="P577" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q577" s="34">
         <v>39356</v>
@@ -15301,7 +15298,7 @@
         <v>54</v>
       </c>
       <c r="P578" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q578" s="34">
         <v>39356</v>
@@ -15367,7 +15364,7 @@
         <v>49</v>
       </c>
       <c r="P579" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q579" s="34">
         <v>39356</v>
@@ -15433,7 +15430,7 @@
         <v>51</v>
       </c>
       <c r="P580" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q580" s="34">
         <v>39356</v>
@@ -15499,7 +15496,7 @@
         <v>51</v>
       </c>
       <c r="P581" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q581" s="34">
         <v>39630</v>
@@ -15565,7 +15562,7 @@
         <v>52</v>
       </c>
       <c r="P582" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q582" s="34">
         <v>39356</v>
@@ -15631,7 +15628,7 @@
         <v>55</v>
       </c>
       <c r="P583" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q583" s="34">
         <v>39356</v>
@@ -15697,7 +15694,7 @@
         <v>50</v>
       </c>
       <c r="P584" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q584" s="34">
         <v>39356</v>
@@ -15763,7 +15760,7 @@
         <v>39</v>
       </c>
       <c r="P585" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q585" s="34">
         <v>39356</v>
@@ -15829,7 +15826,7 @@
         <v>51</v>
       </c>
       <c r="P586" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q586" s="34">
         <v>39356</v>
@@ -15895,7 +15892,7 @@
         <v>50</v>
       </c>
       <c r="P587" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q587" s="34">
         <v>39356</v>
@@ -15961,7 +15958,7 @@
         <v>46</v>
       </c>
       <c r="P588" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q588" s="34">
         <v>39356</v>
@@ -16027,7 +16024,7 @@
         <v>54</v>
       </c>
       <c r="P589" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q589" s="34">
         <v>39356</v>
@@ -16093,7 +16090,7 @@
         <v>49</v>
       </c>
       <c r="P590" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q590" s="34">
         <v>39370</v>
@@ -16159,7 +16156,7 @@
         <v>45</v>
       </c>
       <c r="P591" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q591" s="34">
         <v>39370</v>
@@ -16225,7 +16222,7 @@
         <v>52</v>
       </c>
       <c r="P592" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q592" s="34">
         <v>39370</v>
@@ -16291,7 +16288,7 @@
         <v>43</v>
       </c>
       <c r="P593" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q593" s="34">
         <v>39370</v>
@@ -16357,7 +16354,7 @@
         <v>55</v>
       </c>
       <c r="P594" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q594" s="34">
         <v>39370</v>
@@ -16423,7 +16420,7 @@
         <v>53</v>
       </c>
       <c r="P595" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q595" s="34">
         <v>39370</v>
@@ -16489,7 +16486,7 @@
         <v>44</v>
       </c>
       <c r="P596" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q596" s="34">
         <v>39479</v>
@@ -16555,7 +16552,7 @@
         <v>44</v>
       </c>
       <c r="P597" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q597" s="34">
         <v>39479</v>
@@ -16621,7 +16618,7 @@
         <v>39</v>
       </c>
       <c r="P598" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q598" s="34">
         <v>39479</v>
@@ -16687,7 +16684,7 @@
         <v>48</v>
       </c>
       <c r="P599" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q599" s="34">
         <v>39479</v>
@@ -16753,7 +16750,7 @@
         <v>59</v>
       </c>
       <c r="P600" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q600" s="34">
         <v>39479</v>
@@ -16819,7 +16816,7 @@
         <v>54</v>
       </c>
       <c r="P601" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q601" s="34">
         <v>39479</v>
@@ -16885,7 +16882,7 @@
         <v>45</v>
       </c>
       <c r="P602" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q602" s="34">
         <v>39479</v>
@@ -16951,7 +16948,7 @@
         <v>40</v>
       </c>
       <c r="P603" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q603" s="34">
         <v>39479</v>
@@ -17017,7 +17014,7 @@
         <v>62</v>
       </c>
       <c r="P604" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q604" s="34">
         <v>39479</v>
@@ -17083,7 +17080,7 @@
         <v>39</v>
       </c>
       <c r="P605" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q605" s="34">
         <v>39479</v>
@@ -17149,7 +17146,7 @@
         <v>46</v>
       </c>
       <c r="P606" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q606" s="34">
         <v>39479</v>
@@ -17215,7 +17212,7 @@
         <v>52</v>
       </c>
       <c r="P607" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q607" s="34">
         <v>39479</v>
@@ -17281,7 +17278,7 @@
         <v>56</v>
       </c>
       <c r="P608" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q608" s="34">
         <v>39479</v>
@@ -17347,7 +17344,7 @@
         <v>52</v>
       </c>
       <c r="P609" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q609" s="34">
         <v>39479</v>
@@ -17413,7 +17410,7 @@
         <v>47</v>
       </c>
       <c r="P610" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q610" s="34">
         <v>39479</v>
@@ -17479,7 +17476,7 @@
         <v>43</v>
       </c>
       <c r="P611" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q611" s="34">
         <v>39479</v>
@@ -17545,7 +17542,7 @@
         <v>51</v>
       </c>
       <c r="P612" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q612" s="34">
         <v>39479</v>
@@ -17611,7 +17608,7 @@
         <v>43</v>
       </c>
       <c r="P613" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q613" s="34">
         <v>39479</v>
@@ -17677,7 +17674,7 @@
         <v>48</v>
       </c>
       <c r="P614" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q614" s="34">
         <v>39479</v>
@@ -17743,7 +17740,7 @@
         <v>47</v>
       </c>
       <c r="P615" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q615" s="34">
         <v>39479</v>
@@ -17809,7 +17806,7 @@
         <v>59</v>
       </c>
       <c r="P616" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q616" s="34">
         <v>39479</v>
@@ -17875,7 +17872,7 @@
         <v>50</v>
       </c>
       <c r="P617" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q617" s="34">
         <v>39479</v>
@@ -17941,7 +17938,7 @@
         <v>54</v>
       </c>
       <c r="P618" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q618" s="34">
         <v>39479</v>
@@ -18007,7 +18004,7 @@
         <v>51</v>
       </c>
       <c r="P619" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q619" s="34">
         <v>39479</v>
@@ -18073,7 +18070,7 @@
         <v>45</v>
       </c>
       <c r="P620" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q620" s="34">
         <v>39479</v>
@@ -18139,7 +18136,7 @@
         <v>50</v>
       </c>
       <c r="P621" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q621" s="34">
         <v>39479</v>
@@ -18205,7 +18202,7 @@
         <v>46</v>
       </c>
       <c r="P622" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q622" s="34">
         <v>39479</v>
@@ -18271,7 +18268,7 @@
         <v>49</v>
       </c>
       <c r="P623" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q623" s="34">
         <v>39479</v>
@@ -18337,7 +18334,7 @@
         <v>54</v>
       </c>
       <c r="P624" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q624" s="34">
         <v>39479</v>
@@ -18403,7 +18400,7 @@
         <v>42</v>
       </c>
       <c r="P625" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q625" s="34">
         <v>39479</v>
@@ -18469,7 +18466,7 @@
         <v>45</v>
       </c>
       <c r="P626" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q626" s="34">
         <v>39479</v>
@@ -18535,7 +18532,7 @@
         <v>49</v>
       </c>
       <c r="P627" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q627" s="34">
         <v>39496</v>
@@ -18601,7 +18598,7 @@
         <v>48</v>
       </c>
       <c r="P628" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q628" s="34">
         <v>39693</v>
@@ -18667,7 +18664,7 @@
         <v>46</v>
       </c>
       <c r="P629" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q629" s="34">
         <v>39693</v>
@@ -18733,7 +18730,7 @@
         <v>50</v>
       </c>
       <c r="P630" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q630" s="34">
         <v>39693</v>
@@ -18799,7 +18796,7 @@
         <v>40</v>
       </c>
       <c r="P631" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q631" s="34">
         <v>39693</v>
@@ -18865,7 +18862,7 @@
         <v>44</v>
       </c>
       <c r="P632" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q632" s="34">
         <v>39723</v>
@@ -18931,7 +18928,7 @@
         <v>53</v>
       </c>
       <c r="P633" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q633" s="34">
         <v>39517</v>
@@ -18997,7 +18994,7 @@
         <v>43</v>
       </c>
       <c r="P634" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q634" s="34">
         <v>45200</v>
@@ -19063,7 +19060,7 @@
         <v>56</v>
       </c>
       <c r="P635" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q635" s="34">
         <v>39557</v>
@@ -19129,7 +19126,7 @@
         <v>46</v>
       </c>
       <c r="P636" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q636" s="34">
         <v>39557</v>
@@ -19195,7 +19192,7 @@
         <v>46</v>
       </c>
       <c r="P637" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q637" s="34">
         <v>39924</v>
@@ -19261,7 +19258,7 @@
         <v>48</v>
       </c>
       <c r="P638" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q638" s="34">
         <v>39583</v>
@@ -19327,7 +19324,7 @@
         <v>41</v>
       </c>
       <c r="P639" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q639" s="34">
         <v>39583</v>
@@ -19393,7 +19390,7 @@
         <v>40</v>
       </c>
       <c r="P640" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q640" s="34">
         <v>39583</v>
@@ -19459,7 +19456,7 @@
         <v>57</v>
       </c>
       <c r="P641" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q641" s="34">
         <v>39583</v>
@@ -19525,7 +19522,7 @@
         <v>43</v>
       </c>
       <c r="P642" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q642" s="34">
         <v>39583</v>
@@ -19591,7 +19588,7 @@
         <v>57</v>
       </c>
       <c r="P643" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q643" s="34">
         <v>39583</v>
@@ -19657,7 +19654,7 @@
         <v>57</v>
       </c>
       <c r="P644" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q644" s="34">
         <v>39583</v>
@@ -19723,7 +19720,7 @@
         <v>43</v>
       </c>
       <c r="P645" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q645" s="34">
         <v>39583</v>
@@ -19789,7 +19786,7 @@
         <v>43</v>
       </c>
       <c r="P646" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q646" s="34">
         <v>39583</v>
@@ -19855,7 +19852,7 @@
         <v>63</v>
       </c>
       <c r="P647" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q647" s="34">
         <v>39590</v>
@@ -19921,7 +19918,7 @@
         <v>48</v>
       </c>
       <c r="P648" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q648" s="34">
         <v>39590</v>
@@ -19987,7 +19984,7 @@
         <v>43</v>
       </c>
       <c r="P649" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q649" s="34">
         <v>39590</v>
@@ -20053,7 +20050,7 @@
         <v>44</v>
       </c>
       <c r="P650" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q650" s="34">
         <v>39590</v>
@@ -20119,7 +20116,7 @@
         <v>44</v>
       </c>
       <c r="P651" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q651" s="34">
         <v>39590</v>
@@ -20185,7 +20182,7 @@
         <v>50</v>
       </c>
       <c r="P652" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q652" s="34">
         <v>39590</v>
@@ -20251,7 +20248,7 @@
         <v>55</v>
       </c>
       <c r="P653" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q653" s="34">
         <v>39609</v>
@@ -20317,7 +20314,7 @@
         <v>52</v>
       </c>
       <c r="P654" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q654" s="34">
         <v>39615</v>
@@ -20383,7 +20380,7 @@
         <v>46</v>
       </c>
       <c r="P655" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q655" s="34">
         <v>39722</v>
@@ -20449,7 +20446,7 @@
         <v>45</v>
       </c>
       <c r="P656" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q656" s="34">
         <v>39630</v>
@@ -20515,7 +20512,7 @@
         <v>53</v>
       </c>
       <c r="P657" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q657" s="34">
         <v>39722</v>
@@ -20581,7 +20578,7 @@
         <v>39</v>
       </c>
       <c r="P658" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q658" s="34">
         <v>39734</v>
@@ -20647,7 +20644,7 @@
         <v>54</v>
       </c>
       <c r="P659" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q659" s="34">
         <v>39734</v>
@@ -20713,7 +20710,7 @@
         <v>38</v>
       </c>
       <c r="P660" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q660" s="34">
         <v>39734</v>
@@ -20779,7 +20776,7 @@
         <v>40</v>
       </c>
       <c r="P661" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q661" s="34">
         <v>39734</v>
@@ -20845,7 +20842,7 @@
         <v>56</v>
       </c>
       <c r="P662" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q662" s="34">
         <v>39734</v>
@@ -20911,7 +20908,7 @@
         <v>41</v>
       </c>
       <c r="P663" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q663" s="34">
         <v>39734</v>
@@ -20977,7 +20974,7 @@
         <v>53</v>
       </c>
       <c r="P664" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q664" s="34">
         <v>39734</v>
@@ -21043,7 +21040,7 @@
         <v>51</v>
       </c>
       <c r="P665" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q665" s="34">
         <v>39734</v>
@@ -21109,7 +21106,7 @@
         <v>47</v>
       </c>
       <c r="P666" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q666" s="34">
         <v>39734</v>
@@ -21175,7 +21172,7 @@
         <v>59</v>
       </c>
       <c r="P667" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q667" s="34">
         <v>39734</v>
@@ -21241,7 +21238,7 @@
         <v>59</v>
       </c>
       <c r="P668" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q668" s="34">
         <v>39734</v>
@@ -21307,7 +21304,7 @@
         <v>46</v>
       </c>
       <c r="P669" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q669" s="34">
         <v>39734</v>
@@ -21373,7 +21370,7 @@
         <v>40</v>
       </c>
       <c r="P670" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q670" s="34">
         <v>39734</v>
@@ -21439,7 +21436,7 @@
         <v>48</v>
       </c>
       <c r="P671" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q671" s="34">
         <v>39734</v>
@@ -21505,7 +21502,7 @@
         <v>48</v>
       </c>
       <c r="P672" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q672" s="34">
         <v>39734</v>
@@ -21571,7 +21568,7 @@
         <v>46</v>
       </c>
       <c r="P673" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q673" s="34">
         <v>39753</v>
@@ -21637,7 +21634,7 @@
         <v>57</v>
       </c>
       <c r="P674" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q674" s="34">
         <v>39753</v>
@@ -21703,7 +21700,7 @@
         <v>43</v>
       </c>
       <c r="P675" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q675" s="34">
         <v>39753</v>
@@ -21769,7 +21766,7 @@
         <v>58</v>
       </c>
       <c r="P676" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q676" s="34">
         <v>39762</v>
@@ -21835,7 +21832,7 @@
         <v>48</v>
       </c>
       <c r="P677" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q677" s="34">
         <v>39763</v>
@@ -21901,7 +21898,7 @@
         <v>46</v>
       </c>
       <c r="P678" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q678" s="34">
         <v>39783</v>
@@ -21967,7 +21964,7 @@
         <v>47</v>
       </c>
       <c r="P679" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q679" s="34">
         <v>39805</v>
@@ -22033,7 +22030,7 @@
         <v>43</v>
       </c>
       <c r="P680" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q680" s="34">
         <v>39821</v>
@@ -22099,7 +22096,7 @@
         <v>43</v>
       </c>
       <c r="P681" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q681" s="34">
         <v>39881</v>
@@ -22165,7 +22162,7 @@
         <v>51</v>
       </c>
       <c r="P682" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q682" s="34">
         <v>40009</v>
@@ -22231,7 +22228,7 @@
         <v>55</v>
       </c>
       <c r="P683" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q683" s="34">
         <v>40026</v>
@@ -22297,7 +22294,7 @@
         <v>47</v>
       </c>
       <c r="P684" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q684" s="34">
         <v>40049</v>
@@ -22363,7 +22360,7 @@
         <v>48</v>
       </c>
       <c r="P685" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q685" s="34">
         <v>40049</v>
@@ -22429,7 +22426,7 @@
         <v>41</v>
       </c>
       <c r="P686" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q686" s="34">
         <v>40049</v>
@@ -22495,7 +22492,7 @@
         <v>40</v>
       </c>
       <c r="P687" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q687" s="34">
         <v>40049</v>
@@ -22561,7 +22558,7 @@
         <v>53</v>
       </c>
       <c r="P688" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q688" s="34">
         <v>40049</v>
@@ -22627,7 +22624,7 @@
         <v>52</v>
       </c>
       <c r="P689" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q689" s="34">
         <v>40049</v>
@@ -22693,7 +22690,7 @@
         <v>52</v>
       </c>
       <c r="P690" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q690" s="34">
         <v>40049</v>
@@ -22759,7 +22756,7 @@
         <v>55</v>
       </c>
       <c r="P691" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q691" s="34">
         <v>40108</v>
@@ -22825,7 +22822,7 @@
         <v>40</v>
       </c>
       <c r="P692" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q692" s="34">
         <v>40192</v>
@@ -22891,7 +22888,7 @@
         <v>41</v>
       </c>
       <c r="P693" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q693" s="34">
         <v>40192</v>
@@ -22957,7 +22954,7 @@
         <v>55</v>
       </c>
       <c r="P694" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q694" s="34">
         <v>40192</v>
@@ -23023,7 +23020,7 @@
         <v>42</v>
       </c>
       <c r="P695" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q695" s="34">
         <v>40192</v>
@@ -23089,7 +23086,7 @@
         <v>43</v>
       </c>
       <c r="P696" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q696" s="34">
         <v>40192</v>
@@ -23155,7 +23152,7 @@
         <v>42</v>
       </c>
       <c r="P697" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q697" s="34">
         <v>40192</v>
@@ -23221,7 +23218,7 @@
         <v>48</v>
       </c>
       <c r="P698" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q698" s="34">
         <v>40192</v>
@@ -23287,7 +23284,7 @@
         <v>40</v>
       </c>
       <c r="P699" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q699" s="34">
         <v>40817</v>
@@ -23353,7 +23350,7 @@
         <v>41</v>
       </c>
       <c r="P700" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q700" s="34">
         <v>40210</v>
@@ -23419,7 +23416,7 @@
         <v>46</v>
       </c>
       <c r="P701" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q701" s="34">
         <v>40269</v>
@@ -23485,7 +23482,7 @@
         <v>35</v>
       </c>
       <c r="P702" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q702" s="34">
         <v>40269</v>
@@ -23551,7 +23548,7 @@
         <v>46</v>
       </c>
       <c r="P703" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q703" s="34">
         <v>40709</v>
@@ -23617,7 +23614,7 @@
         <v>39</v>
       </c>
       <c r="P704" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q704" s="34">
         <v>40771</v>
@@ -23683,7 +23680,7 @@
         <v>43</v>
       </c>
       <c r="P705" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q705" s="34">
         <v>40583</v>
@@ -23749,7 +23746,7 @@
         <v>41</v>
       </c>
       <c r="P706" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q706" s="34">
         <v>43952</v>
@@ -23815,7 +23812,7 @@
         <v>43</v>
       </c>
       <c r="P707" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q707" s="34">
         <v>40764</v>
@@ -23881,7 +23878,7 @@
         <v>39</v>
       </c>
       <c r="P708" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q708" s="34">
         <v>40583</v>
@@ -23947,7 +23944,7 @@
         <v>39</v>
       </c>
       <c r="P709" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q709" s="34">
         <v>40583</v>
@@ -24013,7 +24010,7 @@
         <v>47</v>
       </c>
       <c r="P710" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q710" s="34">
         <v>40583</v>
@@ -24079,7 +24076,7 @@
         <v>38</v>
       </c>
       <c r="P711" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q711" s="34">
         <v>40583</v>
@@ -24145,7 +24142,7 @@
         <v>36</v>
       </c>
       <c r="P712" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q712" s="34">
         <v>40764</v>
@@ -24211,7 +24208,7 @@
         <v>40</v>
       </c>
       <c r="P713" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q713" s="34">
         <v>40583</v>
@@ -24277,7 +24274,7 @@
         <v>46</v>
       </c>
       <c r="P714" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q714" s="34">
         <v>40595</v>
@@ -24343,7 +24340,7 @@
         <v>44</v>
       </c>
       <c r="P715" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q715" s="34">
         <v>40595</v>
@@ -24409,7 +24406,7 @@
         <v>42</v>
       </c>
       <c r="P716" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q716" s="34">
         <v>40595</v>
@@ -24475,7 +24472,7 @@
         <v>48</v>
       </c>
       <c r="P717" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q717" s="34">
         <v>40595</v>
@@ -24541,7 +24538,7 @@
         <v>40</v>
       </c>
       <c r="P718" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q718" s="34">
         <v>40595</v>
@@ -24607,7 +24604,7 @@
         <v>40</v>
       </c>
       <c r="P719" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q719" s="34">
         <v>40776</v>
@@ -24673,7 +24670,7 @@
         <v>44</v>
       </c>
       <c r="P720" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q720" s="34">
         <v>40595</v>
@@ -24739,7 +24736,7 @@
         <v>39</v>
       </c>
       <c r="P721" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q721" s="34">
         <v>40595</v>
@@ -24805,7 +24802,7 @@
         <v>43</v>
       </c>
       <c r="P722" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q722" s="34">
         <v>40595</v>
@@ -24871,7 +24868,7 @@
         <v>35</v>
       </c>
       <c r="P723" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q723" s="34">
         <v>40595</v>
@@ -24937,7 +24934,7 @@
         <v>39</v>
       </c>
       <c r="P724" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q724" s="34">
         <v>40595</v>
@@ -25003,7 +25000,7 @@
         <v>36</v>
       </c>
       <c r="P725" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q725" s="34">
         <v>40595</v>
@@ -25069,7 +25066,7 @@
         <v>39</v>
       </c>
       <c r="P726" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q726" s="34">
         <v>40603</v>
@@ -25135,7 +25132,7 @@
         <v>40</v>
       </c>
       <c r="P727" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q727" s="34">
         <v>40603</v>
@@ -25201,7 +25198,7 @@
         <v>36</v>
       </c>
       <c r="P728" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q728" s="34">
         <v>40603</v>
@@ -25267,7 +25264,7 @@
         <v>41</v>
       </c>
       <c r="P729" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q729" s="34">
         <v>40603</v>
@@ -25333,7 +25330,7 @@
         <v>43</v>
       </c>
       <c r="P730" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q730" s="34">
         <v>40603</v>
@@ -25399,7 +25396,7 @@
         <v>43</v>
       </c>
       <c r="P731" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q731" s="34">
         <v>40603</v>
@@ -25465,7 +25462,7 @@
         <v>35</v>
       </c>
       <c r="P732" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q732" s="34">
         <v>40603</v>
@@ -25531,7 +25528,7 @@
         <v>40</v>
       </c>
       <c r="P733" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q733" s="34">
         <v>40603</v>
@@ -25597,7 +25594,7 @@
         <v>43</v>
       </c>
       <c r="P734" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q734" s="34">
         <v>40623</v>
@@ -25663,7 +25660,7 @@
         <v>38</v>
       </c>
       <c r="P735" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q735" s="34">
         <v>40634</v>
@@ -25729,7 +25726,7 @@
         <v>39</v>
       </c>
       <c r="P736" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q736" s="34">
         <v>40634</v>
@@ -25795,7 +25792,7 @@
         <v>36</v>
       </c>
       <c r="P737" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q737" s="34">
         <v>40634</v>
@@ -25861,7 +25858,7 @@
         <v>49</v>
       </c>
       <c r="P738" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q738" s="34">
         <v>40634</v>
@@ -25927,7 +25924,7 @@
         <v>36</v>
       </c>
       <c r="P739" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q739" s="34">
         <v>40634</v>
@@ -25993,7 +25990,7 @@
         <v>44</v>
       </c>
       <c r="P740" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q740" s="34">
         <v>40725</v>
@@ -26059,7 +26056,7 @@
         <v>39</v>
       </c>
       <c r="P741" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q741" s="34">
         <v>40737</v>
@@ -26125,7 +26122,7 @@
         <v>34</v>
       </c>
       <c r="P742" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q742" s="34">
         <v>40737</v>
@@ -26191,7 +26188,7 @@
         <v>37</v>
       </c>
       <c r="P743" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q743" s="34">
         <v>40737</v>
@@ -26257,7 +26254,7 @@
         <v>38</v>
       </c>
       <c r="P744" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q744" s="34">
         <v>40737</v>
@@ -26323,7 +26320,7 @@
         <v>38</v>
       </c>
       <c r="P745" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q745" s="34">
         <v>40737</v>
@@ -26389,7 +26386,7 @@
         <v>51</v>
       </c>
       <c r="P746" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q746" s="34">
         <v>41671</v>
@@ -26455,7 +26452,7 @@
         <v>38</v>
       </c>
       <c r="P747" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q747" s="34">
         <v>41631</v>
@@ -26521,7 +26518,7 @@
         <v>42</v>
       </c>
       <c r="P748" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q748" s="34">
         <v>40896</v>
@@ -26587,7 +26584,7 @@
         <v>47</v>
       </c>
       <c r="P749" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q749" s="34">
         <v>40955</v>
@@ -26653,7 +26650,7 @@
         <v>34</v>
       </c>
       <c r="P750" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q750" s="34">
         <v>44333</v>
@@ -26719,7 +26716,7 @@
         <v>34</v>
       </c>
       <c r="P751" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q751" s="34">
         <v>41631</v>
@@ -26785,7 +26782,7 @@
         <v>35</v>
       </c>
       <c r="P752" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q752" s="34">
         <v>41631</v>
@@ -26851,7 +26848,7 @@
         <v>33</v>
       </c>
       <c r="P753" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q753" s="34">
         <v>41631</v>
@@ -26917,7 +26914,7 @@
         <v>34</v>
       </c>
       <c r="P754" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q754" s="34">
         <v>41631</v>
@@ -26983,7 +26980,7 @@
         <v>45</v>
       </c>
       <c r="P755" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q755" s="34">
         <v>41064</v>
@@ -27049,7 +27046,7 @@
         <v>46</v>
       </c>
       <c r="P756" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q756" s="34">
         <v>44060</v>
@@ -27115,7 +27112,7 @@
         <v>40</v>
       </c>
       <c r="P757" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q757" s="34">
         <v>41129</v>
@@ -27181,7 +27178,7 @@
         <v>42</v>
       </c>
       <c r="P758" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q758" s="34">
         <v>41204</v>
@@ -27247,7 +27244,7 @@
         <v>38</v>
       </c>
       <c r="P759" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q759" s="34">
         <v>41218</v>
@@ -27313,7 +27310,7 @@
         <v>31</v>
       </c>
       <c r="P760" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q760" s="34">
         <v>43191</v>
@@ -27379,7 +27376,7 @@
         <v>34</v>
       </c>
       <c r="P761" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q761" s="34">
         <v>43800</v>
@@ -27445,7 +27442,7 @@
         <v>31</v>
       </c>
       <c r="P762" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q762" s="34">
         <v>41982</v>
@@ -27511,7 +27508,7 @@
         <v>36</v>
       </c>
       <c r="P763" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q763" s="34">
         <v>41852</v>
@@ -27577,7 +27574,7 @@
         <v>33</v>
       </c>
       <c r="P764" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q764" s="34">
         <v>42590</v>
@@ -27643,7 +27640,7 @@
         <v>34</v>
       </c>
       <c r="P765" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q765" s="34">
         <v>42064</v>
@@ -27709,7 +27706,7 @@
         <v>35</v>
       </c>
       <c r="P766" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q766" s="34">
         <v>41982</v>
@@ -27775,7 +27772,7 @@
         <v>33</v>
       </c>
       <c r="P767" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q767" s="34">
         <v>41982</v>
@@ -27841,7 +27838,7 @@
         <v>32</v>
       </c>
       <c r="P768" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q768" s="34">
         <v>42675</v>
@@ -27907,7 +27904,7 @@
         <v>32</v>
       </c>
       <c r="P769" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q769" s="34">
         <v>42675</v>
@@ -27973,7 +27970,7 @@
         <v>46</v>
       </c>
       <c r="P770" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q770" s="34">
         <v>41617</v>
@@ -28039,7 +28036,7 @@
         <v>32</v>
       </c>
       <c r="P771" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q771" s="34">
         <v>44333</v>
@@ -28105,7 +28102,7 @@
         <v>35</v>
       </c>
       <c r="P772" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q772" s="34">
         <v>43040</v>
@@ -28171,7 +28168,7 @@
         <v>37</v>
       </c>
       <c r="P773" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q773" s="34">
         <v>44348</v>
@@ -28237,7 +28234,7 @@
         <v>38</v>
       </c>
       <c r="P774" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q774" s="34">
         <v>41883</v>
@@ -28303,7 +28300,7 @@
         <v>34</v>
       </c>
       <c r="P775" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q775" s="34">
         <v>44333</v>
@@ -28369,7 +28366,7 @@
         <v>36</v>
       </c>
       <c r="P776" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q776" s="34">
         <v>42738</v>
@@ -28435,7 +28432,7 @@
         <v>33</v>
       </c>
       <c r="P777" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q777" s="34">
         <v>42738</v>
@@ -28501,7 +28498,7 @@
         <v>29</v>
       </c>
       <c r="P778" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q778" s="34">
         <v>43206</v>
@@ -28567,7 +28564,7 @@
         <v>37</v>
       </c>
       <c r="P779" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q779" s="34">
         <v>45299</v>
@@ -28633,7 +28630,7 @@
         <v>42</v>
       </c>
       <c r="P780" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q780" s="34">
         <v>42370</v>
@@ -28699,7 +28696,7 @@
         <v>39</v>
       </c>
       <c r="P781" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q781" s="34">
         <v>42370</v>
@@ -28765,7 +28762,7 @@
         <v>37</v>
       </c>
       <c r="P782" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q782" s="34">
         <v>42370</v>
@@ -28831,7 +28828,7 @@
         <v>30</v>
       </c>
       <c r="P783" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q783" s="34">
         <v>44713</v>
@@ -28897,7 +28894,7 @@
         <v>38</v>
       </c>
       <c r="P784" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q784" s="34">
         <v>42493</v>
@@ -28963,7 +28960,7 @@
         <v>33</v>
       </c>
       <c r="P785" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q785" s="34">
         <v>44333</v>
@@ -29029,7 +29026,7 @@
         <v>53</v>
       </c>
       <c r="P786" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q786" s="34">
         <v>42738</v>
@@ -29095,7 +29092,7 @@
         <v>45</v>
       </c>
       <c r="P787" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q787" s="34">
         <v>42979</v>
@@ -29161,7 +29158,7 @@
         <v>43</v>
       </c>
       <c r="P788" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q788" s="34">
         <v>43089</v>
@@ -29227,7 +29224,7 @@
         <v>31</v>
       </c>
       <c r="P789" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q789" s="34">
         <v>43819</v>
@@ -29293,7 +29290,7 @@
         <v>34</v>
       </c>
       <c r="P790" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q790" s="34">
         <v>43472</v>
@@ -29359,7 +29356,7 @@
         <v>32</v>
       </c>
       <c r="P791" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q791" s="34">
         <v>43831</v>
@@ -29425,7 +29422,7 @@
         <v>32</v>
       </c>
       <c r="P792" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q792" s="34">
         <v>43089</v>
@@ -29491,7 +29488,7 @@
         <v>30</v>
       </c>
       <c r="P793" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q793" s="34">
         <v>43089</v>
@@ -29557,7 +29554,7 @@
         <v>37</v>
       </c>
       <c r="P794" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q794" s="34">
         <v>43089</v>
@@ -29623,7 +29620,7 @@
         <v>32</v>
       </c>
       <c r="P795" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q795" s="34">
         <v>43089</v>
@@ -29689,7 +29686,7 @@
         <v>47</v>
       </c>
       <c r="P796" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q796" s="34">
         <v>43089</v>
@@ -29755,7 +29752,7 @@
         <v>32</v>
       </c>
       <c r="P797" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q797" s="34">
         <v>43831</v>
@@ -29821,7 +29818,7 @@
         <v>40</v>
       </c>
       <c r="P798" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q798" s="34">
         <v>43191</v>
@@ -29887,7 +29884,7 @@
         <v>40</v>
       </c>
       <c r="P799" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q799" s="34">
         <v>43206</v>
@@ -29953,7 +29950,7 @@
         <v>31</v>
       </c>
       <c r="P800" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q800" s="34">
         <v>44348</v>
@@ -30019,7 +30016,7 @@
         <v>30</v>
       </c>
       <c r="P801" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q801" s="34">
         <v>44333</v>
@@ -30085,7 +30082,7 @@
         <v>39</v>
       </c>
       <c r="P802" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q802" s="34">
         <v>43472</v>
@@ -30151,7 +30148,7 @@
         <v>38</v>
       </c>
       <c r="P803" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q803" s="34">
         <v>43472</v>
@@ -30217,7 +30214,7 @@
         <v>38</v>
       </c>
       <c r="P804" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q804" s="34">
         <v>43472</v>
@@ -30283,7 +30280,7 @@
         <v>44</v>
       </c>
       <c r="P805" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q805" s="34">
         <v>43472</v>
@@ -30349,7 +30346,7 @@
         <v>37</v>
       </c>
       <c r="P806" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q806" s="34">
         <v>43472</v>
@@ -30415,7 +30412,7 @@
         <v>28</v>
       </c>
       <c r="P807" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q807" s="34">
         <v>43472</v>
@@ -30481,7 +30478,7 @@
         <v>35</v>
       </c>
       <c r="P808" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q808" s="34">
         <v>43472</v>
@@ -30547,7 +30544,7 @@
         <v>37</v>
       </c>
       <c r="P809" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q809" s="34">
         <v>43472</v>
@@ -30613,7 +30610,7 @@
         <v>52</v>
       </c>
       <c r="P810" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q810" s="34">
         <v>43472</v>
@@ -30679,7 +30676,7 @@
         <v>50</v>
       </c>
       <c r="P811" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q811" s="34">
         <v>43497</v>
@@ -30745,7 +30742,7 @@
         <v>50</v>
       </c>
       <c r="P812" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q812" s="34">
         <v>44214</v>
@@ -30811,7 +30808,7 @@
         <v>34</v>
       </c>
       <c r="P813" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q813" s="34">
         <v>43800</v>
@@ -30877,7 +30874,7 @@
         <v>30</v>
       </c>
       <c r="P814" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q814" s="34">
         <v>43819</v>
@@ -30943,7 +30940,7 @@
         <v>31</v>
       </c>
       <c r="P815" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q815" s="34">
         <v>44242</v>
@@ -31009,7 +31006,7 @@
         <v>31</v>
       </c>
       <c r="P816" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q816" s="34">
         <v>44242</v>
@@ -31075,7 +31072,7 @@
         <v>43</v>
       </c>
       <c r="P817" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q817" s="34">
         <v>44317</v>
@@ -31141,7 +31138,7 @@
         <v>43</v>
       </c>
       <c r="P818" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q818" s="34">
         <v>44333</v>
@@ -31207,7 +31204,7 @@
         <v>38</v>
       </c>
       <c r="P819" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q819" s="34">
         <v>44333</v>
@@ -31273,7 +31270,7 @@
         <v>28</v>
       </c>
       <c r="P820" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q820" s="34">
         <v>44333</v>
@@ -31339,7 +31336,7 @@
         <v>31</v>
       </c>
       <c r="P821" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q821" s="34">
         <v>44333</v>
@@ -31405,7 +31402,7 @@
         <v>34</v>
       </c>
       <c r="P822" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q822" s="34">
         <v>44333</v>
@@ -31471,7 +31468,7 @@
         <v>45</v>
       </c>
       <c r="P823" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q823" s="34">
         <v>44333</v>
@@ -31537,7 +31534,7 @@
         <v>32</v>
       </c>
       <c r="P824" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q824" s="34">
         <v>44333</v>
@@ -31603,7 +31600,7 @@
         <v>33</v>
       </c>
       <c r="P825" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q825" s="34">
         <v>44333</v>
@@ -31669,7 +31666,7 @@
         <v>32</v>
       </c>
       <c r="P826" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q826" s="34">
         <v>44333</v>
@@ -31735,7 +31732,7 @@
         <v>44</v>
       </c>
       <c r="P827" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q827" s="34">
         <v>44333</v>
@@ -31801,7 +31798,7 @@
         <v>44</v>
       </c>
       <c r="P828" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q828" s="34">
         <v>44348</v>
@@ -31867,7 +31864,7 @@
         <v>36</v>
       </c>
       <c r="P829" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q829" s="34">
         <v>44410</v>
@@ -31933,7 +31930,7 @@
         <v>34</v>
       </c>
       <c r="P830" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q830" s="34">
         <v>44431</v>
@@ -31999,7 +31996,7 @@
         <v>38</v>
       </c>
       <c r="P831" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q831" s="34">
         <v>44531</v>
@@ -32065,7 +32062,7 @@
         <v>26</v>
       </c>
       <c r="P832" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q832" s="34">
         <v>44531</v>
@@ -32131,7 +32128,7 @@
         <v>32</v>
       </c>
       <c r="P833" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q833" s="34">
         <v>44531</v>
@@ -32197,7 +32194,7 @@
         <v>36</v>
       </c>
       <c r="P834" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q834" s="34">
         <v>44562</v>
@@ -32263,7 +32260,7 @@
         <v>33</v>
       </c>
       <c r="P835" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q835" s="34">
         <v>44562</v>
@@ -32329,7 +32326,7 @@
         <v>30</v>
       </c>
       <c r="P836" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q836" s="34">
         <v>44562</v>
@@ -32395,7 +32392,7 @@
         <v>49</v>
       </c>
       <c r="P837" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q837" s="34">
         <v>44621</v>
@@ -32461,7 +32458,7 @@
         <v>33</v>
       </c>
       <c r="P838" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q838" s="34">
         <v>44634</v>
@@ -32527,7 +32524,7 @@
         <v>43</v>
       </c>
       <c r="P839" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q839" s="34">
         <v>44652</v>
@@ -32593,7 +32590,7 @@
         <v>44</v>
       </c>
       <c r="P840" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q840" s="34">
         <v>44652</v>
@@ -32659,7 +32656,7 @@
         <v>52</v>
       </c>
       <c r="P841" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q841" s="34">
         <v>44662</v>
@@ -32725,7 +32722,7 @@
         <v>31</v>
       </c>
       <c r="P842" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q842" s="34">
         <v>44662</v>
@@ -32791,7 +32788,7 @@
         <v>32</v>
       </c>
       <c r="P843" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q843" s="34">
         <v>44662</v>
@@ -32857,7 +32854,7 @@
         <v>28</v>
       </c>
       <c r="P844" s="35" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
       <c r="Q844" s="34">
         <v>44662</v>
@@ -32923,7 +32920,7 @@
         <v>35</v>
       </c>
       <c r="P845" s="35" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="Q845" s="34">
         <v>44697</v>
@@ -32989,7 +32986,7 @@
         <v>38</v>
       </c>
       <c r="P846" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q846" s="34">
         <v>44713</v>
@@ -33055,7 +33052,7 @@
         <v>50</v>
       </c>
       <c r="P847" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q847" s="34">
         <v>44713</v>
@@ -33121,7 +33118,7 @@
         <v>48</v>
       </c>
       <c r="P848" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q848" s="34">
         <v>44713</v>
@@ -33187,7 +33184,7 @@
         <v>36</v>
       </c>
       <c r="P849" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q849" s="34">
         <v>44713</v>
@@ -33253,7 +33250,7 @@
         <v>43</v>
       </c>
       <c r="P850" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q850" s="34">
         <v>44713</v>
@@ -33319,7 +33316,7 @@
         <v>52</v>
       </c>
       <c r="P851" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q851" s="34">
         <v>44732</v>
@@ -33385,7 +33382,7 @@
         <v>37</v>
       </c>
       <c r="P852" s="35" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="Q852" s="34">
         <v>44732</v>
@@ -33451,7 +33448,7 @@
         <v>36</v>
       </c>
       <c r="P853" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q853" s="34">
         <v>44732</v>
@@ -33517,7 +33514,7 @@
         <v>27</v>
       </c>
       <c r="P854" s="35" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="Q854" s="34">
         <v>46006</v>
@@ -33585,7 +33582,7 @@
         <v>28</v>
       </c>
       <c r="P855" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q855" s="34">
         <v>45250</v>
@@ -33651,7 +33648,7 @@
         <v>49</v>
       </c>
       <c r="P856" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q856" s="34">
         <v>45352</v>
@@ -33717,7 +33714,7 @@
         <v>34</v>
       </c>
       <c r="P857" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q857" s="34">
         <v>45352</v>
@@ -33783,7 +33780,7 @@
         <v>27</v>
       </c>
       <c r="P858" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q858" s="34">
         <v>45352</v>
@@ -33849,7 +33846,7 @@
         <v>30</v>
       </c>
       <c r="P859" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q859" s="34">
         <v>45352</v>
@@ -33915,7 +33912,7 @@
         <v>29</v>
       </c>
       <c r="P860" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q860" s="34">
         <v>45352</v>
@@ -33981,7 +33978,7 @@
         <v>33</v>
       </c>
       <c r="P861" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q861" s="34">
         <v>45352</v>
@@ -34047,7 +34044,7 @@
         <v>32</v>
       </c>
       <c r="P862" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q862" s="34">
         <v>45352</v>
@@ -34113,7 +34110,7 @@
         <v>43</v>
       </c>
       <c r="P863" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q863" s="34">
         <v>45352</v>
@@ -34179,7 +34176,7 @@
         <v>48</v>
       </c>
       <c r="P864" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q864" s="34">
         <v>45352</v>
@@ -34245,7 +34242,7 @@
         <v>32</v>
       </c>
       <c r="P865" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q865" s="34">
         <v>45418</v>
@@ -34311,7 +34308,7 @@
         <v>58</v>
       </c>
       <c r="P866" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q866" s="34">
         <v>45474</v>
@@ -34377,7 +34374,7 @@
         <v>28</v>
       </c>
       <c r="P867" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q867" s="34">
         <v>45627</v>
@@ -34443,7 +34440,7 @@
         <v>32</v>
       </c>
       <c r="P868" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q868" s="34">
         <v>45717</v>
@@ -34511,7 +34508,7 @@
         <v>25</v>
       </c>
       <c r="P869" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q869" s="34">
         <v>45717</v>
@@ -34579,7 +34576,7 @@
         <v>35</v>
       </c>
       <c r="P870" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q870" s="34">
         <v>45717</v>
@@ -34647,7 +34644,7 @@
         <v>30</v>
       </c>
       <c r="P871" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q871" s="34">
         <v>45824</v>
@@ -34715,7 +34712,7 @@
         <v>29</v>
       </c>
       <c r="P872" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q872" s="34">
         <v>45824</v>
@@ -34783,7 +34780,7 @@
         <v>31</v>
       </c>
       <c r="P873" s="35" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="Q873" s="34">
         <v>45824</v>
@@ -34851,7 +34848,7 @@
         <v>31</v>
       </c>
       <c r="P874" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q874" s="34">
         <v>45859</v>
@@ -34917,7 +34914,7 @@
         <v>35</v>
       </c>
       <c r="P875" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q875" s="34">
         <v>45950</v>
@@ -34983,7 +34980,7 @@
         <v>33</v>
       </c>
       <c r="P876" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q876" s="34">
         <v>46006</v>
@@ -35051,7 +35048,7 @@
         <v>22</v>
       </c>
       <c r="P877" s="35" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="Q877" s="34">
         <v>46020</v>
@@ -35119,7 +35116,7 @@
         <v>26</v>
       </c>
       <c r="P878" s="35" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="Q878" s="34">
         <v>46041</v>
@@ -35187,7 +35184,7 @@
         <v>28</v>
       </c>
       <c r="P879" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q879" s="34">
         <v>46041</v>
@@ -35255,7 +35252,7 @@
         <v>46</v>
       </c>
       <c r="P880" s="35" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="Q880" s="34">
         <v>46054</v>
@@ -35321,7 +35318,7 @@
         <v>26</v>
       </c>
       <c r="P881" s="35" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
       <c r="Q881" s="34">
         <v>46054</v>
@@ -35389,7 +35386,7 @@
         <v>24</v>
       </c>
       <c r="P882" s="35" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="Q882" s="34">
         <v>46054</v>
@@ -35457,7 +35454,7 @@
         <v>34</v>
       </c>
       <c r="P883" s="35" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="Q883" s="34">
         <v>46054</v>
@@ -35525,7 +35522,7 @@
         <v>41</v>
       </c>
       <c r="P884" s="35" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="Q884" s="34">
         <v>46143</v>
@@ -35559,7 +35556,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D3B0B5-E7CA-41F3-B584-8BB10868D96B}">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.54296875" customWidth="1"/>
@@ -35610,7 +35607,7 @@
         <v>1607</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>1665</v>
+        <v>1661</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>1608</v>
@@ -35635,7 +35632,7 @@
       <c r="A2" s="5">
         <v>39653</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>184</v>
       </c>
       <c r="C2" s="6" t="s">
@@ -35669,10 +35666,10 @@
         <v>1615</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>1609</v>
+        <v>1675</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="O2" s="8">
         <v>359</v>
@@ -35681,18 +35678,18 @@
         <v>716</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>1197</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="5">
         <v>39667</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>207</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1666</v>
+        <v>1662</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>210</v>
@@ -35722,26 +35719,26 @@
         <v>1615</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>1618</v>
+        <v>1677</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="O3" s="8">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="P3" s="8">
         <v>136</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>1206</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="5">
         <v>51906</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>372</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -35775,10 +35772,10 @@
         <v>1615</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>1609</v>
+        <v>1675</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="O4" s="8">
         <v>360</v>
@@ -35787,14 +35784,14 @@
         <v>720</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>1268</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="5">
         <v>51908</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>376</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -35828,10 +35825,10 @@
         <v>1615</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>1609</v>
+        <v>1675</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="O5" s="8">
         <v>345</v>
@@ -35840,21 +35837,21 @@
         <v>735</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>1270</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="5">
-        <v>53451</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>542</v>
+        <v>53848</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>577</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>34</v>
@@ -35863,51 +35860,51 @@
         <v>1601</v>
       </c>
       <c r="G6" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6" s="9">
-        <v>46189</v>
+        <v>46200</v>
       </c>
       <c r="I6" s="9">
-        <v>46199</v>
+        <v>46229</v>
       </c>
       <c r="J6" s="5">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K6" s="8">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>1609</v>
+        <v>1675</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>1647</v>
+        <v>1676</v>
       </c>
       <c r="O6" s="8">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="P6" s="8">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>1346</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="5">
-        <v>53848</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>577</v>
+        <v>59381</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>716</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>1620</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>34</v>
@@ -35916,45 +35913,45 @@
         <v>1601</v>
       </c>
       <c r="G7" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="9">
-        <v>46200</v>
+        <v>46178</v>
       </c>
       <c r="I7" s="9">
-        <v>46229</v>
+        <v>46207</v>
       </c>
       <c r="J7" s="5">
         <v>30</v>
       </c>
       <c r="K7" s="8">
-        <v>90</v>
+        <v>261</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>1609</v>
+        <v>1675</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="O7" s="8">
-        <v>120</v>
+        <v>261</v>
       </c>
       <c r="P7" s="8">
-        <v>175</v>
+        <v>264</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>1361</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="5">
-        <v>56288</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>675</v>
+        <v>59385</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>724</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1621</v>
@@ -35969,157 +35966,157 @@
         <v>1601</v>
       </c>
       <c r="G8" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="9">
         <v>46191</v>
       </c>
       <c r="I8" s="9">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="J8" s="5">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K8" s="8">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>1609</v>
+        <v>1675</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="O8" s="8">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="P8" s="8">
-        <v>209</v>
+        <v>76</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>1402</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="5">
-        <v>56561</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>683</v>
+        <v>59401</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>736</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>682</v>
+        <v>735</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>1601</v>
       </c>
       <c r="G9" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="9">
-        <v>46189</v>
+        <v>46210</v>
       </c>
       <c r="I9" s="9">
-        <v>46203</v>
+        <v>46239</v>
       </c>
       <c r="J9" s="5">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K9" s="8">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>1618</v>
+        <v>1675</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>1647</v>
+        <v>1676</v>
       </c>
       <c r="O9" s="8">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="P9" s="8">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>1406</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="5">
-        <v>59381</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>716</v>
+        <v>70535</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>893</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1623</v>
+        <v>892</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>1601</v>
       </c>
       <c r="G10" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="9">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="I10" s="9">
-        <v>46207</v>
+        <v>46213</v>
       </c>
       <c r="J10" s="5">
         <v>30</v>
       </c>
       <c r="K10" s="8">
-        <v>261</v>
+        <v>60</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>1609</v>
+        <v>1675</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="O10" s="8">
-        <v>261</v>
+        <v>60</v>
       </c>
       <c r="P10" s="8">
-        <v>264</v>
+        <v>60</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>1420</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="5">
-        <v>59385</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>724</v>
+        <v>74084</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>925</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1624</v>
+        <v>924</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>73</v>
+        <v>326</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>34</v>
@@ -36128,196 +36125,90 @@
         <v>1601</v>
       </c>
       <c r="G11" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="9">
-        <v>46191</v>
+        <v>46202</v>
       </c>
       <c r="I11" s="9">
-        <v>46216</v>
+        <v>46231</v>
       </c>
       <c r="J11" s="5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K11" s="8">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>1609</v>
+        <v>1675</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="O11" s="8">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="P11" s="8">
-        <v>76</v>
+        <v>240</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>1424</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="5">
-        <v>59401</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>736</v>
+        <v>305439</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>1098</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>735</v>
+        <v>1097</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>1601</v>
       </c>
       <c r="G12" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" s="9">
-        <v>46189</v>
+        <v>46211</v>
       </c>
       <c r="I12" s="9">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="J12" s="5">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K12" s="8">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>1609</v>
+        <v>1677</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="O12" s="8">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="P12" s="8">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="A13" s="5">
-        <v>70535</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>893</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>892</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>1601</v>
-      </c>
-      <c r="G13" s="8">
-        <v>2</v>
-      </c>
-      <c r="H13" s="9">
-        <v>46184</v>
-      </c>
-      <c r="I13" s="9">
-        <v>46213</v>
-      </c>
-      <c r="J13" s="5">
-        <v>30</v>
-      </c>
-      <c r="K13" s="8">
-        <v>60</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>1615</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>1609</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>1679</v>
-      </c>
-      <c r="O13" s="8">
-        <v>60</v>
-      </c>
-      <c r="P13" s="8">
-        <v>60</v>
-      </c>
-      <c r="Q13" s="7" t="s">
-        <v>1493</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="A14" s="5">
-        <v>74084</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>925</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>924</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>1601</v>
-      </c>
-      <c r="G14" s="8">
-        <v>2</v>
-      </c>
-      <c r="H14" s="9">
-        <v>46202</v>
-      </c>
-      <c r="I14" s="9">
-        <v>46231</v>
-      </c>
-      <c r="J14" s="5">
-        <v>30</v>
-      </c>
-      <c r="K14" s="8">
-        <v>120</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>1615</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>1609</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>1622</v>
-      </c>
-      <c r="O14" s="8">
-        <v>120</v>
-      </c>
-      <c r="P14" s="8">
-        <v>270</v>
-      </c>
-      <c r="Q14" s="7" t="s">
-        <v>1507</v>
+        <v>1153</v>
       </c>
     </row>
   </sheetData>
@@ -36368,45 +36259,45 @@
     <row r="4" spans="2:14" ht="15.5">
       <c r="B4" s="12"/>
       <c r="C4" s="13" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>1625</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="G4" s="13" t="s">
         <v>1626</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="H4" s="13" t="s">
         <v>1627</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="I4" s="14" t="s">
         <v>1628</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="J4" s="14" t="s">
         <v>1629</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="K4" s="14" t="s">
         <v>1630</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="L4" s="14" t="s">
         <v>1631</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="M4" s="14" t="s">
         <v>1632</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="N4" s="14" t="s">
         <v>1633</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>1634</v>
-      </c>
-      <c r="M4" s="14" t="s">
-        <v>1635</v>
-      </c>
-      <c r="N4" s="14" t="s">
-        <v>1636</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="15.5">
       <c r="B5" s="15" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="C5" s="16">
         <v>4.2900000000000001E-2</v>
@@ -36447,7 +36338,7 @@
     </row>
     <row r="6" spans="2:14" ht="15.5">
       <c r="B6" s="18" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="C6" s="16">
         <v>9.7999999999999997E-3</v>
@@ -36488,7 +36379,7 @@
     </row>
     <row r="7" spans="2:14" ht="15.5">
       <c r="B7" s="18" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="C7" s="19">
         <v>5.2699999999999997E-2</v>
@@ -36559,7 +36450,7 @@
     </row>
     <row r="10" spans="2:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="B10" s="21" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
       <c r="C10" s="22">
         <v>5.8400000000000001E-2</v>
@@ -36589,28 +36480,28 @@
     <row r="11" spans="2:14" ht="15" thickTop="1"/>
     <row r="13" spans="2:14">
       <c r="C13" s="24" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="D13" s="24" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E13" s="24" t="s">
         <v>1638</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>1641</v>
       </c>
     </row>
     <row r="14" spans="2:14">
       <c r="B14" s="25" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="C14" s="27">
-        <v>5.8999999999999999E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="D14" s="27">
-        <v>1E-3</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="E14" s="26">
         <f>SUM(C14:D14)</f>
-        <v>6.8999999999999999E-3</v>
+        <v>4.8000000000000004E-3</v>
       </c>
     </row>
     <row r="15" spans="2:14">
@@ -36618,71 +36509,71 @@
         <v>837</v>
       </c>
       <c r="C15" s="27">
-        <v>3.8E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="D15" s="27">
-        <v>5.0000000000000001E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="E15" s="26">
         <f t="shared" ref="E15:E17" si="0">SUM(C15:D15)</f>
-        <v>4.3E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
     </row>
     <row r="16" spans="2:14">
       <c r="B16" s="25" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="C16" s="27">
-        <v>1.9E-2</v>
+        <v>1.11E-2</v>
       </c>
       <c r="D16" s="27">
-        <v>4.4000000000000003E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="E16" s="26">
         <f t="shared" si="0"/>
-        <v>2.3400000000000001E-2</v>
+        <v>1.2E-2</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="25" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="C17" s="27">
-        <v>1.8E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="D17" s="27">
-        <v>1.1999999999999999E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="E17" s="26">
         <f t="shared" si="0"/>
-        <v>3.0000000000000001E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="C18" s="26">
         <f>SUM(C14:C17)</f>
-        <v>3.0499999999999999E-2</v>
+        <v>2.0300000000000002E-2</v>
       </c>
       <c r="D18" s="26">
         <f>SUM(D14:D17)</f>
-        <v>7.1000000000000004E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="E18" s="26">
         <f>SUM(E14:E17)</f>
-        <v>3.7600000000000001E-2</v>
+        <v>2.2900000000000004E-2</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="C21" s="25" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="28" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="C22" s="27">
-        <v>1.9400000000000001E-2</v>
+        <v>2E-3</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -36690,20 +36581,20 @@
         <v>837</v>
       </c>
       <c r="C23" s="27">
-        <v>8.3000000000000001E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="28" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="C24" s="27">
-        <v>1.95E-2</v>
+        <v>7.4999999999999997E-3</v>
       </c>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="28" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="C25" s="27">
         <v>2.8999999999999998E-3</v>
@@ -36712,24 +36603,24 @@
     <row r="26" spans="2:5">
       <c r="C26" s="26">
         <f>SUM(C22:C25)</f>
-        <v>5.0100000000000006E-2</v>
+        <v>1.41E-2</v>
       </c>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="25" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="C28" s="27">
-        <v>2.3999999999999998E-3</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="25" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="C29" s="27">
         <f>C26-C28</f>
-        <v>4.7700000000000006E-2</v>
+        <v>1.4E-2</v>
       </c>
     </row>
   </sheetData>
@@ -36753,32 +36644,32 @@
   <sheetData>
     <row r="1" spans="2:9">
       <c r="B1" s="37" t="s">
-        <v>1656</v>
+        <v>1652</v>
       </c>
       <c r="C1" s="37"/>
       <c r="E1" s="37" t="s">
-        <v>1657</v>
+        <v>1653</v>
       </c>
       <c r="F1" s="37"/>
       <c r="H1" s="29" t="s">
-        <v>1663</v>
+        <v>1659</v>
       </c>
       <c r="I1" s="29" t="s">
-        <v>1664</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="2" spans="2:9">
       <c r="B2" s="29" t="s">
-        <v>1648</v>
+        <v>1644</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1649</v>
+        <v>1645</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>1648</v>
+        <v>1644</v>
       </c>
       <c r="F2" s="29" t="s">
-        <v>1649</v>
+        <v>1645</v>
       </c>
       <c r="H2" s="26">
         <v>1.2E-2</v>
@@ -36789,11 +36680,11 @@
     </row>
     <row r="3" spans="2:9">
       <c r="B3" s="25" t="s">
-        <v>1650</v>
+        <v>1646</v>
       </c>
       <c r="C3" s="24"/>
       <c r="E3" s="30" t="s">
-        <v>1662</v>
+        <v>1658</v>
       </c>
       <c r="F3" s="24">
         <v>1</v>
@@ -36801,51 +36692,51 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="25" t="s">
-        <v>1651</v>
+        <v>1647</v>
       </c>
       <c r="C4" s="24"/>
       <c r="E4" s="30" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="F4" s="24"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="25" t="s">
-        <v>1652</v>
+        <v>1648</v>
       </c>
       <c r="C5" s="24">
         <v>1</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>1659</v>
+        <v>1655</v>
       </c>
       <c r="F5" s="24"/>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" s="25" t="s">
-        <v>1653</v>
+        <v>1649</v>
       </c>
       <c r="C6" s="24"/>
       <c r="E6" s="30" t="s">
-        <v>1660</v>
+        <v>1656</v>
       </c>
       <c r="F6" s="24"/>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" s="25" t="s">
-        <v>1654</v>
+        <v>1650</v>
       </c>
       <c r="C7" s="24">
         <v>3</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>1661</v>
+        <v>1657</v>
       </c>
       <c r="F7" s="24"/>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="25" t="s">
-        <v>1655</v>
+        <v>1651</v>
       </c>
       <c r="C8" s="24"/>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baray020\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8022D2F1-DC2F-49AA-9DC5-D3B06E6DE2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16E6814-FDDC-4047-A5E7-487CAFC8716E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1890" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1890" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dotaci" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6594" uniqueCount="1679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6575" uniqueCount="1674">
   <si>
     <t>HENRIQUEZ POOL FELIPE ALBERTO</t>
   </si>
@@ -4899,12 +4899,6 @@
     <t>AGUILERA VIDELA EFRAIN DEL CAR</t>
   </si>
   <si>
-    <t xml:space="preserve">Psiquiatría </t>
-  </si>
-  <si>
-    <t>JELVEZ MALDONADO JORGE JONATHA</t>
-  </si>
-  <si>
     <t>HIDALGO MIRANDA MANUEL ALEJAND</t>
   </si>
   <si>
@@ -5028,9 +5022,6 @@
     <t>Acum.</t>
   </si>
   <si>
-    <t>CACERES RODRIGUEZ CLAUDIA ELIS</t>
-  </si>
-  <si>
     <t>mayo</t>
   </si>
   <si>
@@ -5067,16 +5058,10 @@
     <t>febrero</t>
   </si>
   <si>
-    <t xml:space="preserve">Continua </t>
-  </si>
-  <si>
-    <t>Traumatología</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nueva </t>
-  </si>
-  <si>
-    <t>Medicina General</t>
+    <t xml:space="preserve">Traumatología </t>
+  </si>
+  <si>
+    <t>Nueva</t>
   </si>
 </sst>
 </file>
@@ -5860,7 +5845,7 @@
         <v>57</v>
       </c>
       <c r="P435" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q435" s="34">
         <v>45789</v>
@@ -5926,7 +5911,7 @@
         <v>65</v>
       </c>
       <c r="P436" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q436" s="34">
         <v>33119</v>
@@ -5992,7 +5977,7 @@
         <v>65</v>
       </c>
       <c r="P437" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q437" s="34">
         <v>43235</v>
@@ -6058,7 +6043,7 @@
         <v>63</v>
       </c>
       <c r="P438" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q438" s="34">
         <v>34731</v>
@@ -6124,7 +6109,7 @@
         <v>56</v>
       </c>
       <c r="P439" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q439" s="34">
         <v>36923</v>
@@ -6190,7 +6175,7 @@
         <v>61</v>
       </c>
       <c r="P440" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q440" s="34">
         <v>31199</v>
@@ -6256,7 +6241,7 @@
         <v>58</v>
       </c>
       <c r="P441" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q441" s="34">
         <v>32629</v>
@@ -6322,7 +6307,7 @@
         <v>58</v>
       </c>
       <c r="P442" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q442" s="34">
         <v>37501</v>
@@ -6388,7 +6373,7 @@
         <v>59</v>
       </c>
       <c r="P443" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q443" s="34">
         <v>33091</v>
@@ -6454,7 +6439,7 @@
         <v>62</v>
       </c>
       <c r="P444" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q444" s="34">
         <v>32752</v>
@@ -6520,7 +6505,7 @@
         <v>61</v>
       </c>
       <c r="P445" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q445" s="34">
         <v>30817</v>
@@ -6586,7 +6571,7 @@
         <v>57</v>
       </c>
       <c r="P446" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q446" s="34">
         <v>33091</v>
@@ -6652,7 +6637,7 @@
         <v>59</v>
       </c>
       <c r="P447" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q447" s="34">
         <v>32157</v>
@@ -6718,7 +6703,7 @@
         <v>56</v>
       </c>
       <c r="P448" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q448" s="34">
         <v>38462</v>
@@ -6784,7 +6769,7 @@
         <v>57</v>
       </c>
       <c r="P449" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q449" s="34">
         <v>32782</v>
@@ -6850,7 +6835,7 @@
         <v>57</v>
       </c>
       <c r="P450" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q450" s="34">
         <v>33939</v>
@@ -6916,7 +6901,7 @@
         <v>60</v>
       </c>
       <c r="P451" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q451" s="34">
         <v>32660</v>
@@ -6982,7 +6967,7 @@
         <v>61</v>
       </c>
       <c r="P452" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q452" s="34">
         <v>32157</v>
@@ -7048,7 +7033,7 @@
         <v>57</v>
       </c>
       <c r="P453" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q453" s="34">
         <v>32629</v>
@@ -7114,7 +7099,7 @@
         <v>60</v>
       </c>
       <c r="P454" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q454" s="34">
         <v>38078</v>
@@ -7180,7 +7165,7 @@
         <v>59</v>
       </c>
       <c r="P455" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q455" s="34">
         <v>33263</v>
@@ -7246,7 +7231,7 @@
         <v>55</v>
       </c>
       <c r="P456" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q456" s="34">
         <v>33091</v>
@@ -7312,7 +7297,7 @@
         <v>57</v>
       </c>
       <c r="P457" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q457" s="34">
         <v>37015</v>
@@ -7378,7 +7363,7 @@
         <v>59</v>
       </c>
       <c r="P458" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q458" s="34">
         <v>33378</v>
@@ -7444,7 +7429,7 @@
         <v>57</v>
       </c>
       <c r="P459" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q459" s="34">
         <v>33179</v>
@@ -7510,7 +7495,7 @@
         <v>57</v>
       </c>
       <c r="P460" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q460" s="34">
         <v>37501</v>
@@ -7576,7 +7561,7 @@
         <v>58</v>
       </c>
       <c r="P461" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q461" s="34">
         <v>38322</v>
@@ -7642,7 +7627,7 @@
         <v>57</v>
       </c>
       <c r="P462" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q462" s="34">
         <v>33939</v>
@@ -7708,7 +7693,7 @@
         <v>56</v>
       </c>
       <c r="P463" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q463" s="34">
         <v>32752</v>
@@ -7774,7 +7759,7 @@
         <v>56</v>
       </c>
       <c r="P464" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q464" s="34">
         <v>37501</v>
@@ -7840,7 +7825,7 @@
         <v>56</v>
       </c>
       <c r="P465" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q465" s="34">
         <v>33165</v>
@@ -7906,7 +7891,7 @@
         <v>56</v>
       </c>
       <c r="P466" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q466" s="34">
         <v>33170</v>
@@ -7972,7 +7957,7 @@
         <v>55</v>
       </c>
       <c r="P467" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q467" s="34">
         <v>38078</v>
@@ -8038,7 +8023,7 @@
         <v>55</v>
       </c>
       <c r="P468" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q468" s="34">
         <v>37501</v>
@@ -8104,7 +8089,7 @@
         <v>54</v>
       </c>
       <c r="P469" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q469" s="34">
         <v>37012</v>
@@ -8170,7 +8155,7 @@
         <v>55</v>
       </c>
       <c r="P470" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q470" s="34">
         <v>38462</v>
@@ -8236,7 +8221,7 @@
         <v>54</v>
       </c>
       <c r="P471" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q471" s="34">
         <v>38322</v>
@@ -8302,7 +8287,7 @@
         <v>53</v>
       </c>
       <c r="P472" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q472" s="34">
         <v>37501</v>
@@ -8368,7 +8353,7 @@
         <v>57</v>
       </c>
       <c r="P473" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q473" s="34">
         <v>33165</v>
@@ -8434,7 +8419,7 @@
         <v>56</v>
       </c>
       <c r="P474" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q474" s="34">
         <v>33210</v>
@@ -8500,7 +8485,7 @@
         <v>57</v>
       </c>
       <c r="P475" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q475" s="34">
         <v>32752</v>
@@ -8566,7 +8551,7 @@
         <v>57</v>
       </c>
       <c r="P476" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q476" s="34">
         <v>33101</v>
@@ -8632,7 +8617,7 @@
         <v>55</v>
       </c>
       <c r="P477" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q477" s="34">
         <v>37501</v>
@@ -8698,7 +8683,7 @@
         <v>52</v>
       </c>
       <c r="P478" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q478" s="34">
         <v>38034</v>
@@ -8764,7 +8749,7 @@
         <v>53</v>
       </c>
       <c r="P479" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q479" s="34">
         <v>37012</v>
@@ -8830,7 +8815,7 @@
         <v>54</v>
       </c>
       <c r="P480" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q480" s="34">
         <v>37012</v>
@@ -8896,7 +8881,7 @@
         <v>53</v>
       </c>
       <c r="P481" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q481" s="34">
         <v>37501</v>
@@ -8962,7 +8947,7 @@
         <v>53</v>
       </c>
       <c r="P482" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q482" s="34">
         <v>37501</v>
@@ -9028,7 +9013,7 @@
         <v>54</v>
       </c>
       <c r="P483" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q483" s="34">
         <v>37625</v>
@@ -9094,7 +9079,7 @@
         <v>53</v>
       </c>
       <c r="P484" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q484" s="34">
         <v>33504</v>
@@ -9160,7 +9145,7 @@
         <v>52</v>
       </c>
       <c r="P485" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q485" s="34">
         <v>37935</v>
@@ -9226,7 +9211,7 @@
         <v>53</v>
       </c>
       <c r="P486" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q486" s="34">
         <v>37501</v>
@@ -9292,7 +9277,7 @@
         <v>53</v>
       </c>
       <c r="P487" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q487" s="34">
         <v>37501</v>
@@ -9358,7 +9343,7 @@
         <v>52</v>
       </c>
       <c r="P488" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q488" s="34">
         <v>37012</v>
@@ -9424,7 +9409,7 @@
         <v>51</v>
       </c>
       <c r="P489" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q489" s="34">
         <v>38005</v>
@@ -9490,7 +9475,7 @@
         <v>52</v>
       </c>
       <c r="P490" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q490" s="34">
         <v>37012</v>
@@ -9556,7 +9541,7 @@
         <v>50</v>
       </c>
       <c r="P491" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q491" s="34">
         <v>37021</v>
@@ -9622,7 +9607,7 @@
         <v>50</v>
       </c>
       <c r="P492" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q492" s="34">
         <v>37501</v>
@@ -9688,7 +9673,7 @@
         <v>49</v>
       </c>
       <c r="P493" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q493" s="34">
         <v>37502</v>
@@ -9754,7 +9739,7 @@
         <v>49</v>
       </c>
       <c r="P494" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q494" s="34">
         <v>37712</v>
@@ -9820,7 +9805,7 @@
         <v>47</v>
       </c>
       <c r="P495" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q495" s="34">
         <v>37501</v>
@@ -9886,7 +9871,7 @@
         <v>47</v>
       </c>
       <c r="P496" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q496" s="34">
         <v>38173</v>
@@ -9952,7 +9937,7 @@
         <v>48</v>
       </c>
       <c r="P497" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q497" s="34">
         <v>37561</v>
@@ -10018,7 +10003,7 @@
         <v>48</v>
       </c>
       <c r="P498" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q498" s="34">
         <v>37501</v>
@@ -10084,7 +10069,7 @@
         <v>46</v>
       </c>
       <c r="P499" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q499" s="34">
         <v>37935</v>
@@ -10150,7 +10135,7 @@
         <v>46</v>
       </c>
       <c r="P500" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q500" s="34">
         <v>38261</v>
@@ -10216,7 +10201,7 @@
         <v>46</v>
       </c>
       <c r="P501" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q501" s="34">
         <v>37622</v>
@@ -10282,7 +10267,7 @@
         <v>52</v>
       </c>
       <c r="P502" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q502" s="34">
         <v>37165</v>
@@ -10348,7 +10333,7 @@
         <v>57</v>
       </c>
       <c r="P503" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q503" s="34">
         <v>37501</v>
@@ -10414,7 +10399,7 @@
         <v>52</v>
       </c>
       <c r="P504" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q504" s="34">
         <v>37469</v>
@@ -10480,7 +10465,7 @@
         <v>53</v>
       </c>
       <c r="P505" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q505" s="34">
         <v>38462</v>
@@ -10546,7 +10531,7 @@
         <v>52</v>
       </c>
       <c r="P506" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q506" s="34">
         <v>38231</v>
@@ -10612,7 +10597,7 @@
         <v>51</v>
       </c>
       <c r="P507" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q507" s="34">
         <v>37973</v>
@@ -10678,7 +10663,7 @@
         <v>42</v>
       </c>
       <c r="P508" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q508" s="34">
         <v>38231</v>
@@ -10744,7 +10729,7 @@
         <v>42</v>
       </c>
       <c r="P509" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q509" s="34">
         <v>38322</v>
@@ -10810,7 +10795,7 @@
         <v>40</v>
       </c>
       <c r="P510" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q510" s="34">
         <v>38322</v>
@@ -10876,7 +10861,7 @@
         <v>57</v>
       </c>
       <c r="P511" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q511" s="34">
         <v>37622</v>
@@ -10942,7 +10927,7 @@
         <v>65</v>
       </c>
       <c r="P512" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q512" s="34">
         <v>33057</v>
@@ -11008,7 +10993,7 @@
         <v>61</v>
       </c>
       <c r="P513" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q513" s="34">
         <v>32752</v>
@@ -11074,7 +11059,7 @@
         <v>65</v>
       </c>
       <c r="P514" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q514" s="34">
         <v>32629</v>
@@ -11140,7 +11125,7 @@
         <v>63</v>
       </c>
       <c r="P515" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q515" s="34">
         <v>33939</v>
@@ -11206,7 +11191,7 @@
         <v>64</v>
       </c>
       <c r="P516" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q516" s="34">
         <v>30834</v>
@@ -11272,7 +11257,7 @@
         <v>65</v>
       </c>
       <c r="P517" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q517" s="34">
         <v>31731</v>
@@ -11338,7 +11323,7 @@
         <v>47</v>
       </c>
       <c r="P518" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q518" s="34">
         <v>38443</v>
@@ -11404,7 +11389,7 @@
         <v>64</v>
       </c>
       <c r="P519" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q519" s="34">
         <v>38462</v>
@@ -11470,7 +11455,7 @@
         <v>59</v>
       </c>
       <c r="P520" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q520" s="34">
         <v>38322</v>
@@ -11536,7 +11521,7 @@
         <v>59</v>
       </c>
       <c r="P521" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q521" s="34">
         <v>33064</v>
@@ -11602,7 +11587,7 @@
         <v>42</v>
       </c>
       <c r="P522" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q522" s="34">
         <v>40910</v>
@@ -11668,7 +11653,7 @@
         <v>49</v>
       </c>
       <c r="P523" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q523" s="34">
         <v>39114</v>
@@ -11734,7 +11719,7 @@
         <v>48</v>
       </c>
       <c r="P524" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q524" s="34">
         <v>38839</v>
@@ -11800,7 +11785,7 @@
         <v>55</v>
       </c>
       <c r="P525" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q525" s="34">
         <v>39734</v>
@@ -11866,7 +11851,7 @@
         <v>44</v>
       </c>
       <c r="P526" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q526" s="34">
         <v>39694</v>
@@ -11932,7 +11917,7 @@
         <v>54</v>
       </c>
       <c r="P527" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q527" s="34">
         <v>39098</v>
@@ -11998,7 +11983,7 @@
         <v>45</v>
       </c>
       <c r="P528" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q528" s="34">
         <v>39097</v>
@@ -12064,7 +12049,7 @@
         <v>44</v>
       </c>
       <c r="P529" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q529" s="34">
         <v>40301</v>
@@ -12130,7 +12115,7 @@
         <v>50</v>
       </c>
       <c r="P530" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q530" s="34">
         <v>39083</v>
@@ -12196,7 +12181,7 @@
         <v>37</v>
       </c>
       <c r="P531" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q531" s="34">
         <v>39234</v>
@@ -12262,7 +12247,7 @@
         <v>45</v>
       </c>
       <c r="P532" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q532" s="34">
         <v>39234</v>
@@ -12328,7 +12313,7 @@
         <v>50</v>
       </c>
       <c r="P533" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q533" s="34">
         <v>39234</v>
@@ -12394,7 +12379,7 @@
         <v>43</v>
       </c>
       <c r="P534" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q534" s="34">
         <v>39234</v>
@@ -12460,7 +12445,7 @@
         <v>41</v>
       </c>
       <c r="P535" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q535" s="34">
         <v>39234</v>
@@ -12526,7 +12511,7 @@
         <v>40</v>
       </c>
       <c r="P536" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q536" s="34">
         <v>39234</v>
@@ -12592,7 +12577,7 @@
         <v>40</v>
       </c>
       <c r="P537" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q537" s="34">
         <v>39234</v>
@@ -12658,7 +12643,7 @@
         <v>40</v>
       </c>
       <c r="P538" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q538" s="34">
         <v>39234</v>
@@ -12724,7 +12709,7 @@
         <v>52</v>
       </c>
       <c r="P539" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q539" s="34">
         <v>42064</v>
@@ -12790,7 +12775,7 @@
         <v>50</v>
       </c>
       <c r="P540" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q540" s="34">
         <v>39340</v>
@@ -12856,7 +12841,7 @@
         <v>51</v>
       </c>
       <c r="P541" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q541" s="34">
         <v>39340</v>
@@ -12922,7 +12907,7 @@
         <v>50</v>
       </c>
       <c r="P542" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q542" s="34">
         <v>39340</v>
@@ -12988,7 +12973,7 @@
         <v>49</v>
       </c>
       <c r="P543" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q543" s="34">
         <v>39340</v>
@@ -13054,7 +13039,7 @@
         <v>49</v>
       </c>
       <c r="P544" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q544" s="34">
         <v>39340</v>
@@ -13120,7 +13105,7 @@
         <v>54</v>
       </c>
       <c r="P545" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q545" s="34">
         <v>39340</v>
@@ -13186,7 +13171,7 @@
         <v>58</v>
       </c>
       <c r="P546" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q546" s="34">
         <v>39340</v>
@@ -13252,7 +13237,7 @@
         <v>51</v>
       </c>
       <c r="P547" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q547" s="34">
         <v>39340</v>
@@ -13318,7 +13303,7 @@
         <v>57</v>
       </c>
       <c r="P548" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q548" s="34">
         <v>39340</v>
@@ -13384,7 +13369,7 @@
         <v>54</v>
       </c>
       <c r="P549" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q549" s="34">
         <v>39340</v>
@@ -13450,7 +13435,7 @@
         <v>48</v>
       </c>
       <c r="P550" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q550" s="34">
         <v>39340</v>
@@ -13516,7 +13501,7 @@
         <v>53</v>
       </c>
       <c r="P551" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q551" s="34">
         <v>39340</v>
@@ -13582,7 +13567,7 @@
         <v>52</v>
       </c>
       <c r="P552" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q552" s="34">
         <v>39340</v>
@@ -13648,7 +13633,7 @@
         <v>49</v>
       </c>
       <c r="P553" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q553" s="34">
         <v>39340</v>
@@ -13714,7 +13699,7 @@
         <v>63</v>
       </c>
       <c r="P554" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q554" s="34">
         <v>39340</v>
@@ -13780,7 +13765,7 @@
         <v>50</v>
       </c>
       <c r="P555" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q555" s="34">
         <v>39340</v>
@@ -13846,7 +13831,7 @@
         <v>52</v>
       </c>
       <c r="P556" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q556" s="34">
         <v>39340</v>
@@ -13912,7 +13897,7 @@
         <v>53</v>
       </c>
       <c r="P557" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q557" s="34">
         <v>39340</v>
@@ -13978,7 +13963,7 @@
         <v>47</v>
       </c>
       <c r="P558" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q558" s="34">
         <v>39340</v>
@@ -14044,7 +14029,7 @@
         <v>59</v>
       </c>
       <c r="P559" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q559" s="34">
         <v>39340</v>
@@ -14110,7 +14095,7 @@
         <v>45</v>
       </c>
       <c r="P560" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q560" s="34">
         <v>39340</v>
@@ -14176,7 +14161,7 @@
         <v>56</v>
       </c>
       <c r="P561" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q561" s="34">
         <v>39340</v>
@@ -14242,7 +14227,7 @@
         <v>54</v>
       </c>
       <c r="P562" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q562" s="34">
         <v>39340</v>
@@ -14308,7 +14293,7 @@
         <v>60</v>
       </c>
       <c r="P563" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q563" s="34">
         <v>39340</v>
@@ -14374,7 +14359,7 @@
         <v>48</v>
       </c>
       <c r="P564" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q564" s="34">
         <v>39340</v>
@@ -14440,7 +14425,7 @@
         <v>56</v>
       </c>
       <c r="P565" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q565" s="34">
         <v>39340</v>
@@ -14506,7 +14491,7 @@
         <v>57</v>
       </c>
       <c r="P566" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q566" s="34">
         <v>39340</v>
@@ -14572,7 +14557,7 @@
         <v>53</v>
       </c>
       <c r="P567" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q567" s="34">
         <v>39356</v>
@@ -14638,7 +14623,7 @@
         <v>50</v>
       </c>
       <c r="P568" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q568" s="34">
         <v>39356</v>
@@ -14704,7 +14689,7 @@
         <v>53</v>
       </c>
       <c r="P569" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q569" s="34">
         <v>39356</v>
@@ -14770,7 +14755,7 @@
         <v>54</v>
       </c>
       <c r="P570" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q570" s="34">
         <v>39356</v>
@@ -14836,7 +14821,7 @@
         <v>54</v>
       </c>
       <c r="P571" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q571" s="34">
         <v>39356</v>
@@ -14902,7 +14887,7 @@
         <v>52</v>
       </c>
       <c r="P572" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q572" s="34">
         <v>40049</v>
@@ -14968,7 +14953,7 @@
         <v>53</v>
       </c>
       <c r="P573" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q573" s="34">
         <v>39356</v>
@@ -15034,7 +15019,7 @@
         <v>48</v>
       </c>
       <c r="P574" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q574" s="34">
         <v>39356</v>
@@ -15100,7 +15085,7 @@
         <v>49</v>
       </c>
       <c r="P575" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q575" s="34">
         <v>39356</v>
@@ -15166,7 +15151,7 @@
         <v>52</v>
       </c>
       <c r="P576" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q576" s="34">
         <v>39356</v>
@@ -15232,7 +15217,7 @@
         <v>51</v>
       </c>
       <c r="P577" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q577" s="34">
         <v>39356</v>
@@ -15298,7 +15283,7 @@
         <v>54</v>
       </c>
       <c r="P578" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q578" s="34">
         <v>39356</v>
@@ -15364,7 +15349,7 @@
         <v>49</v>
       </c>
       <c r="P579" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q579" s="34">
         <v>39356</v>
@@ -15430,7 +15415,7 @@
         <v>51</v>
       </c>
       <c r="P580" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q580" s="34">
         <v>39356</v>
@@ -15496,7 +15481,7 @@
         <v>51</v>
       </c>
       <c r="P581" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q581" s="34">
         <v>39630</v>
@@ -15562,7 +15547,7 @@
         <v>52</v>
       </c>
       <c r="P582" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q582" s="34">
         <v>39356</v>
@@ -15628,7 +15613,7 @@
         <v>55</v>
       </c>
       <c r="P583" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q583" s="34">
         <v>39356</v>
@@ -15694,7 +15679,7 @@
         <v>50</v>
       </c>
       <c r="P584" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q584" s="34">
         <v>39356</v>
@@ -15760,7 +15745,7 @@
         <v>39</v>
       </c>
       <c r="P585" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q585" s="34">
         <v>39356</v>
@@ -15826,7 +15811,7 @@
         <v>51</v>
       </c>
       <c r="P586" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q586" s="34">
         <v>39356</v>
@@ -15892,7 +15877,7 @@
         <v>50</v>
       </c>
       <c r="P587" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q587" s="34">
         <v>39356</v>
@@ -15958,7 +15943,7 @@
         <v>46</v>
       </c>
       <c r="P588" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q588" s="34">
         <v>39356</v>
@@ -16024,7 +16009,7 @@
         <v>54</v>
       </c>
       <c r="P589" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q589" s="34">
         <v>39356</v>
@@ -16090,7 +16075,7 @@
         <v>49</v>
       </c>
       <c r="P590" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q590" s="34">
         <v>39370</v>
@@ -16156,7 +16141,7 @@
         <v>45</v>
       </c>
       <c r="P591" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q591" s="34">
         <v>39370</v>
@@ -16222,7 +16207,7 @@
         <v>52</v>
       </c>
       <c r="P592" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q592" s="34">
         <v>39370</v>
@@ -16288,7 +16273,7 @@
         <v>43</v>
       </c>
       <c r="P593" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q593" s="34">
         <v>39370</v>
@@ -16354,7 +16339,7 @@
         <v>55</v>
       </c>
       <c r="P594" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q594" s="34">
         <v>39370</v>
@@ -16420,7 +16405,7 @@
         <v>53</v>
       </c>
       <c r="P595" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q595" s="34">
         <v>39370</v>
@@ -16486,7 +16471,7 @@
         <v>44</v>
       </c>
       <c r="P596" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q596" s="34">
         <v>39479</v>
@@ -16552,7 +16537,7 @@
         <v>44</v>
       </c>
       <c r="P597" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q597" s="34">
         <v>39479</v>
@@ -16618,7 +16603,7 @@
         <v>39</v>
       </c>
       <c r="P598" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q598" s="34">
         <v>39479</v>
@@ -16684,7 +16669,7 @@
         <v>48</v>
       </c>
       <c r="P599" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q599" s="34">
         <v>39479</v>
@@ -16750,7 +16735,7 @@
         <v>59</v>
       </c>
       <c r="P600" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q600" s="34">
         <v>39479</v>
@@ -16816,7 +16801,7 @@
         <v>54</v>
       </c>
       <c r="P601" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q601" s="34">
         <v>39479</v>
@@ -16882,7 +16867,7 @@
         <v>45</v>
       </c>
       <c r="P602" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q602" s="34">
         <v>39479</v>
@@ -16948,7 +16933,7 @@
         <v>40</v>
       </c>
       <c r="P603" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q603" s="34">
         <v>39479</v>
@@ -17014,7 +16999,7 @@
         <v>62</v>
       </c>
       <c r="P604" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q604" s="34">
         <v>39479</v>
@@ -17080,7 +17065,7 @@
         <v>39</v>
       </c>
       <c r="P605" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q605" s="34">
         <v>39479</v>
@@ -17146,7 +17131,7 @@
         <v>46</v>
       </c>
       <c r="P606" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q606" s="34">
         <v>39479</v>
@@ -17212,7 +17197,7 @@
         <v>52</v>
       </c>
       <c r="P607" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q607" s="34">
         <v>39479</v>
@@ -17278,7 +17263,7 @@
         <v>56</v>
       </c>
       <c r="P608" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q608" s="34">
         <v>39479</v>
@@ -17344,7 +17329,7 @@
         <v>52</v>
       </c>
       <c r="P609" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q609" s="34">
         <v>39479</v>
@@ -17410,7 +17395,7 @@
         <v>47</v>
       </c>
       <c r="P610" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q610" s="34">
         <v>39479</v>
@@ -17476,7 +17461,7 @@
         <v>43</v>
       </c>
       <c r="P611" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q611" s="34">
         <v>39479</v>
@@ -17542,7 +17527,7 @@
         <v>51</v>
       </c>
       <c r="P612" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q612" s="34">
         <v>39479</v>
@@ -17608,7 +17593,7 @@
         <v>43</v>
       </c>
       <c r="P613" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q613" s="34">
         <v>39479</v>
@@ -17674,7 +17659,7 @@
         <v>48</v>
       </c>
       <c r="P614" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q614" s="34">
         <v>39479</v>
@@ -17740,7 +17725,7 @@
         <v>47</v>
       </c>
       <c r="P615" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q615" s="34">
         <v>39479</v>
@@ -17806,7 +17791,7 @@
         <v>59</v>
       </c>
       <c r="P616" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q616" s="34">
         <v>39479</v>
@@ -17872,7 +17857,7 @@
         <v>50</v>
       </c>
       <c r="P617" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q617" s="34">
         <v>39479</v>
@@ -17938,7 +17923,7 @@
         <v>54</v>
       </c>
       <c r="P618" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q618" s="34">
         <v>39479</v>
@@ -18004,7 +17989,7 @@
         <v>51</v>
       </c>
       <c r="P619" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q619" s="34">
         <v>39479</v>
@@ -18070,7 +18055,7 @@
         <v>45</v>
       </c>
       <c r="P620" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q620" s="34">
         <v>39479</v>
@@ -18136,7 +18121,7 @@
         <v>50</v>
       </c>
       <c r="P621" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q621" s="34">
         <v>39479</v>
@@ -18202,7 +18187,7 @@
         <v>46</v>
       </c>
       <c r="P622" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q622" s="34">
         <v>39479</v>
@@ -18268,7 +18253,7 @@
         <v>49</v>
       </c>
       <c r="P623" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q623" s="34">
         <v>39479</v>
@@ -18334,7 +18319,7 @@
         <v>54</v>
       </c>
       <c r="P624" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q624" s="34">
         <v>39479</v>
@@ -18400,7 +18385,7 @@
         <v>42</v>
       </c>
       <c r="P625" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q625" s="34">
         <v>39479</v>
@@ -18466,7 +18451,7 @@
         <v>45</v>
       </c>
       <c r="P626" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q626" s="34">
         <v>39479</v>
@@ -18532,7 +18517,7 @@
         <v>49</v>
       </c>
       <c r="P627" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q627" s="34">
         <v>39496</v>
@@ -18598,7 +18583,7 @@
         <v>48</v>
       </c>
       <c r="P628" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q628" s="34">
         <v>39693</v>
@@ -18664,7 +18649,7 @@
         <v>46</v>
       </c>
       <c r="P629" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q629" s="34">
         <v>39693</v>
@@ -18730,7 +18715,7 @@
         <v>50</v>
       </c>
       <c r="P630" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q630" s="34">
         <v>39693</v>
@@ -18796,7 +18781,7 @@
         <v>40</v>
       </c>
       <c r="P631" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q631" s="34">
         <v>39693</v>
@@ -18862,7 +18847,7 @@
         <v>44</v>
       </c>
       <c r="P632" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q632" s="34">
         <v>39723</v>
@@ -18928,7 +18913,7 @@
         <v>53</v>
       </c>
       <c r="P633" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q633" s="34">
         <v>39517</v>
@@ -18994,7 +18979,7 @@
         <v>43</v>
       </c>
       <c r="P634" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q634" s="34">
         <v>45200</v>
@@ -19060,7 +19045,7 @@
         <v>56</v>
       </c>
       <c r="P635" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q635" s="34">
         <v>39557</v>
@@ -19126,7 +19111,7 @@
         <v>46</v>
       </c>
       <c r="P636" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q636" s="34">
         <v>39557</v>
@@ -19192,7 +19177,7 @@
         <v>46</v>
       </c>
       <c r="P637" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q637" s="34">
         <v>39924</v>
@@ -19258,7 +19243,7 @@
         <v>48</v>
       </c>
       <c r="P638" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q638" s="34">
         <v>39583</v>
@@ -19324,7 +19309,7 @@
         <v>41</v>
       </c>
       <c r="P639" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q639" s="34">
         <v>39583</v>
@@ -19390,7 +19375,7 @@
         <v>40</v>
       </c>
       <c r="P640" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q640" s="34">
         <v>39583</v>
@@ -19456,7 +19441,7 @@
         <v>57</v>
       </c>
       <c r="P641" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q641" s="34">
         <v>39583</v>
@@ -19522,7 +19507,7 @@
         <v>43</v>
       </c>
       <c r="P642" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q642" s="34">
         <v>39583</v>
@@ -19588,7 +19573,7 @@
         <v>57</v>
       </c>
       <c r="P643" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q643" s="34">
         <v>39583</v>
@@ -19654,7 +19639,7 @@
         <v>57</v>
       </c>
       <c r="P644" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q644" s="34">
         <v>39583</v>
@@ -19720,7 +19705,7 @@
         <v>43</v>
       </c>
       <c r="P645" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q645" s="34">
         <v>39583</v>
@@ -19786,7 +19771,7 @@
         <v>43</v>
       </c>
       <c r="P646" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q646" s="34">
         <v>39583</v>
@@ -19852,7 +19837,7 @@
         <v>63</v>
       </c>
       <c r="P647" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q647" s="34">
         <v>39590</v>
@@ -19918,7 +19903,7 @@
         <v>48</v>
       </c>
       <c r="P648" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q648" s="34">
         <v>39590</v>
@@ -19984,7 +19969,7 @@
         <v>43</v>
       </c>
       <c r="P649" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q649" s="34">
         <v>39590</v>
@@ -20050,7 +20035,7 @@
         <v>44</v>
       </c>
       <c r="P650" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q650" s="34">
         <v>39590</v>
@@ -20116,7 +20101,7 @@
         <v>44</v>
       </c>
       <c r="P651" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q651" s="34">
         <v>39590</v>
@@ -20182,7 +20167,7 @@
         <v>50</v>
       </c>
       <c r="P652" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q652" s="34">
         <v>39590</v>
@@ -20248,7 +20233,7 @@
         <v>55</v>
       </c>
       <c r="P653" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q653" s="34">
         <v>39609</v>
@@ -20314,7 +20299,7 @@
         <v>52</v>
       </c>
       <c r="P654" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q654" s="34">
         <v>39615</v>
@@ -20380,7 +20365,7 @@
         <v>46</v>
       </c>
       <c r="P655" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q655" s="34">
         <v>39722</v>
@@ -20446,7 +20431,7 @@
         <v>45</v>
       </c>
       <c r="P656" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q656" s="34">
         <v>39630</v>
@@ -20512,7 +20497,7 @@
         <v>53</v>
       </c>
       <c r="P657" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q657" s="34">
         <v>39722</v>
@@ -20578,7 +20563,7 @@
         <v>39</v>
       </c>
       <c r="P658" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q658" s="34">
         <v>39734</v>
@@ -20644,7 +20629,7 @@
         <v>54</v>
       </c>
       <c r="P659" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q659" s="34">
         <v>39734</v>
@@ -20710,7 +20695,7 @@
         <v>38</v>
       </c>
       <c r="P660" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q660" s="34">
         <v>39734</v>
@@ -20776,7 +20761,7 @@
         <v>40</v>
       </c>
       <c r="P661" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q661" s="34">
         <v>39734</v>
@@ -20842,7 +20827,7 @@
         <v>56</v>
       </c>
       <c r="P662" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q662" s="34">
         <v>39734</v>
@@ -20908,7 +20893,7 @@
         <v>41</v>
       </c>
       <c r="P663" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q663" s="34">
         <v>39734</v>
@@ -20974,7 +20959,7 @@
         <v>53</v>
       </c>
       <c r="P664" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q664" s="34">
         <v>39734</v>
@@ -21040,7 +21025,7 @@
         <v>51</v>
       </c>
       <c r="P665" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q665" s="34">
         <v>39734</v>
@@ -21106,7 +21091,7 @@
         <v>47</v>
       </c>
       <c r="P666" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q666" s="34">
         <v>39734</v>
@@ -21172,7 +21157,7 @@
         <v>59</v>
       </c>
       <c r="P667" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q667" s="34">
         <v>39734</v>
@@ -21238,7 +21223,7 @@
         <v>59</v>
       </c>
       <c r="P668" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q668" s="34">
         <v>39734</v>
@@ -21304,7 +21289,7 @@
         <v>46</v>
       </c>
       <c r="P669" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q669" s="34">
         <v>39734</v>
@@ -21370,7 +21355,7 @@
         <v>40</v>
       </c>
       <c r="P670" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q670" s="34">
         <v>39734</v>
@@ -21436,7 +21421,7 @@
         <v>48</v>
       </c>
       <c r="P671" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q671" s="34">
         <v>39734</v>
@@ -21502,7 +21487,7 @@
         <v>48</v>
       </c>
       <c r="P672" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q672" s="34">
         <v>39734</v>
@@ -21568,7 +21553,7 @@
         <v>46</v>
       </c>
       <c r="P673" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q673" s="34">
         <v>39753</v>
@@ -21634,7 +21619,7 @@
         <v>57</v>
       </c>
       <c r="P674" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q674" s="34">
         <v>39753</v>
@@ -21700,7 +21685,7 @@
         <v>43</v>
       </c>
       <c r="P675" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q675" s="34">
         <v>39753</v>
@@ -21766,7 +21751,7 @@
         <v>58</v>
       </c>
       <c r="P676" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q676" s="34">
         <v>39762</v>
@@ -21832,7 +21817,7 @@
         <v>48</v>
       </c>
       <c r="P677" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q677" s="34">
         <v>39763</v>
@@ -21898,7 +21883,7 @@
         <v>46</v>
       </c>
       <c r="P678" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q678" s="34">
         <v>39783</v>
@@ -21964,7 +21949,7 @@
         <v>47</v>
       </c>
       <c r="P679" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q679" s="34">
         <v>39805</v>
@@ -22030,7 +22015,7 @@
         <v>43</v>
       </c>
       <c r="P680" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q680" s="34">
         <v>39821</v>
@@ -22096,7 +22081,7 @@
         <v>43</v>
       </c>
       <c r="P681" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q681" s="34">
         <v>39881</v>
@@ -22162,7 +22147,7 @@
         <v>51</v>
       </c>
       <c r="P682" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q682" s="34">
         <v>40009</v>
@@ -22228,7 +22213,7 @@
         <v>55</v>
       </c>
       <c r="P683" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q683" s="34">
         <v>40026</v>
@@ -22294,7 +22279,7 @@
         <v>47</v>
       </c>
       <c r="P684" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q684" s="34">
         <v>40049</v>
@@ -22360,7 +22345,7 @@
         <v>48</v>
       </c>
       <c r="P685" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q685" s="34">
         <v>40049</v>
@@ -22426,7 +22411,7 @@
         <v>41</v>
       </c>
       <c r="P686" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q686" s="34">
         <v>40049</v>
@@ -22492,7 +22477,7 @@
         <v>40</v>
       </c>
       <c r="P687" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q687" s="34">
         <v>40049</v>
@@ -22558,7 +22543,7 @@
         <v>53</v>
       </c>
       <c r="P688" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q688" s="34">
         <v>40049</v>
@@ -22624,7 +22609,7 @@
         <v>52</v>
       </c>
       <c r="P689" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q689" s="34">
         <v>40049</v>
@@ -22690,7 +22675,7 @@
         <v>52</v>
       </c>
       <c r="P690" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q690" s="34">
         <v>40049</v>
@@ -22756,7 +22741,7 @@
         <v>55</v>
       </c>
       <c r="P691" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q691" s="34">
         <v>40108</v>
@@ -22822,7 +22807,7 @@
         <v>40</v>
       </c>
       <c r="P692" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q692" s="34">
         <v>40192</v>
@@ -22888,7 +22873,7 @@
         <v>41</v>
       </c>
       <c r="P693" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q693" s="34">
         <v>40192</v>
@@ -22954,7 +22939,7 @@
         <v>55</v>
       </c>
       <c r="P694" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q694" s="34">
         <v>40192</v>
@@ -23020,7 +23005,7 @@
         <v>42</v>
       </c>
       <c r="P695" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q695" s="34">
         <v>40192</v>
@@ -23086,7 +23071,7 @@
         <v>43</v>
       </c>
       <c r="P696" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q696" s="34">
         <v>40192</v>
@@ -23152,7 +23137,7 @@
         <v>42</v>
       </c>
       <c r="P697" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q697" s="34">
         <v>40192</v>
@@ -23218,7 +23203,7 @@
         <v>48</v>
       </c>
       <c r="P698" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q698" s="34">
         <v>40192</v>
@@ -23284,7 +23269,7 @@
         <v>40</v>
       </c>
       <c r="P699" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q699" s="34">
         <v>40817</v>
@@ -23350,7 +23335,7 @@
         <v>41</v>
       </c>
       <c r="P700" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q700" s="34">
         <v>40210</v>
@@ -23416,7 +23401,7 @@
         <v>46</v>
       </c>
       <c r="P701" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q701" s="34">
         <v>40269</v>
@@ -23482,7 +23467,7 @@
         <v>35</v>
       </c>
       <c r="P702" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q702" s="34">
         <v>40269</v>
@@ -23548,7 +23533,7 @@
         <v>46</v>
       </c>
       <c r="P703" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q703" s="34">
         <v>40709</v>
@@ -23614,7 +23599,7 @@
         <v>39</v>
       </c>
       <c r="P704" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q704" s="34">
         <v>40771</v>
@@ -23680,7 +23665,7 @@
         <v>43</v>
       </c>
       <c r="P705" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q705" s="34">
         <v>40583</v>
@@ -23746,7 +23731,7 @@
         <v>41</v>
       </c>
       <c r="P706" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q706" s="34">
         <v>43952</v>
@@ -23812,7 +23797,7 @@
         <v>43</v>
       </c>
       <c r="P707" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q707" s="34">
         <v>40764</v>
@@ -23878,7 +23863,7 @@
         <v>39</v>
       </c>
       <c r="P708" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q708" s="34">
         <v>40583</v>
@@ -23944,7 +23929,7 @@
         <v>39</v>
       </c>
       <c r="P709" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q709" s="34">
         <v>40583</v>
@@ -24010,7 +23995,7 @@
         <v>47</v>
       </c>
       <c r="P710" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q710" s="34">
         <v>40583</v>
@@ -24076,7 +24061,7 @@
         <v>38</v>
       </c>
       <c r="P711" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q711" s="34">
         <v>40583</v>
@@ -24142,7 +24127,7 @@
         <v>36</v>
       </c>
       <c r="P712" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q712" s="34">
         <v>40764</v>
@@ -24208,7 +24193,7 @@
         <v>40</v>
       </c>
       <c r="P713" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q713" s="34">
         <v>40583</v>
@@ -24274,7 +24259,7 @@
         <v>46</v>
       </c>
       <c r="P714" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q714" s="34">
         <v>40595</v>
@@ -24340,7 +24325,7 @@
         <v>44</v>
       </c>
       <c r="P715" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q715" s="34">
         <v>40595</v>
@@ -24406,7 +24391,7 @@
         <v>42</v>
       </c>
       <c r="P716" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q716" s="34">
         <v>40595</v>
@@ -24472,7 +24457,7 @@
         <v>48</v>
       </c>
       <c r="P717" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q717" s="34">
         <v>40595</v>
@@ -24538,7 +24523,7 @@
         <v>40</v>
       </c>
       <c r="P718" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q718" s="34">
         <v>40595</v>
@@ -24604,7 +24589,7 @@
         <v>40</v>
       </c>
       <c r="P719" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q719" s="34">
         <v>40776</v>
@@ -24670,7 +24655,7 @@
         <v>44</v>
       </c>
       <c r="P720" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q720" s="34">
         <v>40595</v>
@@ -24736,7 +24721,7 @@
         <v>39</v>
       </c>
       <c r="P721" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q721" s="34">
         <v>40595</v>
@@ -24802,7 +24787,7 @@
         <v>43</v>
       </c>
       <c r="P722" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q722" s="34">
         <v>40595</v>
@@ -24868,7 +24853,7 @@
         <v>35</v>
       </c>
       <c r="P723" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q723" s="34">
         <v>40595</v>
@@ -24934,7 +24919,7 @@
         <v>39</v>
       </c>
       <c r="P724" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q724" s="34">
         <v>40595</v>
@@ -25000,7 +24985,7 @@
         <v>36</v>
       </c>
       <c r="P725" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q725" s="34">
         <v>40595</v>
@@ -25066,7 +25051,7 @@
         <v>39</v>
       </c>
       <c r="P726" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q726" s="34">
         <v>40603</v>
@@ -25132,7 +25117,7 @@
         <v>40</v>
       </c>
       <c r="P727" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q727" s="34">
         <v>40603</v>
@@ -25198,7 +25183,7 @@
         <v>36</v>
       </c>
       <c r="P728" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q728" s="34">
         <v>40603</v>
@@ -25264,7 +25249,7 @@
         <v>41</v>
       </c>
       <c r="P729" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q729" s="34">
         <v>40603</v>
@@ -25330,7 +25315,7 @@
         <v>43</v>
       </c>
       <c r="P730" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q730" s="34">
         <v>40603</v>
@@ -25396,7 +25381,7 @@
         <v>43</v>
       </c>
       <c r="P731" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q731" s="34">
         <v>40603</v>
@@ -25462,7 +25447,7 @@
         <v>35</v>
       </c>
       <c r="P732" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q732" s="34">
         <v>40603</v>
@@ -25528,7 +25513,7 @@
         <v>40</v>
       </c>
       <c r="P733" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q733" s="34">
         <v>40603</v>
@@ -25594,7 +25579,7 @@
         <v>43</v>
       </c>
       <c r="P734" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q734" s="34">
         <v>40623</v>
@@ -25660,7 +25645,7 @@
         <v>38</v>
       </c>
       <c r="P735" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q735" s="34">
         <v>40634</v>
@@ -25726,7 +25711,7 @@
         <v>39</v>
       </c>
       <c r="P736" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q736" s="34">
         <v>40634</v>
@@ -25792,7 +25777,7 @@
         <v>36</v>
       </c>
       <c r="P737" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q737" s="34">
         <v>40634</v>
@@ -25858,7 +25843,7 @@
         <v>49</v>
       </c>
       <c r="P738" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q738" s="34">
         <v>40634</v>
@@ -25924,7 +25909,7 @@
         <v>36</v>
       </c>
       <c r="P739" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q739" s="34">
         <v>40634</v>
@@ -25990,7 +25975,7 @@
         <v>44</v>
       </c>
       <c r="P740" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q740" s="34">
         <v>40725</v>
@@ -26056,7 +26041,7 @@
         <v>39</v>
       </c>
       <c r="P741" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q741" s="34">
         <v>40737</v>
@@ -26122,7 +26107,7 @@
         <v>34</v>
       </c>
       <c r="P742" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q742" s="34">
         <v>40737</v>
@@ -26188,7 +26173,7 @@
         <v>37</v>
       </c>
       <c r="P743" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q743" s="34">
         <v>40737</v>
@@ -26254,7 +26239,7 @@
         <v>38</v>
       </c>
       <c r="P744" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q744" s="34">
         <v>40737</v>
@@ -26320,7 +26305,7 @@
         <v>38</v>
       </c>
       <c r="P745" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q745" s="34">
         <v>40737</v>
@@ -26386,7 +26371,7 @@
         <v>51</v>
       </c>
       <c r="P746" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q746" s="34">
         <v>41671</v>
@@ -26452,7 +26437,7 @@
         <v>38</v>
       </c>
       <c r="P747" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q747" s="34">
         <v>41631</v>
@@ -26518,7 +26503,7 @@
         <v>42</v>
       </c>
       <c r="P748" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q748" s="34">
         <v>40896</v>
@@ -26584,7 +26569,7 @@
         <v>47</v>
       </c>
       <c r="P749" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q749" s="34">
         <v>40955</v>
@@ -26650,7 +26635,7 @@
         <v>34</v>
       </c>
       <c r="P750" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q750" s="34">
         <v>44333</v>
@@ -26716,7 +26701,7 @@
         <v>34</v>
       </c>
       <c r="P751" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q751" s="34">
         <v>41631</v>
@@ -26782,7 +26767,7 @@
         <v>35</v>
       </c>
       <c r="P752" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q752" s="34">
         <v>41631</v>
@@ -26848,7 +26833,7 @@
         <v>33</v>
       </c>
       <c r="P753" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q753" s="34">
         <v>41631</v>
@@ -26914,7 +26899,7 @@
         <v>34</v>
       </c>
       <c r="P754" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q754" s="34">
         <v>41631</v>
@@ -26980,7 +26965,7 @@
         <v>45</v>
       </c>
       <c r="P755" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q755" s="34">
         <v>41064</v>
@@ -27046,7 +27031,7 @@
         <v>46</v>
       </c>
       <c r="P756" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q756" s="34">
         <v>44060</v>
@@ -27112,7 +27097,7 @@
         <v>40</v>
       </c>
       <c r="P757" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q757" s="34">
         <v>41129</v>
@@ -27178,7 +27163,7 @@
         <v>42</v>
       </c>
       <c r="P758" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q758" s="34">
         <v>41204</v>
@@ -27244,7 +27229,7 @@
         <v>38</v>
       </c>
       <c r="P759" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q759" s="34">
         <v>41218</v>
@@ -27310,7 +27295,7 @@
         <v>31</v>
       </c>
       <c r="P760" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q760" s="34">
         <v>43191</v>
@@ -27376,7 +27361,7 @@
         <v>34</v>
       </c>
       <c r="P761" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q761" s="34">
         <v>43800</v>
@@ -27442,7 +27427,7 @@
         <v>31</v>
       </c>
       <c r="P762" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q762" s="34">
         <v>41982</v>
@@ -27508,7 +27493,7 @@
         <v>36</v>
       </c>
       <c r="P763" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q763" s="34">
         <v>41852</v>
@@ -27574,7 +27559,7 @@
         <v>33</v>
       </c>
       <c r="P764" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q764" s="34">
         <v>42590</v>
@@ -27640,7 +27625,7 @@
         <v>34</v>
       </c>
       <c r="P765" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q765" s="34">
         <v>42064</v>
@@ -27706,7 +27691,7 @@
         <v>35</v>
       </c>
       <c r="P766" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q766" s="34">
         <v>41982</v>
@@ -27772,7 +27757,7 @@
         <v>33</v>
       </c>
       <c r="P767" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q767" s="34">
         <v>41982</v>
@@ -27838,7 +27823,7 @@
         <v>32</v>
       </c>
       <c r="P768" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q768" s="34">
         <v>42675</v>
@@ -27904,7 +27889,7 @@
         <v>32</v>
       </c>
       <c r="P769" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q769" s="34">
         <v>42675</v>
@@ -27970,7 +27955,7 @@
         <v>46</v>
       </c>
       <c r="P770" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q770" s="34">
         <v>41617</v>
@@ -28036,7 +28021,7 @@
         <v>32</v>
       </c>
       <c r="P771" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q771" s="34">
         <v>44333</v>
@@ -28102,7 +28087,7 @@
         <v>35</v>
       </c>
       <c r="P772" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q772" s="34">
         <v>43040</v>
@@ -28168,7 +28153,7 @@
         <v>37</v>
       </c>
       <c r="P773" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q773" s="34">
         <v>44348</v>
@@ -28234,7 +28219,7 @@
         <v>38</v>
       </c>
       <c r="P774" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q774" s="34">
         <v>41883</v>
@@ -28300,7 +28285,7 @@
         <v>34</v>
       </c>
       <c r="P775" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q775" s="34">
         <v>44333</v>
@@ -28366,7 +28351,7 @@
         <v>36</v>
       </c>
       <c r="P776" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q776" s="34">
         <v>42738</v>
@@ -28432,7 +28417,7 @@
         <v>33</v>
       </c>
       <c r="P777" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q777" s="34">
         <v>42738</v>
@@ -28498,7 +28483,7 @@
         <v>29</v>
       </c>
       <c r="P778" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q778" s="34">
         <v>43206</v>
@@ -28564,7 +28549,7 @@
         <v>37</v>
       </c>
       <c r="P779" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q779" s="34">
         <v>45299</v>
@@ -28630,7 +28615,7 @@
         <v>42</v>
       </c>
       <c r="P780" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q780" s="34">
         <v>42370</v>
@@ -28696,7 +28681,7 @@
         <v>39</v>
       </c>
       <c r="P781" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q781" s="34">
         <v>42370</v>
@@ -28762,7 +28747,7 @@
         <v>37</v>
       </c>
       <c r="P782" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q782" s="34">
         <v>42370</v>
@@ -28828,7 +28813,7 @@
         <v>30</v>
       </c>
       <c r="P783" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q783" s="34">
         <v>44713</v>
@@ -28894,7 +28879,7 @@
         <v>38</v>
       </c>
       <c r="P784" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q784" s="34">
         <v>42493</v>
@@ -28960,7 +28945,7 @@
         <v>33</v>
       </c>
       <c r="P785" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q785" s="34">
         <v>44333</v>
@@ -29026,7 +29011,7 @@
         <v>53</v>
       </c>
       <c r="P786" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q786" s="34">
         <v>42738</v>
@@ -29092,7 +29077,7 @@
         <v>45</v>
       </c>
       <c r="P787" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q787" s="34">
         <v>42979</v>
@@ -29158,7 +29143,7 @@
         <v>43</v>
       </c>
       <c r="P788" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q788" s="34">
         <v>43089</v>
@@ -29224,7 +29209,7 @@
         <v>31</v>
       </c>
       <c r="P789" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q789" s="34">
         <v>43819</v>
@@ -29290,7 +29275,7 @@
         <v>34</v>
       </c>
       <c r="P790" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q790" s="34">
         <v>43472</v>
@@ -29356,7 +29341,7 @@
         <v>32</v>
       </c>
       <c r="P791" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q791" s="34">
         <v>43831</v>
@@ -29422,7 +29407,7 @@
         <v>32</v>
       </c>
       <c r="P792" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q792" s="34">
         <v>43089</v>
@@ -29488,7 +29473,7 @@
         <v>30</v>
       </c>
       <c r="P793" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q793" s="34">
         <v>43089</v>
@@ -29554,7 +29539,7 @@
         <v>37</v>
       </c>
       <c r="P794" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q794" s="34">
         <v>43089</v>
@@ -29620,7 +29605,7 @@
         <v>32</v>
       </c>
       <c r="P795" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q795" s="34">
         <v>43089</v>
@@ -29686,7 +29671,7 @@
         <v>47</v>
       </c>
       <c r="P796" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q796" s="34">
         <v>43089</v>
@@ -29752,7 +29737,7 @@
         <v>32</v>
       </c>
       <c r="P797" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q797" s="34">
         <v>43831</v>
@@ -29818,7 +29803,7 @@
         <v>40</v>
       </c>
       <c r="P798" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q798" s="34">
         <v>43191</v>
@@ -29884,7 +29869,7 @@
         <v>40</v>
       </c>
       <c r="P799" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q799" s="34">
         <v>43206</v>
@@ -29950,7 +29935,7 @@
         <v>31</v>
       </c>
       <c r="P800" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q800" s="34">
         <v>44348</v>
@@ -30016,7 +30001,7 @@
         <v>30</v>
       </c>
       <c r="P801" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q801" s="34">
         <v>44333</v>
@@ -30082,7 +30067,7 @@
         <v>39</v>
       </c>
       <c r="P802" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q802" s="34">
         <v>43472</v>
@@ -30148,7 +30133,7 @@
         <v>38</v>
       </c>
       <c r="P803" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q803" s="34">
         <v>43472</v>
@@ -30214,7 +30199,7 @@
         <v>38</v>
       </c>
       <c r="P804" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q804" s="34">
         <v>43472</v>
@@ -30280,7 +30265,7 @@
         <v>44</v>
       </c>
       <c r="P805" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q805" s="34">
         <v>43472</v>
@@ -30346,7 +30331,7 @@
         <v>37</v>
       </c>
       <c r="P806" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q806" s="34">
         <v>43472</v>
@@ -30412,7 +30397,7 @@
         <v>28</v>
       </c>
       <c r="P807" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q807" s="34">
         <v>43472</v>
@@ -30478,7 +30463,7 @@
         <v>35</v>
       </c>
       <c r="P808" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q808" s="34">
         <v>43472</v>
@@ -30544,7 +30529,7 @@
         <v>37</v>
       </c>
       <c r="P809" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q809" s="34">
         <v>43472</v>
@@ -30610,7 +30595,7 @@
         <v>52</v>
       </c>
       <c r="P810" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q810" s="34">
         <v>43472</v>
@@ -30676,7 +30661,7 @@
         <v>50</v>
       </c>
       <c r="P811" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q811" s="34">
         <v>43497</v>
@@ -30742,7 +30727,7 @@
         <v>50</v>
       </c>
       <c r="P812" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q812" s="34">
         <v>44214</v>
@@ -30808,7 +30793,7 @@
         <v>34</v>
       </c>
       <c r="P813" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q813" s="34">
         <v>43800</v>
@@ -30874,7 +30859,7 @@
         <v>30</v>
       </c>
       <c r="P814" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q814" s="34">
         <v>43819</v>
@@ -30940,7 +30925,7 @@
         <v>31</v>
       </c>
       <c r="P815" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q815" s="34">
         <v>44242</v>
@@ -31006,7 +30991,7 @@
         <v>31</v>
       </c>
       <c r="P816" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q816" s="34">
         <v>44242</v>
@@ -31072,7 +31057,7 @@
         <v>43</v>
       </c>
       <c r="P817" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q817" s="34">
         <v>44317</v>
@@ -31138,7 +31123,7 @@
         <v>43</v>
       </c>
       <c r="P818" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q818" s="34">
         <v>44333</v>
@@ -31204,7 +31189,7 @@
         <v>38</v>
       </c>
       <c r="P819" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q819" s="34">
         <v>44333</v>
@@ -31270,7 +31255,7 @@
         <v>28</v>
       </c>
       <c r="P820" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q820" s="34">
         <v>44333</v>
@@ -31336,7 +31321,7 @@
         <v>31</v>
       </c>
       <c r="P821" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q821" s="34">
         <v>44333</v>
@@ -31402,7 +31387,7 @@
         <v>34</v>
       </c>
       <c r="P822" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q822" s="34">
         <v>44333</v>
@@ -31468,7 +31453,7 @@
         <v>45</v>
       </c>
       <c r="P823" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q823" s="34">
         <v>44333</v>
@@ -31534,7 +31519,7 @@
         <v>32</v>
       </c>
       <c r="P824" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q824" s="34">
         <v>44333</v>
@@ -31600,7 +31585,7 @@
         <v>33</v>
       </c>
       <c r="P825" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q825" s="34">
         <v>44333</v>
@@ -31666,7 +31651,7 @@
         <v>32</v>
       </c>
       <c r="P826" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q826" s="34">
         <v>44333</v>
@@ -31732,7 +31717,7 @@
         <v>44</v>
       </c>
       <c r="P827" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q827" s="34">
         <v>44333</v>
@@ -31798,7 +31783,7 @@
         <v>44</v>
       </c>
       <c r="P828" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q828" s="34">
         <v>44348</v>
@@ -31864,7 +31849,7 @@
         <v>36</v>
       </c>
       <c r="P829" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q829" s="34">
         <v>44410</v>
@@ -31930,7 +31915,7 @@
         <v>34</v>
       </c>
       <c r="P830" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q830" s="34">
         <v>44431</v>
@@ -31996,7 +31981,7 @@
         <v>38</v>
       </c>
       <c r="P831" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q831" s="34">
         <v>44531</v>
@@ -32062,7 +32047,7 @@
         <v>26</v>
       </c>
       <c r="P832" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q832" s="34">
         <v>44531</v>
@@ -32128,7 +32113,7 @@
         <v>32</v>
       </c>
       <c r="P833" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q833" s="34">
         <v>44531</v>
@@ -32194,7 +32179,7 @@
         <v>36</v>
       </c>
       <c r="P834" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q834" s="34">
         <v>44562</v>
@@ -32260,7 +32245,7 @@
         <v>33</v>
       </c>
       <c r="P835" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q835" s="34">
         <v>44562</v>
@@ -32326,7 +32311,7 @@
         <v>30</v>
       </c>
       <c r="P836" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q836" s="34">
         <v>44562</v>
@@ -32392,7 +32377,7 @@
         <v>49</v>
       </c>
       <c r="P837" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q837" s="34">
         <v>44621</v>
@@ -32458,7 +32443,7 @@
         <v>33</v>
       </c>
       <c r="P838" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q838" s="34">
         <v>44634</v>
@@ -32524,7 +32509,7 @@
         <v>43</v>
       </c>
       <c r="P839" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q839" s="34">
         <v>44652</v>
@@ -32590,7 +32575,7 @@
         <v>44</v>
       </c>
       <c r="P840" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q840" s="34">
         <v>44652</v>
@@ -32656,7 +32641,7 @@
         <v>52</v>
       </c>
       <c r="P841" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q841" s="34">
         <v>44662</v>
@@ -32722,7 +32707,7 @@
         <v>31</v>
       </c>
       <c r="P842" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q842" s="34">
         <v>44662</v>
@@ -32788,7 +32773,7 @@
         <v>32</v>
       </c>
       <c r="P843" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q843" s="34">
         <v>44662</v>
@@ -32854,7 +32839,7 @@
         <v>28</v>
       </c>
       <c r="P844" s="35" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="Q844" s="34">
         <v>44662</v>
@@ -32920,7 +32905,7 @@
         <v>35</v>
       </c>
       <c r="P845" s="35" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
       <c r="Q845" s="34">
         <v>44697</v>
@@ -32986,7 +32971,7 @@
         <v>38</v>
       </c>
       <c r="P846" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q846" s="34">
         <v>44713</v>
@@ -33052,7 +33037,7 @@
         <v>50</v>
       </c>
       <c r="P847" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q847" s="34">
         <v>44713</v>
@@ -33118,7 +33103,7 @@
         <v>48</v>
       </c>
       <c r="P848" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q848" s="34">
         <v>44713</v>
@@ -33184,7 +33169,7 @@
         <v>36</v>
       </c>
       <c r="P849" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q849" s="34">
         <v>44713</v>
@@ -33250,7 +33235,7 @@
         <v>43</v>
       </c>
       <c r="P850" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q850" s="34">
         <v>44713</v>
@@ -33316,7 +33301,7 @@
         <v>52</v>
       </c>
       <c r="P851" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q851" s="34">
         <v>44732</v>
@@ -33382,7 +33367,7 @@
         <v>37</v>
       </c>
       <c r="P852" s="35" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="Q852" s="34">
         <v>44732</v>
@@ -33448,7 +33433,7 @@
         <v>36</v>
       </c>
       <c r="P853" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q853" s="34">
         <v>44732</v>
@@ -33514,7 +33499,7 @@
         <v>27</v>
       </c>
       <c r="P854" s="35" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="Q854" s="34">
         <v>46006</v>
@@ -33582,7 +33567,7 @@
         <v>28</v>
       </c>
       <c r="P855" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q855" s="34">
         <v>45250</v>
@@ -33648,7 +33633,7 @@
         <v>49</v>
       </c>
       <c r="P856" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q856" s="34">
         <v>45352</v>
@@ -33714,7 +33699,7 @@
         <v>34</v>
       </c>
       <c r="P857" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q857" s="34">
         <v>45352</v>
@@ -33780,7 +33765,7 @@
         <v>27</v>
       </c>
       <c r="P858" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q858" s="34">
         <v>45352</v>
@@ -33846,7 +33831,7 @@
         <v>30</v>
       </c>
       <c r="P859" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q859" s="34">
         <v>45352</v>
@@ -33912,7 +33897,7 @@
         <v>29</v>
       </c>
       <c r="P860" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q860" s="34">
         <v>45352</v>
@@ -33978,7 +33963,7 @@
         <v>33</v>
       </c>
       <c r="P861" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q861" s="34">
         <v>45352</v>
@@ -34044,7 +34029,7 @@
         <v>32</v>
       </c>
       <c r="P862" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q862" s="34">
         <v>45352</v>
@@ -34110,7 +34095,7 @@
         <v>43</v>
       </c>
       <c r="P863" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q863" s="34">
         <v>45352</v>
@@ -34176,7 +34161,7 @@
         <v>48</v>
       </c>
       <c r="P864" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q864" s="34">
         <v>45352</v>
@@ -34242,7 +34227,7 @@
         <v>32</v>
       </c>
       <c r="P865" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q865" s="34">
         <v>45418</v>
@@ -34308,7 +34293,7 @@
         <v>58</v>
       </c>
       <c r="P866" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q866" s="34">
         <v>45474</v>
@@ -34374,7 +34359,7 @@
         <v>28</v>
       </c>
       <c r="P867" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q867" s="34">
         <v>45627</v>
@@ -34440,7 +34425,7 @@
         <v>32</v>
       </c>
       <c r="P868" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q868" s="34">
         <v>45717</v>
@@ -34508,7 +34493,7 @@
         <v>25</v>
       </c>
       <c r="P869" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q869" s="34">
         <v>45717</v>
@@ -34576,7 +34561,7 @@
         <v>35</v>
       </c>
       <c r="P870" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q870" s="34">
         <v>45717</v>
@@ -34644,7 +34629,7 @@
         <v>30</v>
       </c>
       <c r="P871" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q871" s="34">
         <v>45824</v>
@@ -34712,7 +34697,7 @@
         <v>29</v>
       </c>
       <c r="P872" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q872" s="34">
         <v>45824</v>
@@ -34780,7 +34765,7 @@
         <v>31</v>
       </c>
       <c r="P873" s="35" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="Q873" s="34">
         <v>45824</v>
@@ -34848,7 +34833,7 @@
         <v>31</v>
       </c>
       <c r="P874" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q874" s="34">
         <v>45859</v>
@@ -34914,7 +34899,7 @@
         <v>35</v>
       </c>
       <c r="P875" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q875" s="34">
         <v>45950</v>
@@ -34980,7 +34965,7 @@
         <v>33</v>
       </c>
       <c r="P876" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q876" s="34">
         <v>46006</v>
@@ -35048,7 +35033,7 @@
         <v>22</v>
       </c>
       <c r="P877" s="35" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="Q877" s="34">
         <v>46020</v>
@@ -35116,7 +35101,7 @@
         <v>26</v>
       </c>
       <c r="P878" s="35" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="Q878" s="34">
         <v>46041</v>
@@ -35184,7 +35169,7 @@
         <v>28</v>
       </c>
       <c r="P879" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q879" s="34">
         <v>46041</v>
@@ -35252,7 +35237,7 @@
         <v>46</v>
       </c>
       <c r="P880" s="35" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
       <c r="Q880" s="34">
         <v>46054</v>
@@ -35318,7 +35303,7 @@
         <v>26</v>
       </c>
       <c r="P881" s="35" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="Q881" s="34">
         <v>46054</v>
@@ -35386,7 +35371,7 @@
         <v>24</v>
       </c>
       <c r="P882" s="35" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
       <c r="Q882" s="34">
         <v>46054</v>
@@ -35454,7 +35439,7 @@
         <v>34</v>
       </c>
       <c r="P883" s="35" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
       <c r="Q883" s="34">
         <v>46054</v>
@@ -35522,7 +35507,7 @@
         <v>41</v>
       </c>
       <c r="P884" s="35" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="Q884" s="34">
         <v>46143</v>
@@ -35556,7 +35541,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D3B0B5-E7CA-41F3-B584-8BB10868D96B}">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.54296875" customWidth="1"/>
@@ -35607,7 +35592,7 @@
         <v>1607</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>1608</v>
@@ -35632,7 +35617,7 @@
       <c r="A2" s="5">
         <v>39653</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>184</v>
       </c>
       <c r="C2" s="6" t="s">
@@ -35651,31 +35636,31 @@
         <v>4</v>
       </c>
       <c r="H2" s="9">
-        <v>46183</v>
+        <v>46213</v>
       </c>
       <c r="I2" s="9">
-        <v>46212</v>
+        <v>46242</v>
       </c>
       <c r="J2" s="5">
         <v>30</v>
       </c>
       <c r="K2" s="8">
-        <v>716</v>
+        <v>1175</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>1675</v>
+        <v>1609</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="O2" s="8">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="P2" s="8">
-        <v>716</v>
+        <v>746</v>
       </c>
       <c r="Q2" s="7" t="s">
         <v>1153</v>
@@ -35683,66 +35668,66 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="5">
-        <v>39667</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>207</v>
+        <v>51906</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>372</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1662</v>
+        <v>1616</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1599</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>1146</v>
+        <v>1601</v>
+      </c>
+      <c r="G3" s="8">
+        <v>4</v>
       </c>
       <c r="H3" s="9">
-        <v>46195</v>
+        <v>46190</v>
       </c>
       <c r="I3" s="9">
-        <v>46205</v>
+        <v>46219</v>
       </c>
       <c r="J3" s="5">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K3" s="8">
-        <v>11</v>
+        <v>942</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>1677</v>
+        <v>1609</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>1619</v>
+        <v>1672</v>
       </c>
       <c r="O3" s="8">
-        <v>77</v>
+        <v>390</v>
       </c>
       <c r="P3" s="8">
-        <v>136</v>
+        <v>750</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="5">
-        <v>51906</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>372</v>
+        <v>51908</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>376</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>73</v>
@@ -35754,48 +35739,48 @@
         <v>1601</v>
       </c>
       <c r="G4" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" s="9">
-        <v>46190</v>
+        <v>46161</v>
       </c>
       <c r="I4" s="9">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="J4" s="5">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K4" s="8">
-        <v>912</v>
+        <v>776</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>1675</v>
+        <v>1609</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="O4" s="8">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="P4" s="8">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="5">
-        <v>51908</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>376</v>
+        <v>53848</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>577</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>73</v>
@@ -35810,48 +35795,48 @@
         <v>2</v>
       </c>
       <c r="H5" s="9">
-        <v>46161</v>
+        <v>46200</v>
       </c>
       <c r="I5" s="9">
-        <v>46220</v>
+        <v>46229</v>
       </c>
       <c r="J5" s="5">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="K5" s="8">
-        <v>1145</v>
+        <v>90</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>1675</v>
+        <v>1609</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="O5" s="8">
-        <v>345</v>
+        <v>120</v>
       </c>
       <c r="P5" s="8">
-        <v>735</v>
+        <v>145</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="5">
-        <v>53848</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>577</v>
+        <v>57143</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>698</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1618</v>
+        <v>697</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>34</v>
@@ -35863,48 +35848,48 @@
         <v>2</v>
       </c>
       <c r="H6" s="9">
-        <v>46200</v>
+        <v>46215</v>
       </c>
       <c r="I6" s="9">
-        <v>46229</v>
+        <v>46235</v>
       </c>
       <c r="J6" s="5">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K6" s="8">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="O6" s="8">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="P6" s="8">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="5">
-        <v>59381</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>716</v>
+        <v>59385</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>724</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>34</v>
@@ -35916,31 +35901,31 @@
         <v>1</v>
       </c>
       <c r="H7" s="9">
-        <v>46178</v>
+        <v>46191</v>
       </c>
       <c r="I7" s="9">
-        <v>46207</v>
+        <v>46216</v>
       </c>
       <c r="J7" s="5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K7" s="8">
-        <v>261</v>
+        <v>76</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>1675</v>
+        <v>1609</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="O7" s="8">
-        <v>261</v>
+        <v>76</v>
       </c>
       <c r="P7" s="8">
-        <v>264</v>
+        <v>76</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>1153</v>
@@ -35948,105 +35933,105 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="5">
-        <v>59385</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>724</v>
+        <v>59401</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>736</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1621</v>
+        <v>735</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>1601</v>
       </c>
       <c r="G8" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" s="9">
-        <v>46191</v>
+        <v>46210</v>
       </c>
       <c r="I8" s="9">
-        <v>46216</v>
+        <v>46239</v>
       </c>
       <c r="J8" s="5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K8" s="8">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>1675</v>
+        <v>1609</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="O8" s="8">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="P8" s="8">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="5">
-        <v>59401</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>736</v>
+        <v>70535</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>893</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>735</v>
+        <v>892</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>1601</v>
       </c>
       <c r="G9" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" s="9">
-        <v>46210</v>
+        <v>46214</v>
       </c>
       <c r="I9" s="9">
-        <v>46239</v>
+        <v>46228</v>
       </c>
       <c r="J9" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K9" s="8">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>1675</v>
+        <v>1609</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="O9" s="8">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="P9" s="8">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="Q9" s="7" t="s">
         <v>1151</v>
@@ -36054,19 +36039,19 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="5">
-        <v>70535</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>893</v>
+        <v>74084</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>925</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>892</v>
+        <v>924</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>119</v>
+        <v>326</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>1601</v>
@@ -36075,139 +36060,33 @@
         <v>2</v>
       </c>
       <c r="H10" s="9">
-        <v>46184</v>
+        <v>46202</v>
       </c>
       <c r="I10" s="9">
-        <v>46213</v>
+        <v>46231</v>
       </c>
       <c r="J10" s="5">
         <v>30</v>
       </c>
       <c r="K10" s="8">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>1615</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>1675</v>
+        <v>1609</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="O10" s="8">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P10" s="8">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11" s="5">
-        <v>74084</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>925</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>924</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>1601</v>
-      </c>
-      <c r="G11" s="8">
-        <v>2</v>
-      </c>
-      <c r="H11" s="9">
-        <v>46202</v>
-      </c>
-      <c r="I11" s="9">
-        <v>46231</v>
-      </c>
-      <c r="J11" s="5">
-        <v>30</v>
-      </c>
-      <c r="K11" s="8">
-        <v>120</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>1615</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>1675</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>1676</v>
-      </c>
-      <c r="O11" s="8">
-        <v>120</v>
-      </c>
-      <c r="P11" s="8">
-        <v>240</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="A12" s="5">
-        <v>305439</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>1601</v>
-      </c>
-      <c r="G12" s="8">
-        <v>4</v>
-      </c>
-      <c r="H12" s="9">
-        <v>46211</v>
-      </c>
-      <c r="I12" s="9">
-        <v>46212</v>
-      </c>
-      <c r="J12" s="5">
-        <v>2</v>
-      </c>
-      <c r="K12" s="8">
-        <v>2</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>1615</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>1677</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>1678</v>
-      </c>
-      <c r="O12" s="8">
-        <v>2</v>
-      </c>
-      <c r="P12" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="7" t="s">
         <v>1153</v>
       </c>
     </row>
@@ -36259,45 +36138,45 @@
     <row r="4" spans="2:14" ht="15.5">
       <c r="B4" s="12"/>
       <c r="C4" s="13" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>1621</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>1622</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>1623</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="G4" s="13" t="s">
         <v>1624</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="H4" s="13" t="s">
         <v>1625</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="I4" s="14" t="s">
         <v>1626</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="J4" s="14" t="s">
         <v>1627</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="K4" s="14" t="s">
         <v>1628</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="L4" s="14" t="s">
         <v>1629</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="M4" s="14" t="s">
         <v>1630</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="N4" s="14" t="s">
         <v>1631</v>
-      </c>
-      <c r="M4" s="14" t="s">
-        <v>1632</v>
-      </c>
-      <c r="N4" s="14" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="15.5">
       <c r="B5" s="15" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="C5" s="16">
         <v>4.2900000000000001E-2</v>
@@ -36338,7 +36217,7 @@
     </row>
     <row r="6" spans="2:14" ht="15.5">
       <c r="B6" s="18" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="C6" s="16">
         <v>9.7999999999999997E-3</v>
@@ -36379,7 +36258,7 @@
     </row>
     <row r="7" spans="2:14" ht="15.5">
       <c r="B7" s="18" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="C7" s="19">
         <v>5.2699999999999997E-2</v>
@@ -36450,7 +36329,7 @@
     </row>
     <row r="10" spans="2:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="B10" s="21" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="C10" s="22">
         <v>5.8400000000000001E-2</v>
@@ -36480,28 +36359,28 @@
     <row r="11" spans="2:14" ht="15" thickTop="1"/>
     <row r="13" spans="2:14">
       <c r="C13" s="24" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="14" spans="2:14">
       <c r="B14" s="25" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="C14" s="27">
-        <v>4.4000000000000003E-3</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="D14" s="27">
-        <v>4.0000000000000002E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="E14" s="26">
         <f>SUM(C14:D14)</f>
-        <v>4.8000000000000004E-3</v>
+        <v>4.6999999999999993E-3</v>
       </c>
     </row>
     <row r="15" spans="2:14">
@@ -36509,71 +36388,71 @@
         <v>837</v>
       </c>
       <c r="C15" s="27">
-        <v>2E-3</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="D15" s="27">
-        <v>2.0000000000000001E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="E15" s="26">
         <f t="shared" ref="E15:E17" si="0">SUM(C15:D15)</f>
-        <v>2.2000000000000001E-3</v>
+        <v>2.8E-3</v>
       </c>
     </row>
     <row r="16" spans="2:14">
       <c r="B16" s="25" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="C16" s="27">
-        <v>1.11E-2</v>
+        <v>1.17E-2</v>
       </c>
       <c r="D16" s="27">
-        <v>8.9999999999999998E-4</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="E16" s="26">
         <f t="shared" si="0"/>
-        <v>1.2E-2</v>
+        <v>1.44E-2</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="25" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="C17" s="27">
-        <v>2.8E-3</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="D17" s="27">
-        <v>1.1000000000000001E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="E17" s="26">
         <f t="shared" si="0"/>
-        <v>3.8999999999999998E-3</v>
+        <v>3.5999999999999999E-3</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="C18" s="26">
         <f>SUM(C14:C17)</f>
-        <v>2.0300000000000002E-2</v>
+        <v>2.1499999999999998E-2</v>
       </c>
       <c r="D18" s="26">
         <f>SUM(D14:D17)</f>
-        <v>2.5999999999999999E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="E18" s="26">
         <f>SUM(E14:E17)</f>
-        <v>2.2900000000000004E-2</v>
+        <v>2.5499999999999998E-2</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="C21" s="25" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="28" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="C22" s="27">
-        <v>2E-3</v>
+        <v>5.1999999999999998E-3</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -36581,46 +36460,46 @@
         <v>837</v>
       </c>
       <c r="C23" s="27">
-        <v>1.6999999999999999E-3</v>
+        <v>2.8E-3</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="28" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="C24" s="27">
-        <v>7.4999999999999997E-3</v>
+        <v>1.6299999999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="28" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="C25" s="27">
-        <v>2.8999999999999998E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="26" spans="2:5">
       <c r="C26" s="26">
         <f>SUM(C22:C25)</f>
-        <v>1.41E-2</v>
+        <v>2.7299999999999998E-2</v>
       </c>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="25" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="C28" s="27">
-        <v>1E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="25" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="C29" s="27">
         <f>C26-C28</f>
-        <v>1.4E-2</v>
+        <v>2.7099999999999999E-2</v>
       </c>
     </row>
   </sheetData>
@@ -36644,32 +36523,32 @@
   <sheetData>
     <row r="1" spans="2:9">
       <c r="B1" s="37" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="C1" s="37"/>
       <c r="E1" s="37" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="F1" s="37"/>
       <c r="H1" s="29" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="I1" s="29" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="2" spans="2:9">
       <c r="B2" s="29" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="F2" s="29" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="H2" s="26">
         <v>1.2E-2</v>
@@ -36680,11 +36559,11 @@
     </row>
     <row r="3" spans="2:9">
       <c r="B3" s="25" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="C3" s="24"/>
       <c r="E3" s="30" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="F3" s="24">
         <v>1</v>
@@ -36692,51 +36571,51 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="25" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="C4" s="24"/>
       <c r="E4" s="30" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="F4" s="24"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="25" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="C5" s="24">
         <v>1</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="F5" s="24"/>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" s="25" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="C6" s="24"/>
       <c r="E6" s="30" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="F6" s="24"/>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" s="25" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="C7" s="24">
         <v>3</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="F7" s="24"/>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="25" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="C8" s="24"/>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baray020\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C757AAB-E307-4D7B-A180-F72AE218D63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F959F0-150A-49C0-B3D4-6F32185EB77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1890" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dotaci" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Comuna" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dotaci!$A$1:$V$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dotaci!$A$1:$V$449</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5108,6 +5108,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="dd/mmm/yyyy"/>
+  </numFmts>
   <fonts count="10">
     <font>
       <sz val="11"/>
@@ -5309,7 +5312,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -5422,23 +5425,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Celda de comprobación" xfId="2" builtinId="23"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5898,7 +5894,7 @@
       <c r="M2" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="34">
+      <c r="N2" s="38">
         <v>25338</v>
       </c>
       <c r="O2" s="33">
@@ -5966,7 +5962,7 @@
       <c r="M3" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="34">
+      <c r="N3" s="38">
         <v>22455</v>
       </c>
       <c r="O3" s="33">
@@ -6034,7 +6030,7 @@
       <c r="M4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="38">
         <v>22344</v>
       </c>
       <c r="O4" s="33">
@@ -6102,7 +6098,7 @@
       <c r="M5" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N5" s="34">
+      <c r="N5" s="38">
         <v>23037</v>
       </c>
       <c r="O5" s="33">
@@ -6170,7 +6166,7 @@
       <c r="M6" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="38">
         <v>25711</v>
       </c>
       <c r="O6" s="33">
@@ -6238,7 +6234,7 @@
       <c r="M7" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N7" s="34">
+      <c r="N7" s="38">
         <v>23650</v>
       </c>
       <c r="O7" s="33">
@@ -6306,7 +6302,7 @@
       <c r="M8" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="34">
+      <c r="N8" s="38">
         <v>24734</v>
       </c>
       <c r="O8" s="33">
@@ -6374,7 +6370,7 @@
       <c r="M9" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N9" s="34">
+      <c r="N9" s="38">
         <v>24962</v>
       </c>
       <c r="O9" s="33">
@@ -6442,7 +6438,7 @@
       <c r="M10" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N10" s="34">
+      <c r="N10" s="38">
         <v>24375</v>
       </c>
       <c r="O10" s="33">
@@ -6510,7 +6506,7 @@
       <c r="M11" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N11" s="34">
+      <c r="N11" s="38">
         <v>23403</v>
       </c>
       <c r="O11" s="33">
@@ -6578,7 +6574,7 @@
       <c r="M12" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N12" s="34">
+      <c r="N12" s="38">
         <v>23870</v>
       </c>
       <c r="O12" s="33">
@@ -6646,7 +6642,7 @@
       <c r="M13" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N13" s="34">
+      <c r="N13" s="38">
         <v>25084</v>
       </c>
       <c r="O13" s="33">
@@ -6714,7 +6710,7 @@
       <c r="M14" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N14" s="34">
+      <c r="N14" s="38">
         <v>24618</v>
       </c>
       <c r="O14" s="33">
@@ -6782,7 +6778,7 @@
       <c r="M15" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N15" s="34">
+      <c r="N15" s="38">
         <v>25597</v>
       </c>
       <c r="O15" s="33">
@@ -6850,7 +6846,7 @@
       <c r="M16" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="34">
+      <c r="N16" s="38">
         <v>25198</v>
       </c>
       <c r="O16" s="33">
@@ -6918,7 +6914,7 @@
       <c r="M17" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N17" s="34">
+      <c r="N17" s="38">
         <v>25317</v>
       </c>
       <c r="O17" s="33">
@@ -6986,7 +6982,7 @@
       <c r="M18" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N18" s="34">
+      <c r="N18" s="38">
         <v>24047</v>
       </c>
       <c r="O18" s="33">
@@ -7054,7 +7050,7 @@
       <c r="M19" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N19" s="34">
+      <c r="N19" s="38">
         <v>23901</v>
       </c>
       <c r="O19" s="33">
@@ -7122,7 +7118,7 @@
       <c r="M20" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N20" s="34">
+      <c r="N20" s="38">
         <v>25072</v>
       </c>
       <c r="O20" s="33">
@@ -7190,7 +7186,7 @@
       <c r="M21" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N21" s="34">
+      <c r="N21" s="38">
         <v>24100</v>
       </c>
       <c r="O21" s="33">
@@ -7258,7 +7254,7 @@
       <c r="M22" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N22" s="34">
+      <c r="N22" s="38">
         <v>24544</v>
       </c>
       <c r="O22" s="33">
@@ -7326,7 +7322,7 @@
       <c r="M23" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N23" s="34">
+      <c r="N23" s="38">
         <v>25818</v>
       </c>
       <c r="O23" s="33">
@@ -7394,7 +7390,7 @@
       <c r="M24" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N24" s="34">
+      <c r="N24" s="38">
         <v>25286</v>
       </c>
       <c r="O24" s="33">
@@ -7462,7 +7458,7 @@
       <c r="M25" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N25" s="34">
+      <c r="N25" s="38">
         <v>24587</v>
       </c>
       <c r="O25" s="33">
@@ -7530,7 +7526,7 @@
       <c r="M26" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N26" s="34">
+      <c r="N26" s="38">
         <v>25370</v>
       </c>
       <c r="O26" s="33">
@@ -7598,7 +7594,7 @@
       <c r="M27" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N27" s="34">
+      <c r="N27" s="38">
         <v>25053</v>
       </c>
       <c r="O27" s="33">
@@ -7666,7 +7662,7 @@
       <c r="M28" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N28" s="34">
+      <c r="N28" s="38">
         <v>24907</v>
       </c>
       <c r="O28" s="33">
@@ -7734,7 +7730,7 @@
       <c r="M29" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N29" s="34">
+      <c r="N29" s="38">
         <v>25224</v>
       </c>
       <c r="O29" s="33">
@@ -7802,7 +7798,7 @@
       <c r="M30" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N30" s="34">
+      <c r="N30" s="38">
         <v>25487</v>
       </c>
       <c r="O30" s="33">
@@ -7870,7 +7866,7 @@
       <c r="M31" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="34">
+      <c r="N31" s="38">
         <v>25489</v>
       </c>
       <c r="O31" s="33">
@@ -7938,7 +7934,7 @@
       <c r="M32" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N32" s="34">
+      <c r="N32" s="38">
         <v>25397</v>
       </c>
       <c r="O32" s="33">
@@ -8006,7 +8002,7 @@
       <c r="M33" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N33" s="34">
+      <c r="N33" s="38">
         <v>25565</v>
       </c>
       <c r="O33" s="33">
@@ -8074,7 +8070,7 @@
       <c r="M34" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N34" s="34">
+      <c r="N34" s="38">
         <v>26069</v>
       </c>
       <c r="O34" s="33">
@@ -8142,7 +8138,7 @@
       <c r="M35" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N35" s="34">
+      <c r="N35" s="38">
         <v>26156</v>
       </c>
       <c r="O35" s="33">
@@ -8210,7 +8206,7 @@
       <c r="M36" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N36" s="34">
+      <c r="N36" s="38">
         <v>26106</v>
       </c>
       <c r="O36" s="33">
@@ -8278,7 +8274,7 @@
       <c r="M37" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N37" s="34">
+      <c r="N37" s="38">
         <v>26449</v>
       </c>
       <c r="O37" s="33">
@@ -8346,7 +8342,7 @@
       <c r="M38" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N38" s="34">
+      <c r="N38" s="38">
         <v>26588</v>
       </c>
       <c r="O38" s="33">
@@ -8414,7 +8410,7 @@
       <c r="M39" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N39" s="34">
+      <c r="N39" s="38">
         <v>25154</v>
       </c>
       <c r="O39" s="33">
@@ -8482,7 +8478,7 @@
       <c r="M40" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N40" s="34">
+      <c r="N40" s="38">
         <v>25469</v>
       </c>
       <c r="O40" s="33">
@@ -8550,7 +8546,7 @@
       <c r="M41" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N41" s="34">
+      <c r="N41" s="38">
         <v>25104</v>
       </c>
       <c r="O41" s="33">
@@ -8618,7 +8614,7 @@
       <c r="M42" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N42" s="34">
+      <c r="N42" s="38">
         <v>25368</v>
       </c>
       <c r="O42" s="33">
@@ -8686,7 +8682,7 @@
       <c r="M43" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N43" s="34">
+      <c r="N43" s="38">
         <v>25780</v>
       </c>
       <c r="O43" s="33">
@@ -8754,7 +8750,7 @@
       <c r="M44" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N44" s="34">
+      <c r="N44" s="38">
         <v>26872</v>
       </c>
       <c r="O44" s="33">
@@ -8822,7 +8818,7 @@
       <c r="M45" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N45" s="34">
+      <c r="N45" s="38">
         <v>26528</v>
       </c>
       <c r="O45" s="33">
@@ -8890,7 +8886,7 @@
       <c r="M46" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N46" s="34">
+      <c r="N46" s="38">
         <v>26315</v>
       </c>
       <c r="O46" s="33">
@@ -8958,7 +8954,7 @@
       <c r="M47" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N47" s="34">
+      <c r="N47" s="38">
         <v>26625</v>
       </c>
       <c r="O47" s="33">
@@ -9026,7 +9022,7 @@
       <c r="M48" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N48" s="34">
+      <c r="N48" s="38">
         <v>26537</v>
       </c>
       <c r="O48" s="33">
@@ -9094,7 +9090,7 @@
       <c r="M49" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N49" s="34">
+      <c r="N49" s="38">
         <v>26442</v>
       </c>
       <c r="O49" s="33">
@@ -9162,7 +9158,7 @@
       <c r="M50" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N50" s="34">
+      <c r="N50" s="38">
         <v>26599</v>
       </c>
       <c r="O50" s="33">
@@ -9230,7 +9226,7 @@
       <c r="M51" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N51" s="34">
+      <c r="N51" s="38">
         <v>26950</v>
       </c>
       <c r="O51" s="33">
@@ -9298,7 +9294,7 @@
       <c r="M52" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N52" s="34">
+      <c r="N52" s="38">
         <v>26695</v>
       </c>
       <c r="O52" s="33">
@@ -9366,7 +9362,7 @@
       <c r="M53" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N53" s="34">
+      <c r="N53" s="38">
         <v>26760</v>
       </c>
       <c r="O53" s="33">
@@ -9434,7 +9430,7 @@
       <c r="M54" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N54" s="34">
+      <c r="N54" s="38">
         <v>26871</v>
       </c>
       <c r="O54" s="33">
@@ -9502,7 +9498,7 @@
       <c r="M55" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N55" s="34">
+      <c r="N55" s="38">
         <v>27322</v>
       </c>
       <c r="O55" s="33">
@@ -9570,7 +9566,7 @@
       <c r="M56" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N56" s="34">
+      <c r="N56" s="38">
         <v>27117</v>
       </c>
       <c r="O56" s="33">
@@ -9638,7 +9634,7 @@
       <c r="M57" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N57" s="34">
+      <c r="N57" s="38">
         <v>27668</v>
       </c>
       <c r="O57" s="33">
@@ -9706,7 +9702,7 @@
       <c r="M58" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N58" s="34">
+      <c r="N58" s="38">
         <v>27729</v>
       </c>
       <c r="O58" s="33">
@@ -9774,7 +9770,7 @@
       <c r="M59" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N59" s="34">
+      <c r="N59" s="38">
         <v>28089</v>
       </c>
       <c r="O59" s="33">
@@ -9842,7 +9838,7 @@
       <c r="M60" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N60" s="34">
+      <c r="N60" s="38">
         <v>28713</v>
       </c>
       <c r="O60" s="33">
@@ -9910,7 +9906,7 @@
       <c r="M61" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N61" s="34">
+      <c r="N61" s="38">
         <v>28719</v>
       </c>
       <c r="O61" s="33">
@@ -9978,7 +9974,7 @@
       <c r="M62" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N62" s="34">
+      <c r="N62" s="38">
         <v>28514</v>
       </c>
       <c r="O62" s="33">
@@ -10046,7 +10042,7 @@
       <c r="M63" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N63" s="34">
+      <c r="N63" s="38">
         <v>28521</v>
       </c>
       <c r="O63" s="33">
@@ -10114,7 +10110,7 @@
       <c r="M64" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N64" s="34">
+      <c r="N64" s="38">
         <v>29086</v>
       </c>
       <c r="O64" s="33">
@@ -10182,7 +10178,7 @@
       <c r="M65" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N65" s="34">
+      <c r="N65" s="38">
         <v>29321</v>
       </c>
       <c r="O65" s="33">
@@ -10250,7 +10246,7 @@
       <c r="M66" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N66" s="34">
+      <c r="N66" s="38">
         <v>29301</v>
       </c>
       <c r="O66" s="33">
@@ -10318,7 +10314,7 @@
       <c r="M67" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N67" s="34">
+      <c r="N67" s="38">
         <v>27178</v>
       </c>
       <c r="O67" s="33">
@@ -10386,7 +10382,7 @@
       <c r="M68" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N68" s="34">
+      <c r="N68" s="38">
         <v>25323</v>
       </c>
       <c r="O68" s="33">
@@ -10454,7 +10450,7 @@
       <c r="M69" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N69" s="34">
+      <c r="N69" s="38">
         <v>27211</v>
       </c>
       <c r="O69" s="33">
@@ -10522,7 +10518,7 @@
       <c r="M70" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="N70" s="34">
+      <c r="N70" s="38">
         <v>26769</v>
       </c>
       <c r="O70" s="33">
@@ -10590,7 +10586,7 @@
       <c r="M71" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N71" s="34">
+      <c r="N71" s="38">
         <v>26884</v>
       </c>
       <c r="O71" s="33">
@@ -10658,7 +10654,7 @@
       <c r="M72" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N72" s="34">
+      <c r="N72" s="38">
         <v>27510</v>
       </c>
       <c r="O72" s="33">
@@ -10726,7 +10722,7 @@
       <c r="M73" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N73" s="34">
+      <c r="N73" s="38">
         <v>30549</v>
       </c>
       <c r="O73" s="33">
@@ -10794,7 +10790,7 @@
       <c r="M74" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N74" s="34">
+      <c r="N74" s="38">
         <v>30782</v>
       </c>
       <c r="O74" s="33">
@@ -10862,7 +10858,7 @@
       <c r="M75" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N75" s="34">
+      <c r="N75" s="38">
         <v>31303</v>
       </c>
       <c r="O75" s="33">
@@ -10930,7 +10926,7 @@
       <c r="M76" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N76" s="34">
+      <c r="N76" s="38">
         <v>25382</v>
       </c>
       <c r="O76" s="33">
@@ -10998,7 +10994,7 @@
       <c r="M77" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N77" s="34">
+      <c r="N77" s="38">
         <v>22396</v>
       </c>
       <c r="O77" s="33">
@@ -11066,7 +11062,7 @@
       <c r="M78" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N78" s="34">
+      <c r="N78" s="38">
         <v>23925</v>
       </c>
       <c r="O78" s="33">
@@ -11134,7 +11130,7 @@
       <c r="M79" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N79" s="34">
+      <c r="N79" s="38">
         <v>22229</v>
       </c>
       <c r="O79" s="33">
@@ -11202,7 +11198,7 @@
       <c r="M80" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N80" s="34">
+      <c r="N80" s="38">
         <v>22999</v>
       </c>
       <c r="O80" s="33">
@@ -11270,7 +11266,7 @@
       <c r="M81" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N81" s="34">
+      <c r="N81" s="38">
         <v>22521</v>
       </c>
       <c r="O81" s="33">
@@ -11338,7 +11334,7 @@
       <c r="M82" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N82" s="34">
+      <c r="N82" s="38">
         <v>22379</v>
       </c>
       <c r="O82" s="33">
@@ -11406,7 +11402,7 @@
       <c r="M83" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N83" s="34">
+      <c r="N83" s="38">
         <v>28892</v>
       </c>
       <c r="O83" s="33">
@@ -11474,7 +11470,7 @@
       <c r="M84" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N84" s="34">
+      <c r="N84" s="38">
         <v>22630</v>
       </c>
       <c r="O84" s="33">
@@ -11542,7 +11538,7 @@
       <c r="M85" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N85" s="34">
+      <c r="N85" s="38">
         <v>24460</v>
       </c>
       <c r="O85" s="33">
@@ -11610,7 +11606,7 @@
       <c r="M86" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N86" s="34">
+      <c r="N86" s="38">
         <v>24349</v>
       </c>
       <c r="O86" s="33">
@@ -11678,7 +11674,7 @@
       <c r="M87" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N87" s="34">
+      <c r="N87" s="38">
         <v>30609</v>
       </c>
       <c r="O87" s="33">
@@ -11746,7 +11742,7 @@
       <c r="M88" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N88" s="34">
+      <c r="N88" s="38">
         <v>27971</v>
       </c>
       <c r="O88" s="33">
@@ -11814,7 +11810,7 @@
       <c r="M89" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N89" s="34">
+      <c r="N89" s="38">
         <v>28617</v>
       </c>
       <c r="O89" s="33">
@@ -11882,7 +11878,7 @@
       <c r="M90" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N90" s="34">
+      <c r="N90" s="38">
         <v>25892</v>
       </c>
       <c r="O90" s="33">
@@ -11950,7 +11946,7 @@
       <c r="M91" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N91" s="34">
+      <c r="N91" s="38">
         <v>30111</v>
       </c>
       <c r="O91" s="33">
@@ -12018,7 +12014,7 @@
       <c r="M92" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N92" s="34">
+      <c r="N92" s="38">
         <v>26221</v>
       </c>
       <c r="O92" s="33">
@@ -12086,7 +12082,7 @@
       <c r="M93" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N93" s="34">
+      <c r="N93" s="38">
         <v>29493</v>
       </c>
       <c r="O93" s="33">
@@ -12154,7 +12150,7 @@
       <c r="M94" s="32" t="s">
         <v>310</v>
       </c>
-      <c r="N94" s="34">
+      <c r="N94" s="38">
         <v>30100</v>
       </c>
       <c r="O94" s="33">
@@ -12222,7 +12218,7 @@
       <c r="M95" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N95" s="34">
+      <c r="N95" s="38">
         <v>27811</v>
       </c>
       <c r="O95" s="33">
@@ -12290,7 +12286,7 @@
       <c r="M96" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N96" s="34">
+      <c r="N96" s="38">
         <v>32435</v>
       </c>
       <c r="O96" s="33">
@@ -12358,7 +12354,7 @@
       <c r="M97" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N97" s="34">
+      <c r="N97" s="38">
         <v>29693</v>
       </c>
       <c r="O97" s="33">
@@ -12426,7 +12422,7 @@
       <c r="M98" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N98" s="34">
+      <c r="N98" s="38">
         <v>27813</v>
       </c>
       <c r="O98" s="33">
@@ -12494,7 +12490,7 @@
       <c r="M99" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N99" s="34">
+      <c r="N99" s="38">
         <v>30391</v>
       </c>
       <c r="O99" s="33">
@@ -12562,7 +12558,7 @@
       <c r="M100" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N100" s="34">
+      <c r="N100" s="38">
         <v>31061</v>
       </c>
       <c r="O100" s="33">
@@ -12630,7 +12626,7 @@
       <c r="M101" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N101" s="34">
+      <c r="N101" s="38">
         <v>31313</v>
       </c>
       <c r="O101" s="33">
@@ -12698,7 +12694,7 @@
       <c r="M102" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N102" s="34">
+      <c r="N102" s="38">
         <v>31295</v>
       </c>
       <c r="O102" s="33">
@@ -12766,7 +12762,7 @@
       <c r="M103" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N103" s="34">
+      <c r="N103" s="38">
         <v>31493</v>
       </c>
       <c r="O103" s="33">
@@ -12834,7 +12830,7 @@
       <c r="M104" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N104" s="34">
+      <c r="N104" s="38">
         <v>27192</v>
       </c>
       <c r="O104" s="33">
@@ -12902,7 +12898,7 @@
       <c r="M105" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N105" s="34">
+      <c r="N105" s="38">
         <v>27628</v>
       </c>
       <c r="O105" s="33">
@@ -12970,7 +12966,7 @@
       <c r="M106" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N106" s="34">
+      <c r="N106" s="38">
         <v>27264</v>
       </c>
       <c r="O106" s="33">
@@ -13038,7 +13034,7 @@
       <c r="M107" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N107" s="34">
+      <c r="N107" s="38">
         <v>27770</v>
       </c>
       <c r="O107" s="33">
@@ -13106,7 +13102,7 @@
       <c r="M108" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N108" s="34">
+      <c r="N108" s="38">
         <v>28014</v>
       </c>
       <c r="O108" s="33">
@@ -13174,7 +13170,7 @@
       <c r="M109" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N109" s="34">
+      <c r="N109" s="38">
         <v>28170</v>
       </c>
       <c r="O109" s="33">
@@ -13242,7 +13238,7 @@
       <c r="M110" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N110" s="34">
+      <c r="N110" s="38">
         <v>26412</v>
       </c>
       <c r="O110" s="33">
@@ -13310,7 +13306,7 @@
       <c r="M111" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N111" s="34">
+      <c r="N111" s="38">
         <v>24988</v>
       </c>
       <c r="O111" s="33">
@@ -13378,7 +13374,7 @@
       <c r="M112" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N112" s="34">
+      <c r="N112" s="38">
         <v>27404</v>
       </c>
       <c r="O112" s="33">
@@ -13446,7 +13442,7 @@
       <c r="M113" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N113" s="34">
+      <c r="N113" s="38">
         <v>25124</v>
       </c>
       <c r="O113" s="33">
@@ -13514,7 +13510,7 @@
       <c r="M114" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N114" s="34">
+      <c r="N114" s="38">
         <v>26464</v>
       </c>
       <c r="O114" s="33">
@@ -13582,7 +13578,7 @@
       <c r="M115" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N115" s="34">
+      <c r="N115" s="38">
         <v>28459</v>
       </c>
       <c r="O115" s="33">
@@ -13650,7 +13646,7 @@
       <c r="M116" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N116" s="34">
+      <c r="N116" s="38">
         <v>26789</v>
       </c>
       <c r="O116" s="33">
@@ -13718,7 +13714,7 @@
       <c r="M117" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N117" s="34">
+      <c r="N117" s="38">
         <v>26868</v>
       </c>
       <c r="O117" s="33">
@@ -13786,7 +13782,7 @@
       <c r="M118" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N118" s="34">
+      <c r="N118" s="38">
         <v>28020</v>
       </c>
       <c r="O118" s="33">
@@ -13854,7 +13850,7 @@
       <c r="M119" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N119" s="34">
+      <c r="N119" s="38">
         <v>22911</v>
       </c>
       <c r="O119" s="33">
@@ -13922,7 +13918,7 @@
       <c r="M120" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N120" s="34">
+      <c r="N120" s="38">
         <v>27844</v>
       </c>
       <c r="O120" s="33">
@@ -13990,7 +13986,7 @@
       <c r="M121" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N121" s="34">
+      <c r="N121" s="38">
         <v>27020</v>
       </c>
       <c r="O121" s="33">
@@ -14058,7 +14054,7 @@
       <c r="M122" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N122" s="34">
+      <c r="N122" s="38">
         <v>26591</v>
       </c>
       <c r="O122" s="33">
@@ -14126,7 +14122,7 @@
       <c r="M123" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N123" s="34">
+      <c r="N123" s="38">
         <v>28854</v>
       </c>
       <c r="O123" s="33">
@@ -14194,7 +14190,7 @@
       <c r="M124" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N124" s="34">
+      <c r="N124" s="38">
         <v>24495</v>
       </c>
       <c r="O124" s="33">
@@ -14262,7 +14258,7 @@
       <c r="M125" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N125" s="34">
+      <c r="N125" s="38">
         <v>29651</v>
       </c>
       <c r="O125" s="33">
@@ -14330,7 +14326,7 @@
       <c r="M126" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N126" s="34">
+      <c r="N126" s="38">
         <v>25393</v>
       </c>
       <c r="O126" s="33">
@@ -14398,7 +14394,7 @@
       <c r="M127" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N127" s="34">
+      <c r="N127" s="38">
         <v>26387</v>
       </c>
       <c r="O127" s="33">
@@ -14466,7 +14462,7 @@
       <c r="M128" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N128" s="34">
+      <c r="N128" s="38">
         <v>24247</v>
       </c>
       <c r="O128" s="33">
@@ -14534,7 +14530,7 @@
       <c r="M129" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N129" s="34">
+      <c r="N129" s="38">
         <v>28323</v>
       </c>
       <c r="O129" s="33">
@@ -14602,7 +14598,7 @@
       <c r="M130" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N130" s="34">
+      <c r="N130" s="38">
         <v>25528</v>
       </c>
       <c r="O130" s="33">
@@ -14670,7 +14666,7 @@
       <c r="M131" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N131" s="34">
+      <c r="N131" s="38">
         <v>25213</v>
       </c>
       <c r="O131" s="33">
@@ -14738,7 +14734,7 @@
       <c r="M132" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N132" s="34">
+      <c r="N132" s="38">
         <v>26615</v>
       </c>
       <c r="O132" s="33">
@@ -14806,7 +14802,7 @@
       <c r="M133" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N133" s="34">
+      <c r="N133" s="38">
         <v>27870</v>
       </c>
       <c r="O133" s="33">
@@ -14874,7 +14870,7 @@
       <c r="M134" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N134" s="34">
+      <c r="N134" s="38">
         <v>26598</v>
       </c>
       <c r="O134" s="33">
@@ -14942,7 +14938,7 @@
       <c r="M135" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N135" s="34">
+      <c r="N135" s="38">
         <v>26153</v>
       </c>
       <c r="O135" s="33">
@@ -15010,7 +15006,7 @@
       <c r="M136" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N136" s="34">
+      <c r="N136" s="38">
         <v>26437</v>
       </c>
       <c r="O136" s="33">
@@ -15078,7 +15074,7 @@
       <c r="M137" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N137" s="34">
+      <c r="N137" s="38">
         <v>27048</v>
       </c>
       <c r="O137" s="33">
@@ -15146,7 +15142,7 @@
       <c r="M138" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N138" s="34">
+      <c r="N138" s="38">
         <v>26759</v>
       </c>
       <c r="O138" s="33">
@@ -15214,7 +15210,7 @@
       <c r="M139" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N139" s="34">
+      <c r="N139" s="38">
         <v>28350</v>
       </c>
       <c r="O139" s="33">
@@ -15282,7 +15278,7 @@
       <c r="M140" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N140" s="34">
+      <c r="N140" s="38">
         <v>28106</v>
       </c>
       <c r="O140" s="33">
@@ -15350,7 +15346,7 @@
       <c r="M141" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N141" s="34">
+      <c r="N141" s="38">
         <v>26945</v>
       </c>
       <c r="O141" s="33">
@@ -15418,7 +15414,7 @@
       <c r="M142" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N142" s="34">
+      <c r="N142" s="38">
         <v>27498</v>
       </c>
       <c r="O142" s="33">
@@ -15486,7 +15482,7 @@
       <c r="M143" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N143" s="34">
+      <c r="N143" s="38">
         <v>26261</v>
       </c>
       <c r="O143" s="33">
@@ -15554,7 +15550,7 @@
       <c r="M144" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N144" s="34">
+      <c r="N144" s="38">
         <v>28267</v>
       </c>
       <c r="O144" s="33">
@@ -15622,7 +15618,7 @@
       <c r="M145" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N145" s="34">
+      <c r="N145" s="38">
         <v>27256</v>
       </c>
       <c r="O145" s="33">
@@ -15690,7 +15686,7 @@
       <c r="M146" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N146" s="34">
+      <c r="N146" s="38">
         <v>27382</v>
       </c>
       <c r="O146" s="33">
@@ -15758,7 +15754,7 @@
       <c r="M147" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N147" s="34">
+      <c r="N147" s="38">
         <v>26960</v>
       </c>
       <c r="O147" s="33">
@@ -15826,7 +15822,7 @@
       <c r="M148" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N148" s="34">
+      <c r="N148" s="38">
         <v>25799</v>
       </c>
       <c r="O148" s="33">
@@ -15894,7 +15890,7 @@
       <c r="M149" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N149" s="34">
+      <c r="N149" s="38">
         <v>27933</v>
       </c>
       <c r="O149" s="33">
@@ -15962,7 +15958,7 @@
       <c r="M150" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N150" s="34">
+      <c r="N150" s="38">
         <v>31840</v>
       </c>
       <c r="O150" s="33">
@@ -16030,7 +16026,7 @@
       <c r="M151" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N151" s="34">
+      <c r="N151" s="38">
         <v>27371</v>
       </c>
       <c r="O151" s="33">
@@ -16098,7 +16094,7 @@
       <c r="M152" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N152" s="34">
+      <c r="N152" s="38">
         <v>27777</v>
       </c>
       <c r="O152" s="33">
@@ -16166,7 +16162,7 @@
       <c r="M153" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N153" s="34">
+      <c r="N153" s="38">
         <v>29097</v>
       </c>
       <c r="O153" s="33">
@@ -16234,7 +16230,7 @@
       <c r="M154" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N154" s="34">
+      <c r="N154" s="38">
         <v>26390</v>
       </c>
       <c r="O154" s="33">
@@ -16302,7 +16298,7 @@
       <c r="M155" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N155" s="34">
+      <c r="N155" s="38">
         <v>28091</v>
       </c>
       <c r="O155" s="33">
@@ -16370,7 +16366,7 @@
       <c r="M156" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N156" s="34">
+      <c r="N156" s="38">
         <v>29715</v>
       </c>
       <c r="O156" s="33">
@@ -16438,7 +16434,7 @@
       <c r="M157" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N157" s="34">
+      <c r="N157" s="38">
         <v>26880</v>
       </c>
       <c r="O157" s="33">
@@ -16506,7 +16502,7 @@
       <c r="M158" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N158" s="34">
+      <c r="N158" s="38">
         <v>30362</v>
       </c>
       <c r="O158" s="33">
@@ -16574,7 +16570,7 @@
       <c r="M159" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N159" s="34">
+      <c r="N159" s="38">
         <v>26003</v>
       </c>
       <c r="O159" s="33">
@@ -16642,7 +16638,7 @@
       <c r="M160" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N160" s="34">
+      <c r="N160" s="38">
         <v>26517</v>
       </c>
       <c r="O160" s="33">
@@ -16710,7 +16706,7 @@
       <c r="M161" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N161" s="34">
+      <c r="N161" s="38">
         <v>29868</v>
       </c>
       <c r="O161" s="33">
@@ -16778,7 +16774,7 @@
       <c r="M162" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N162" s="34">
+      <c r="N162" s="38">
         <v>29844</v>
       </c>
       <c r="O162" s="33">
@@ -16846,7 +16842,7 @@
       <c r="M163" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N163" s="34">
+      <c r="N163" s="38">
         <v>31767</v>
       </c>
       <c r="O163" s="33">
@@ -16914,7 +16910,7 @@
       <c r="M164" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N164" s="34">
+      <c r="N164" s="38">
         <v>28371</v>
       </c>
       <c r="O164" s="33">
@@ -16982,7 +16978,7 @@
       <c r="M165" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N165" s="34">
+      <c r="N165" s="38">
         <v>24449</v>
       </c>
       <c r="O165" s="33">
@@ -17050,7 +17046,7 @@
       <c r="M166" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N166" s="34">
+      <c r="N166" s="38">
         <v>26164</v>
       </c>
       <c r="O166" s="33">
@@ -17118,7 +17114,7 @@
       <c r="M167" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N167" s="34">
+      <c r="N167" s="38">
         <v>29629</v>
       </c>
       <c r="O167" s="33">
@@ -17186,7 +17182,7 @@
       <c r="M168" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N168" s="34">
+      <c r="N168" s="38">
         <v>31548</v>
       </c>
       <c r="O168" s="33">
@@ -17254,7 +17250,7 @@
       <c r="M169" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N169" s="34">
+      <c r="N169" s="38">
         <v>23439</v>
       </c>
       <c r="O169" s="33">
@@ -17322,7 +17318,7 @@
       <c r="M170" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N170" s="34">
+      <c r="N170" s="38">
         <v>31785</v>
       </c>
       <c r="O170" s="33">
@@ -17390,7 +17386,7 @@
       <c r="M171" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N171" s="34">
+      <c r="N171" s="38">
         <v>29187</v>
       </c>
       <c r="O171" s="33">
@@ -17458,7 +17454,7 @@
       <c r="M172" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N172" s="34">
+      <c r="N172" s="38">
         <v>27175</v>
       </c>
       <c r="O172" s="33">
@@ -17526,7 +17522,7 @@
       <c r="M173" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N173" s="34">
+      <c r="N173" s="38">
         <v>25445</v>
       </c>
       <c r="O173" s="33">
@@ -17594,7 +17590,7 @@
       <c r="M174" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N174" s="34">
+      <c r="N174" s="38">
         <v>26899</v>
       </c>
       <c r="O174" s="33">
@@ -17662,7 +17658,7 @@
       <c r="M175" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N175" s="34">
+      <c r="N175" s="38">
         <v>28703</v>
       </c>
       <c r="O175" s="33">
@@ -17730,7 +17726,7 @@
       <c r="M176" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N176" s="34">
+      <c r="N176" s="38">
         <v>30401</v>
       </c>
       <c r="O176" s="33">
@@ -17798,7 +17794,7 @@
       <c r="M177" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N177" s="34">
+      <c r="N177" s="38">
         <v>27445</v>
       </c>
       <c r="O177" s="33">
@@ -17866,7 +17862,7 @@
       <c r="M178" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N178" s="34">
+      <c r="N178" s="38">
         <v>30367</v>
       </c>
       <c r="O178" s="33">
@@ -17934,7 +17930,7 @@
       <c r="M179" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N179" s="34">
+      <c r="N179" s="38">
         <v>28499</v>
       </c>
       <c r="O179" s="33">
@@ -18002,7 +17998,7 @@
       <c r="M180" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N180" s="34">
+      <c r="N180" s="38">
         <v>28982</v>
       </c>
       <c r="O180" s="33">
@@ -18070,7 +18066,7 @@
       <c r="M181" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N181" s="34">
+      <c r="N181" s="38">
         <v>24294</v>
       </c>
       <c r="O181" s="33">
@@ -18138,7 +18134,7 @@
       <c r="M182" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N182" s="34">
+      <c r="N182" s="38">
         <v>27729</v>
       </c>
       <c r="O182" s="33">
@@ -18206,7 +18202,7 @@
       <c r="M183" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N183" s="34">
+      <c r="N183" s="38">
         <v>26247</v>
       </c>
       <c r="O183" s="33">
@@ -18274,7 +18270,7 @@
       <c r="M184" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N184" s="34">
+      <c r="N184" s="38">
         <v>27349</v>
       </c>
       <c r="O184" s="33">
@@ -18342,7 +18338,7 @@
       <c r="M185" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N185" s="34">
+      <c r="N185" s="38">
         <v>29747</v>
       </c>
       <c r="O185" s="33">
@@ -18410,7 +18406,7 @@
       <c r="M186" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N186" s="34">
+      <c r="N186" s="38">
         <v>27920</v>
       </c>
       <c r="O186" s="33">
@@ -18478,7 +18474,7 @@
       <c r="M187" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N187" s="34">
+      <c r="N187" s="38">
         <v>29365</v>
       </c>
       <c r="O187" s="33">
@@ -18546,7 +18542,7 @@
       <c r="M188" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N188" s="34">
+      <c r="N188" s="38">
         <v>28199</v>
       </c>
       <c r="O188" s="33">
@@ -18614,7 +18610,7 @@
       <c r="M189" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N189" s="34">
+      <c r="N189" s="38">
         <v>26407</v>
       </c>
       <c r="O189" s="33">
@@ -18682,7 +18678,7 @@
       <c r="M190" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N190" s="34">
+      <c r="N190" s="38">
         <v>30770</v>
       </c>
       <c r="O190" s="33">
@@ -18750,7 +18746,7 @@
       <c r="M191" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N191" s="34">
+      <c r="N191" s="38">
         <v>29708</v>
       </c>
       <c r="O191" s="33">
@@ -18818,7 +18814,7 @@
       <c r="M192" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N192" s="34">
+      <c r="N192" s="38">
         <v>28226</v>
       </c>
       <c r="O192" s="33">
@@ -18886,7 +18882,7 @@
       <c r="M193" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N193" s="34">
+      <c r="N193" s="38">
         <v>28471</v>
       </c>
       <c r="O193" s="33">
@@ -18954,7 +18950,7 @@
       <c r="M194" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N194" s="34">
+      <c r="N194" s="38">
         <v>29353</v>
       </c>
       <c r="O194" s="33">
@@ -19022,7 +19018,7 @@
       <c r="M195" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N195" s="34">
+      <c r="N195" s="38">
         <v>27868</v>
       </c>
       <c r="O195" s="33">
@@ -19090,7 +19086,7 @@
       <c r="M196" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N196" s="34">
+      <c r="N196" s="38">
         <v>31432</v>
       </c>
       <c r="O196" s="33">
@@ -19158,7 +19154,7 @@
       <c r="M197" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N197" s="34">
+      <c r="N197" s="38">
         <v>29785</v>
       </c>
       <c r="O197" s="33">
@@ -19226,7 +19222,7 @@
       <c r="M198" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N198" s="34">
+      <c r="N198" s="38">
         <v>26659</v>
       </c>
       <c r="O198" s="33">
@@ -19294,7 +19290,7 @@
       <c r="M199" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N199" s="34">
+      <c r="N199" s="38">
         <v>30330</v>
       </c>
       <c r="O199" s="33">
@@ -19362,7 +19358,7 @@
       <c r="M200" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N200" s="34">
+      <c r="N200" s="38">
         <v>25605</v>
       </c>
       <c r="O200" s="33">
@@ -19430,7 +19426,7 @@
       <c r="M201" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N201" s="34">
+      <c r="N201" s="38">
         <v>29357</v>
       </c>
       <c r="O201" s="33">
@@ -19498,7 +19494,7 @@
       <c r="M202" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N202" s="34">
+      <c r="N202" s="38">
         <v>29370</v>
       </c>
       <c r="O202" s="33">
@@ -19566,7 +19562,7 @@
       <c r="M203" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N203" s="34">
+      <c r="N203" s="38">
         <v>28350</v>
       </c>
       <c r="O203" s="33">
@@ -19634,7 +19630,7 @@
       <c r="M204" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N204" s="34">
+      <c r="N204" s="38">
         <v>31161</v>
       </c>
       <c r="O204" s="33">
@@ -19702,7 +19698,7 @@
       <c r="M205" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N205" s="34">
+      <c r="N205" s="38">
         <v>31251</v>
       </c>
       <c r="O205" s="33">
@@ -19770,7 +19766,7 @@
       <c r="M206" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N206" s="34">
+      <c r="N206" s="38">
         <v>25062</v>
       </c>
       <c r="O206" s="33">
@@ -19838,7 +19834,7 @@
       <c r="M207" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N207" s="34">
+      <c r="N207" s="38">
         <v>30274</v>
       </c>
       <c r="O207" s="33">
@@ -19906,7 +19902,7 @@
       <c r="M208" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N208" s="34">
+      <c r="N208" s="38">
         <v>25238</v>
       </c>
       <c r="O208" s="33">
@@ -19974,7 +19970,7 @@
       <c r="M209" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N209" s="34">
+      <c r="N209" s="38">
         <v>25123</v>
       </c>
       <c r="O209" s="33">
@@ -20042,7 +20038,7 @@
       <c r="M210" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N210" s="34">
+      <c r="N210" s="38">
         <v>30201</v>
       </c>
       <c r="O210" s="33">
@@ -20110,7 +20106,7 @@
       <c r="M211" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N211" s="34">
+      <c r="N211" s="38">
         <v>30428</v>
       </c>
       <c r="O211" s="33">
@@ -20178,7 +20174,7 @@
       <c r="M212" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N212" s="34">
+      <c r="N212" s="38">
         <v>23084</v>
       </c>
       <c r="O212" s="33">
@@ -20246,7 +20242,7 @@
       <c r="M213" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N213" s="34">
+      <c r="N213" s="38">
         <v>28422</v>
       </c>
       <c r="O213" s="33">
@@ -20314,7 +20310,7 @@
       <c r="M214" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N214" s="34">
+      <c r="N214" s="38">
         <v>30238</v>
       </c>
       <c r="O214" s="33">
@@ -20382,7 +20378,7 @@
       <c r="M215" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N215" s="34">
+      <c r="N215" s="38">
         <v>30120</v>
       </c>
       <c r="O215" s="33">
@@ -20450,7 +20446,7 @@
       <c r="M216" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N216" s="34">
+      <c r="N216" s="38">
         <v>29892</v>
       </c>
       <c r="O216" s="33">
@@ -20518,7 +20514,7 @@
       <c r="M217" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N217" s="34">
+      <c r="N217" s="38">
         <v>27689</v>
       </c>
       <c r="O217" s="33">
@@ -20586,7 +20582,7 @@
       <c r="M218" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N218" s="34">
+      <c r="N218" s="38">
         <v>26085</v>
       </c>
       <c r="O218" s="33">
@@ -20654,7 +20650,7 @@
       <c r="M219" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N219" s="34">
+      <c r="N219" s="38">
         <v>26995</v>
       </c>
       <c r="O219" s="33">
@@ -20722,7 +20718,7 @@
       <c r="M220" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N220" s="34">
+      <c r="N220" s="38">
         <v>29224</v>
       </c>
       <c r="O220" s="33">
@@ -20790,7 +20786,7 @@
       <c r="M221" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="N221" s="34">
+      <c r="N221" s="38">
         <v>29688</v>
       </c>
       <c r="O221" s="33">
@@ -20858,7 +20854,7 @@
       <c r="M222" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N222" s="34">
+      <c r="N222" s="38">
         <v>26839</v>
       </c>
       <c r="O222" s="33">
@@ -20926,7 +20922,7 @@
       <c r="M223" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N223" s="34">
+      <c r="N223" s="38">
         <v>31628</v>
       </c>
       <c r="O223" s="33">
@@ -20994,7 +20990,7 @@
       <c r="M224" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N224" s="34">
+      <c r="N224" s="38">
         <v>26331</v>
       </c>
       <c r="O224" s="33">
@@ -21062,7 +21058,7 @@
       <c r="M225" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N225" s="34">
+      <c r="N225" s="38">
         <v>32059</v>
       </c>
       <c r="O225" s="33">
@@ -21130,7 +21126,7 @@
       <c r="M226" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N226" s="34">
+      <c r="N226" s="38">
         <v>31539</v>
       </c>
       <c r="O226" s="33">
@@ -21198,7 +21194,7 @@
       <c r="M227" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N227" s="34">
+      <c r="N227" s="38">
         <v>25691</v>
       </c>
       <c r="O227" s="33">
@@ -21266,7 +21262,7 @@
       <c r="M228" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N228" s="34">
+      <c r="N228" s="38">
         <v>30939</v>
       </c>
       <c r="O228" s="33">
@@ -21334,7 +21330,7 @@
       <c r="M229" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N229" s="34">
+      <c r="N229" s="38">
         <v>26741</v>
       </c>
       <c r="O229" s="33">
@@ -21402,7 +21398,7 @@
       <c r="M230" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N230" s="34">
+      <c r="N230" s="38">
         <v>27502</v>
       </c>
       <c r="O230" s="33">
@@ -21470,7 +21466,7 @@
       <c r="M231" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N231" s="34">
+      <c r="N231" s="38">
         <v>28792</v>
       </c>
       <c r="O231" s="33">
@@ -21538,7 +21534,7 @@
       <c r="M232" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N232" s="34">
+      <c r="N232" s="38">
         <v>24387</v>
       </c>
       <c r="O232" s="33">
@@ -21606,7 +21602,7 @@
       <c r="M233" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N233" s="34">
+      <c r="N233" s="38">
         <v>24405</v>
       </c>
       <c r="O233" s="33">
@@ -21674,7 +21670,7 @@
       <c r="M234" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N234" s="34">
+      <c r="N234" s="38">
         <v>29203</v>
       </c>
       <c r="O234" s="33">
@@ -21742,7 +21738,7 @@
       <c r="M235" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N235" s="34">
+      <c r="N235" s="38">
         <v>31280</v>
       </c>
       <c r="O235" s="33">
@@ -21810,7 +21806,7 @@
       <c r="M236" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N236" s="34">
+      <c r="N236" s="38">
         <v>28346</v>
       </c>
       <c r="O236" s="33">
@@ -21878,7 +21874,7 @@
       <c r="M237" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N237" s="34">
+      <c r="N237" s="38">
         <v>28425</v>
       </c>
       <c r="O237" s="33">
@@ -21946,7 +21942,7 @@
       <c r="M238" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N238" s="34">
+      <c r="N238" s="38">
         <v>29384</v>
       </c>
       <c r="O238" s="33">
@@ -22014,7 +22010,7 @@
       <c r="M239" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N239" s="34">
+      <c r="N239" s="38">
         <v>25334</v>
       </c>
       <c r="O239" s="33">
@@ -22082,7 +22078,7 @@
       <c r="M240" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N240" s="34">
+      <c r="N240" s="38">
         <v>30239</v>
       </c>
       <c r="O240" s="33">
@@ -22150,7 +22146,7 @@
       <c r="M241" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N241" s="34">
+      <c r="N241" s="38">
         <v>24981</v>
       </c>
       <c r="O241" s="33">
@@ -22218,7 +22214,7 @@
       <c r="M242" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N242" s="34">
+      <c r="N242" s="38">
         <v>28461</v>
       </c>
       <c r="O242" s="33">
@@ -22286,7 +22282,7 @@
       <c r="M243" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N243" s="34">
+      <c r="N243" s="38">
         <v>29180</v>
       </c>
       <c r="O243" s="33">
@@ -22354,7 +22350,7 @@
       <c r="M244" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N244" s="34">
+      <c r="N244" s="38">
         <v>28891</v>
       </c>
       <c r="O244" s="33">
@@ -22422,7 +22418,7 @@
       <c r="M245" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N245" s="34">
+      <c r="N245" s="38">
         <v>30343</v>
       </c>
       <c r="O245" s="33">
@@ -22490,7 +22486,7 @@
       <c r="M246" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N246" s="34">
+      <c r="N246" s="38">
         <v>30260</v>
       </c>
       <c r="O246" s="33">
@@ -22558,7 +22554,7 @@
       <c r="M247" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N247" s="34">
+      <c r="N247" s="38">
         <v>27217</v>
       </c>
       <c r="O247" s="33">
@@ -22626,7 +22622,7 @@
       <c r="M248" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N248" s="34">
+      <c r="N248" s="38">
         <v>25850</v>
       </c>
       <c r="O248" s="33">
@@ -22694,7 +22690,7 @@
       <c r="M249" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N249" s="34">
+      <c r="N249" s="38">
         <v>28720</v>
       </c>
       <c r="O249" s="33">
@@ -22762,7 +22758,7 @@
       <c r="M250" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N250" s="34">
+      <c r="N250" s="38">
         <v>28476</v>
       </c>
       <c r="O250" s="33">
@@ -22830,7 +22826,7 @@
       <c r="M251" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N251" s="34">
+      <c r="N251" s="38">
         <v>30889</v>
       </c>
       <c r="O251" s="33">
@@ -22898,7 +22894,7 @@
       <c r="M252" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N252" s="34">
+      <c r="N252" s="38">
         <v>31231</v>
       </c>
       <c r="O252" s="33">
@@ -22966,7 +22962,7 @@
       <c r="M253" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N253" s="34">
+      <c r="N253" s="38">
         <v>26617</v>
       </c>
       <c r="O253" s="33">
@@ -23034,7 +23030,7 @@
       <c r="M254" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N254" s="34">
+      <c r="N254" s="38">
         <v>27109</v>
       </c>
       <c r="O254" s="33">
@@ -23102,7 +23098,7 @@
       <c r="M255" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N255" s="34">
+      <c r="N255" s="38">
         <v>26888</v>
       </c>
       <c r="O255" s="33">
@@ -23170,7 +23166,7 @@
       <c r="M256" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N256" s="34">
+      <c r="N256" s="38">
         <v>26066</v>
       </c>
       <c r="O256" s="33">
@@ -23238,7 +23234,7 @@
       <c r="M257" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N257" s="34">
+      <c r="N257" s="38">
         <v>31565</v>
       </c>
       <c r="O257" s="33">
@@ -23306,7 +23302,7 @@
       <c r="M258" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N258" s="34">
+      <c r="N258" s="38">
         <v>31220</v>
       </c>
       <c r="O258" s="33">
@@ -23374,7 +23370,7 @@
       <c r="M259" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N259" s="34">
+      <c r="N259" s="38">
         <v>25853</v>
       </c>
       <c r="O259" s="33">
@@ -23442,7 +23438,7 @@
       <c r="M260" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N260" s="34">
+      <c r="N260" s="38">
         <v>30546</v>
       </c>
       <c r="O260" s="33">
@@ -23510,7 +23506,7 @@
       <c r="M261" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N261" s="34">
+      <c r="N261" s="38">
         <v>30472</v>
       </c>
       <c r="O261" s="33">
@@ -23578,7 +23574,7 @@
       <c r="M262" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N262" s="34">
+      <c r="N262" s="38">
         <v>30654</v>
       </c>
       <c r="O262" s="33">
@@ -23646,7 +23642,7 @@
       <c r="M263" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N263" s="34">
+      <c r="N263" s="38">
         <v>28650</v>
       </c>
       <c r="O263" s="33">
@@ -23714,7 +23710,7 @@
       <c r="M264" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N264" s="34">
+      <c r="N264" s="38">
         <v>31241</v>
       </c>
       <c r="O264" s="33">
@@ -23782,7 +23778,7 @@
       <c r="M265" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N265" s="34">
+      <c r="N265" s="38">
         <v>31118</v>
       </c>
       <c r="O265" s="33">
@@ -23850,7 +23846,7 @@
       <c r="M266" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N266" s="34">
+      <c r="N266" s="38">
         <v>29131</v>
       </c>
       <c r="O266" s="33">
@@ -23918,7 +23914,7 @@
       <c r="M267" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N267" s="34">
+      <c r="N267" s="38">
         <v>33163</v>
       </c>
       <c r="O267" s="33">
@@ -23986,7 +23982,7 @@
       <c r="M268" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N268" s="34">
+      <c r="N268" s="38">
         <v>31879</v>
       </c>
       <c r="O268" s="33">
@@ -24054,7 +24050,7 @@
       <c r="M269" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N269" s="34">
+      <c r="N269" s="38">
         <v>30278</v>
       </c>
       <c r="O269" s="33">
@@ -24122,7 +24118,7 @@
       <c r="M270" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N270" s="34">
+      <c r="N270" s="38">
         <v>31225</v>
       </c>
       <c r="O270" s="33">
@@ -24190,7 +24186,7 @@
       <c r="M271" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N271" s="34">
+      <c r="N271" s="38">
         <v>30169</v>
       </c>
       <c r="O271" s="33">
@@ -24258,7 +24254,7 @@
       <c r="M272" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N272" s="34">
+      <c r="N272" s="38">
         <v>31862</v>
       </c>
       <c r="O272" s="33">
@@ -24326,7 +24322,7 @@
       <c r="M273" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N273" s="34">
+      <c r="N273" s="38">
         <v>31875</v>
       </c>
       <c r="O273" s="33">
@@ -24394,7 +24390,7 @@
       <c r="M274" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N274" s="34">
+      <c r="N274" s="38">
         <v>28713</v>
       </c>
       <c r="O274" s="33">
@@ -24462,7 +24458,7 @@
       <c r="M275" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N275" s="34">
+      <c r="N275" s="38">
         <v>32321</v>
       </c>
       <c r="O275" s="33">
@@ -24530,7 +24526,7 @@
       <c r="M276" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N276" s="34">
+      <c r="N276" s="38">
         <v>32964</v>
       </c>
       <c r="O276" s="33">
@@ -24598,7 +24594,7 @@
       <c r="M277" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N277" s="34">
+      <c r="N277" s="38">
         <v>31579</v>
       </c>
       <c r="O277" s="33">
@@ -24666,7 +24662,7 @@
       <c r="M278" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N278" s="34">
+      <c r="N278" s="38">
         <v>29151</v>
       </c>
       <c r="O278" s="33">
@@ -24734,7 +24730,7 @@
       <c r="M279" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N279" s="34">
+      <c r="N279" s="38">
         <v>29910</v>
       </c>
       <c r="O279" s="33">
@@ -24802,7 +24798,7 @@
       <c r="M280" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N280" s="34">
+      <c r="N280" s="38">
         <v>30749</v>
       </c>
       <c r="O280" s="33">
@@ -24870,7 +24866,7 @@
       <c r="M281" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N281" s="34">
+      <c r="N281" s="38">
         <v>28375</v>
       </c>
       <c r="O281" s="33">
@@ -24938,7 +24934,7 @@
       <c r="M282" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N282" s="34">
+      <c r="N282" s="38">
         <v>31563</v>
       </c>
       <c r="O282" s="33">
@@ -25006,7 +25002,7 @@
       <c r="M283" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N283" s="34">
+      <c r="N283" s="38">
         <v>31548</v>
       </c>
       <c r="O283" s="33">
@@ -25074,7 +25070,7 @@
       <c r="M284" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N284" s="34">
+      <c r="N284" s="38">
         <v>29917</v>
       </c>
       <c r="O284" s="33">
@@ -25142,7 +25138,7 @@
       <c r="M285" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N285" s="34">
+      <c r="N285" s="38">
         <v>31633</v>
       </c>
       <c r="O285" s="33">
@@ -25210,7 +25206,7 @@
       <c r="M286" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N286" s="34">
+      <c r="N286" s="38">
         <v>30315</v>
       </c>
       <c r="O286" s="33">
@@ -25278,7 +25274,7 @@
       <c r="M287" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N287" s="34">
+      <c r="N287" s="38">
         <v>33295</v>
       </c>
       <c r="O287" s="33">
@@ -25346,7 +25342,7 @@
       <c r="M288" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N288" s="34">
+      <c r="N288" s="38">
         <v>31709</v>
       </c>
       <c r="O288" s="33">
@@ -25414,7 +25410,7 @@
       <c r="M289" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N289" s="34">
+      <c r="N289" s="38">
         <v>32997</v>
       </c>
       <c r="O289" s="33">
@@ -25482,7 +25478,7 @@
       <c r="M290" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N290" s="34">
+      <c r="N290" s="38">
         <v>31676</v>
       </c>
       <c r="O290" s="33">
@@ -25550,7 +25546,7 @@
       <c r="M291" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N291" s="34">
+      <c r="N291" s="38">
         <v>31339</v>
       </c>
       <c r="O291" s="33">
@@ -25618,7 +25614,7 @@
       <c r="M292" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N292" s="34">
+      <c r="N292" s="38">
         <v>32777</v>
       </c>
       <c r="O292" s="33">
@@ -25686,7 +25682,7 @@
       <c r="M293" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N293" s="34">
+      <c r="N293" s="38">
         <v>31180</v>
       </c>
       <c r="O293" s="33">
@@ -25754,7 +25750,7 @@
       <c r="M294" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N294" s="34">
+      <c r="N294" s="38">
         <v>30374</v>
       </c>
       <c r="O294" s="33">
@@ -25822,7 +25818,7 @@
       <c r="M295" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N295" s="34">
+      <c r="N295" s="38">
         <v>30231</v>
       </c>
       <c r="O295" s="33">
@@ -25890,7 +25886,7 @@
       <c r="M296" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N296" s="34">
+      <c r="N296" s="38">
         <v>33173</v>
       </c>
       <c r="O296" s="33">
@@ -25958,7 +25954,7 @@
       <c r="M297" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N297" s="34">
+      <c r="N297" s="38">
         <v>31455</v>
       </c>
       <c r="O297" s="33">
@@ -26026,7 +26022,7 @@
       <c r="M298" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N298" s="34">
+      <c r="N298" s="38">
         <v>30207</v>
       </c>
       <c r="O298" s="33">
@@ -26094,7 +26090,7 @@
       <c r="M299" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N299" s="34">
+      <c r="N299" s="38">
         <v>32222</v>
       </c>
       <c r="O299" s="33">
@@ -26162,7 +26158,7 @@
       <c r="M300" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N300" s="34">
+      <c r="N300" s="38">
         <v>31854</v>
       </c>
       <c r="O300" s="33">
@@ -26230,7 +26226,7 @@
       <c r="M301" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N301" s="34">
+      <c r="N301" s="38">
         <v>32710</v>
       </c>
       <c r="O301" s="33">
@@ -26298,7 +26294,7 @@
       <c r="M302" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N302" s="34">
+      <c r="N302" s="38">
         <v>28096</v>
       </c>
       <c r="O302" s="33">
@@ -26366,7 +26362,7 @@
       <c r="M303" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N303" s="34">
+      <c r="N303" s="38">
         <v>33012</v>
       </c>
       <c r="O303" s="33">
@@ -26434,7 +26430,7 @@
       <c r="M304" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N304" s="34">
+      <c r="N304" s="38">
         <v>30046</v>
       </c>
       <c r="O304" s="33">
@@ -26502,7 +26498,7 @@
       <c r="M305" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N305" s="34">
+      <c r="N305" s="38">
         <v>31845</v>
       </c>
       <c r="O305" s="33">
@@ -26570,7 +26566,7 @@
       <c r="M306" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N306" s="34">
+      <c r="N306" s="38">
         <v>33758</v>
       </c>
       <c r="O306" s="33">
@@ -26638,7 +26634,7 @@
       <c r="M307" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N307" s="34">
+      <c r="N307" s="38">
         <v>32589</v>
       </c>
       <c r="O307" s="33">
@@ -26706,7 +26702,7 @@
       <c r="M308" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N308" s="34">
+      <c r="N308" s="38">
         <v>32267</v>
       </c>
       <c r="O308" s="33">
@@ -26774,7 +26770,7 @@
       <c r="M309" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N309" s="34">
+      <c r="N309" s="38">
         <v>32321</v>
       </c>
       <c r="O309" s="33">
@@ -26842,7 +26838,7 @@
       <c r="M310" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N310" s="34">
+      <c r="N310" s="38">
         <v>27484</v>
       </c>
       <c r="O310" s="33">
@@ -26910,7 +26906,7 @@
       <c r="M311" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N311" s="34">
+      <c r="N311" s="38">
         <v>32087</v>
       </c>
       <c r="O311" s="33">
@@ -26978,7 +26974,7 @@
       <c r="M312" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N312" s="34">
+      <c r="N312" s="38">
         <v>30603</v>
       </c>
       <c r="O312" s="33">
@@ -27046,7 +27042,7 @@
       <c r="M313" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N313" s="34">
+      <c r="N313" s="38">
         <v>28997</v>
       </c>
       <c r="O313" s="33">
@@ -27114,7 +27110,7 @@
       <c r="M314" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N314" s="34">
+      <c r="N314" s="38">
         <v>33479</v>
       </c>
       <c r="O314" s="33">
@@ -27182,7 +27178,7 @@
       <c r="M315" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N315" s="34">
+      <c r="N315" s="38">
         <v>33486</v>
       </c>
       <c r="O315" s="33">
@@ -27250,7 +27246,7 @@
       <c r="M316" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N316" s="34">
+      <c r="N316" s="38">
         <v>33129</v>
       </c>
       <c r="O316" s="33">
@@ -27318,7 +27314,7 @@
       <c r="M317" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N317" s="34">
+      <c r="N317" s="38">
         <v>33854</v>
       </c>
       <c r="O317" s="33">
@@ -27386,7 +27382,7 @@
       <c r="M318" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N318" s="34">
+      <c r="N318" s="38">
         <v>33571</v>
       </c>
       <c r="O318" s="33">
@@ -27454,7 +27450,7 @@
       <c r="M319" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="N319" s="34">
+      <c r="N319" s="38">
         <v>29762</v>
       </c>
       <c r="O319" s="33">
@@ -27522,7 +27518,7 @@
       <c r="M320" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="N320" s="34">
+      <c r="N320" s="38">
         <v>29258</v>
       </c>
       <c r="O320" s="33">
@@ -27590,7 +27586,7 @@
       <c r="M321" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N321" s="34">
+      <c r="N321" s="38">
         <v>31379</v>
       </c>
       <c r="O321" s="33">
@@ -27658,7 +27654,7 @@
       <c r="M322" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N322" s="34">
+      <c r="N322" s="38">
         <v>30688</v>
       </c>
       <c r="O322" s="33">
@@ -27726,7 +27722,7 @@
       <c r="M323" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N323" s="34">
+      <c r="N323" s="38">
         <v>32203</v>
       </c>
       <c r="O323" s="33">
@@ -27794,7 +27790,7 @@
       <c r="M324" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N324" s="34">
+      <c r="N324" s="38">
         <v>34741</v>
       </c>
       <c r="O324" s="33">
@@ -27862,7 +27858,7 @@
       <c r="M325" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N325" s="34">
+      <c r="N325" s="38">
         <v>33610</v>
       </c>
       <c r="O325" s="33">
@@ -27930,7 +27926,7 @@
       <c r="M326" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N326" s="34">
+      <c r="N326" s="38">
         <v>34739</v>
       </c>
       <c r="O326" s="33">
@@ -27998,7 +27994,7 @@
       <c r="M327" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N327" s="34">
+      <c r="N327" s="38">
         <v>32817</v>
       </c>
       <c r="O327" s="33">
@@ -28066,7 +28062,7 @@
       <c r="M328" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N328" s="34">
+      <c r="N328" s="38">
         <v>33812</v>
       </c>
       <c r="O328" s="33">
@@ -28134,7 +28130,7 @@
       <c r="M329" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N329" s="34">
+      <c r="N329" s="38">
         <v>33701</v>
       </c>
       <c r="O329" s="33">
@@ -28202,7 +28198,7 @@
       <c r="M330" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N330" s="34">
+      <c r="N330" s="38">
         <v>33251</v>
       </c>
       <c r="O330" s="33">
@@ -28270,7 +28266,7 @@
       <c r="M331" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N331" s="34">
+      <c r="N331" s="38">
         <v>33896</v>
       </c>
       <c r="O331" s="33">
@@ -28338,7 +28334,7 @@
       <c r="M332" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N332" s="34">
+      <c r="N332" s="38">
         <v>34307</v>
       </c>
       <c r="O332" s="33">
@@ -28406,7 +28402,7 @@
       <c r="M333" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N333" s="34">
+      <c r="N333" s="38">
         <v>34270</v>
       </c>
       <c r="O333" s="33">
@@ -28474,7 +28470,7 @@
       <c r="M334" s="32" t="s">
         <v>859</v>
       </c>
-      <c r="N334" s="34">
+      <c r="N334" s="38">
         <v>29301</v>
       </c>
       <c r="O334" s="33">
@@ -28542,7 +28538,7 @@
       <c r="M335" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N335" s="34">
+      <c r="N335" s="38">
         <v>34269</v>
       </c>
       <c r="O335" s="33">
@@ -28610,7 +28606,7 @@
       <c r="M336" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N336" s="34">
+      <c r="N336" s="38">
         <v>33229</v>
       </c>
       <c r="O336" s="33">
@@ -28678,7 +28674,7 @@
       <c r="M337" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N337" s="34">
+      <c r="N337" s="38">
         <v>32436</v>
       </c>
       <c r="O337" s="33">
@@ -28746,7 +28742,7 @@
       <c r="M338" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N338" s="34">
+      <c r="N338" s="38">
         <v>32289</v>
       </c>
       <c r="O338" s="33">
@@ -28814,7 +28810,7 @@
       <c r="M339" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N339" s="34">
+      <c r="N339" s="38">
         <v>33780</v>
       </c>
       <c r="O339" s="33">
@@ -28882,7 +28878,7 @@
       <c r="M340" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N340" s="34">
+      <c r="N340" s="38">
         <v>32880</v>
       </c>
       <c r="O340" s="33">
@@ -28950,7 +28946,7 @@
       <c r="M341" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N341" s="34">
+      <c r="N341" s="38">
         <v>33809</v>
       </c>
       <c r="O341" s="33">
@@ -29018,7 +29014,7 @@
       <c r="M342" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N342" s="34">
+      <c r="N342" s="38">
         <v>35512</v>
       </c>
       <c r="O342" s="33">
@@ -29086,7 +29082,7 @@
       <c r="M343" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N343" s="34">
+      <c r="N343" s="38">
         <v>32660</v>
       </c>
       <c r="O343" s="33">
@@ -29154,7 +29150,7 @@
       <c r="M344" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N344" s="34">
+      <c r="N344" s="38">
         <v>30817</v>
       </c>
       <c r="O344" s="33">
@@ -29222,7 +29218,7 @@
       <c r="M345" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N345" s="34">
+      <c r="N345" s="38">
         <v>31941</v>
       </c>
       <c r="O345" s="33">
@@ -29290,7 +29286,7 @@
       <c r="M346" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N346" s="34">
+      <c r="N346" s="38">
         <v>32658</v>
       </c>
       <c r="O346" s="33">
@@ -29358,7 +29354,7 @@
       <c r="M347" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N347" s="34">
+      <c r="N347" s="38">
         <v>34968</v>
       </c>
       <c r="O347" s="33">
@@ -29426,7 +29422,7 @@
       <c r="M348" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N348" s="34">
+      <c r="N348" s="38">
         <v>32002</v>
       </c>
       <c r="O348" s="33">
@@ -29494,7 +29490,7 @@
       <c r="M349" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N349" s="34">
+      <c r="N349" s="38">
         <v>33888</v>
       </c>
       <c r="O349" s="33">
@@ -29562,7 +29558,7 @@
       <c r="M350" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N350" s="34">
+      <c r="N350" s="38">
         <v>26760</v>
       </c>
       <c r="O350" s="33">
@@ -29630,7 +29626,7 @@
       <c r="M351" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N351" s="34">
+      <c r="N351" s="38">
         <v>29570</v>
       </c>
       <c r="O351" s="33">
@@ -29698,7 +29694,7 @@
       <c r="M352" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N352" s="34">
+      <c r="N352" s="38">
         <v>30159</v>
       </c>
       <c r="O352" s="33">
@@ -29766,7 +29762,7 @@
       <c r="M353" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N353" s="34">
+      <c r="N353" s="38">
         <v>34797</v>
       </c>
       <c r="O353" s="33">
@@ -29834,7 +29830,7 @@
       <c r="M354" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N354" s="34">
+      <c r="N354" s="38">
         <v>33578</v>
       </c>
       <c r="O354" s="33">
@@ -29902,7 +29898,7 @@
       <c r="M355" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N355" s="34">
+      <c r="N355" s="38">
         <v>34276</v>
       </c>
       <c r="O355" s="33">
@@ -29970,7 +29966,7 @@
       <c r="M356" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N356" s="34">
+      <c r="N356" s="38">
         <v>34472</v>
       </c>
       <c r="O356" s="33">
@@ -30038,7 +30034,7 @@
       <c r="M357" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N357" s="34">
+      <c r="N357" s="38">
         <v>35132</v>
       </c>
       <c r="O357" s="33">
@@ -30106,7 +30102,7 @@
       <c r="M358" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N358" s="34">
+      <c r="N358" s="38">
         <v>32493</v>
       </c>
       <c r="O358" s="33">
@@ -30174,7 +30170,7 @@
       <c r="M359" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N359" s="34">
+      <c r="N359" s="38">
         <v>34324</v>
       </c>
       <c r="O359" s="33">
@@ -30242,7 +30238,7 @@
       <c r="M360" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N360" s="34">
+      <c r="N360" s="38">
         <v>28780</v>
       </c>
       <c r="O360" s="33">
@@ -30310,7 +30306,7 @@
       <c r="M361" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N361" s="34">
+      <c r="N361" s="38">
         <v>34388</v>
       </c>
       <c r="O361" s="33">
@@ -30378,7 +30374,7 @@
       <c r="M362" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N362" s="34">
+      <c r="N362" s="38">
         <v>31289</v>
       </c>
       <c r="O362" s="33">
@@ -30446,7 +30442,7 @@
       <c r="M363" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N363" s="34">
+      <c r="N363" s="38">
         <v>31331</v>
       </c>
       <c r="O363" s="33">
@@ -30514,7 +30510,7 @@
       <c r="M364" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N364" s="34">
+      <c r="N364" s="38">
         <v>34607</v>
       </c>
       <c r="O364" s="33">
@@ -30582,7 +30578,7 @@
       <c r="M365" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N365" s="34">
+      <c r="N365" s="38">
         <v>34934</v>
       </c>
       <c r="O365" s="33">
@@ -30650,7 +30646,7 @@
       <c r="M366" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N366" s="34">
+      <c r="N366" s="38">
         <v>31926</v>
       </c>
       <c r="O366" s="33">
@@ -30718,7 +30714,7 @@
       <c r="M367" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N367" s="34">
+      <c r="N367" s="38">
         <v>32253</v>
       </c>
       <c r="O367" s="33">
@@ -30786,7 +30782,7 @@
       <c r="M368" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N368" s="34">
+      <c r="N368" s="38">
         <v>32074</v>
       </c>
       <c r="O368" s="33">
@@ -30854,7 +30850,7 @@
       <c r="M369" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N369" s="34">
+      <c r="N369" s="38">
         <v>30076</v>
       </c>
       <c r="O369" s="33">
@@ -30922,7 +30918,7 @@
       <c r="M370" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N370" s="34">
+      <c r="N370" s="38">
         <v>32409</v>
       </c>
       <c r="O370" s="33">
@@ -30990,7 +30986,7 @@
       <c r="M371" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N371" s="34">
+      <c r="N371" s="38">
         <v>35784</v>
       </c>
       <c r="O371" s="33">
@@ -31058,7 +31054,7 @@
       <c r="M372" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N372" s="34">
+      <c r="N372" s="38">
         <v>33190</v>
       </c>
       <c r="O372" s="33">
@@ -31126,7 +31122,7 @@
       <c r="M373" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N373" s="34">
+      <c r="N373" s="38">
         <v>32609</v>
       </c>
       <c r="O373" s="33">
@@ -31194,7 +31190,7 @@
       <c r="M374" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N374" s="34">
+      <c r="N374" s="38">
         <v>27199</v>
       </c>
       <c r="O374" s="33">
@@ -31262,7 +31258,7 @@
       <c r="M375" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N375" s="34">
+      <c r="N375" s="38">
         <v>27808</v>
       </c>
       <c r="O375" s="33">
@@ -31330,7 +31326,7 @@
       <c r="M376" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N376" s="34">
+      <c r="N376" s="38">
         <v>27925</v>
       </c>
       <c r="O376" s="33">
@@ -31398,7 +31394,7 @@
       <c r="M377" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N377" s="34">
+      <c r="N377" s="38">
         <v>33612</v>
       </c>
       <c r="O377" s="33">
@@ -31466,7 +31462,7 @@
       <c r="M378" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N378" s="34">
+      <c r="N378" s="38">
         <v>35096</v>
       </c>
       <c r="O378" s="33">
@@ -31534,7 +31530,7 @@
       <c r="M379" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N379" s="34">
+      <c r="N379" s="38">
         <v>34702</v>
       </c>
       <c r="O379" s="33">
@@ -31602,7 +31598,7 @@
       <c r="M380" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N380" s="34">
+      <c r="N380" s="38">
         <v>34709</v>
       </c>
       <c r="O380" s="33">
@@ -31670,7 +31666,7 @@
       <c r="M381" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N381" s="34">
+      <c r="N381" s="38">
         <v>30386</v>
       </c>
       <c r="O381" s="33">
@@ -31738,7 +31734,7 @@
       <c r="M382" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N382" s="34">
+      <c r="N382" s="38">
         <v>30209</v>
       </c>
       <c r="O382" s="33">
@@ -31806,7 +31802,7 @@
       <c r="M383" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N383" s="34">
+      <c r="N383" s="38">
         <v>31988</v>
       </c>
       <c r="O383" s="33">
@@ -31874,7 +31870,7 @@
       <c r="M384" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N384" s="34">
+      <c r="N384" s="38">
         <v>35937</v>
       </c>
       <c r="O384" s="33">
@@ -31942,7 +31938,7 @@
       <c r="M385" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N385" s="34">
+      <c r="N385" s="38">
         <v>34544</v>
       </c>
       <c r="O385" s="33">
@@ -32010,7 +32006,7 @@
       <c r="M386" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N386" s="34">
+      <c r="N386" s="38">
         <v>33705</v>
       </c>
       <c r="O386" s="33">
@@ -32078,7 +32074,7 @@
       <c r="M387" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N387" s="34">
+      <c r="N387" s="38">
         <v>29578</v>
       </c>
       <c r="O387" s="33">
@@ -32146,7 +32142,7 @@
       <c r="M388" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N388" s="34">
+      <c r="N388" s="38">
         <v>34194</v>
       </c>
       <c r="O388" s="33">
@@ -32214,7 +32210,7 @@
       <c r="M389" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N389" s="34">
+      <c r="N389" s="38">
         <v>33806</v>
       </c>
       <c r="O389" s="33">
@@ -32282,7 +32278,7 @@
       <c r="M390" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N390" s="34">
+      <c r="N390" s="38">
         <v>34239</v>
       </c>
       <c r="O390" s="33">
@@ -32350,7 +32346,7 @@
       <c r="M391" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N391" s="34">
+      <c r="N391" s="38">
         <v>29987</v>
       </c>
       <c r="O391" s="33">
@@ -32418,7 +32414,7 @@
       <c r="M392" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N392" s="34">
+      <c r="N392" s="38">
         <v>29803</v>
       </c>
       <c r="O392" s="33">
@@ -32486,7 +32482,7 @@
       <c r="M393" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="N393" s="34">
+      <c r="N393" s="38">
         <v>32736</v>
       </c>
       <c r="O393" s="33">
@@ -32554,7 +32550,7 @@
       <c r="M394" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N394" s="34">
+      <c r="N394" s="38">
         <v>33425</v>
       </c>
       <c r="O394" s="33">
@@ -32622,7 +32618,7 @@
       <c r="M395" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N395" s="34">
+      <c r="N395" s="38">
         <v>32240</v>
       </c>
       <c r="O395" s="33">
@@ -32690,7 +32686,7 @@
       <c r="M396" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N396" s="34">
+      <c r="N396" s="38">
         <v>36640</v>
       </c>
       <c r="O396" s="33">
@@ -32758,7 +32754,7 @@
       <c r="M397" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N397" s="34">
+      <c r="N397" s="38">
         <v>34434</v>
       </c>
       <c r="O397" s="33">
@@ -32826,7 +32822,7 @@
       <c r="M398" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N398" s="34">
+      <c r="N398" s="38">
         <v>32696</v>
       </c>
       <c r="O398" s="33">
@@ -32894,7 +32890,7 @@
       <c r="M399" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N399" s="34">
+      <c r="N399" s="38">
         <v>33866</v>
       </c>
       <c r="O399" s="33">
@@ -32962,7 +32958,7 @@
       <c r="M400" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N400" s="34">
+      <c r="N400" s="38">
         <v>35055</v>
       </c>
       <c r="O400" s="33">
@@ -33030,7 +33026,7 @@
       <c r="M401" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="N401" s="34">
+      <c r="N401" s="38">
         <v>28073</v>
       </c>
       <c r="O401" s="33">
@@ -33098,7 +33094,7 @@
       <c r="M402" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N402" s="34">
+      <c r="N402" s="38">
         <v>33862</v>
       </c>
       <c r="O402" s="33">
@@ -33166,7 +33162,7 @@
       <c r="M403" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N403" s="34">
+      <c r="N403" s="38">
         <v>30238</v>
       </c>
       <c r="O403" s="33">
@@ -33234,7 +33230,7 @@
       <c r="M404" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N404" s="34">
+      <c r="N404" s="38">
         <v>29813</v>
       </c>
       <c r="O404" s="33">
@@ -33302,7 +33298,7 @@
       <c r="M405" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N405" s="34">
+      <c r="N405" s="38">
         <v>26994</v>
       </c>
       <c r="O405" s="33">
@@ -33370,7 +33366,7 @@
       <c r="M406" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N406" s="34">
+      <c r="N406" s="38">
         <v>34771</v>
       </c>
       <c r="O406" s="33">
@@ -33438,7 +33434,7 @@
       <c r="M407" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N407" s="34">
+      <c r="N407" s="38">
         <v>34336</v>
       </c>
       <c r="O407" s="33">
@@ -33506,7 +33502,7 @@
       <c r="M408" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N408" s="34">
+      <c r="N408" s="38">
         <v>35865</v>
       </c>
       <c r="O408" s="33">
@@ -33574,7 +33570,7 @@
       <c r="M409" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N409" s="34">
+      <c r="N409" s="38">
         <v>33143</v>
       </c>
       <c r="O409" s="33">
@@ -33642,7 +33638,7 @@
       <c r="M410" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N410" s="34">
+      <c r="N410" s="38">
         <v>31973</v>
       </c>
       <c r="O410" s="33">
@@ -33710,7 +33706,7 @@
       <c r="M411" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N411" s="34">
+      <c r="N411" s="38">
         <v>27704</v>
       </c>
       <c r="O411" s="33">
@@ -33778,7 +33774,7 @@
       <c r="M412" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N412" s="34">
+      <c r="N412" s="38">
         <v>28549</v>
       </c>
       <c r="O412" s="33">
@@ -33846,7 +33842,7 @@
       <c r="M413" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N413" s="34">
+      <c r="N413" s="38">
         <v>32815</v>
       </c>
       <c r="O413" s="33">
@@ -33914,7 +33910,7 @@
       <c r="M414" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N414" s="34">
+      <c r="N414" s="38">
         <v>30411</v>
       </c>
       <c r="O414" s="33">
@@ -33982,7 +33978,7 @@
       <c r="M415" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N415" s="34">
+      <c r="N415" s="38">
         <v>26997</v>
       </c>
       <c r="O415" s="33">
@@ -34050,7 +34046,7 @@
       <c r="M416" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N416" s="34">
+      <c r="N416" s="38">
         <v>32420</v>
       </c>
       <c r="O416" s="33">
@@ -34118,7 +34114,7 @@
       <c r="M417" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N417" s="34">
+      <c r="N417" s="38">
         <v>32856</v>
       </c>
       <c r="O417" s="33">
@@ -34186,7 +34182,7 @@
       <c r="M418" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N418" s="34">
+      <c r="N418" s="38">
         <v>36166</v>
       </c>
       <c r="O418" s="33">
@@ -34256,7 +34252,7 @@
       <c r="M419" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N419" s="34">
+      <c r="N419" s="38">
         <v>35781</v>
       </c>
       <c r="O419" s="33">
@@ -34324,7 +34320,7 @@
       <c r="M420" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N420" s="34">
+      <c r="N420" s="38">
         <v>28243</v>
       </c>
       <c r="O420" s="33">
@@ -34392,7 +34388,7 @@
       <c r="M421" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N421" s="34">
+      <c r="N421" s="38">
         <v>33560</v>
       </c>
       <c r="O421" s="33">
@@ -34460,7 +34456,7 @@
       <c r="M422" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N422" s="34">
+      <c r="N422" s="38">
         <v>36112</v>
       </c>
       <c r="O422" s="33">
@@ -34528,7 +34524,7 @@
       <c r="M423" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N423" s="34">
+      <c r="N423" s="38">
         <v>35178</v>
       </c>
       <c r="O423" s="33">
@@ -34596,7 +34592,7 @@
       <c r="M424" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N424" s="34">
+      <c r="N424" s="38">
         <v>35563</v>
       </c>
       <c r="O424" s="33">
@@ -34664,7 +34660,7 @@
       <c r="M425" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N425" s="34">
+      <c r="N425" s="38">
         <v>34085</v>
       </c>
       <c r="O425" s="33">
@@ -34732,7 +34728,7 @@
       <c r="M426" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N426" s="34">
+      <c r="N426" s="38">
         <v>34275</v>
       </c>
       <c r="O426" s="33">
@@ -34800,7 +34796,7 @@
       <c r="M427" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N427" s="34">
+      <c r="N427" s="38">
         <v>30256</v>
       </c>
       <c r="O427" s="33">
@@ -34868,7 +34864,7 @@
       <c r="M428" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N428" s="34">
+      <c r="N428" s="38">
         <v>28531</v>
       </c>
       <c r="O428" s="33">
@@ -34936,7 +34932,7 @@
       <c r="M429" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N429" s="34">
+      <c r="N429" s="38">
         <v>34307</v>
       </c>
       <c r="O429" s="33">
@@ -35004,7 +35000,7 @@
       <c r="M430" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N430" s="34">
+      <c r="N430" s="38">
         <v>24782</v>
       </c>
       <c r="O430" s="33">
@@ -35072,7 +35068,7 @@
       <c r="M431" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N431" s="34">
+      <c r="N431" s="38">
         <v>35973</v>
       </c>
       <c r="O431" s="33">
@@ -35140,7 +35136,7 @@
       <c r="M432" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N432" s="34">
+      <c r="N432" s="38">
         <v>34323</v>
       </c>
       <c r="O432" s="33">
@@ -35210,7 +35206,7 @@
       <c r="M433" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N433" s="34">
+      <c r="N433" s="38">
         <v>37046</v>
       </c>
       <c r="O433" s="33">
@@ -35280,7 +35276,7 @@
       <c r="M434" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N434" s="34">
+      <c r="N434" s="38">
         <v>33361</v>
       </c>
       <c r="O434" s="33">
@@ -35350,7 +35346,7 @@
       <c r="M435" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N435" s="34">
+      <c r="N435" s="38">
         <v>35165</v>
       </c>
       <c r="O435" s="33">
@@ -35420,7 +35416,7 @@
       <c r="M436" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N436" s="34">
+      <c r="N436" s="38">
         <v>35308</v>
       </c>
       <c r="O436" s="33">
@@ -35490,7 +35486,7 @@
       <c r="M437" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N437" s="34">
+      <c r="N437" s="38">
         <v>34753</v>
       </c>
       <c r="O437" s="33">
@@ -35560,7 +35556,7 @@
       <c r="M438" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N438" s="34">
+      <c r="N438" s="38">
         <v>34693</v>
       </c>
       <c r="O438" s="33">
@@ -35628,7 +35624,7 @@
       <c r="M439" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N439" s="34">
+      <c r="N439" s="38">
         <v>33097</v>
       </c>
       <c r="O439" s="33">
@@ -35696,7 +35692,7 @@
       <c r="M440" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N440" s="34">
+      <c r="N440" s="38">
         <v>33846</v>
       </c>
       <c r="O440" s="33">
@@ -35766,7 +35762,7 @@
       <c r="M441" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N441" s="34">
+      <c r="N441" s="38">
         <v>38113</v>
       </c>
       <c r="O441" s="33">
@@ -35836,7 +35832,7 @@
       <c r="M442" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N442" s="34">
+      <c r="N442" s="38">
         <v>36384</v>
       </c>
       <c r="O442" s="33">
@@ -35906,7 +35902,7 @@
       <c r="M443" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N443" s="34">
+      <c r="N443" s="38">
         <v>35738</v>
       </c>
       <c r="O443" s="33">
@@ -35976,7 +35972,7 @@
       <c r="M444" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N444" s="34">
+      <c r="N444" s="38">
         <v>29218</v>
       </c>
       <c r="O444" s="33">
@@ -36044,7 +36040,7 @@
       <c r="M445" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N445" s="34">
+      <c r="N445" s="38">
         <v>36692</v>
       </c>
       <c r="O445" s="33">
@@ -36114,7 +36110,7 @@
       <c r="M446" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N446" s="34">
+      <c r="N446" s="38">
         <v>37199</v>
       </c>
       <c r="O446" s="33">
@@ -36184,7 +36180,7 @@
       <c r="M447" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N447" s="34">
+      <c r="N447" s="38">
         <v>33432</v>
       </c>
       <c r="O447" s="33">
@@ -36254,7 +36250,7 @@
       <c r="M448" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N448" s="34">
+      <c r="N448" s="38">
         <v>31140</v>
       </c>
       <c r="O448" s="33">
@@ -36324,7 +36320,7 @@
       <c r="M449" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N449" s="34">
+      <c r="N449" s="38">
         <v>33332</v>
       </c>
       <c r="O449" s="33">
@@ -46769,7 +46765,7 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="V449" r:id="rId1" xr:uid="{B2086A4E-C0B7-47F9-8ED2-BE4CA433A8EC}"/>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baray020\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F959F0-150A-49C0-B3D4-6F32185EB77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E03D7DC-0641-42EF-97F2-85705711621C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="1740" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dotaci" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7900" uniqueCount="1687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7928" uniqueCount="1692">
   <si>
     <t>HENRIQUEZ POOL FELIPE ALBERTO</t>
   </si>
@@ -4858,9 +4858,6 @@
     <t>MENESES ARRIAGADA FERNANDO ADO</t>
   </si>
   <si>
-    <t>Medicina Curativa</t>
-  </si>
-  <si>
     <t>SEPULVEDA REINOSO ISAIAS PATRI</t>
   </si>
   <si>
@@ -4870,9 +4867,6 @@
     <t>AGUILERA VIDELA EFRAIN DEL CAR</t>
   </si>
   <si>
-    <t>HIDALGO MIRANDA MANUEL ALEJAND</t>
-  </si>
-  <si>
     <t>Enero</t>
   </si>
   <si>
@@ -4996,9 +4990,6 @@
     <t xml:space="preserve">Traumatología </t>
   </si>
   <si>
-    <t>Nueva</t>
-  </si>
-  <si>
     <t>VASQUEZ MARTINEZ CAMILO ANTONIO</t>
   </si>
   <si>
@@ -5102,6 +5093,30 @@
   </si>
   <si>
     <t>Concepción</t>
+  </si>
+  <si>
+    <t>Medicina Curatica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continuación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CirugíaVascular Periférica </t>
+  </si>
+  <si>
+    <t>CARVAJAL DIAZ ORIANA DEL CARME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psiquiatría </t>
+  </si>
+  <si>
+    <t>Medicina General</t>
+  </si>
+  <si>
+    <t>TORRES OSORIO CRISTOPHER NICOL</t>
   </si>
 </sst>
 </file>
@@ -5109,7 +5124,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mmm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mmm/yyyy"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -5419,13 +5434,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -5894,7 +5909,7 @@
       <c r="M2" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="38">
+      <c r="N2" s="36">
         <v>25338</v>
       </c>
       <c r="O2" s="33">
@@ -5962,7 +5977,7 @@
       <c r="M3" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="38">
+      <c r="N3" s="36">
         <v>22455</v>
       </c>
       <c r="O3" s="33">
@@ -6030,7 +6045,7 @@
       <c r="M4" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="36">
         <v>22344</v>
       </c>
       <c r="O4" s="33">
@@ -6098,7 +6113,7 @@
       <c r="M5" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N5" s="38">
+      <c r="N5" s="36">
         <v>23037</v>
       </c>
       <c r="O5" s="33">
@@ -6166,7 +6181,7 @@
       <c r="M6" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="38">
+      <c r="N6" s="36">
         <v>25711</v>
       </c>
       <c r="O6" s="33">
@@ -6234,7 +6249,7 @@
       <c r="M7" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N7" s="38">
+      <c r="N7" s="36">
         <v>23650</v>
       </c>
       <c r="O7" s="33">
@@ -6302,7 +6317,7 @@
       <c r="M8" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="38">
+      <c r="N8" s="36">
         <v>24734</v>
       </c>
       <c r="O8" s="33">
@@ -6370,7 +6385,7 @@
       <c r="M9" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N9" s="38">
+      <c r="N9" s="36">
         <v>24962</v>
       </c>
       <c r="O9" s="33">
@@ -6438,7 +6453,7 @@
       <c r="M10" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N10" s="38">
+      <c r="N10" s="36">
         <v>24375</v>
       </c>
       <c r="O10" s="33">
@@ -6506,7 +6521,7 @@
       <c r="M11" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N11" s="38">
+      <c r="N11" s="36">
         <v>23403</v>
       </c>
       <c r="O11" s="33">
@@ -6574,7 +6589,7 @@
       <c r="M12" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N12" s="38">
+      <c r="N12" s="36">
         <v>23870</v>
       </c>
       <c r="O12" s="33">
@@ -6642,7 +6657,7 @@
       <c r="M13" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N13" s="38">
+      <c r="N13" s="36">
         <v>25084</v>
       </c>
       <c r="O13" s="33">
@@ -6710,7 +6725,7 @@
       <c r="M14" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N14" s="38">
+      <c r="N14" s="36">
         <v>24618</v>
       </c>
       <c r="O14" s="33">
@@ -6778,7 +6793,7 @@
       <c r="M15" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N15" s="38">
+      <c r="N15" s="36">
         <v>25597</v>
       </c>
       <c r="O15" s="33">
@@ -6846,7 +6861,7 @@
       <c r="M16" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="38">
+      <c r="N16" s="36">
         <v>25198</v>
       </c>
       <c r="O16" s="33">
@@ -6914,7 +6929,7 @@
       <c r="M17" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N17" s="38">
+      <c r="N17" s="36">
         <v>25317</v>
       </c>
       <c r="O17" s="33">
@@ -6982,7 +6997,7 @@
       <c r="M18" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N18" s="38">
+      <c r="N18" s="36">
         <v>24047</v>
       </c>
       <c r="O18" s="33">
@@ -7050,7 +7065,7 @@
       <c r="M19" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N19" s="38">
+      <c r="N19" s="36">
         <v>23901</v>
       </c>
       <c r="O19" s="33">
@@ -7118,7 +7133,7 @@
       <c r="M20" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N20" s="38">
+      <c r="N20" s="36">
         <v>25072</v>
       </c>
       <c r="O20" s="33">
@@ -7186,7 +7201,7 @@
       <c r="M21" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N21" s="38">
+      <c r="N21" s="36">
         <v>24100</v>
       </c>
       <c r="O21" s="33">
@@ -7254,7 +7269,7 @@
       <c r="M22" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N22" s="38">
+      <c r="N22" s="36">
         <v>24544</v>
       </c>
       <c r="O22" s="33">
@@ -7322,7 +7337,7 @@
       <c r="M23" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N23" s="38">
+      <c r="N23" s="36">
         <v>25818</v>
       </c>
       <c r="O23" s="33">
@@ -7390,7 +7405,7 @@
       <c r="M24" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N24" s="38">
+      <c r="N24" s="36">
         <v>25286</v>
       </c>
       <c r="O24" s="33">
@@ -7458,7 +7473,7 @@
       <c r="M25" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N25" s="38">
+      <c r="N25" s="36">
         <v>24587</v>
       </c>
       <c r="O25" s="33">
@@ -7526,7 +7541,7 @@
       <c r="M26" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N26" s="38">
+      <c r="N26" s="36">
         <v>25370</v>
       </c>
       <c r="O26" s="33">
@@ -7594,7 +7609,7 @@
       <c r="M27" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N27" s="38">
+      <c r="N27" s="36">
         <v>25053</v>
       </c>
       <c r="O27" s="33">
@@ -7662,7 +7677,7 @@
       <c r="M28" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N28" s="38">
+      <c r="N28" s="36">
         <v>24907</v>
       </c>
       <c r="O28" s="33">
@@ -7730,7 +7745,7 @@
       <c r="M29" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N29" s="38">
+      <c r="N29" s="36">
         <v>25224</v>
       </c>
       <c r="O29" s="33">
@@ -7798,7 +7813,7 @@
       <c r="M30" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N30" s="38">
+      <c r="N30" s="36">
         <v>25487</v>
       </c>
       <c r="O30" s="33">
@@ -7866,7 +7881,7 @@
       <c r="M31" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="38">
+      <c r="N31" s="36">
         <v>25489</v>
       </c>
       <c r="O31" s="33">
@@ -7934,7 +7949,7 @@
       <c r="M32" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N32" s="38">
+      <c r="N32" s="36">
         <v>25397</v>
       </c>
       <c r="O32" s="33">
@@ -8002,7 +8017,7 @@
       <c r="M33" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N33" s="38">
+      <c r="N33" s="36">
         <v>25565</v>
       </c>
       <c r="O33" s="33">
@@ -8070,7 +8085,7 @@
       <c r="M34" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N34" s="38">
+      <c r="N34" s="36">
         <v>26069</v>
       </c>
       <c r="O34" s="33">
@@ -8138,7 +8153,7 @@
       <c r="M35" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N35" s="38">
+      <c r="N35" s="36">
         <v>26156</v>
       </c>
       <c r="O35" s="33">
@@ -8206,7 +8221,7 @@
       <c r="M36" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N36" s="38">
+      <c r="N36" s="36">
         <v>26106</v>
       </c>
       <c r="O36" s="33">
@@ -8274,7 +8289,7 @@
       <c r="M37" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N37" s="38">
+      <c r="N37" s="36">
         <v>26449</v>
       </c>
       <c r="O37" s="33">
@@ -8342,7 +8357,7 @@
       <c r="M38" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N38" s="38">
+      <c r="N38" s="36">
         <v>26588</v>
       </c>
       <c r="O38" s="33">
@@ -8410,7 +8425,7 @@
       <c r="M39" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N39" s="38">
+      <c r="N39" s="36">
         <v>25154</v>
       </c>
       <c r="O39" s="33">
@@ -8478,7 +8493,7 @@
       <c r="M40" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N40" s="38">
+      <c r="N40" s="36">
         <v>25469</v>
       </c>
       <c r="O40" s="33">
@@ -8546,7 +8561,7 @@
       <c r="M41" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N41" s="38">
+      <c r="N41" s="36">
         <v>25104</v>
       </c>
       <c r="O41" s="33">
@@ -8614,7 +8629,7 @@
       <c r="M42" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N42" s="38">
+      <c r="N42" s="36">
         <v>25368</v>
       </c>
       <c r="O42" s="33">
@@ -8682,7 +8697,7 @@
       <c r="M43" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N43" s="38">
+      <c r="N43" s="36">
         <v>25780</v>
       </c>
       <c r="O43" s="33">
@@ -8750,7 +8765,7 @@
       <c r="M44" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N44" s="38">
+      <c r="N44" s="36">
         <v>26872</v>
       </c>
       <c r="O44" s="33">
@@ -8818,7 +8833,7 @@
       <c r="M45" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N45" s="38">
+      <c r="N45" s="36">
         <v>26528</v>
       </c>
       <c r="O45" s="33">
@@ -8886,7 +8901,7 @@
       <c r="M46" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N46" s="38">
+      <c r="N46" s="36">
         <v>26315</v>
       </c>
       <c r="O46" s="33">
@@ -8954,7 +8969,7 @@
       <c r="M47" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N47" s="38">
+      <c r="N47" s="36">
         <v>26625</v>
       </c>
       <c r="O47" s="33">
@@ -9022,7 +9037,7 @@
       <c r="M48" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N48" s="38">
+      <c r="N48" s="36">
         <v>26537</v>
       </c>
       <c r="O48" s="33">
@@ -9090,7 +9105,7 @@
       <c r="M49" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N49" s="38">
+      <c r="N49" s="36">
         <v>26442</v>
       </c>
       <c r="O49" s="33">
@@ -9158,7 +9173,7 @@
       <c r="M50" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N50" s="38">
+      <c r="N50" s="36">
         <v>26599</v>
       </c>
       <c r="O50" s="33">
@@ -9226,7 +9241,7 @@
       <c r="M51" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N51" s="38">
+      <c r="N51" s="36">
         <v>26950</v>
       </c>
       <c r="O51" s="33">
@@ -9294,7 +9309,7 @@
       <c r="M52" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N52" s="38">
+      <c r="N52" s="36">
         <v>26695</v>
       </c>
       <c r="O52" s="33">
@@ -9362,7 +9377,7 @@
       <c r="M53" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N53" s="38">
+      <c r="N53" s="36">
         <v>26760</v>
       </c>
       <c r="O53" s="33">
@@ -9430,7 +9445,7 @@
       <c r="M54" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N54" s="38">
+      <c r="N54" s="36">
         <v>26871</v>
       </c>
       <c r="O54" s="33">
@@ -9498,7 +9513,7 @@
       <c r="M55" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N55" s="38">
+      <c r="N55" s="36">
         <v>27322</v>
       </c>
       <c r="O55" s="33">
@@ -9566,7 +9581,7 @@
       <c r="M56" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N56" s="38">
+      <c r="N56" s="36">
         <v>27117</v>
       </c>
       <c r="O56" s="33">
@@ -9634,7 +9649,7 @@
       <c r="M57" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N57" s="38">
+      <c r="N57" s="36">
         <v>27668</v>
       </c>
       <c r="O57" s="33">
@@ -9702,7 +9717,7 @@
       <c r="M58" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N58" s="38">
+      <c r="N58" s="36">
         <v>27729</v>
       </c>
       <c r="O58" s="33">
@@ -9770,7 +9785,7 @@
       <c r="M59" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N59" s="38">
+      <c r="N59" s="36">
         <v>28089</v>
       </c>
       <c r="O59" s="33">
@@ -9838,7 +9853,7 @@
       <c r="M60" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N60" s="38">
+      <c r="N60" s="36">
         <v>28713</v>
       </c>
       <c r="O60" s="33">
@@ -9906,7 +9921,7 @@
       <c r="M61" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N61" s="38">
+      <c r="N61" s="36">
         <v>28719</v>
       </c>
       <c r="O61" s="33">
@@ -9974,7 +9989,7 @@
       <c r="M62" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N62" s="38">
+      <c r="N62" s="36">
         <v>28514</v>
       </c>
       <c r="O62" s="33">
@@ -10042,7 +10057,7 @@
       <c r="M63" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N63" s="38">
+      <c r="N63" s="36">
         <v>28521</v>
       </c>
       <c r="O63" s="33">
@@ -10110,7 +10125,7 @@
       <c r="M64" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N64" s="38">
+      <c r="N64" s="36">
         <v>29086</v>
       </c>
       <c r="O64" s="33">
@@ -10178,7 +10193,7 @@
       <c r="M65" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N65" s="38">
+      <c r="N65" s="36">
         <v>29321</v>
       </c>
       <c r="O65" s="33">
@@ -10246,7 +10261,7 @@
       <c r="M66" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N66" s="38">
+      <c r="N66" s="36">
         <v>29301</v>
       </c>
       <c r="O66" s="33">
@@ -10314,7 +10329,7 @@
       <c r="M67" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N67" s="38">
+      <c r="N67" s="36">
         <v>27178</v>
       </c>
       <c r="O67" s="33">
@@ -10382,7 +10397,7 @@
       <c r="M68" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N68" s="38">
+      <c r="N68" s="36">
         <v>25323</v>
       </c>
       <c r="O68" s="33">
@@ -10450,7 +10465,7 @@
       <c r="M69" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N69" s="38">
+      <c r="N69" s="36">
         <v>27211</v>
       </c>
       <c r="O69" s="33">
@@ -10518,7 +10533,7 @@
       <c r="M70" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="N70" s="38">
+      <c r="N70" s="36">
         <v>26769</v>
       </c>
       <c r="O70" s="33">
@@ -10586,7 +10601,7 @@
       <c r="M71" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N71" s="38">
+      <c r="N71" s="36">
         <v>26884</v>
       </c>
       <c r="O71" s="33">
@@ -10654,7 +10669,7 @@
       <c r="M72" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N72" s="38">
+      <c r="N72" s="36">
         <v>27510</v>
       </c>
       <c r="O72" s="33">
@@ -10722,7 +10737,7 @@
       <c r="M73" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N73" s="38">
+      <c r="N73" s="36">
         <v>30549</v>
       </c>
       <c r="O73" s="33">
@@ -10790,7 +10805,7 @@
       <c r="M74" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N74" s="38">
+      <c r="N74" s="36">
         <v>30782</v>
       </c>
       <c r="O74" s="33">
@@ -10858,7 +10873,7 @@
       <c r="M75" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N75" s="38">
+      <c r="N75" s="36">
         <v>31303</v>
       </c>
       <c r="O75" s="33">
@@ -10926,7 +10941,7 @@
       <c r="M76" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N76" s="38">
+      <c r="N76" s="36">
         <v>25382</v>
       </c>
       <c r="O76" s="33">
@@ -10994,7 +11009,7 @@
       <c r="M77" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N77" s="38">
+      <c r="N77" s="36">
         <v>22396</v>
       </c>
       <c r="O77" s="33">
@@ -11062,7 +11077,7 @@
       <c r="M78" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N78" s="38">
+      <c r="N78" s="36">
         <v>23925</v>
       </c>
       <c r="O78" s="33">
@@ -11130,7 +11145,7 @@
       <c r="M79" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N79" s="38">
+      <c r="N79" s="36">
         <v>22229</v>
       </c>
       <c r="O79" s="33">
@@ -11198,7 +11213,7 @@
       <c r="M80" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N80" s="38">
+      <c r="N80" s="36">
         <v>22999</v>
       </c>
       <c r="O80" s="33">
@@ -11266,7 +11281,7 @@
       <c r="M81" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N81" s="38">
+      <c r="N81" s="36">
         <v>22521</v>
       </c>
       <c r="O81" s="33">
@@ -11334,7 +11349,7 @@
       <c r="M82" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N82" s="38">
+      <c r="N82" s="36">
         <v>22379</v>
       </c>
       <c r="O82" s="33">
@@ -11402,7 +11417,7 @@
       <c r="M83" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N83" s="38">
+      <c r="N83" s="36">
         <v>28892</v>
       </c>
       <c r="O83" s="33">
@@ -11470,7 +11485,7 @@
       <c r="M84" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N84" s="38">
+      <c r="N84" s="36">
         <v>22630</v>
       </c>
       <c r="O84" s="33">
@@ -11538,7 +11553,7 @@
       <c r="M85" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N85" s="38">
+      <c r="N85" s="36">
         <v>24460</v>
       </c>
       <c r="O85" s="33">
@@ -11606,7 +11621,7 @@
       <c r="M86" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N86" s="38">
+      <c r="N86" s="36">
         <v>24349</v>
       </c>
       <c r="O86" s="33">
@@ -11674,7 +11689,7 @@
       <c r="M87" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N87" s="38">
+      <c r="N87" s="36">
         <v>30609</v>
       </c>
       <c r="O87" s="33">
@@ -11742,7 +11757,7 @@
       <c r="M88" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N88" s="38">
+      <c r="N88" s="36">
         <v>27971</v>
       </c>
       <c r="O88" s="33">
@@ -11810,7 +11825,7 @@
       <c r="M89" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N89" s="38">
+      <c r="N89" s="36">
         <v>28617</v>
       </c>
       <c r="O89" s="33">
@@ -11878,7 +11893,7 @@
       <c r="M90" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N90" s="38">
+      <c r="N90" s="36">
         <v>25892</v>
       </c>
       <c r="O90" s="33">
@@ -11946,7 +11961,7 @@
       <c r="M91" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N91" s="38">
+      <c r="N91" s="36">
         <v>30111</v>
       </c>
       <c r="O91" s="33">
@@ -12014,7 +12029,7 @@
       <c r="M92" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N92" s="38">
+      <c r="N92" s="36">
         <v>26221</v>
       </c>
       <c r="O92" s="33">
@@ -12082,7 +12097,7 @@
       <c r="M93" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N93" s="38">
+      <c r="N93" s="36">
         <v>29493</v>
       </c>
       <c r="O93" s="33">
@@ -12150,7 +12165,7 @@
       <c r="M94" s="32" t="s">
         <v>310</v>
       </c>
-      <c r="N94" s="38">
+      <c r="N94" s="36">
         <v>30100</v>
       </c>
       <c r="O94" s="33">
@@ -12218,7 +12233,7 @@
       <c r="M95" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N95" s="38">
+      <c r="N95" s="36">
         <v>27811</v>
       </c>
       <c r="O95" s="33">
@@ -12286,7 +12301,7 @@
       <c r="M96" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N96" s="38">
+      <c r="N96" s="36">
         <v>32435</v>
       </c>
       <c r="O96" s="33">
@@ -12354,7 +12369,7 @@
       <c r="M97" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N97" s="38">
+      <c r="N97" s="36">
         <v>29693</v>
       </c>
       <c r="O97" s="33">
@@ -12422,7 +12437,7 @@
       <c r="M98" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N98" s="38">
+      <c r="N98" s="36">
         <v>27813</v>
       </c>
       <c r="O98" s="33">
@@ -12490,7 +12505,7 @@
       <c r="M99" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N99" s="38">
+      <c r="N99" s="36">
         <v>30391</v>
       </c>
       <c r="O99" s="33">
@@ -12558,7 +12573,7 @@
       <c r="M100" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N100" s="38">
+      <c r="N100" s="36">
         <v>31061</v>
       </c>
       <c r="O100" s="33">
@@ -12626,7 +12641,7 @@
       <c r="M101" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N101" s="38">
+      <c r="N101" s="36">
         <v>31313</v>
       </c>
       <c r="O101" s="33">
@@ -12694,7 +12709,7 @@
       <c r="M102" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N102" s="38">
+      <c r="N102" s="36">
         <v>31295</v>
       </c>
       <c r="O102" s="33">
@@ -12762,7 +12777,7 @@
       <c r="M103" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N103" s="38">
+      <c r="N103" s="36">
         <v>31493</v>
       </c>
       <c r="O103" s="33">
@@ -12830,7 +12845,7 @@
       <c r="M104" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N104" s="38">
+      <c r="N104" s="36">
         <v>27192</v>
       </c>
       <c r="O104" s="33">
@@ -12898,7 +12913,7 @@
       <c r="M105" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N105" s="38">
+      <c r="N105" s="36">
         <v>27628</v>
       </c>
       <c r="O105" s="33">
@@ -12966,7 +12981,7 @@
       <c r="M106" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N106" s="38">
+      <c r="N106" s="36">
         <v>27264</v>
       </c>
       <c r="O106" s="33">
@@ -13034,7 +13049,7 @@
       <c r="M107" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N107" s="38">
+      <c r="N107" s="36">
         <v>27770</v>
       </c>
       <c r="O107" s="33">
@@ -13102,7 +13117,7 @@
       <c r="M108" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N108" s="38">
+      <c r="N108" s="36">
         <v>28014</v>
       </c>
       <c r="O108" s="33">
@@ -13170,7 +13185,7 @@
       <c r="M109" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N109" s="38">
+      <c r="N109" s="36">
         <v>28170</v>
       </c>
       <c r="O109" s="33">
@@ -13238,7 +13253,7 @@
       <c r="M110" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N110" s="38">
+      <c r="N110" s="36">
         <v>26412</v>
       </c>
       <c r="O110" s="33">
@@ -13306,7 +13321,7 @@
       <c r="M111" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N111" s="38">
+      <c r="N111" s="36">
         <v>24988</v>
       </c>
       <c r="O111" s="33">
@@ -13374,7 +13389,7 @@
       <c r="M112" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N112" s="38">
+      <c r="N112" s="36">
         <v>27404</v>
       </c>
       <c r="O112" s="33">
@@ -13442,7 +13457,7 @@
       <c r="M113" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N113" s="38">
+      <c r="N113" s="36">
         <v>25124</v>
       </c>
       <c r="O113" s="33">
@@ -13510,7 +13525,7 @@
       <c r="M114" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N114" s="38">
+      <c r="N114" s="36">
         <v>26464</v>
       </c>
       <c r="O114" s="33">
@@ -13578,7 +13593,7 @@
       <c r="M115" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N115" s="38">
+      <c r="N115" s="36">
         <v>28459</v>
       </c>
       <c r="O115" s="33">
@@ -13646,7 +13661,7 @@
       <c r="M116" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N116" s="38">
+      <c r="N116" s="36">
         <v>26789</v>
       </c>
       <c r="O116" s="33">
@@ -13714,12 +13729,12 @@
       <c r="M117" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N117" s="38">
+      <c r="N117" s="36">
         <v>26868</v>
       </c>
       <c r="O117" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P117" s="35" t="str">
         <f t="shared" si="3"/>
@@ -13782,7 +13797,7 @@
       <c r="M118" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N118" s="38">
+      <c r="N118" s="36">
         <v>28020</v>
       </c>
       <c r="O118" s="33">
@@ -13850,7 +13865,7 @@
       <c r="M119" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N119" s="38">
+      <c r="N119" s="36">
         <v>22911</v>
       </c>
       <c r="O119" s="33">
@@ -13918,7 +13933,7 @@
       <c r="M120" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N120" s="38">
+      <c r="N120" s="36">
         <v>27844</v>
       </c>
       <c r="O120" s="33">
@@ -13986,7 +14001,7 @@
       <c r="M121" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N121" s="38">
+      <c r="N121" s="36">
         <v>27020</v>
       </c>
       <c r="O121" s="33">
@@ -14054,7 +14069,7 @@
       <c r="M122" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N122" s="38">
+      <c r="N122" s="36">
         <v>26591</v>
       </c>
       <c r="O122" s="33">
@@ -14122,7 +14137,7 @@
       <c r="M123" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N123" s="38">
+      <c r="N123" s="36">
         <v>28854</v>
       </c>
       <c r="O123" s="33">
@@ -14190,7 +14205,7 @@
       <c r="M124" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N124" s="38">
+      <c r="N124" s="36">
         <v>24495</v>
       </c>
       <c r="O124" s="33">
@@ -14258,7 +14273,7 @@
       <c r="M125" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N125" s="38">
+      <c r="N125" s="36">
         <v>29651</v>
       </c>
       <c r="O125" s="33">
@@ -14326,7 +14341,7 @@
       <c r="M126" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N126" s="38">
+      <c r="N126" s="36">
         <v>25393</v>
       </c>
       <c r="O126" s="33">
@@ -14394,7 +14409,7 @@
       <c r="M127" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N127" s="38">
+      <c r="N127" s="36">
         <v>26387</v>
       </c>
       <c r="O127" s="33">
@@ -14462,7 +14477,7 @@
       <c r="M128" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N128" s="38">
+      <c r="N128" s="36">
         <v>24247</v>
       </c>
       <c r="O128" s="33">
@@ -14530,7 +14545,7 @@
       <c r="M129" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N129" s="38">
+      <c r="N129" s="36">
         <v>28323</v>
       </c>
       <c r="O129" s="33">
@@ -14598,7 +14613,7 @@
       <c r="M130" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N130" s="38">
+      <c r="N130" s="36">
         <v>25528</v>
       </c>
       <c r="O130" s="33">
@@ -14666,7 +14681,7 @@
       <c r="M131" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N131" s="38">
+      <c r="N131" s="36">
         <v>25213</v>
       </c>
       <c r="O131" s="33">
@@ -14734,7 +14749,7 @@
       <c r="M132" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N132" s="38">
+      <c r="N132" s="36">
         <v>26615</v>
       </c>
       <c r="O132" s="33">
@@ -14802,7 +14817,7 @@
       <c r="M133" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N133" s="38">
+      <c r="N133" s="36">
         <v>27870</v>
       </c>
       <c r="O133" s="33">
@@ -14870,7 +14885,7 @@
       <c r="M134" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N134" s="38">
+      <c r="N134" s="36">
         <v>26598</v>
       </c>
       <c r="O134" s="33">
@@ -14938,7 +14953,7 @@
       <c r="M135" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N135" s="38">
+      <c r="N135" s="36">
         <v>26153</v>
       </c>
       <c r="O135" s="33">
@@ -15006,7 +15021,7 @@
       <c r="M136" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N136" s="38">
+      <c r="N136" s="36">
         <v>26437</v>
       </c>
       <c r="O136" s="33">
@@ -15074,7 +15089,7 @@
       <c r="M137" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N137" s="38">
+      <c r="N137" s="36">
         <v>27048</v>
       </c>
       <c r="O137" s="33">
@@ -15142,7 +15157,7 @@
       <c r="M138" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N138" s="38">
+      <c r="N138" s="36">
         <v>26759</v>
       </c>
       <c r="O138" s="33">
@@ -15210,7 +15225,7 @@
       <c r="M139" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N139" s="38">
+      <c r="N139" s="36">
         <v>28350</v>
       </c>
       <c r="O139" s="33">
@@ -15278,7 +15293,7 @@
       <c r="M140" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N140" s="38">
+      <c r="N140" s="36">
         <v>28106</v>
       </c>
       <c r="O140" s="33">
@@ -15346,7 +15361,7 @@
       <c r="M141" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N141" s="38">
+      <c r="N141" s="36">
         <v>26945</v>
       </c>
       <c r="O141" s="33">
@@ -15414,7 +15429,7 @@
       <c r="M142" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N142" s="38">
+      <c r="N142" s="36">
         <v>27498</v>
       </c>
       <c r="O142" s="33">
@@ -15482,7 +15497,7 @@
       <c r="M143" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N143" s="38">
+      <c r="N143" s="36">
         <v>26261</v>
       </c>
       <c r="O143" s="33">
@@ -15550,7 +15565,7 @@
       <c r="M144" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N144" s="38">
+      <c r="N144" s="36">
         <v>28267</v>
       </c>
       <c r="O144" s="33">
@@ -15618,7 +15633,7 @@
       <c r="M145" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N145" s="38">
+      <c r="N145" s="36">
         <v>27256</v>
       </c>
       <c r="O145" s="33">
@@ -15686,7 +15701,7 @@
       <c r="M146" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N146" s="38">
+      <c r="N146" s="36">
         <v>27382</v>
       </c>
       <c r="O146" s="33">
@@ -15754,7 +15769,7 @@
       <c r="M147" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N147" s="38">
+      <c r="N147" s="36">
         <v>26960</v>
       </c>
       <c r="O147" s="33">
@@ -15822,7 +15837,7 @@
       <c r="M148" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N148" s="38">
+      <c r="N148" s="36">
         <v>25799</v>
       </c>
       <c r="O148" s="33">
@@ -15890,7 +15905,7 @@
       <c r="M149" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N149" s="38">
+      <c r="N149" s="36">
         <v>27933</v>
       </c>
       <c r="O149" s="33">
@@ -15958,7 +15973,7 @@
       <c r="M150" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N150" s="38">
+      <c r="N150" s="36">
         <v>31840</v>
       </c>
       <c r="O150" s="33">
@@ -16026,7 +16041,7 @@
       <c r="M151" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N151" s="38">
+      <c r="N151" s="36">
         <v>27371</v>
       </c>
       <c r="O151" s="33">
@@ -16094,7 +16109,7 @@
       <c r="M152" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N152" s="38">
+      <c r="N152" s="36">
         <v>27777</v>
       </c>
       <c r="O152" s="33">
@@ -16162,7 +16177,7 @@
       <c r="M153" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N153" s="38">
+      <c r="N153" s="36">
         <v>29097</v>
       </c>
       <c r="O153" s="33">
@@ -16230,7 +16245,7 @@
       <c r="M154" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N154" s="38">
+      <c r="N154" s="36">
         <v>26390</v>
       </c>
       <c r="O154" s="33">
@@ -16298,7 +16313,7 @@
       <c r="M155" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N155" s="38">
+      <c r="N155" s="36">
         <v>28091</v>
       </c>
       <c r="O155" s="33">
@@ -16366,7 +16381,7 @@
       <c r="M156" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N156" s="38">
+      <c r="N156" s="36">
         <v>29715</v>
       </c>
       <c r="O156" s="33">
@@ -16434,7 +16449,7 @@
       <c r="M157" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N157" s="38">
+      <c r="N157" s="36">
         <v>26880</v>
       </c>
       <c r="O157" s="33">
@@ -16502,7 +16517,7 @@
       <c r="M158" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N158" s="38">
+      <c r="N158" s="36">
         <v>30362</v>
       </c>
       <c r="O158" s="33">
@@ -16570,7 +16585,7 @@
       <c r="M159" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N159" s="38">
+      <c r="N159" s="36">
         <v>26003</v>
       </c>
       <c r="O159" s="33">
@@ -16638,7 +16653,7 @@
       <c r="M160" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N160" s="38">
+      <c r="N160" s="36">
         <v>26517</v>
       </c>
       <c r="O160" s="33">
@@ -16706,7 +16721,7 @@
       <c r="M161" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N161" s="38">
+      <c r="N161" s="36">
         <v>29868</v>
       </c>
       <c r="O161" s="33">
@@ -16774,7 +16789,7 @@
       <c r="M162" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N162" s="38">
+      <c r="N162" s="36">
         <v>29844</v>
       </c>
       <c r="O162" s="33">
@@ -16842,7 +16857,7 @@
       <c r="M163" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N163" s="38">
+      <c r="N163" s="36">
         <v>31767</v>
       </c>
       <c r="O163" s="33">
@@ -16910,7 +16925,7 @@
       <c r="M164" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N164" s="38">
+      <c r="N164" s="36">
         <v>28371</v>
       </c>
       <c r="O164" s="33">
@@ -16978,7 +16993,7 @@
       <c r="M165" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N165" s="38">
+      <c r="N165" s="36">
         <v>24449</v>
       </c>
       <c r="O165" s="33">
@@ -17046,7 +17061,7 @@
       <c r="M166" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N166" s="38">
+      <c r="N166" s="36">
         <v>26164</v>
       </c>
       <c r="O166" s="33">
@@ -17114,7 +17129,7 @@
       <c r="M167" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N167" s="38">
+      <c r="N167" s="36">
         <v>29629</v>
       </c>
       <c r="O167" s="33">
@@ -17182,7 +17197,7 @@
       <c r="M168" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N168" s="38">
+      <c r="N168" s="36">
         <v>31548</v>
       </c>
       <c r="O168" s="33">
@@ -17250,7 +17265,7 @@
       <c r="M169" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N169" s="38">
+      <c r="N169" s="36">
         <v>23439</v>
       </c>
       <c r="O169" s="33">
@@ -17318,7 +17333,7 @@
       <c r="M170" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N170" s="38">
+      <c r="N170" s="36">
         <v>31785</v>
       </c>
       <c r="O170" s="33">
@@ -17386,7 +17401,7 @@
       <c r="M171" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N171" s="38">
+      <c r="N171" s="36">
         <v>29187</v>
       </c>
       <c r="O171" s="33">
@@ -17454,7 +17469,7 @@
       <c r="M172" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N172" s="38">
+      <c r="N172" s="36">
         <v>27175</v>
       </c>
       <c r="O172" s="33">
@@ -17522,7 +17537,7 @@
       <c r="M173" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N173" s="38">
+      <c r="N173" s="36">
         <v>25445</v>
       </c>
       <c r="O173" s="33">
@@ -17590,7 +17605,7 @@
       <c r="M174" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N174" s="38">
+      <c r="N174" s="36">
         <v>26899</v>
       </c>
       <c r="O174" s="33">
@@ -17658,7 +17673,7 @@
       <c r="M175" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N175" s="38">
+      <c r="N175" s="36">
         <v>28703</v>
       </c>
       <c r="O175" s="33">
@@ -17726,7 +17741,7 @@
       <c r="M176" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N176" s="38">
+      <c r="N176" s="36">
         <v>30401</v>
       </c>
       <c r="O176" s="33">
@@ -17794,7 +17809,7 @@
       <c r="M177" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N177" s="38">
+      <c r="N177" s="36">
         <v>27445</v>
       </c>
       <c r="O177" s="33">
@@ -17862,7 +17877,7 @@
       <c r="M178" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N178" s="38">
+      <c r="N178" s="36">
         <v>30367</v>
       </c>
       <c r="O178" s="33">
@@ -17930,7 +17945,7 @@
       <c r="M179" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N179" s="38">
+      <c r="N179" s="36">
         <v>28499</v>
       </c>
       <c r="O179" s="33">
@@ -17998,7 +18013,7 @@
       <c r="M180" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N180" s="38">
+      <c r="N180" s="36">
         <v>28982</v>
       </c>
       <c r="O180" s="33">
@@ -18066,7 +18081,7 @@
       <c r="M181" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N181" s="38">
+      <c r="N181" s="36">
         <v>24294</v>
       </c>
       <c r="O181" s="33">
@@ -18134,7 +18149,7 @@
       <c r="M182" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N182" s="38">
+      <c r="N182" s="36">
         <v>27729</v>
       </c>
       <c r="O182" s="33">
@@ -18202,7 +18217,7 @@
       <c r="M183" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N183" s="38">
+      <c r="N183" s="36">
         <v>26247</v>
       </c>
       <c r="O183" s="33">
@@ -18270,7 +18285,7 @@
       <c r="M184" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N184" s="38">
+      <c r="N184" s="36">
         <v>27349</v>
       </c>
       <c r="O184" s="33">
@@ -18338,7 +18353,7 @@
       <c r="M185" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N185" s="38">
+      <c r="N185" s="36">
         <v>29747</v>
       </c>
       <c r="O185" s="33">
@@ -18406,7 +18421,7 @@
       <c r="M186" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N186" s="38">
+      <c r="N186" s="36">
         <v>27920</v>
       </c>
       <c r="O186" s="33">
@@ -18474,7 +18489,7 @@
       <c r="M187" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N187" s="38">
+      <c r="N187" s="36">
         <v>29365</v>
       </c>
       <c r="O187" s="33">
@@ -18542,7 +18557,7 @@
       <c r="M188" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N188" s="38">
+      <c r="N188" s="36">
         <v>28199</v>
       </c>
       <c r="O188" s="33">
@@ -18610,7 +18625,7 @@
       <c r="M189" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N189" s="38">
+      <c r="N189" s="36">
         <v>26407</v>
       </c>
       <c r="O189" s="33">
@@ -18678,7 +18693,7 @@
       <c r="M190" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N190" s="38">
+      <c r="N190" s="36">
         <v>30770</v>
       </c>
       <c r="O190" s="33">
@@ -18746,7 +18761,7 @@
       <c r="M191" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N191" s="38">
+      <c r="N191" s="36">
         <v>29708</v>
       </c>
       <c r="O191" s="33">
@@ -18814,7 +18829,7 @@
       <c r="M192" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N192" s="38">
+      <c r="N192" s="36">
         <v>28226</v>
       </c>
       <c r="O192" s="33">
@@ -18882,7 +18897,7 @@
       <c r="M193" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N193" s="38">
+      <c r="N193" s="36">
         <v>28471</v>
       </c>
       <c r="O193" s="33">
@@ -18950,7 +18965,7 @@
       <c r="M194" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N194" s="38">
+      <c r="N194" s="36">
         <v>29353</v>
       </c>
       <c r="O194" s="33">
@@ -19018,7 +19033,7 @@
       <c r="M195" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N195" s="38">
+      <c r="N195" s="36">
         <v>27868</v>
       </c>
       <c r="O195" s="33">
@@ -19086,7 +19101,7 @@
       <c r="M196" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N196" s="38">
+      <c r="N196" s="36">
         <v>31432</v>
       </c>
       <c r="O196" s="33">
@@ -19154,7 +19169,7 @@
       <c r="M197" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N197" s="38">
+      <c r="N197" s="36">
         <v>29785</v>
       </c>
       <c r="O197" s="33">
@@ -19222,7 +19237,7 @@
       <c r="M198" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N198" s="38">
+      <c r="N198" s="36">
         <v>26659</v>
       </c>
       <c r="O198" s="33">
@@ -19290,7 +19305,7 @@
       <c r="M199" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N199" s="38">
+      <c r="N199" s="36">
         <v>30330</v>
       </c>
       <c r="O199" s="33">
@@ -19358,7 +19373,7 @@
       <c r="M200" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N200" s="38">
+      <c r="N200" s="36">
         <v>25605</v>
       </c>
       <c r="O200" s="33">
@@ -19426,7 +19441,7 @@
       <c r="M201" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N201" s="38">
+      <c r="N201" s="36">
         <v>29357</v>
       </c>
       <c r="O201" s="33">
@@ -19494,7 +19509,7 @@
       <c r="M202" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N202" s="38">
+      <c r="N202" s="36">
         <v>29370</v>
       </c>
       <c r="O202" s="33">
@@ -19562,7 +19577,7 @@
       <c r="M203" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N203" s="38">
+      <c r="N203" s="36">
         <v>28350</v>
       </c>
       <c r="O203" s="33">
@@ -19630,7 +19645,7 @@
       <c r="M204" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N204" s="38">
+      <c r="N204" s="36">
         <v>31161</v>
       </c>
       <c r="O204" s="33">
@@ -19698,12 +19713,12 @@
       <c r="M205" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N205" s="38">
+      <c r="N205" s="36">
         <v>31251</v>
       </c>
       <c r="O205" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P205" s="35" t="str">
         <f t="shared" si="7"/>
@@ -19766,7 +19781,7 @@
       <c r="M206" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N206" s="38">
+      <c r="N206" s="36">
         <v>25062</v>
       </c>
       <c r="O206" s="33">
@@ -19834,7 +19849,7 @@
       <c r="M207" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N207" s="38">
+      <c r="N207" s="36">
         <v>30274</v>
       </c>
       <c r="O207" s="33">
@@ -19902,7 +19917,7 @@
       <c r="M208" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N208" s="38">
+      <c r="N208" s="36">
         <v>25238</v>
       </c>
       <c r="O208" s="33">
@@ -19970,7 +19985,7 @@
       <c r="M209" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N209" s="38">
+      <c r="N209" s="36">
         <v>25123</v>
       </c>
       <c r="O209" s="33">
@@ -20038,7 +20053,7 @@
       <c r="M210" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N210" s="38">
+      <c r="N210" s="36">
         <v>30201</v>
       </c>
       <c r="O210" s="33">
@@ -20106,7 +20121,7 @@
       <c r="M211" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N211" s="38">
+      <c r="N211" s="36">
         <v>30428</v>
       </c>
       <c r="O211" s="33">
@@ -20174,7 +20189,7 @@
       <c r="M212" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N212" s="38">
+      <c r="N212" s="36">
         <v>23084</v>
       </c>
       <c r="O212" s="33">
@@ -20242,7 +20257,7 @@
       <c r="M213" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N213" s="38">
+      <c r="N213" s="36">
         <v>28422</v>
       </c>
       <c r="O213" s="33">
@@ -20310,7 +20325,7 @@
       <c r="M214" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N214" s="38">
+      <c r="N214" s="36">
         <v>30238</v>
       </c>
       <c r="O214" s="33">
@@ -20378,7 +20393,7 @@
       <c r="M215" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N215" s="38">
+      <c r="N215" s="36">
         <v>30120</v>
       </c>
       <c r="O215" s="33">
@@ -20446,7 +20461,7 @@
       <c r="M216" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N216" s="38">
+      <c r="N216" s="36">
         <v>29892</v>
       </c>
       <c r="O216" s="33">
@@ -20514,7 +20529,7 @@
       <c r="M217" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N217" s="38">
+      <c r="N217" s="36">
         <v>27689</v>
       </c>
       <c r="O217" s="33">
@@ -20582,7 +20597,7 @@
       <c r="M218" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N218" s="38">
+      <c r="N218" s="36">
         <v>26085</v>
       </c>
       <c r="O218" s="33">
@@ -20650,7 +20665,7 @@
       <c r="M219" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N219" s="38">
+      <c r="N219" s="36">
         <v>26995</v>
       </c>
       <c r="O219" s="33">
@@ -20718,7 +20733,7 @@
       <c r="M220" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N220" s="38">
+      <c r="N220" s="36">
         <v>29224</v>
       </c>
       <c r="O220" s="33">
@@ -20786,7 +20801,7 @@
       <c r="M221" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="N221" s="38">
+      <c r="N221" s="36">
         <v>29688</v>
       </c>
       <c r="O221" s="33">
@@ -20854,7 +20869,7 @@
       <c r="M222" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N222" s="38">
+      <c r="N222" s="36">
         <v>26839</v>
       </c>
       <c r="O222" s="33">
@@ -20922,7 +20937,7 @@
       <c r="M223" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N223" s="38">
+      <c r="N223" s="36">
         <v>31628</v>
       </c>
       <c r="O223" s="33">
@@ -20990,7 +21005,7 @@
       <c r="M224" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N224" s="38">
+      <c r="N224" s="36">
         <v>26331</v>
       </c>
       <c r="O224" s="33">
@@ -21058,7 +21073,7 @@
       <c r="M225" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N225" s="38">
+      <c r="N225" s="36">
         <v>32059</v>
       </c>
       <c r="O225" s="33">
@@ -21126,7 +21141,7 @@
       <c r="M226" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N226" s="38">
+      <c r="N226" s="36">
         <v>31539</v>
       </c>
       <c r="O226" s="33">
@@ -21194,7 +21209,7 @@
       <c r="M227" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N227" s="38">
+      <c r="N227" s="36">
         <v>25691</v>
       </c>
       <c r="O227" s="33">
@@ -21262,7 +21277,7 @@
       <c r="M228" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N228" s="38">
+      <c r="N228" s="36">
         <v>30939</v>
       </c>
       <c r="O228" s="33">
@@ -21330,7 +21345,7 @@
       <c r="M229" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N229" s="38">
+      <c r="N229" s="36">
         <v>26741</v>
       </c>
       <c r="O229" s="33">
@@ -21398,7 +21413,7 @@
       <c r="M230" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N230" s="38">
+      <c r="N230" s="36">
         <v>27502</v>
       </c>
       <c r="O230" s="33">
@@ -21466,7 +21481,7 @@
       <c r="M231" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N231" s="38">
+      <c r="N231" s="36">
         <v>28792</v>
       </c>
       <c r="O231" s="33">
@@ -21534,7 +21549,7 @@
       <c r="M232" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N232" s="38">
+      <c r="N232" s="36">
         <v>24387</v>
       </c>
       <c r="O232" s="33">
@@ -21602,7 +21617,7 @@
       <c r="M233" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N233" s="38">
+      <c r="N233" s="36">
         <v>24405</v>
       </c>
       <c r="O233" s="33">
@@ -21670,7 +21685,7 @@
       <c r="M234" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N234" s="38">
+      <c r="N234" s="36">
         <v>29203</v>
       </c>
       <c r="O234" s="33">
@@ -21738,7 +21753,7 @@
       <c r="M235" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N235" s="38">
+      <c r="N235" s="36">
         <v>31280</v>
       </c>
       <c r="O235" s="33">
@@ -21806,7 +21821,7 @@
       <c r="M236" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N236" s="38">
+      <c r="N236" s="36">
         <v>28346</v>
       </c>
       <c r="O236" s="33">
@@ -21874,7 +21889,7 @@
       <c r="M237" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N237" s="38">
+      <c r="N237" s="36">
         <v>28425</v>
       </c>
       <c r="O237" s="33">
@@ -21942,7 +21957,7 @@
       <c r="M238" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N238" s="38">
+      <c r="N238" s="36">
         <v>29384</v>
       </c>
       <c r="O238" s="33">
@@ -22010,7 +22025,7 @@
       <c r="M239" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N239" s="38">
+      <c r="N239" s="36">
         <v>25334</v>
       </c>
       <c r="O239" s="33">
@@ -22078,7 +22093,7 @@
       <c r="M240" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N240" s="38">
+      <c r="N240" s="36">
         <v>30239</v>
       </c>
       <c r="O240" s="33">
@@ -22146,7 +22161,7 @@
       <c r="M241" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N241" s="38">
+      <c r="N241" s="36">
         <v>24981</v>
       </c>
       <c r="O241" s="33">
@@ -22214,7 +22229,7 @@
       <c r="M242" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N242" s="38">
+      <c r="N242" s="36">
         <v>28461</v>
       </c>
       <c r="O242" s="33">
@@ -22282,7 +22297,7 @@
       <c r="M243" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N243" s="38">
+      <c r="N243" s="36">
         <v>29180</v>
       </c>
       <c r="O243" s="33">
@@ -22350,7 +22365,7 @@
       <c r="M244" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N244" s="38">
+      <c r="N244" s="36">
         <v>28891</v>
       </c>
       <c r="O244" s="33">
@@ -22418,7 +22433,7 @@
       <c r="M245" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N245" s="38">
+      <c r="N245" s="36">
         <v>30343</v>
       </c>
       <c r="O245" s="33">
@@ -22486,7 +22501,7 @@
       <c r="M246" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N246" s="38">
+      <c r="N246" s="36">
         <v>30260</v>
       </c>
       <c r="O246" s="33">
@@ -22554,7 +22569,7 @@
       <c r="M247" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N247" s="38">
+      <c r="N247" s="36">
         <v>27217</v>
       </c>
       <c r="O247" s="33">
@@ -22622,7 +22637,7 @@
       <c r="M248" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N248" s="38">
+      <c r="N248" s="36">
         <v>25850</v>
       </c>
       <c r="O248" s="33">
@@ -22690,7 +22705,7 @@
       <c r="M249" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N249" s="38">
+      <c r="N249" s="36">
         <v>28720</v>
       </c>
       <c r="O249" s="33">
@@ -22758,7 +22773,7 @@
       <c r="M250" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N250" s="38">
+      <c r="N250" s="36">
         <v>28476</v>
       </c>
       <c r="O250" s="33">
@@ -22826,7 +22841,7 @@
       <c r="M251" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N251" s="38">
+      <c r="N251" s="36">
         <v>30889</v>
       </c>
       <c r="O251" s="33">
@@ -22894,7 +22909,7 @@
       <c r="M252" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N252" s="38">
+      <c r="N252" s="36">
         <v>31231</v>
       </c>
       <c r="O252" s="33">
@@ -22962,7 +22977,7 @@
       <c r="M253" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N253" s="38">
+      <c r="N253" s="36">
         <v>26617</v>
       </c>
       <c r="O253" s="33">
@@ -23030,7 +23045,7 @@
       <c r="M254" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N254" s="38">
+      <c r="N254" s="36">
         <v>27109</v>
       </c>
       <c r="O254" s="33">
@@ -23098,7 +23113,7 @@
       <c r="M255" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N255" s="38">
+      <c r="N255" s="36">
         <v>26888</v>
       </c>
       <c r="O255" s="33">
@@ -23166,7 +23181,7 @@
       <c r="M256" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N256" s="38">
+      <c r="N256" s="36">
         <v>26066</v>
       </c>
       <c r="O256" s="33">
@@ -23234,7 +23249,7 @@
       <c r="M257" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N257" s="38">
+      <c r="N257" s="36">
         <v>31565</v>
       </c>
       <c r="O257" s="33">
@@ -23302,7 +23317,7 @@
       <c r="M258" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N258" s="38">
+      <c r="N258" s="36">
         <v>31220</v>
       </c>
       <c r="O258" s="33">
@@ -23370,7 +23385,7 @@
       <c r="M259" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N259" s="38">
+      <c r="N259" s="36">
         <v>25853</v>
       </c>
       <c r="O259" s="33">
@@ -23438,7 +23453,7 @@
       <c r="M260" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N260" s="38">
+      <c r="N260" s="36">
         <v>30546</v>
       </c>
       <c r="O260" s="33">
@@ -23506,7 +23521,7 @@
       <c r="M261" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N261" s="38">
+      <c r="N261" s="36">
         <v>30472</v>
       </c>
       <c r="O261" s="33">
@@ -23574,7 +23589,7 @@
       <c r="M262" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N262" s="38">
+      <c r="N262" s="36">
         <v>30654</v>
       </c>
       <c r="O262" s="33">
@@ -23642,7 +23657,7 @@
       <c r="M263" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N263" s="38">
+      <c r="N263" s="36">
         <v>28650</v>
       </c>
       <c r="O263" s="33">
@@ -23710,7 +23725,7 @@
       <c r="M264" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N264" s="38">
+      <c r="N264" s="36">
         <v>31241</v>
       </c>
       <c r="O264" s="33">
@@ -23778,7 +23793,7 @@
       <c r="M265" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N265" s="38">
+      <c r="N265" s="36">
         <v>31118</v>
       </c>
       <c r="O265" s="33">
@@ -23846,7 +23861,7 @@
       <c r="M266" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N266" s="38">
+      <c r="N266" s="36">
         <v>29131</v>
       </c>
       <c r="O266" s="33">
@@ -23914,7 +23929,7 @@
       <c r="M267" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N267" s="38">
+      <c r="N267" s="36">
         <v>33163</v>
       </c>
       <c r="O267" s="33">
@@ -23982,7 +23997,7 @@
       <c r="M268" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N268" s="38">
+      <c r="N268" s="36">
         <v>31879</v>
       </c>
       <c r="O268" s="33">
@@ -24050,7 +24065,7 @@
       <c r="M269" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N269" s="38">
+      <c r="N269" s="36">
         <v>30278</v>
       </c>
       <c r="O269" s="33">
@@ -24118,7 +24133,7 @@
       <c r="M270" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N270" s="38">
+      <c r="N270" s="36">
         <v>31225</v>
       </c>
       <c r="O270" s="33">
@@ -24186,7 +24201,7 @@
       <c r="M271" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N271" s="38">
+      <c r="N271" s="36">
         <v>30169</v>
       </c>
       <c r="O271" s="33">
@@ -24254,7 +24269,7 @@
       <c r="M272" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N272" s="38">
+      <c r="N272" s="36">
         <v>31862</v>
       </c>
       <c r="O272" s="33">
@@ -24322,7 +24337,7 @@
       <c r="M273" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N273" s="38">
+      <c r="N273" s="36">
         <v>31875</v>
       </c>
       <c r="O273" s="33">
@@ -24390,7 +24405,7 @@
       <c r="M274" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N274" s="38">
+      <c r="N274" s="36">
         <v>28713</v>
       </c>
       <c r="O274" s="33">
@@ -24458,7 +24473,7 @@
       <c r="M275" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N275" s="38">
+      <c r="N275" s="36">
         <v>32321</v>
       </c>
       <c r="O275" s="33">
@@ -24526,7 +24541,7 @@
       <c r="M276" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N276" s="38">
+      <c r="N276" s="36">
         <v>32964</v>
       </c>
       <c r="O276" s="33">
@@ -24594,7 +24609,7 @@
       <c r="M277" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N277" s="38">
+      <c r="N277" s="36">
         <v>31579</v>
       </c>
       <c r="O277" s="33">
@@ -24662,7 +24677,7 @@
       <c r="M278" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N278" s="38">
+      <c r="N278" s="36">
         <v>29151</v>
       </c>
       <c r="O278" s="33">
@@ -24730,7 +24745,7 @@
       <c r="M279" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N279" s="38">
+      <c r="N279" s="36">
         <v>29910</v>
       </c>
       <c r="O279" s="33">
@@ -24798,7 +24813,7 @@
       <c r="M280" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N280" s="38">
+      <c r="N280" s="36">
         <v>30749</v>
       </c>
       <c r="O280" s="33">
@@ -24866,7 +24881,7 @@
       <c r="M281" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N281" s="38">
+      <c r="N281" s="36">
         <v>28375</v>
       </c>
       <c r="O281" s="33">
@@ -24934,7 +24949,7 @@
       <c r="M282" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N282" s="38">
+      <c r="N282" s="36">
         <v>31563</v>
       </c>
       <c r="O282" s="33">
@@ -25002,7 +25017,7 @@
       <c r="M283" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N283" s="38">
+      <c r="N283" s="36">
         <v>31548</v>
       </c>
       <c r="O283" s="33">
@@ -25070,7 +25085,7 @@
       <c r="M284" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N284" s="38">
+      <c r="N284" s="36">
         <v>29917</v>
       </c>
       <c r="O284" s="33">
@@ -25138,7 +25153,7 @@
       <c r="M285" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N285" s="38">
+      <c r="N285" s="36">
         <v>31633</v>
       </c>
       <c r="O285" s="33">
@@ -25206,7 +25221,7 @@
       <c r="M286" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N286" s="38">
+      <c r="N286" s="36">
         <v>30315</v>
       </c>
       <c r="O286" s="33">
@@ -25274,7 +25289,7 @@
       <c r="M287" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N287" s="38">
+      <c r="N287" s="36">
         <v>33295</v>
       </c>
       <c r="O287" s="33">
@@ -25342,7 +25357,7 @@
       <c r="M288" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N288" s="38">
+      <c r="N288" s="36">
         <v>31709</v>
       </c>
       <c r="O288" s="33">
@@ -25410,7 +25425,7 @@
       <c r="M289" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N289" s="38">
+      <c r="N289" s="36">
         <v>32997</v>
       </c>
       <c r="O289" s="33">
@@ -25478,7 +25493,7 @@
       <c r="M290" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N290" s="38">
+      <c r="N290" s="36">
         <v>31676</v>
       </c>
       <c r="O290" s="33">
@@ -25546,7 +25561,7 @@
       <c r="M291" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N291" s="38">
+      <c r="N291" s="36">
         <v>31339</v>
       </c>
       <c r="O291" s="33">
@@ -25614,7 +25629,7 @@
       <c r="M292" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N292" s="38">
+      <c r="N292" s="36">
         <v>32777</v>
       </c>
       <c r="O292" s="33">
@@ -25682,7 +25697,7 @@
       <c r="M293" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N293" s="38">
+      <c r="N293" s="36">
         <v>31180</v>
       </c>
       <c r="O293" s="33">
@@ -25750,7 +25765,7 @@
       <c r="M294" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N294" s="38">
+      <c r="N294" s="36">
         <v>30374</v>
       </c>
       <c r="O294" s="33">
@@ -25818,7 +25833,7 @@
       <c r="M295" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N295" s="38">
+      <c r="N295" s="36">
         <v>30231</v>
       </c>
       <c r="O295" s="33">
@@ -25886,7 +25901,7 @@
       <c r="M296" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N296" s="38">
+      <c r="N296" s="36">
         <v>33173</v>
       </c>
       <c r="O296" s="33">
@@ -25954,7 +25969,7 @@
       <c r="M297" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N297" s="38">
+      <c r="N297" s="36">
         <v>31455</v>
       </c>
       <c r="O297" s="33">
@@ -26022,7 +26037,7 @@
       <c r="M298" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N298" s="38">
+      <c r="N298" s="36">
         <v>30207</v>
       </c>
       <c r="O298" s="33">
@@ -26090,7 +26105,7 @@
       <c r="M299" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N299" s="38">
+      <c r="N299" s="36">
         <v>32222</v>
       </c>
       <c r="O299" s="33">
@@ -26158,7 +26173,7 @@
       <c r="M300" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N300" s="38">
+      <c r="N300" s="36">
         <v>31854</v>
       </c>
       <c r="O300" s="33">
@@ -26226,12 +26241,12 @@
       <c r="M301" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N301" s="38">
+      <c r="N301" s="36">
         <v>32710</v>
       </c>
       <c r="O301" s="33">
         <f t="shared" ca="1" si="8"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P301" s="35" t="str">
         <f t="shared" si="9"/>
@@ -26294,7 +26309,7 @@
       <c r="M302" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N302" s="38">
+      <c r="N302" s="36">
         <v>28096</v>
       </c>
       <c r="O302" s="33">
@@ -26362,7 +26377,7 @@
       <c r="M303" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N303" s="38">
+      <c r="N303" s="36">
         <v>33012</v>
       </c>
       <c r="O303" s="33">
@@ -26430,7 +26445,7 @@
       <c r="M304" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N304" s="38">
+      <c r="N304" s="36">
         <v>30046</v>
       </c>
       <c r="O304" s="33">
@@ -26498,7 +26513,7 @@
       <c r="M305" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N305" s="38">
+      <c r="N305" s="36">
         <v>31845</v>
       </c>
       <c r="O305" s="33">
@@ -26566,7 +26581,7 @@
       <c r="M306" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N306" s="38">
+      <c r="N306" s="36">
         <v>33758</v>
       </c>
       <c r="O306" s="33">
@@ -26634,7 +26649,7 @@
       <c r="M307" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N307" s="38">
+      <c r="N307" s="36">
         <v>32589</v>
       </c>
       <c r="O307" s="33">
@@ -26702,7 +26717,7 @@
       <c r="M308" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N308" s="38">
+      <c r="N308" s="36">
         <v>32267</v>
       </c>
       <c r="O308" s="33">
@@ -26770,7 +26785,7 @@
       <c r="M309" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N309" s="38">
+      <c r="N309" s="36">
         <v>32321</v>
       </c>
       <c r="O309" s="33">
@@ -26838,7 +26853,7 @@
       <c r="M310" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N310" s="38">
+      <c r="N310" s="36">
         <v>27484</v>
       </c>
       <c r="O310" s="33">
@@ -26906,7 +26921,7 @@
       <c r="M311" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N311" s="38">
+      <c r="N311" s="36">
         <v>32087</v>
       </c>
       <c r="O311" s="33">
@@ -26974,7 +26989,7 @@
       <c r="M312" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N312" s="38">
+      <c r="N312" s="36">
         <v>30603</v>
       </c>
       <c r="O312" s="33">
@@ -27042,7 +27057,7 @@
       <c r="M313" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N313" s="38">
+      <c r="N313" s="36">
         <v>28997</v>
       </c>
       <c r="O313" s="33">
@@ -27110,7 +27125,7 @@
       <c r="M314" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N314" s="38">
+      <c r="N314" s="36">
         <v>33479</v>
       </c>
       <c r="O314" s="33">
@@ -27178,7 +27193,7 @@
       <c r="M315" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N315" s="38">
+      <c r="N315" s="36">
         <v>33486</v>
       </c>
       <c r="O315" s="33">
@@ -27246,7 +27261,7 @@
       <c r="M316" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N316" s="38">
+      <c r="N316" s="36">
         <v>33129</v>
       </c>
       <c r="O316" s="33">
@@ -27314,7 +27329,7 @@
       <c r="M317" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N317" s="38">
+      <c r="N317" s="36">
         <v>33854</v>
       </c>
       <c r="O317" s="33">
@@ -27382,7 +27397,7 @@
       <c r="M318" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N318" s="38">
+      <c r="N318" s="36">
         <v>33571</v>
       </c>
       <c r="O318" s="33">
@@ -27450,7 +27465,7 @@
       <c r="M319" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="N319" s="38">
+      <c r="N319" s="36">
         <v>29762</v>
       </c>
       <c r="O319" s="33">
@@ -27518,7 +27533,7 @@
       <c r="M320" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="N320" s="38">
+      <c r="N320" s="36">
         <v>29258</v>
       </c>
       <c r="O320" s="33">
@@ -27586,7 +27601,7 @@
       <c r="M321" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N321" s="38">
+      <c r="N321" s="36">
         <v>31379</v>
       </c>
       <c r="O321" s="33">
@@ -27654,7 +27669,7 @@
       <c r="M322" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N322" s="38">
+      <c r="N322" s="36">
         <v>30688</v>
       </c>
       <c r="O322" s="33">
@@ -27722,7 +27737,7 @@
       <c r="M323" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N323" s="38">
+      <c r="N323" s="36">
         <v>32203</v>
       </c>
       <c r="O323" s="33">
@@ -27790,7 +27805,7 @@
       <c r="M324" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N324" s="38">
+      <c r="N324" s="36">
         <v>34741</v>
       </c>
       <c r="O324" s="33">
@@ -27858,7 +27873,7 @@
       <c r="M325" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N325" s="38">
+      <c r="N325" s="36">
         <v>33610</v>
       </c>
       <c r="O325" s="33">
@@ -27926,7 +27941,7 @@
       <c r="M326" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N326" s="38">
+      <c r="N326" s="36">
         <v>34739</v>
       </c>
       <c r="O326" s="33">
@@ -27994,7 +28009,7 @@
       <c r="M327" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N327" s="38">
+      <c r="N327" s="36">
         <v>32817</v>
       </c>
       <c r="O327" s="33">
@@ -28062,7 +28077,7 @@
       <c r="M328" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N328" s="38">
+      <c r="N328" s="36">
         <v>33812</v>
       </c>
       <c r="O328" s="33">
@@ -28130,7 +28145,7 @@
       <c r="M329" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N329" s="38">
+      <c r="N329" s="36">
         <v>33701</v>
       </c>
       <c r="O329" s="33">
@@ -28198,7 +28213,7 @@
       <c r="M330" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N330" s="38">
+      <c r="N330" s="36">
         <v>33251</v>
       </c>
       <c r="O330" s="33">
@@ -28266,7 +28281,7 @@
       <c r="M331" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N331" s="38">
+      <c r="N331" s="36">
         <v>33896</v>
       </c>
       <c r="O331" s="33">
@@ -28334,7 +28349,7 @@
       <c r="M332" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N332" s="38">
+      <c r="N332" s="36">
         <v>34307</v>
       </c>
       <c r="O332" s="33">
@@ -28402,7 +28417,7 @@
       <c r="M333" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N333" s="38">
+      <c r="N333" s="36">
         <v>34270</v>
       </c>
       <c r="O333" s="33">
@@ -28470,7 +28485,7 @@
       <c r="M334" s="32" t="s">
         <v>859</v>
       </c>
-      <c r="N334" s="38">
+      <c r="N334" s="36">
         <v>29301</v>
       </c>
       <c r="O334" s="33">
@@ -28538,7 +28553,7 @@
       <c r="M335" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N335" s="38">
+      <c r="N335" s="36">
         <v>34269</v>
       </c>
       <c r="O335" s="33">
@@ -28606,7 +28621,7 @@
       <c r="M336" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N336" s="38">
+      <c r="N336" s="36">
         <v>33229</v>
       </c>
       <c r="O336" s="33">
@@ -28674,7 +28689,7 @@
       <c r="M337" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N337" s="38">
+      <c r="N337" s="36">
         <v>32436</v>
       </c>
       <c r="O337" s="33">
@@ -28742,7 +28757,7 @@
       <c r="M338" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N338" s="38">
+      <c r="N338" s="36">
         <v>32289</v>
       </c>
       <c r="O338" s="33">
@@ -28810,7 +28825,7 @@
       <c r="M339" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N339" s="38">
+      <c r="N339" s="36">
         <v>33780</v>
       </c>
       <c r="O339" s="33">
@@ -28878,7 +28893,7 @@
       <c r="M340" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N340" s="38">
+      <c r="N340" s="36">
         <v>32880</v>
       </c>
       <c r="O340" s="33">
@@ -28946,7 +28961,7 @@
       <c r="M341" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N341" s="38">
+      <c r="N341" s="36">
         <v>33809</v>
       </c>
       <c r="O341" s="33">
@@ -29014,7 +29029,7 @@
       <c r="M342" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N342" s="38">
+      <c r="N342" s="36">
         <v>35512</v>
       </c>
       <c r="O342" s="33">
@@ -29082,7 +29097,7 @@
       <c r="M343" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N343" s="38">
+      <c r="N343" s="36">
         <v>32660</v>
       </c>
       <c r="O343" s="33">
@@ -29150,7 +29165,7 @@
       <c r="M344" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N344" s="38">
+      <c r="N344" s="36">
         <v>30817</v>
       </c>
       <c r="O344" s="33">
@@ -29218,7 +29233,7 @@
       <c r="M345" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N345" s="38">
+      <c r="N345" s="36">
         <v>31941</v>
       </c>
       <c r="O345" s="33">
@@ -29286,7 +29301,7 @@
       <c r="M346" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N346" s="38">
+      <c r="N346" s="36">
         <v>32658</v>
       </c>
       <c r="O346" s="33">
@@ -29354,7 +29369,7 @@
       <c r="M347" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N347" s="38">
+      <c r="N347" s="36">
         <v>34968</v>
       </c>
       <c r="O347" s="33">
@@ -29422,7 +29437,7 @@
       <c r="M348" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N348" s="38">
+      <c r="N348" s="36">
         <v>32002</v>
       </c>
       <c r="O348" s="33">
@@ -29490,7 +29505,7 @@
       <c r="M349" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N349" s="38">
+      <c r="N349" s="36">
         <v>33888</v>
       </c>
       <c r="O349" s="33">
@@ -29558,7 +29573,7 @@
       <c r="M350" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N350" s="38">
+      <c r="N350" s="36">
         <v>26760</v>
       </c>
       <c r="O350" s="33">
@@ -29626,7 +29641,7 @@
       <c r="M351" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N351" s="38">
+      <c r="N351" s="36">
         <v>29570</v>
       </c>
       <c r="O351" s="33">
@@ -29694,7 +29709,7 @@
       <c r="M352" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N352" s="38">
+      <c r="N352" s="36">
         <v>30159</v>
       </c>
       <c r="O352" s="33">
@@ -29762,7 +29777,7 @@
       <c r="M353" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N353" s="38">
+      <c r="N353" s="36">
         <v>34797</v>
       </c>
       <c r="O353" s="33">
@@ -29830,7 +29845,7 @@
       <c r="M354" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N354" s="38">
+      <c r="N354" s="36">
         <v>33578</v>
       </c>
       <c r="O354" s="33">
@@ -29898,7 +29913,7 @@
       <c r="M355" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N355" s="38">
+      <c r="N355" s="36">
         <v>34276</v>
       </c>
       <c r="O355" s="33">
@@ -29966,7 +29981,7 @@
       <c r="M356" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N356" s="38">
+      <c r="N356" s="36">
         <v>34472</v>
       </c>
       <c r="O356" s="33">
@@ -30034,7 +30049,7 @@
       <c r="M357" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N357" s="38">
+      <c r="N357" s="36">
         <v>35132</v>
       </c>
       <c r="O357" s="33">
@@ -30102,7 +30117,7 @@
       <c r="M358" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N358" s="38">
+      <c r="N358" s="36">
         <v>32493</v>
       </c>
       <c r="O358" s="33">
@@ -30170,7 +30185,7 @@
       <c r="M359" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N359" s="38">
+      <c r="N359" s="36">
         <v>34324</v>
       </c>
       <c r="O359" s="33">
@@ -30238,7 +30253,7 @@
       <c r="M360" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N360" s="38">
+      <c r="N360" s="36">
         <v>28780</v>
       </c>
       <c r="O360" s="33">
@@ -30306,7 +30321,7 @@
       <c r="M361" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N361" s="38">
+      <c r="N361" s="36">
         <v>34388</v>
       </c>
       <c r="O361" s="33">
@@ -30374,7 +30389,7 @@
       <c r="M362" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N362" s="38">
+      <c r="N362" s="36">
         <v>31289</v>
       </c>
       <c r="O362" s="33">
@@ -30442,7 +30457,7 @@
       <c r="M363" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N363" s="38">
+      <c r="N363" s="36">
         <v>31331</v>
       </c>
       <c r="O363" s="33">
@@ -30510,7 +30525,7 @@
       <c r="M364" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N364" s="38">
+      <c r="N364" s="36">
         <v>34607</v>
       </c>
       <c r="O364" s="33">
@@ -30578,7 +30593,7 @@
       <c r="M365" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N365" s="38">
+      <c r="N365" s="36">
         <v>34934</v>
       </c>
       <c r="O365" s="33">
@@ -30646,7 +30661,7 @@
       <c r="M366" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N366" s="38">
+      <c r="N366" s="36">
         <v>31926</v>
       </c>
       <c r="O366" s="33">
@@ -30714,7 +30729,7 @@
       <c r="M367" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N367" s="38">
+      <c r="N367" s="36">
         <v>32253</v>
       </c>
       <c r="O367" s="33">
@@ -30782,7 +30797,7 @@
       <c r="M368" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N368" s="38">
+      <c r="N368" s="36">
         <v>32074</v>
       </c>
       <c r="O368" s="33">
@@ -30850,7 +30865,7 @@
       <c r="M369" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N369" s="38">
+      <c r="N369" s="36">
         <v>30076</v>
       </c>
       <c r="O369" s="33">
@@ -30918,7 +30933,7 @@
       <c r="M370" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N370" s="38">
+      <c r="N370" s="36">
         <v>32409</v>
       </c>
       <c r="O370" s="33">
@@ -30986,7 +31001,7 @@
       <c r="M371" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N371" s="38">
+      <c r="N371" s="36">
         <v>35784</v>
       </c>
       <c r="O371" s="33">
@@ -31054,7 +31069,7 @@
       <c r="M372" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N372" s="38">
+      <c r="N372" s="36">
         <v>33190</v>
       </c>
       <c r="O372" s="33">
@@ -31122,7 +31137,7 @@
       <c r="M373" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N373" s="38">
+      <c r="N373" s="36">
         <v>32609</v>
       </c>
       <c r="O373" s="33">
@@ -31190,7 +31205,7 @@
       <c r="M374" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N374" s="38">
+      <c r="N374" s="36">
         <v>27199</v>
       </c>
       <c r="O374" s="33">
@@ -31258,7 +31273,7 @@
       <c r="M375" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N375" s="38">
+      <c r="N375" s="36">
         <v>27808</v>
       </c>
       <c r="O375" s="33">
@@ -31326,7 +31341,7 @@
       <c r="M376" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N376" s="38">
+      <c r="N376" s="36">
         <v>27925</v>
       </c>
       <c r="O376" s="33">
@@ -31394,7 +31409,7 @@
       <c r="M377" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N377" s="38">
+      <c r="N377" s="36">
         <v>33612</v>
       </c>
       <c r="O377" s="33">
@@ -31462,7 +31477,7 @@
       <c r="M378" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N378" s="38">
+      <c r="N378" s="36">
         <v>35096</v>
       </c>
       <c r="O378" s="33">
@@ -31530,7 +31545,7 @@
       <c r="M379" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N379" s="38">
+      <c r="N379" s="36">
         <v>34702</v>
       </c>
       <c r="O379" s="33">
@@ -31598,7 +31613,7 @@
       <c r="M380" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N380" s="38">
+      <c r="N380" s="36">
         <v>34709</v>
       </c>
       <c r="O380" s="33">
@@ -31666,7 +31681,7 @@
       <c r="M381" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N381" s="38">
+      <c r="N381" s="36">
         <v>30386</v>
       </c>
       <c r="O381" s="33">
@@ -31734,7 +31749,7 @@
       <c r="M382" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N382" s="38">
+      <c r="N382" s="36">
         <v>30209</v>
       </c>
       <c r="O382" s="33">
@@ -31802,7 +31817,7 @@
       <c r="M383" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N383" s="38">
+      <c r="N383" s="36">
         <v>31988</v>
       </c>
       <c r="O383" s="33">
@@ -31870,7 +31885,7 @@
       <c r="M384" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N384" s="38">
+      <c r="N384" s="36">
         <v>35937</v>
       </c>
       <c r="O384" s="33">
@@ -31938,7 +31953,7 @@
       <c r="M385" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N385" s="38">
+      <c r="N385" s="36">
         <v>34544</v>
       </c>
       <c r="O385" s="33">
@@ -32006,7 +32021,7 @@
       <c r="M386" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N386" s="38">
+      <c r="N386" s="36">
         <v>33705</v>
       </c>
       <c r="O386" s="33">
@@ -32074,7 +32089,7 @@
       <c r="M387" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N387" s="38">
+      <c r="N387" s="36">
         <v>29578</v>
       </c>
       <c r="O387" s="33">
@@ -32142,7 +32157,7 @@
       <c r="M388" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N388" s="38">
+      <c r="N388" s="36">
         <v>34194</v>
       </c>
       <c r="O388" s="33">
@@ -32210,12 +32225,12 @@
       <c r="M389" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N389" s="38">
+      <c r="N389" s="36">
         <v>33806</v>
       </c>
       <c r="O389" s="33">
         <f t="shared" ca="1" si="12"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P389" s="35" t="str">
         <f t="shared" si="13"/>
@@ -32278,7 +32293,7 @@
       <c r="M390" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N390" s="38">
+      <c r="N390" s="36">
         <v>34239</v>
       </c>
       <c r="O390" s="33">
@@ -32346,7 +32361,7 @@
       <c r="M391" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N391" s="38">
+      <c r="N391" s="36">
         <v>29987</v>
       </c>
       <c r="O391" s="33">
@@ -32414,7 +32429,7 @@
       <c r="M392" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N392" s="38">
+      <c r="N392" s="36">
         <v>29803</v>
       </c>
       <c r="O392" s="33">
@@ -32482,7 +32497,7 @@
       <c r="M393" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="N393" s="38">
+      <c r="N393" s="36">
         <v>32736</v>
       </c>
       <c r="O393" s="33">
@@ -32550,7 +32565,7 @@
       <c r="M394" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N394" s="38">
+      <c r="N394" s="36">
         <v>33425</v>
       </c>
       <c r="O394" s="33">
@@ -32618,7 +32633,7 @@
       <c r="M395" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N395" s="38">
+      <c r="N395" s="36">
         <v>32240</v>
       </c>
       <c r="O395" s="33">
@@ -32686,7 +32701,7 @@
       <c r="M396" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N396" s="38">
+      <c r="N396" s="36">
         <v>36640</v>
       </c>
       <c r="O396" s="33">
@@ -32754,7 +32769,7 @@
       <c r="M397" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N397" s="38">
+      <c r="N397" s="36">
         <v>34434</v>
       </c>
       <c r="O397" s="33">
@@ -32822,7 +32837,7 @@
       <c r="M398" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N398" s="38">
+      <c r="N398" s="36">
         <v>32696</v>
       </c>
       <c r="O398" s="33">
@@ -32890,7 +32905,7 @@
       <c r="M399" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N399" s="38">
+      <c r="N399" s="36">
         <v>33866</v>
       </c>
       <c r="O399" s="33">
@@ -32958,7 +32973,7 @@
       <c r="M400" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N400" s="38">
+      <c r="N400" s="36">
         <v>35055</v>
       </c>
       <c r="O400" s="33">
@@ -33026,7 +33041,7 @@
       <c r="M401" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="N401" s="38">
+      <c r="N401" s="36">
         <v>28073</v>
       </c>
       <c r="O401" s="33">
@@ -33094,7 +33109,7 @@
       <c r="M402" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N402" s="38">
+      <c r="N402" s="36">
         <v>33862</v>
       </c>
       <c r="O402" s="33">
@@ -33162,7 +33177,7 @@
       <c r="M403" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N403" s="38">
+      <c r="N403" s="36">
         <v>30238</v>
       </c>
       <c r="O403" s="33">
@@ -33230,7 +33245,7 @@
       <c r="M404" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N404" s="38">
+      <c r="N404" s="36">
         <v>29813</v>
       </c>
       <c r="O404" s="33">
@@ -33298,7 +33313,7 @@
       <c r="M405" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N405" s="38">
+      <c r="N405" s="36">
         <v>26994</v>
       </c>
       <c r="O405" s="33">
@@ -33366,7 +33381,7 @@
       <c r="M406" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N406" s="38">
+      <c r="N406" s="36">
         <v>34771</v>
       </c>
       <c r="O406" s="33">
@@ -33434,7 +33449,7 @@
       <c r="M407" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N407" s="38">
+      <c r="N407" s="36">
         <v>34336</v>
       </c>
       <c r="O407" s="33">
@@ -33502,7 +33517,7 @@
       <c r="M408" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N408" s="38">
+      <c r="N408" s="36">
         <v>35865</v>
       </c>
       <c r="O408" s="33">
@@ -33570,7 +33585,7 @@
       <c r="M409" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N409" s="38">
+      <c r="N409" s="36">
         <v>33143</v>
       </c>
       <c r="O409" s="33">
@@ -33638,7 +33653,7 @@
       <c r="M410" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N410" s="38">
+      <c r="N410" s="36">
         <v>31973</v>
       </c>
       <c r="O410" s="33">
@@ -33706,7 +33721,7 @@
       <c r="M411" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N411" s="38">
+      <c r="N411" s="36">
         <v>27704</v>
       </c>
       <c r="O411" s="33">
@@ -33774,7 +33789,7 @@
       <c r="M412" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N412" s="38">
+      <c r="N412" s="36">
         <v>28549</v>
       </c>
       <c r="O412" s="33">
@@ -33842,7 +33857,7 @@
       <c r="M413" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N413" s="38">
+      <c r="N413" s="36">
         <v>32815</v>
       </c>
       <c r="O413" s="33">
@@ -33910,7 +33925,7 @@
       <c r="M414" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N414" s="38">
+      <c r="N414" s="36">
         <v>30411</v>
       </c>
       <c r="O414" s="33">
@@ -33978,7 +33993,7 @@
       <c r="M415" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N415" s="38">
+      <c r="N415" s="36">
         <v>26997</v>
       </c>
       <c r="O415" s="33">
@@ -34046,7 +34061,7 @@
       <c r="M416" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N416" s="38">
+      <c r="N416" s="36">
         <v>32420</v>
       </c>
       <c r="O416" s="33">
@@ -34114,7 +34129,7 @@
       <c r="M417" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N417" s="38">
+      <c r="N417" s="36">
         <v>32856</v>
       </c>
       <c r="O417" s="33">
@@ -34182,7 +34197,7 @@
       <c r="M418" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N418" s="38">
+      <c r="N418" s="36">
         <v>36166</v>
       </c>
       <c r="O418" s="33">
@@ -34252,7 +34267,7 @@
       <c r="M419" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N419" s="38">
+      <c r="N419" s="36">
         <v>35781</v>
       </c>
       <c r="O419" s="33">
@@ -34320,7 +34335,7 @@
       <c r="M420" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N420" s="38">
+      <c r="N420" s="36">
         <v>28243</v>
       </c>
       <c r="O420" s="33">
@@ -34388,7 +34403,7 @@
       <c r="M421" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N421" s="38">
+      <c r="N421" s="36">
         <v>33560</v>
       </c>
       <c r="O421" s="33">
@@ -34456,7 +34471,7 @@
       <c r="M422" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N422" s="38">
+      <c r="N422" s="36">
         <v>36112</v>
       </c>
       <c r="O422" s="33">
@@ -34524,7 +34539,7 @@
       <c r="M423" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N423" s="38">
+      <c r="N423" s="36">
         <v>35178</v>
       </c>
       <c r="O423" s="33">
@@ -34592,7 +34607,7 @@
       <c r="M424" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N424" s="38">
+      <c r="N424" s="36">
         <v>35563</v>
       </c>
       <c r="O424" s="33">
@@ -34660,7 +34675,7 @@
       <c r="M425" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N425" s="38">
+      <c r="N425" s="36">
         <v>34085</v>
       </c>
       <c r="O425" s="33">
@@ -34728,7 +34743,7 @@
       <c r="M426" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N426" s="38">
+      <c r="N426" s="36">
         <v>34275</v>
       </c>
       <c r="O426" s="33">
@@ -34796,7 +34811,7 @@
       <c r="M427" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N427" s="38">
+      <c r="N427" s="36">
         <v>30256</v>
       </c>
       <c r="O427" s="33">
@@ -34864,7 +34879,7 @@
       <c r="M428" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N428" s="38">
+      <c r="N428" s="36">
         <v>28531</v>
       </c>
       <c r="O428" s="33">
@@ -34932,7 +34947,7 @@
       <c r="M429" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="N429" s="38">
+      <c r="N429" s="36">
         <v>34307</v>
       </c>
       <c r="O429" s="33">
@@ -35000,7 +35015,7 @@
       <c r="M430" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="N430" s="38">
+      <c r="N430" s="36">
         <v>24782</v>
       </c>
       <c r="O430" s="33">
@@ -35068,7 +35083,7 @@
       <c r="M431" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N431" s="38">
+      <c r="N431" s="36">
         <v>35973</v>
       </c>
       <c r="O431" s="33">
@@ -35136,7 +35151,7 @@
       <c r="M432" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N432" s="38">
+      <c r="N432" s="36">
         <v>34323</v>
       </c>
       <c r="O432" s="33">
@@ -35206,7 +35221,7 @@
       <c r="M433" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N433" s="38">
+      <c r="N433" s="36">
         <v>37046</v>
       </c>
       <c r="O433" s="33">
@@ -35276,7 +35291,7 @@
       <c r="M434" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N434" s="38">
+      <c r="N434" s="36">
         <v>33361</v>
       </c>
       <c r="O434" s="33">
@@ -35346,7 +35361,7 @@
       <c r="M435" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N435" s="38">
+      <c r="N435" s="36">
         <v>35165</v>
       </c>
       <c r="O435" s="33">
@@ -35416,7 +35431,7 @@
       <c r="M436" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N436" s="38">
+      <c r="N436" s="36">
         <v>35308</v>
       </c>
       <c r="O436" s="33">
@@ -35486,7 +35501,7 @@
       <c r="M437" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N437" s="38">
+      <c r="N437" s="36">
         <v>34753</v>
       </c>
       <c r="O437" s="33">
@@ -35556,7 +35571,7 @@
       <c r="M438" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="N438" s="38">
+      <c r="N438" s="36">
         <v>34693</v>
       </c>
       <c r="O438" s="33">
@@ -35624,7 +35639,7 @@
       <c r="M439" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N439" s="38">
+      <c r="N439" s="36">
         <v>33097</v>
       </c>
       <c r="O439" s="33">
@@ -35692,7 +35707,7 @@
       <c r="M440" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N440" s="38">
+      <c r="N440" s="36">
         <v>33846</v>
       </c>
       <c r="O440" s="33">
@@ -35762,7 +35777,7 @@
       <c r="M441" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N441" s="38">
+      <c r="N441" s="36">
         <v>38113</v>
       </c>
       <c r="O441" s="33">
@@ -35832,7 +35847,7 @@
       <c r="M442" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N442" s="38">
+      <c r="N442" s="36">
         <v>36384</v>
       </c>
       <c r="O442" s="33">
@@ -35902,7 +35917,7 @@
       <c r="M443" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N443" s="38">
+      <c r="N443" s="36">
         <v>35738</v>
       </c>
       <c r="O443" s="33">
@@ -35972,7 +35987,7 @@
       <c r="M444" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N444" s="38">
+      <c r="N444" s="36">
         <v>29218</v>
       </c>
       <c r="O444" s="33">
@@ -36040,7 +36055,7 @@
       <c r="M445" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N445" s="38">
+      <c r="N445" s="36">
         <v>36692</v>
       </c>
       <c r="O445" s="33">
@@ -36110,7 +36125,7 @@
       <c r="M446" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N446" s="38">
+      <c r="N446" s="36">
         <v>37199</v>
       </c>
       <c r="O446" s="33">
@@ -36180,7 +36195,7 @@
       <c r="M447" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N447" s="38">
+      <c r="N447" s="36">
         <v>33432</v>
       </c>
       <c r="O447" s="33">
@@ -36250,7 +36265,7 @@
       <c r="M448" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N448" s="38">
+      <c r="N448" s="36">
         <v>31140</v>
       </c>
       <c r="O448" s="33">
@@ -36285,16 +36300,16 @@
         <v>306530</v>
       </c>
       <c r="B449" s="32" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
       <c r="C449" s="32" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
       <c r="D449" s="31" t="s">
         <v>2</v>
       </c>
       <c r="E449" s="32" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="F449" s="31" t="s">
         <v>1591</v>
@@ -36320,7 +36335,7 @@
       <c r="M449" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="N449" s="38">
+      <c r="N449" s="36">
         <v>33332</v>
       </c>
       <c r="O449" s="33">
@@ -36343,7 +36358,7 @@
       <c r="T449" s="31"/>
       <c r="U449" s="35"/>
       <c r="V449" s="35" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="450" spans="1:22">
@@ -46778,7 +46793,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D3B0B5-E7CA-41F3-B584-8BB10868D96B}">
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.54296875" customWidth="1"/>
@@ -46829,7 +46844,7 @@
         <v>1597</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>1598</v>
@@ -46882,19 +46897,19 @@
         <v>30</v>
       </c>
       <c r="K2" s="8">
-        <v>1175</v>
+        <v>746</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>1605</v>
+        <v>1684</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>1599</v>
+        <v>1685</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="O2" s="8">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="P2" s="8">
         <v>746</v>
@@ -46905,52 +46920,52 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="5">
-        <v>51906</v>
+        <v>39674</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>367</v>
+        <v>215</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1606</v>
+        <v>214</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>1591</v>
       </c>
       <c r="G3" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" s="9">
-        <v>46190</v>
+        <v>46225</v>
       </c>
       <c r="I3" s="9">
-        <v>46219</v>
+        <v>46239</v>
       </c>
       <c r="J3" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K3" s="8">
-        <v>942</v>
+        <v>15</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>1605</v>
+        <v>1684</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>1599</v>
+        <v>1686</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>1650</v>
+        <v>1687</v>
       </c>
       <c r="O3" s="8">
-        <v>390</v>
+        <v>44</v>
       </c>
       <c r="P3" s="8">
-        <v>750</v>
+        <v>44</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>1144</v>
@@ -46958,52 +46973,52 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="5">
-        <v>51908</v>
+        <v>39691</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>371</v>
+        <v>241</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1607</v>
+        <v>1688</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>73</v>
+        <v>244</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>1591</v>
-      </c>
-      <c r="G4" s="8">
-        <v>2</v>
+        <v>1589</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>1139</v>
       </c>
       <c r="H4" s="9">
-        <v>46161</v>
+        <v>46223</v>
       </c>
       <c r="I4" s="9">
-        <v>46220</v>
+        <v>46237</v>
       </c>
       <c r="J4" s="5">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="K4" s="8">
-        <v>776</v>
+        <v>15</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>1605</v>
+        <v>1684</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>1599</v>
+        <v>1686</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>1650</v>
+        <v>1689</v>
       </c>
       <c r="O4" s="8">
-        <v>375</v>
+        <v>33</v>
       </c>
       <c r="P4" s="8">
-        <v>735</v>
+        <v>33</v>
       </c>
       <c r="Q4" s="7" t="s">
         <v>1146</v>
@@ -47011,13 +47026,13 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="5">
-        <v>53848</v>
+        <v>51906</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>572</v>
+        <v>367</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>73</v>
@@ -47029,34 +47044,34 @@
         <v>1591</v>
       </c>
       <c r="G5" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" s="9">
-        <v>46200</v>
+        <v>46220</v>
       </c>
       <c r="I5" s="9">
-        <v>46229</v>
+        <v>46249</v>
       </c>
       <c r="J5" s="5">
         <v>30</v>
       </c>
       <c r="K5" s="8">
-        <v>90</v>
+        <v>912</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>1605</v>
+        <v>1684</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>1599</v>
+        <v>1685</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="O5" s="8">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="P5" s="8">
-        <v>145</v>
+        <v>750</v>
       </c>
       <c r="Q5" s="7" t="s">
         <v>1144</v>
@@ -47064,16 +47079,16 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="5">
-        <v>57143</v>
+        <v>51908</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>693</v>
+        <v>371</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>692</v>
+        <v>1606</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>34</v>
@@ -47085,31 +47100,31 @@
         <v>2</v>
       </c>
       <c r="H6" s="9">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="I6" s="9">
-        <v>46235</v>
+        <v>46250</v>
       </c>
       <c r="J6" s="5">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K6" s="8">
-        <v>21</v>
+        <v>1175</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>1605</v>
+        <v>1684</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>1651</v>
+        <v>1685</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="O6" s="8">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="P6" s="8">
-        <v>36</v>
+        <v>735</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>1146</v>
@@ -47117,13 +47132,13 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="5">
-        <v>59385</v>
+        <v>53848</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>717</v>
+        <v>572</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>73</v>
@@ -47135,107 +47150,107 @@
         <v>1591</v>
       </c>
       <c r="G7" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="9">
-        <v>46191</v>
+        <v>46200</v>
       </c>
       <c r="I7" s="9">
-        <v>46216</v>
+        <v>46229</v>
       </c>
       <c r="J7" s="5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K7" s="8">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>1605</v>
+        <v>1684</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>1599</v>
+        <v>1685</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="O7" s="8">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="P7" s="8">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="5">
-        <v>59401</v>
+        <v>56282</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>729</v>
+        <v>664</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>728</v>
+        <v>663</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>1591</v>
       </c>
       <c r="G8" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="9">
-        <v>46210</v>
+        <v>46224</v>
       </c>
       <c r="I8" s="9">
-        <v>46239</v>
+        <v>46234</v>
       </c>
       <c r="J8" s="5">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="K8" s="8">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>1605</v>
+        <v>1684</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>1599</v>
+        <v>1686</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>1650</v>
+        <v>1690</v>
       </c>
       <c r="O8" s="8">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="P8" s="8">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="5">
-        <v>70535</v>
+        <v>57143</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>886</v>
+        <v>693</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>885</v>
+        <v>692</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>1591</v>
@@ -47244,86 +47259,245 @@
         <v>2</v>
       </c>
       <c r="H9" s="9">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="I9" s="9">
-        <v>46228</v>
+        <v>46235</v>
       </c>
       <c r="J9" s="5">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K9" s="8">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>1605</v>
+        <v>1684</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>1599</v>
+        <v>1686</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="O9" s="8">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="P9" s="8">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="5">
-        <v>74084</v>
+        <v>59401</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>918</v>
+        <v>729</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>917</v>
+        <v>728</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>321</v>
+        <v>48</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>1591</v>
       </c>
       <c r="G10" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="9">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="I10" s="9">
-        <v>46231</v>
+        <v>46239</v>
       </c>
       <c r="J10" s="5">
         <v>30</v>
       </c>
       <c r="K10" s="8">
+        <v>51</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>1684</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>1685</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>1648</v>
+      </c>
+      <c r="O10" s="8">
+        <v>51</v>
+      </c>
+      <c r="P10" s="8">
+        <v>65</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="5">
+        <v>62449</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G11" s="8">
+        <v>1</v>
+      </c>
+      <c r="H11" s="9">
+        <v>46219</v>
+      </c>
+      <c r="I11" s="9">
+        <v>46222</v>
+      </c>
+      <c r="J11" s="5">
+        <v>4</v>
+      </c>
+      <c r="K11" s="8">
+        <v>4</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>1684</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>1686</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>1690</v>
+      </c>
+      <c r="O11" s="8">
+        <v>11</v>
+      </c>
+      <c r="P11" s="8">
+        <v>33</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="5">
+        <v>70535</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>886</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G12" s="8">
+        <v>2</v>
+      </c>
+      <c r="H12" s="9">
+        <v>46214</v>
+      </c>
+      <c r="I12" s="9">
+        <v>46228</v>
+      </c>
+      <c r="J12" s="5">
+        <v>15</v>
+      </c>
+      <c r="K12" s="8">
+        <v>75</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>1684</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>1685</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>1648</v>
+      </c>
+      <c r="O12" s="8">
+        <v>75</v>
+      </c>
+      <c r="P12" s="8">
+        <v>75</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="5">
+        <v>74084</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G13" s="8">
+        <v>2</v>
+      </c>
+      <c r="H13" s="9">
+        <v>46202</v>
+      </c>
+      <c r="I13" s="9">
+        <v>46231</v>
+      </c>
+      <c r="J13" s="5">
+        <v>30</v>
+      </c>
+      <c r="K13" s="8">
         <v>120</v>
       </c>
-      <c r="L10" s="7" t="s">
-        <v>1605</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>1599</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>1650</v>
-      </c>
-      <c r="O10" s="8">
+      <c r="L13" s="7" t="s">
+        <v>1684</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>1685</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>1648</v>
+      </c>
+      <c r="O13" s="8">
         <v>120</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P13" s="8">
         <v>240</v>
       </c>
-      <c r="Q10" s="7" t="s">
+      <c r="Q13" s="7" t="s">
         <v>1146</v>
       </c>
     </row>
@@ -47342,78 +47516,78 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" s="10"/>
-      <c r="C2" s="36">
+      <c r="C2" s="37">
         <v>2026</v>
       </c>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
     </row>
     <row r="3" spans="2:14" ht="15.5">
       <c r="B3" s="11"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
     </row>
     <row r="4" spans="2:14" ht="15.5">
       <c r="B4" s="12"/>
       <c r="C4" s="13" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>1610</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>1611</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="G4" s="13" t="s">
         <v>1612</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="H4" s="13" t="s">
         <v>1613</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="I4" s="14" t="s">
         <v>1614</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="J4" s="14" t="s">
         <v>1615</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="K4" s="14" t="s">
         <v>1616</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="L4" s="14" t="s">
         <v>1617</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="M4" s="14" t="s">
         <v>1618</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="N4" s="14" t="s">
         <v>1619</v>
-      </c>
-      <c r="M4" s="14" t="s">
-        <v>1620</v>
-      </c>
-      <c r="N4" s="14" t="s">
-        <v>1621</v>
       </c>
     </row>
     <row r="5" spans="2:14" ht="15.5">
       <c r="B5" s="15" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="C5" s="16">
         <v>4.2900000000000001E-2</v>
@@ -47454,7 +47628,7 @@
     </row>
     <row r="6" spans="2:14" ht="15.5">
       <c r="B6" s="18" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="C6" s="16">
         <v>9.7999999999999997E-3</v>
@@ -47495,7 +47669,7 @@
     </row>
     <row r="7" spans="2:14" ht="15.5">
       <c r="B7" s="18" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="C7" s="19">
         <v>5.2699999999999997E-2</v>
@@ -47566,7 +47740,7 @@
     </row>
     <row r="10" spans="2:14" ht="16.5" thickTop="1" thickBot="1">
       <c r="B10" s="21" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="C10" s="22">
         <v>5.8400000000000001E-2</v>
@@ -47596,28 +47770,28 @@
     <row r="11" spans="2:14" ht="15" thickTop="1"/>
     <row r="13" spans="2:14">
       <c r="C13" s="24" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="14" spans="2:14">
       <c r="B14" s="25" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="C14" s="27">
-        <v>4.4999999999999997E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D14" s="27">
-        <v>2.0000000000000001E-4</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="E14" s="26">
         <f>SUM(C14:D14)</f>
-        <v>4.6999999999999993E-3</v>
+        <v>5.8000000000000005E-3</v>
       </c>
     </row>
     <row r="15" spans="2:14">
@@ -47628,68 +47802,68 @@
         <v>2.3999999999999998E-3</v>
       </c>
       <c r="D15" s="27">
-        <v>4.0000000000000002E-4</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="E15" s="26">
         <f t="shared" ref="E15:E17" si="0">SUM(C15:D15)</f>
-        <v>2.8E-3</v>
+        <v>3.4999999999999996E-3</v>
       </c>
     </row>
     <row r="16" spans="2:14">
       <c r="B16" s="25" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="C16" s="27">
-        <v>1.17E-2</v>
+        <v>1.2200000000000001E-2</v>
       </c>
       <c r="D16" s="27">
-        <v>2.7000000000000001E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E16" s="26">
         <f t="shared" si="0"/>
-        <v>1.44E-2</v>
+        <v>1.8200000000000001E-2</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="25" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="C17" s="27">
-        <v>2.8999999999999998E-3</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="D17" s="27">
-        <v>6.9999999999999999E-4</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="E17" s="26">
         <f t="shared" si="0"/>
-        <v>3.5999999999999999E-3</v>
+        <v>5.4999999999999997E-3</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="C18" s="26">
         <f>SUM(C14:C17)</f>
-        <v>2.1499999999999998E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="D18" s="26">
         <f>SUM(D14:D17)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.01</v>
       </c>
       <c r="E18" s="26">
         <f>SUM(E14:E17)</f>
-        <v>2.5499999999999998E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="C21" s="25" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="28" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="C22" s="27">
-        <v>5.1999999999999998E-3</v>
+        <v>1.0699999999999999E-2</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -47697,46 +47871,46 @@
         <v>830</v>
       </c>
       <c r="C23" s="27">
-        <v>2.8E-3</v>
+        <v>4.7999999999999996E-3</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="28" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="C24" s="27">
-        <v>1.6299999999999999E-2</v>
+        <v>1.35E-2</v>
       </c>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="28" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="C25" s="27">
-        <v>3.0000000000000001E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
     </row>
     <row r="26" spans="2:5">
       <c r="C26" s="26">
         <f>SUM(C22:C25)</f>
-        <v>2.7299999999999998E-2</v>
+        <v>3.5199999999999995E-2</v>
       </c>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="25" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="C28" s="27">
-        <v>2.0000000000000001E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="25" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="C29" s="27">
         <f>C26-C28</f>
-        <v>2.7099999999999999E-2</v>
+        <v>3.4899999999999994E-2</v>
       </c>
     </row>
   </sheetData>
@@ -47759,33 +47933,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9">
-      <c r="B1" s="37" t="s">
-        <v>1640</v>
-      </c>
-      <c r="C1" s="37"/>
-      <c r="E1" s="37" t="s">
-        <v>1641</v>
-      </c>
-      <c r="F1" s="37"/>
+      <c r="B1" s="38" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C1" s="38"/>
+      <c r="E1" s="38" t="s">
+        <v>1639</v>
+      </c>
+      <c r="F1" s="38"/>
       <c r="H1" s="29" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="I1" s="29" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="2" spans="2:9">
       <c r="B2" s="29" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="F2" s="29" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="H2" s="26">
         <v>1.2E-2</v>
@@ -47796,11 +47970,11 @@
     </row>
     <row r="3" spans="2:9">
       <c r="B3" s="25" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="C3" s="24"/>
       <c r="E3" s="30" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="F3" s="24">
         <v>1</v>
@@ -47808,51 +47982,51 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="25" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="C4" s="24"/>
       <c r="E4" s="30" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="F4" s="24"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="25" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="C5" s="24">
         <v>1</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="F5" s="24"/>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" s="25" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="C6" s="24"/>
       <c r="E6" s="30" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="F6" s="24"/>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" s="25" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="C7" s="24">
         <v>3</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="F7" s="24"/>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="25" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="C8" s="24"/>
     </row>
@@ -47892,7 +48066,7 @@
         <v>1120</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -47909,7 +48083,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -47926,7 +48100,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>1658</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -47943,7 +48117,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -47960,7 +48134,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -47977,7 +48151,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -47994,7 +48168,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -48011,7 +48185,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -48028,7 +48202,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -48045,7 +48219,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -48062,7 +48236,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -48079,7 +48253,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -48096,7 +48270,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -48113,7 +48287,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -48130,7 +48304,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -48147,7 +48321,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -48164,7 +48338,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -48181,7 +48355,7 @@
         <v>2</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -48198,7 +48372,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -48215,7 +48389,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -48232,7 +48406,7 @@
         <v>88</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -48249,7 +48423,7 @@
         <v>2</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -48266,7 +48440,7 @@
         <v>2</v>
       </c>
       <c r="E23" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -48283,7 +48457,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -48300,7 +48474,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -48317,7 +48491,7 @@
         <v>2</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -48334,7 +48508,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -48351,7 +48525,7 @@
         <v>2</v>
       </c>
       <c r="E28" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -48368,7 +48542,7 @@
         <v>2</v>
       </c>
       <c r="E29" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -48385,7 +48559,7 @@
         <v>2</v>
       </c>
       <c r="E30" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -48402,7 +48576,7 @@
         <v>2</v>
       </c>
       <c r="E31" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -48419,7 +48593,7 @@
         <v>2</v>
       </c>
       <c r="E32" s="32" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -48436,7 +48610,7 @@
         <v>2</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -48453,7 +48627,7 @@
         <v>2</v>
       </c>
       <c r="E34" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -48470,7 +48644,7 @@
         <v>2</v>
       </c>
       <c r="E35" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -48487,7 +48661,7 @@
         <v>2</v>
       </c>
       <c r="E36" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -48504,7 +48678,7 @@
         <v>2</v>
       </c>
       <c r="E37" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -48521,7 +48695,7 @@
         <v>2</v>
       </c>
       <c r="E38" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -48538,7 +48712,7 @@
         <v>2</v>
       </c>
       <c r="E39" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -48555,7 +48729,7 @@
         <v>2</v>
       </c>
       <c r="E40" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -48572,7 +48746,7 @@
         <v>2</v>
       </c>
       <c r="E41" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -48589,7 +48763,7 @@
         <v>2</v>
       </c>
       <c r="E42" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -48606,7 +48780,7 @@
         <v>2</v>
       </c>
       <c r="E43" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -48623,7 +48797,7 @@
         <v>2</v>
       </c>
       <c r="E44" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -48640,7 +48814,7 @@
         <v>2</v>
       </c>
       <c r="E45" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -48657,7 +48831,7 @@
         <v>88</v>
       </c>
       <c r="E46" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -48674,7 +48848,7 @@
         <v>2</v>
       </c>
       <c r="E47" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -48691,7 +48865,7 @@
         <v>88</v>
       </c>
       <c r="E48" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -48708,7 +48882,7 @@
         <v>2</v>
       </c>
       <c r="E49" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -48725,7 +48899,7 @@
         <v>2</v>
       </c>
       <c r="E50" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -48742,7 +48916,7 @@
         <v>2</v>
       </c>
       <c r="E51" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -48759,7 +48933,7 @@
         <v>88</v>
       </c>
       <c r="E52" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -48776,7 +48950,7 @@
         <v>88</v>
       </c>
       <c r="E53" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -48793,7 +48967,7 @@
         <v>2</v>
       </c>
       <c r="E54" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -48810,7 +48984,7 @@
         <v>2</v>
       </c>
       <c r="E55" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -48827,7 +49001,7 @@
         <v>2</v>
       </c>
       <c r="E56" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -48844,7 +49018,7 @@
         <v>2</v>
       </c>
       <c r="E57" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -48861,7 +49035,7 @@
         <v>88</v>
       </c>
       <c r="E58" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -48878,7 +49052,7 @@
         <v>2</v>
       </c>
       <c r="E59" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -48895,7 +49069,7 @@
         <v>88</v>
       </c>
       <c r="E60" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -48912,7 +49086,7 @@
         <v>88</v>
       </c>
       <c r="E61" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -48929,7 +49103,7 @@
         <v>2</v>
       </c>
       <c r="E62" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -48946,7 +49120,7 @@
         <v>2</v>
       </c>
       <c r="E63" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -48963,7 +49137,7 @@
         <v>2</v>
       </c>
       <c r="E64" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -48980,7 +49154,7 @@
         <v>2</v>
       </c>
       <c r="E65" s="32" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -48997,7 +49171,7 @@
         <v>2</v>
       </c>
       <c r="E66" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -49014,7 +49188,7 @@
         <v>2</v>
       </c>
       <c r="E67" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -49031,7 +49205,7 @@
         <v>88</v>
       </c>
       <c r="E68" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -49048,7 +49222,7 @@
         <v>2</v>
       </c>
       <c r="E69" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -49065,7 +49239,7 @@
         <v>2</v>
       </c>
       <c r="E70" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -49082,7 +49256,7 @@
         <v>88</v>
       </c>
       <c r="E71" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -49099,7 +49273,7 @@
         <v>2</v>
       </c>
       <c r="E72" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -49116,7 +49290,7 @@
         <v>2</v>
       </c>
       <c r="E73" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -49133,7 +49307,7 @@
         <v>2</v>
       </c>
       <c r="E74" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -49150,7 +49324,7 @@
         <v>2</v>
       </c>
       <c r="E75" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -49167,7 +49341,7 @@
         <v>2</v>
       </c>
       <c r="E76" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -49184,7 +49358,7 @@
         <v>2</v>
       </c>
       <c r="E77" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -49201,7 +49375,7 @@
         <v>2</v>
       </c>
       <c r="E78" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -49218,7 +49392,7 @@
         <v>2</v>
       </c>
       <c r="E79" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -49235,7 +49409,7 @@
         <v>2</v>
       </c>
       <c r="E80" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -49252,7 +49426,7 @@
         <v>2</v>
       </c>
       <c r="E81" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -49269,7 +49443,7 @@
         <v>2</v>
       </c>
       <c r="E82" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -49286,7 +49460,7 @@
         <v>2</v>
       </c>
       <c r="E83" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -49303,7 +49477,7 @@
         <v>2</v>
       </c>
       <c r="E84" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -49320,7 +49494,7 @@
         <v>2</v>
       </c>
       <c r="E85" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -49337,7 +49511,7 @@
         <v>2</v>
       </c>
       <c r="E86" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -49354,7 +49528,7 @@
         <v>2</v>
       </c>
       <c r="E87" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -49371,7 +49545,7 @@
         <v>88</v>
       </c>
       <c r="E88" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -49388,7 +49562,7 @@
         <v>88</v>
       </c>
       <c r="E89" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -49405,7 +49579,7 @@
         <v>2</v>
       </c>
       <c r="E90" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -49422,7 +49596,7 @@
         <v>2</v>
       </c>
       <c r="E91" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -49439,7 +49613,7 @@
         <v>2</v>
       </c>
       <c r="E92" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -49456,7 +49630,7 @@
         <v>88</v>
       </c>
       <c r="E93" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -49473,7 +49647,7 @@
         <v>88</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -49490,7 +49664,7 @@
         <v>88</v>
       </c>
       <c r="E95" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -49507,7 +49681,7 @@
         <v>2</v>
       </c>
       <c r="E96" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -49524,7 +49698,7 @@
         <v>2</v>
       </c>
       <c r="E97" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -49541,7 +49715,7 @@
         <v>2</v>
       </c>
       <c r="E98" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -49558,7 +49732,7 @@
         <v>2</v>
       </c>
       <c r="E99" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -49575,7 +49749,7 @@
         <v>2</v>
       </c>
       <c r="E100" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -49592,7 +49766,7 @@
         <v>2</v>
       </c>
       <c r="E101" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -49609,7 +49783,7 @@
         <v>2</v>
       </c>
       <c r="E102" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -49626,7 +49800,7 @@
         <v>2</v>
       </c>
       <c r="E103" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -49643,7 +49817,7 @@
         <v>88</v>
       </c>
       <c r="E104" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -49660,7 +49834,7 @@
         <v>2</v>
       </c>
       <c r="E105" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -49677,7 +49851,7 @@
         <v>2</v>
       </c>
       <c r="E106" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -49694,7 +49868,7 @@
         <v>2</v>
       </c>
       <c r="E107" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -49711,7 +49885,7 @@
         <v>2</v>
       </c>
       <c r="E108" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -49728,7 +49902,7 @@
         <v>2</v>
       </c>
       <c r="E109" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -49745,7 +49919,7 @@
         <v>2</v>
       </c>
       <c r="E110" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -49762,7 +49936,7 @@
         <v>2</v>
       </c>
       <c r="E111" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -49779,7 +49953,7 @@
         <v>2</v>
       </c>
       <c r="E112" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -49796,7 +49970,7 @@
         <v>2</v>
       </c>
       <c r="E113" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -49813,7 +49987,7 @@
         <v>2</v>
       </c>
       <c r="E114" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -49830,7 +50004,7 @@
         <v>2</v>
       </c>
       <c r="E115" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -49847,7 +50021,7 @@
         <v>2</v>
       </c>
       <c r="E116" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -49864,7 +50038,7 @@
         <v>2</v>
       </c>
       <c r="E117" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -49881,7 +50055,7 @@
         <v>2</v>
       </c>
       <c r="E118" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -49898,7 +50072,7 @@
         <v>2</v>
       </c>
       <c r="E119" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -49915,7 +50089,7 @@
         <v>2</v>
       </c>
       <c r="E120" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -49932,7 +50106,7 @@
         <v>2</v>
       </c>
       <c r="E121" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -49949,7 +50123,7 @@
         <v>2</v>
       </c>
       <c r="E122" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -49966,7 +50140,7 @@
         <v>2</v>
       </c>
       <c r="E123" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -49983,7 +50157,7 @@
         <v>2</v>
       </c>
       <c r="E124" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -50000,7 +50174,7 @@
         <v>2</v>
       </c>
       <c r="E125" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -50017,7 +50191,7 @@
         <v>2</v>
       </c>
       <c r="E126" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -50034,7 +50208,7 @@
         <v>2</v>
       </c>
       <c r="E127" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -50051,7 +50225,7 @@
         <v>2</v>
       </c>
       <c r="E128" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -50068,7 +50242,7 @@
         <v>2</v>
       </c>
       <c r="E129" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -50085,7 +50259,7 @@
         <v>2</v>
       </c>
       <c r="E130" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -50102,7 +50276,7 @@
         <v>2</v>
       </c>
       <c r="E131" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -50119,7 +50293,7 @@
         <v>2</v>
       </c>
       <c r="E132" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -50136,7 +50310,7 @@
         <v>2</v>
       </c>
       <c r="E133" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -50153,7 +50327,7 @@
         <v>2</v>
       </c>
       <c r="E134" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -50170,7 +50344,7 @@
         <v>2</v>
       </c>
       <c r="E135" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -50187,7 +50361,7 @@
         <v>2</v>
       </c>
       <c r="E136" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -50204,7 +50378,7 @@
         <v>2</v>
       </c>
       <c r="E137" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -50221,7 +50395,7 @@
         <v>2</v>
       </c>
       <c r="E138" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -50238,7 +50412,7 @@
         <v>2</v>
       </c>
       <c r="E139" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -50255,7 +50429,7 @@
         <v>2</v>
       </c>
       <c r="E140" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -50272,7 +50446,7 @@
         <v>2</v>
       </c>
       <c r="E141" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -50289,7 +50463,7 @@
         <v>2</v>
       </c>
       <c r="E142" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -50306,7 +50480,7 @@
         <v>2</v>
       </c>
       <c r="E143" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -50323,7 +50497,7 @@
         <v>2</v>
       </c>
       <c r="E144" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -50340,7 +50514,7 @@
         <v>2</v>
       </c>
       <c r="E145" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -50357,7 +50531,7 @@
         <v>2</v>
       </c>
       <c r="E146" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -50374,7 +50548,7 @@
         <v>2</v>
       </c>
       <c r="E147" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -50391,7 +50565,7 @@
         <v>2</v>
       </c>
       <c r="E148" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -50408,7 +50582,7 @@
         <v>2</v>
       </c>
       <c r="E149" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -50425,7 +50599,7 @@
         <v>2</v>
       </c>
       <c r="E150" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -50442,7 +50616,7 @@
         <v>2</v>
       </c>
       <c r="E151" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -50459,7 +50633,7 @@
         <v>2</v>
       </c>
       <c r="E152" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -50476,7 +50650,7 @@
         <v>2</v>
       </c>
       <c r="E153" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -50493,7 +50667,7 @@
         <v>2</v>
       </c>
       <c r="E154" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -50510,7 +50684,7 @@
         <v>2</v>
       </c>
       <c r="E155" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -50527,7 +50701,7 @@
         <v>2</v>
       </c>
       <c r="E156" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -50544,7 +50718,7 @@
         <v>2</v>
       </c>
       <c r="E157" s="32" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -50561,7 +50735,7 @@
         <v>2</v>
       </c>
       <c r="E158" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -50578,7 +50752,7 @@
         <v>2</v>
       </c>
       <c r="E159" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -50595,7 +50769,7 @@
         <v>2</v>
       </c>
       <c r="E160" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -50612,7 +50786,7 @@
         <v>2</v>
       </c>
       <c r="E161" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -50629,7 +50803,7 @@
         <v>2</v>
       </c>
       <c r="E162" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -50646,7 +50820,7 @@
         <v>2</v>
       </c>
       <c r="E163" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -50663,7 +50837,7 @@
         <v>2</v>
       </c>
       <c r="E164" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -50680,7 +50854,7 @@
         <v>2</v>
       </c>
       <c r="E165" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -50697,7 +50871,7 @@
         <v>2</v>
       </c>
       <c r="E166" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -50714,7 +50888,7 @@
         <v>2</v>
       </c>
       <c r="E167" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -50731,7 +50905,7 @@
         <v>2</v>
       </c>
       <c r="E168" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -50748,7 +50922,7 @@
         <v>2</v>
       </c>
       <c r="E169" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -50765,7 +50939,7 @@
         <v>2</v>
       </c>
       <c r="E170" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -50782,7 +50956,7 @@
         <v>2</v>
       </c>
       <c r="E171" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -50799,7 +50973,7 @@
         <v>2</v>
       </c>
       <c r="E172" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -50816,7 +50990,7 @@
         <v>2</v>
       </c>
       <c r="E173" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -50833,7 +51007,7 @@
         <v>2</v>
       </c>
       <c r="E174" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -50850,7 +51024,7 @@
         <v>2</v>
       </c>
       <c r="E175" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -50867,7 +51041,7 @@
         <v>2</v>
       </c>
       <c r="E176" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -50884,7 +51058,7 @@
         <v>2</v>
       </c>
       <c r="E177" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -50901,7 +51075,7 @@
         <v>2</v>
       </c>
       <c r="E178" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -50918,7 +51092,7 @@
         <v>2</v>
       </c>
       <c r="E179" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -50935,7 +51109,7 @@
         <v>2</v>
       </c>
       <c r="E180" s="32" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -50952,7 +51126,7 @@
         <v>2</v>
       </c>
       <c r="E181" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -50969,7 +51143,7 @@
         <v>2</v>
       </c>
       <c r="E182" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -50986,7 +51160,7 @@
         <v>2</v>
       </c>
       <c r="E183" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -51003,7 +51177,7 @@
         <v>2</v>
       </c>
       <c r="E184" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -51020,7 +51194,7 @@
         <v>2</v>
       </c>
       <c r="E185" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -51037,7 +51211,7 @@
         <v>2</v>
       </c>
       <c r="E186" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -51054,7 +51228,7 @@
         <v>2</v>
       </c>
       <c r="E187" s="32" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -51071,7 +51245,7 @@
         <v>2</v>
       </c>
       <c r="E188" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -51088,7 +51262,7 @@
         <v>2</v>
       </c>
       <c r="E189" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -51105,7 +51279,7 @@
         <v>2</v>
       </c>
       <c r="E190" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -51122,7 +51296,7 @@
         <v>2</v>
       </c>
       <c r="E191" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -51139,7 +51313,7 @@
         <v>88</v>
       </c>
       <c r="E192" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -51156,7 +51330,7 @@
         <v>2</v>
       </c>
       <c r="E193" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -51173,7 +51347,7 @@
         <v>2</v>
       </c>
       <c r="E194" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -51190,7 +51364,7 @@
         <v>2</v>
       </c>
       <c r="E195" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -51207,7 +51381,7 @@
         <v>2</v>
       </c>
       <c r="E196" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -51224,7 +51398,7 @@
         <v>2</v>
       </c>
       <c r="E197" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -51241,7 +51415,7 @@
         <v>2</v>
       </c>
       <c r="E198" s="32" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -51258,7 +51432,7 @@
         <v>2</v>
       </c>
       <c r="E199" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -51275,7 +51449,7 @@
         <v>2</v>
       </c>
       <c r="E200" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -51292,7 +51466,7 @@
         <v>2</v>
       </c>
       <c r="E201" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -51309,7 +51483,7 @@
         <v>2</v>
       </c>
       <c r="E202" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -51326,7 +51500,7 @@
         <v>2</v>
       </c>
       <c r="E203" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -51343,7 +51517,7 @@
         <v>2</v>
       </c>
       <c r="E204" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -51360,7 +51534,7 @@
         <v>2</v>
       </c>
       <c r="E205" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -51377,7 +51551,7 @@
         <v>2</v>
       </c>
       <c r="E206" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -51394,7 +51568,7 @@
         <v>2</v>
       </c>
       <c r="E207" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -51411,7 +51585,7 @@
         <v>2</v>
       </c>
       <c r="E208" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -51428,7 +51602,7 @@
         <v>2</v>
       </c>
       <c r="E209" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -51445,7 +51619,7 @@
         <v>2</v>
       </c>
       <c r="E210" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -51462,7 +51636,7 @@
         <v>2</v>
       </c>
       <c r="E211" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -51479,7 +51653,7 @@
         <v>2</v>
       </c>
       <c r="E212" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -51496,7 +51670,7 @@
         <v>2</v>
       </c>
       <c r="E213" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -51513,7 +51687,7 @@
         <v>2</v>
       </c>
       <c r="E214" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -51530,7 +51704,7 @@
         <v>2</v>
       </c>
       <c r="E215" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -51547,7 +51721,7 @@
         <v>2</v>
       </c>
       <c r="E216" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -51564,7 +51738,7 @@
         <v>2</v>
       </c>
       <c r="E217" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -51581,7 +51755,7 @@
         <v>2</v>
       </c>
       <c r="E218" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -51598,7 +51772,7 @@
         <v>2</v>
       </c>
       <c r="E219" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -51615,7 +51789,7 @@
         <v>2</v>
       </c>
       <c r="E220" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -51632,7 +51806,7 @@
         <v>88</v>
       </c>
       <c r="E221" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -51649,7 +51823,7 @@
         <v>2</v>
       </c>
       <c r="E222" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -51666,7 +51840,7 @@
         <v>2</v>
       </c>
       <c r="E223" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -51683,7 +51857,7 @@
         <v>2</v>
       </c>
       <c r="E224" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -51700,7 +51874,7 @@
         <v>2</v>
       </c>
       <c r="E225" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -51717,7 +51891,7 @@
         <v>2</v>
       </c>
       <c r="E226" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -51734,7 +51908,7 @@
         <v>2</v>
       </c>
       <c r="E227" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -51751,7 +51925,7 @@
         <v>2</v>
       </c>
       <c r="E228" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -51768,7 +51942,7 @@
         <v>2</v>
       </c>
       <c r="E229" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -51785,7 +51959,7 @@
         <v>2</v>
       </c>
       <c r="E230" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -51802,7 +51976,7 @@
         <v>2</v>
       </c>
       <c r="E231" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -51819,7 +51993,7 @@
         <v>2</v>
       </c>
       <c r="E232" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -51836,7 +52010,7 @@
         <v>2</v>
       </c>
       <c r="E233" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -51853,7 +52027,7 @@
         <v>2</v>
       </c>
       <c r="E234" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -51870,7 +52044,7 @@
         <v>2</v>
       </c>
       <c r="E235" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -51887,7 +52061,7 @@
         <v>2</v>
       </c>
       <c r="E236" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -51904,7 +52078,7 @@
         <v>2</v>
       </c>
       <c r="E237" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -51921,7 +52095,7 @@
         <v>88</v>
       </c>
       <c r="E238" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -51938,7 +52112,7 @@
         <v>2</v>
       </c>
       <c r="E239" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -51955,7 +52129,7 @@
         <v>2</v>
       </c>
       <c r="E240" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -51972,7 +52146,7 @@
         <v>2</v>
       </c>
       <c r="E241" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -51989,7 +52163,7 @@
         <v>2</v>
       </c>
       <c r="E242" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -52006,7 +52180,7 @@
         <v>2</v>
       </c>
       <c r="E243" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -52023,7 +52197,7 @@
         <v>2</v>
       </c>
       <c r="E244" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -52040,7 +52214,7 @@
         <v>2</v>
       </c>
       <c r="E245" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -52057,7 +52231,7 @@
         <v>2</v>
       </c>
       <c r="E246" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -52074,7 +52248,7 @@
         <v>88</v>
       </c>
       <c r="E247" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -52091,7 +52265,7 @@
         <v>2</v>
       </c>
       <c r="E248" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -52108,7 +52282,7 @@
         <v>2</v>
       </c>
       <c r="E249" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -52125,7 +52299,7 @@
         <v>2</v>
       </c>
       <c r="E250" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -52142,7 +52316,7 @@
         <v>2</v>
       </c>
       <c r="E251" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -52159,7 +52333,7 @@
         <v>2</v>
       </c>
       <c r="E252" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -52176,7 +52350,7 @@
         <v>2</v>
       </c>
       <c r="E253" s="32" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -52193,7 +52367,7 @@
         <v>2</v>
       </c>
       <c r="E254" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -52210,7 +52384,7 @@
         <v>2</v>
       </c>
       <c r="E255" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -52227,7 +52401,7 @@
         <v>2</v>
       </c>
       <c r="E256" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -52244,7 +52418,7 @@
         <v>88</v>
       </c>
       <c r="E257" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -52261,7 +52435,7 @@
         <v>2</v>
       </c>
       <c r="E258" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -52278,7 +52452,7 @@
         <v>2</v>
       </c>
       <c r="E259" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -52295,7 +52469,7 @@
         <v>2</v>
       </c>
       <c r="E260" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -52312,7 +52486,7 @@
         <v>2</v>
       </c>
       <c r="E261" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -52329,7 +52503,7 @@
         <v>2</v>
       </c>
       <c r="E262" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -52346,7 +52520,7 @@
         <v>2</v>
       </c>
       <c r="E263" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -52363,7 +52537,7 @@
         <v>2</v>
       </c>
       <c r="E264" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -52380,7 +52554,7 @@
         <v>2</v>
       </c>
       <c r="E265" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -52397,7 +52571,7 @@
         <v>2</v>
       </c>
       <c r="E266" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -52414,7 +52588,7 @@
         <v>2</v>
       </c>
       <c r="E267" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -52422,16 +52596,16 @@
         <v>57468</v>
       </c>
       <c r="B268" s="32" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
       <c r="C268" s="32" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
       <c r="D268" s="31" t="s">
         <v>2</v>
       </c>
       <c r="E268" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -52448,7 +52622,7 @@
         <v>2</v>
       </c>
       <c r="E269" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -52465,7 +52639,7 @@
         <v>2</v>
       </c>
       <c r="E270" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -52482,7 +52656,7 @@
         <v>88</v>
       </c>
       <c r="E271" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -52499,7 +52673,7 @@
         <v>2</v>
       </c>
       <c r="E272" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -52516,7 +52690,7 @@
         <v>2</v>
       </c>
       <c r="E273" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -52533,7 +52707,7 @@
         <v>2</v>
       </c>
       <c r="E274" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -52550,7 +52724,7 @@
         <v>2</v>
       </c>
       <c r="E275" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -52567,7 +52741,7 @@
         <v>2</v>
       </c>
       <c r="E276" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -52584,7 +52758,7 @@
         <v>2</v>
       </c>
       <c r="E277" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -52601,7 +52775,7 @@
         <v>2</v>
       </c>
       <c r="E278" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -52618,7 +52792,7 @@
         <v>2</v>
       </c>
       <c r="E279" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -52635,7 +52809,7 @@
         <v>2</v>
       </c>
       <c r="E280" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -52652,7 +52826,7 @@
         <v>2</v>
       </c>
       <c r="E281" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -52669,7 +52843,7 @@
         <v>2</v>
       </c>
       <c r="E282" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -52686,7 +52860,7 @@
         <v>2</v>
       </c>
       <c r="E283" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -52703,7 +52877,7 @@
         <v>2</v>
       </c>
       <c r="E284" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -52720,7 +52894,7 @@
         <v>2</v>
       </c>
       <c r="E285" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -52737,7 +52911,7 @@
         <v>88</v>
       </c>
       <c r="E286" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -52754,7 +52928,7 @@
         <v>2</v>
       </c>
       <c r="E287" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -52771,7 +52945,7 @@
         <v>88</v>
       </c>
       <c r="E288" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -52788,7 +52962,7 @@
         <v>2</v>
       </c>
       <c r="E289" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -52805,7 +52979,7 @@
         <v>88</v>
       </c>
       <c r="E290" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -52822,7 +52996,7 @@
         <v>2</v>
       </c>
       <c r="E291" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -52839,7 +53013,7 @@
         <v>2</v>
       </c>
       <c r="E292" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -52856,7 +53030,7 @@
         <v>2</v>
       </c>
       <c r="E293" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -52873,7 +53047,7 @@
         <v>2</v>
       </c>
       <c r="E294" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -52890,7 +53064,7 @@
         <v>2</v>
       </c>
       <c r="E295" s="32" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -52907,7 +53081,7 @@
         <v>2</v>
       </c>
       <c r="E296" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -52924,7 +53098,7 @@
         <v>88</v>
       </c>
       <c r="E297" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -52941,7 +53115,7 @@
         <v>2</v>
       </c>
       <c r="E298" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -52958,7 +53132,7 @@
         <v>2</v>
       </c>
       <c r="E299" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -52975,7 +53149,7 @@
         <v>2</v>
       </c>
       <c r="E300" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -52992,7 +53166,7 @@
         <v>2</v>
       </c>
       <c r="E301" s="32" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -53009,7 +53183,7 @@
         <v>2</v>
       </c>
       <c r="E302" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -53026,7 +53200,7 @@
         <v>2</v>
       </c>
       <c r="E303" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -53043,7 +53217,7 @@
         <v>2</v>
       </c>
       <c r="E304" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -53060,7 +53234,7 @@
         <v>88</v>
       </c>
       <c r="E305" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -53077,7 +53251,7 @@
         <v>2</v>
       </c>
       <c r="E306" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -53094,7 +53268,7 @@
         <v>2</v>
       </c>
       <c r="E307" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -53111,7 +53285,7 @@
         <v>2</v>
       </c>
       <c r="E308" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -53128,7 +53302,7 @@
         <v>2</v>
       </c>
       <c r="E309" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -53145,7 +53319,7 @@
         <v>2</v>
       </c>
       <c r="E310" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -53162,7 +53336,7 @@
         <v>2</v>
       </c>
       <c r="E311" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -53179,7 +53353,7 @@
         <v>2</v>
       </c>
       <c r="E312" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -53196,7 +53370,7 @@
         <v>88</v>
       </c>
       <c r="E313" s="32" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -53213,7 +53387,7 @@
         <v>88</v>
       </c>
       <c r="E314" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -53230,7 +53404,7 @@
         <v>2</v>
       </c>
       <c r="E315" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -53247,7 +53421,7 @@
         <v>2</v>
       </c>
       <c r="E316" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -53264,7 +53438,7 @@
         <v>2</v>
       </c>
       <c r="E317" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -53281,7 +53455,7 @@
         <v>2</v>
       </c>
       <c r="E318" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -53298,7 +53472,7 @@
         <v>2</v>
       </c>
       <c r="E319" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -53315,7 +53489,7 @@
         <v>88</v>
       </c>
       <c r="E320" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -53332,7 +53506,7 @@
         <v>88</v>
       </c>
       <c r="E321" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -53349,7 +53523,7 @@
         <v>88</v>
       </c>
       <c r="E322" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -53366,7 +53540,7 @@
         <v>88</v>
       </c>
       <c r="E323" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -53383,7 +53557,7 @@
         <v>2</v>
       </c>
       <c r="E324" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -53400,7 +53574,7 @@
         <v>88</v>
       </c>
       <c r="E325" s="32" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -53417,7 +53591,7 @@
         <v>2</v>
       </c>
       <c r="E326" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -53434,7 +53608,7 @@
         <v>2</v>
       </c>
       <c r="E327" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -53451,7 +53625,7 @@
         <v>2</v>
       </c>
       <c r="E328" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -53468,7 +53642,7 @@
         <v>2</v>
       </c>
       <c r="E329" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -53485,7 +53659,7 @@
         <v>2</v>
       </c>
       <c r="E330" s="32" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -53502,7 +53676,7 @@
         <v>2</v>
       </c>
       <c r="E331" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -53519,7 +53693,7 @@
         <v>2</v>
       </c>
       <c r="E332" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -53536,7 +53710,7 @@
         <v>2</v>
       </c>
       <c r="E333" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -53553,7 +53727,7 @@
         <v>2</v>
       </c>
       <c r="E334" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -53570,7 +53744,7 @@
         <v>2</v>
       </c>
       <c r="E335" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -53587,7 +53761,7 @@
         <v>2</v>
       </c>
       <c r="E336" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -53604,7 +53778,7 @@
         <v>88</v>
       </c>
       <c r="E337" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -53621,7 +53795,7 @@
         <v>2</v>
       </c>
       <c r="E338" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -53638,7 +53812,7 @@
         <v>88</v>
       </c>
       <c r="E339" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -53655,7 +53829,7 @@
         <v>2</v>
       </c>
       <c r="E340" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -53672,7 +53846,7 @@
         <v>2</v>
       </c>
       <c r="E341" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -53689,7 +53863,7 @@
         <v>2</v>
       </c>
       <c r="E342" s="32" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -53706,7 +53880,7 @@
         <v>2</v>
       </c>
       <c r="E343" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -53723,7 +53897,7 @@
         <v>2</v>
       </c>
       <c r="E344" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -53740,7 +53914,7 @@
         <v>2</v>
       </c>
       <c r="E345" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -53757,7 +53931,7 @@
         <v>2</v>
       </c>
       <c r="E346" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -53774,7 +53948,7 @@
         <v>2</v>
       </c>
       <c r="E347" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -53791,7 +53965,7 @@
         <v>2</v>
       </c>
       <c r="E348" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -53808,7 +53982,7 @@
         <v>2</v>
       </c>
       <c r="E349" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -53825,7 +53999,7 @@
         <v>2</v>
       </c>
       <c r="E350" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -53842,7 +54016,7 @@
         <v>2</v>
       </c>
       <c r="E351" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -53859,7 +54033,7 @@
         <v>2</v>
       </c>
       <c r="E352" s="32" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -53876,7 +54050,7 @@
         <v>88</v>
       </c>
       <c r="E353" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -53893,7 +54067,7 @@
         <v>88</v>
       </c>
       <c r="E354" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -53910,7 +54084,7 @@
         <v>2</v>
       </c>
       <c r="E355" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -53927,7 +54101,7 @@
         <v>2</v>
       </c>
       <c r="E356" s="32" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -53944,7 +54118,7 @@
         <v>88</v>
       </c>
       <c r="E357" s="32" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -53961,7 +54135,7 @@
         <v>2</v>
       </c>
       <c r="E358" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -53978,7 +54152,7 @@
         <v>2</v>
       </c>
       <c r="E359" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -53995,7 +54169,7 @@
         <v>88</v>
       </c>
       <c r="E360" s="32" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -54012,7 +54186,7 @@
         <v>88</v>
       </c>
       <c r="E361" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -54029,7 +54203,7 @@
         <v>2</v>
       </c>
       <c r="E362" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -54046,7 +54220,7 @@
         <v>88</v>
       </c>
       <c r="E363" s="32" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -54063,7 +54237,7 @@
         <v>2</v>
       </c>
       <c r="E364" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -54080,7 +54254,7 @@
         <v>88</v>
       </c>
       <c r="E365" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -54097,7 +54271,7 @@
         <v>2</v>
       </c>
       <c r="E366" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -54114,7 +54288,7 @@
         <v>2</v>
       </c>
       <c r="E367" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -54131,7 +54305,7 @@
         <v>2</v>
       </c>
       <c r="E368" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -54148,7 +54322,7 @@
         <v>2</v>
       </c>
       <c r="E369" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -54165,7 +54339,7 @@
         <v>2</v>
       </c>
       <c r="E370" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -54182,7 +54356,7 @@
         <v>2</v>
       </c>
       <c r="E371" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -54199,7 +54373,7 @@
         <v>2</v>
       </c>
       <c r="E372" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -54216,7 +54390,7 @@
         <v>2</v>
       </c>
       <c r="E373" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -54233,7 +54407,7 @@
         <v>2</v>
       </c>
       <c r="E374" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -54250,7 +54424,7 @@
         <v>2</v>
       </c>
       <c r="E375" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -54267,7 +54441,7 @@
         <v>2</v>
       </c>
       <c r="E376" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -54284,7 +54458,7 @@
         <v>2</v>
       </c>
       <c r="E377" s="32" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -54301,7 +54475,7 @@
         <v>2</v>
       </c>
       <c r="E378" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -54318,7 +54492,7 @@
         <v>2</v>
       </c>
       <c r="E379" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -54335,7 +54509,7 @@
         <v>88</v>
       </c>
       <c r="E380" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -54352,7 +54526,7 @@
         <v>2</v>
       </c>
       <c r="E381" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -54369,7 +54543,7 @@
         <v>2</v>
       </c>
       <c r="E382" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -54386,7 +54560,7 @@
         <v>2</v>
       </c>
       <c r="E383" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -54403,7 +54577,7 @@
         <v>2</v>
       </c>
       <c r="E384" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -54420,7 +54594,7 @@
         <v>2</v>
       </c>
       <c r="E385" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -54437,7 +54611,7 @@
         <v>2</v>
       </c>
       <c r="E386" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -54454,7 +54628,7 @@
         <v>2</v>
       </c>
       <c r="E387" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -54471,7 +54645,7 @@
         <v>2</v>
       </c>
       <c r="E388" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -54488,7 +54662,7 @@
         <v>2</v>
       </c>
       <c r="E389" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -54505,7 +54679,7 @@
         <v>2</v>
       </c>
       <c r="E390" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -54522,7 +54696,7 @@
         <v>2</v>
       </c>
       <c r="E391" s="32" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -54539,7 +54713,7 @@
         <v>2</v>
       </c>
       <c r="E392" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -54556,7 +54730,7 @@
         <v>2</v>
       </c>
       <c r="E393" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -54573,7 +54747,7 @@
         <v>88</v>
       </c>
       <c r="E394" s="32" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -54590,7 +54764,7 @@
         <v>88</v>
       </c>
       <c r="E395" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -54607,7 +54781,7 @@
         <v>2</v>
       </c>
       <c r="E396" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -54624,7 +54798,7 @@
         <v>2</v>
       </c>
       <c r="E397" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -54641,7 +54815,7 @@
         <v>2</v>
       </c>
       <c r="E398" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -54658,7 +54832,7 @@
         <v>2</v>
       </c>
       <c r="E399" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -54675,7 +54849,7 @@
         <v>2</v>
       </c>
       <c r="E400" s="32" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -54692,7 +54866,7 @@
         <v>2</v>
       </c>
       <c r="E401" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -54709,7 +54883,7 @@
         <v>2</v>
       </c>
       <c r="E402" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -54726,7 +54900,7 @@
         <v>2</v>
       </c>
       <c r="E403" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -54743,7 +54917,7 @@
         <v>88</v>
       </c>
       <c r="E404" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -54760,7 +54934,7 @@
         <v>2</v>
       </c>
       <c r="E405" s="32" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -54777,7 +54951,7 @@
         <v>2</v>
       </c>
       <c r="E406" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -54794,7 +54968,7 @@
         <v>2</v>
       </c>
       <c r="E407" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -54811,7 +54985,7 @@
         <v>2</v>
       </c>
       <c r="E408" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -54828,7 +55002,7 @@
         <v>2</v>
       </c>
       <c r="E409" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -54845,7 +55019,7 @@
         <v>2</v>
       </c>
       <c r="E410" s="32" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -54862,7 +55036,7 @@
         <v>2</v>
       </c>
       <c r="E411" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -54879,7 +55053,7 @@
         <v>2</v>
       </c>
       <c r="E412" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -54896,7 +55070,7 @@
         <v>2</v>
       </c>
       <c r="E413" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -54913,7 +55087,7 @@
         <v>2</v>
       </c>
       <c r="E414" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -54930,7 +55104,7 @@
         <v>2</v>
       </c>
       <c r="E415" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -54947,7 +55121,7 @@
         <v>88</v>
       </c>
       <c r="E416" s="32" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -54964,7 +55138,7 @@
         <v>2</v>
       </c>
       <c r="E417" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -54981,7 +55155,7 @@
         <v>2</v>
       </c>
       <c r="E418" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -54998,7 +55172,7 @@
         <v>88</v>
       </c>
       <c r="E419" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -55015,7 +55189,7 @@
         <v>88</v>
       </c>
       <c r="E420" s="32" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -55032,7 +55206,7 @@
         <v>88</v>
       </c>
       <c r="E421" s="32" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -55049,7 +55223,7 @@
         <v>88</v>
       </c>
       <c r="E422" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -55066,7 +55240,7 @@
         <v>88</v>
       </c>
       <c r="E423" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -55083,7 +55257,7 @@
         <v>2</v>
       </c>
       <c r="E424" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -55100,7 +55274,7 @@
         <v>2</v>
       </c>
       <c r="E425" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -55117,7 +55291,7 @@
         <v>2</v>
       </c>
       <c r="E426" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -55134,7 +55308,7 @@
         <v>2</v>
       </c>
       <c r="E427" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -55151,7 +55325,7 @@
         <v>2</v>
       </c>
       <c r="E428" s="32" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -55168,7 +55342,7 @@
         <v>2</v>
       </c>
       <c r="E429" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -55185,7 +55359,7 @@
         <v>2</v>
       </c>
       <c r="E430" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -55202,7 +55376,7 @@
         <v>2</v>
       </c>
       <c r="E431" s="32" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -55219,7 +55393,7 @@
         <v>2</v>
       </c>
       <c r="E432" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -55236,7 +55410,7 @@
         <v>2</v>
       </c>
       <c r="E433" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -55253,7 +55427,7 @@
         <v>2</v>
       </c>
       <c r="E434" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -55270,7 +55444,7 @@
         <v>2</v>
       </c>
       <c r="E435" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -55287,7 +55461,7 @@
         <v>2</v>
       </c>
       <c r="E436" s="32" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -55304,7 +55478,7 @@
         <v>88</v>
       </c>
       <c r="E437" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -55321,7 +55495,7 @@
         <v>88</v>
       </c>
       <c r="E438" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -55338,7 +55512,7 @@
         <v>2</v>
       </c>
       <c r="E439" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -55355,7 +55529,7 @@
         <v>2</v>
       </c>
       <c r="E440" s="32" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -55372,7 +55546,7 @@
         <v>88</v>
       </c>
       <c r="E441" s="32" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -55389,7 +55563,7 @@
         <v>88</v>
       </c>
       <c r="E442" s="32" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -55406,7 +55580,7 @@
         <v>2</v>
       </c>
       <c r="E443" s="32" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -55423,7 +55597,7 @@
         <v>88</v>
       </c>
       <c r="E444" s="32" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -55440,7 +55614,7 @@
         <v>2</v>
       </c>
       <c r="E445" s="32" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -55457,7 +55631,7 @@
         <v>2</v>
       </c>
       <c r="E446" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -55474,7 +55648,7 @@
         <v>2</v>
       </c>
       <c r="E447" s="32" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -55491,7 +55665,7 @@
         <v>2</v>
       </c>
       <c r="E448" s="32" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -55508,7 +55682,7 @@
         <v>88</v>
       </c>
       <c r="E449" s="32" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baray020\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E03D7DC-0641-42EF-97F2-85705711621C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F2D440-7E17-466B-A952-5A408B32AEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="1740" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1890" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dotaci" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7928" uniqueCount="1692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7938" uniqueCount="1692">
   <si>
     <t>HENRIQUEZ POOL FELIPE ALBERTO</t>
   </si>
@@ -4987,9 +4987,6 @@
     <t>Acum.</t>
   </si>
   <si>
-    <t xml:space="preserve">Traumatología </t>
-  </si>
-  <si>
     <t>VASQUEZ MARTINEZ CAMILO ANTONIO</t>
   </si>
   <si>
@@ -5095,28 +5092,31 @@
     <t>Concepción</t>
   </si>
   <si>
-    <t>Medicina Curatica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Continuación </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nueva </t>
-  </si>
-  <si>
     <t xml:space="preserve">CirugíaVascular Periférica </t>
   </si>
   <si>
     <t>CARVAJAL DIAZ ORIANA DEL CARME</t>
   </si>
   <si>
-    <t xml:space="preserve">Psiquiatría </t>
-  </si>
-  <si>
     <t>Medicina General</t>
   </si>
   <si>
-    <t>TORRES OSORIO CRISTOPHER NICOL</t>
+    <t>Medicina Curativa</t>
+  </si>
+  <si>
+    <t>Traumatología</t>
+  </si>
+  <si>
+    <t>Nueva</t>
+  </si>
+  <si>
+    <t>Psiquiatría</t>
+  </si>
+  <si>
+    <t>Neurocirugía</t>
+  </si>
+  <si>
+    <t>INOSTROZA TORRES SEBASTIAN IGN</t>
   </si>
 </sst>
 </file>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="O44" s="33">
         <f t="shared" ca="1" si="0"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P44" s="35" t="str">
         <f t="shared" si="1"/>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="O54" s="33">
         <f t="shared" ca="1" si="0"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P54" s="35" t="str">
         <f t="shared" si="1"/>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="O88" s="33">
         <f t="shared" ca="1" si="2"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P88" s="35" t="str">
         <f t="shared" si="3"/>
@@ -22846,7 +22846,7 @@
       </c>
       <c r="O251" s="33">
         <f t="shared" ca="1" si="6"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P251" s="35" t="str">
         <f t="shared" si="7"/>
@@ -28082,7 +28082,7 @@
       </c>
       <c r="O328" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P328" s="35" t="str">
         <f t="shared" si="11"/>
@@ -28966,7 +28966,7 @@
       </c>
       <c r="O341" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P341" s="35" t="str">
         <f t="shared" si="11"/>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="O352" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P352" s="35" t="str">
         <f t="shared" si="11"/>
@@ -31822,7 +31822,7 @@
       </c>
       <c r="O383" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P383" s="35" t="str">
         <f t="shared" si="11"/>
@@ -31958,7 +31958,7 @@
       </c>
       <c r="O385" s="33">
         <f t="shared" ca="1" si="10"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P385" s="35" t="str">
         <f t="shared" si="11"/>
@@ -36300,16 +36300,16 @@
         <v>306530</v>
       </c>
       <c r="B449" s="32" t="s">
+        <v>1648</v>
+      </c>
+      <c r="C449" s="32" t="s">
         <v>1649</v>
       </c>
-      <c r="C449" s="32" t="s">
+      <c r="D449" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="E449" s="32" t="s">
         <v>1650</v>
-      </c>
-      <c r="D449" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="E449" s="32" t="s">
-        <v>1651</v>
       </c>
       <c r="F449" s="31" t="s">
         <v>1591</v>
@@ -36358,7 +36358,7 @@
       <c r="T449" s="31"/>
       <c r="U449" s="35"/>
       <c r="V449" s="35" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="450" spans="1:22">
@@ -46793,7 +46793,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D3B0B5-E7CA-41F3-B584-8BB10868D96B}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.54296875" customWidth="1"/>
@@ -46900,19 +46900,19 @@
         <v>746</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>1685</v>
+        <v>1599</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>1648</v>
+        <v>1687</v>
       </c>
       <c r="O2" s="8">
         <v>359</v>
       </c>
       <c r="P2" s="8">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="Q2" s="7" t="s">
         <v>1146</v>
@@ -46953,16 +46953,16 @@
         <v>15</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>1687</v>
+        <v>1683</v>
       </c>
       <c r="O3" s="8">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="P3" s="8">
         <v>44</v>
@@ -46979,7 +46979,7 @@
         <v>241</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1688</v>
+        <v>1684</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>244</v>
@@ -47006,10 +47006,10 @@
         <v>15</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>1689</v>
@@ -47059,19 +47059,19 @@
         <v>912</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>1685</v>
+        <v>1599</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>1648</v>
+        <v>1687</v>
       </c>
       <c r="O5" s="8">
         <v>360</v>
       </c>
       <c r="P5" s="8">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="Q5" s="7" t="s">
         <v>1144</v>
@@ -47112,13 +47112,13 @@
         <v>1175</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>1685</v>
+        <v>1599</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>1648</v>
+        <v>1690</v>
       </c>
       <c r="O6" s="8">
         <v>375</v>
@@ -47153,31 +47153,31 @@
         <v>2</v>
       </c>
       <c r="H7" s="9">
-        <v>46200</v>
+        <v>46230</v>
       </c>
       <c r="I7" s="9">
-        <v>46229</v>
+        <v>46259</v>
       </c>
       <c r="J7" s="5">
         <v>30</v>
       </c>
       <c r="K7" s="8">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>1685</v>
+        <v>1599</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>1648</v>
+        <v>1687</v>
       </c>
       <c r="O7" s="8">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="P7" s="8">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>1144</v>
@@ -47218,13 +47218,13 @@
         <v>11</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>1690</v>
+        <v>1685</v>
       </c>
       <c r="O8" s="8">
         <v>11</v>
@@ -47271,19 +47271,19 @@
         <v>21</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>1648</v>
+        <v>1687</v>
       </c>
       <c r="O9" s="8">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="P9" s="8">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="Q9" s="7" t="s">
         <v>1146</v>
@@ -47324,13 +47324,13 @@
         <v>51</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>1685</v>
+        <v>1599</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>1648</v>
+        <v>1687</v>
       </c>
       <c r="O10" s="8">
         <v>51</v>
@@ -47344,52 +47344,52 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="5">
-        <v>62449</v>
+        <v>68067</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>811</v>
+        <v>877</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>1691</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="G11" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="9">
-        <v>46219</v>
+        <v>46231</v>
       </c>
       <c r="I11" s="9">
-        <v>46222</v>
+        <v>46245</v>
       </c>
       <c r="J11" s="5">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K11" s="8">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="O11" s="8">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P11" s="8">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="Q11" s="7" t="s">
         <v>1146</v>
@@ -47418,31 +47418,31 @@
         <v>2</v>
       </c>
       <c r="H12" s="9">
-        <v>46214</v>
+        <v>46229</v>
       </c>
       <c r="I12" s="9">
-        <v>46228</v>
+        <v>46258</v>
       </c>
       <c r="J12" s="5">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K12" s="8">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>1685</v>
+        <v>1599</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>1648</v>
+        <v>1687</v>
       </c>
       <c r="O12" s="8">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="P12" s="8">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="Q12" s="7" t="s">
         <v>1144</v>
@@ -47471,34 +47471,87 @@
         <v>2</v>
       </c>
       <c r="H13" s="9">
-        <v>46202</v>
+        <v>46232</v>
       </c>
       <c r="I13" s="9">
-        <v>46231</v>
+        <v>46261</v>
       </c>
       <c r="J13" s="5">
         <v>30</v>
       </c>
       <c r="K13" s="8">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>1685</v>
+        <v>1599</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>1648</v>
+        <v>1687</v>
       </c>
       <c r="O13" s="8">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="P13" s="8">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="Q13" s="7" t="s">
         <v>1146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="5">
+        <v>303933</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>1589</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>1139</v>
+      </c>
+      <c r="H14" s="9">
+        <v>46226</v>
+      </c>
+      <c r="I14" s="9">
+        <v>46246</v>
+      </c>
+      <c r="J14" s="5">
+        <v>21</v>
+      </c>
+      <c r="K14" s="8">
+        <v>21</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>1686</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>1688</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>1685</v>
+      </c>
+      <c r="O14" s="8">
+        <v>21</v>
+      </c>
+      <c r="P14" s="8">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>1139</v>
       </c>
     </row>
   </sheetData>
@@ -47784,14 +47837,14 @@
         <v>1625</v>
       </c>
       <c r="C14" s="27">
-        <v>5.0000000000000001E-3</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="D14" s="27">
-        <v>8.0000000000000004E-4</v>
+        <v>1.4E-3</v>
       </c>
       <c r="E14" s="26">
         <f>SUM(C14:D14)</f>
-        <v>5.8000000000000005E-3</v>
+        <v>6.6E-3</v>
       </c>
     </row>
     <row r="15" spans="2:14">
@@ -47799,14 +47852,14 @@
         <v>830</v>
       </c>
       <c r="C15" s="27">
-        <v>2.3999999999999998E-3</v>
+        <v>2.3E-3</v>
       </c>
       <c r="D15" s="27">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="E15" s="26">
         <f t="shared" ref="E15:E17" si="0">SUM(C15:D15)</f>
-        <v>3.4999999999999996E-3</v>
+        <v>3.4000000000000002E-3</v>
       </c>
     </row>
     <row r="16" spans="2:14">
@@ -47817,11 +47870,11 @@
         <v>1.2200000000000001E-2</v>
       </c>
       <c r="D16" s="27">
-        <v>6.0000000000000001E-3</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="E16" s="26">
         <f t="shared" si="0"/>
-        <v>1.8200000000000001E-2</v>
+        <v>1.9599999999999999E-2</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -47829,28 +47882,28 @@
         <v>1627</v>
       </c>
       <c r="C17" s="27">
-        <v>3.3999999999999998E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="D17" s="27">
-        <v>2.0999999999999999E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="E17" s="26">
         <f t="shared" si="0"/>
-        <v>5.4999999999999997E-3</v>
+        <v>6.8000000000000005E-3</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="C18" s="26">
         <f>SUM(C14:C17)</f>
-        <v>2.3E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="D18" s="26">
         <f>SUM(D14:D17)</f>
-        <v>0.01</v>
+        <v>1.2400000000000001E-2</v>
       </c>
       <c r="E18" s="26">
         <f>SUM(E14:E17)</f>
-        <v>3.3000000000000002E-2</v>
+        <v>3.6400000000000002E-2</v>
       </c>
     </row>
     <row r="21" spans="2:5">
@@ -47863,7 +47916,7 @@
         <v>1625</v>
       </c>
       <c r="C22" s="27">
-        <v>1.0699999999999999E-2</v>
+        <v>1.72E-2</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -47871,7 +47924,7 @@
         <v>830</v>
       </c>
       <c r="C23" s="27">
-        <v>4.7999999999999996E-3</v>
+        <v>9.1000000000000004E-3</v>
       </c>
     </row>
     <row r="24" spans="2:5">
@@ -47879,7 +47932,7 @@
         <v>1626</v>
       </c>
       <c r="C24" s="27">
-        <v>1.35E-2</v>
+        <v>1.6299999999999999E-2</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -47887,13 +47940,13 @@
         <v>1627</v>
       </c>
       <c r="C25" s="27">
-        <v>6.1999999999999998E-3</v>
+        <v>7.4000000000000003E-3</v>
       </c>
     </row>
     <row r="26" spans="2:5">
       <c r="C26" s="26">
         <f>SUM(C22:C25)</f>
-        <v>3.5199999999999995E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="28" spans="2:5">
@@ -47901,7 +47954,7 @@
         <v>1628</v>
       </c>
       <c r="C28" s="27">
-        <v>2.9999999999999997E-4</v>
+        <v>1.5E-3</v>
       </c>
     </row>
     <row r="29" spans="2:5">
@@ -47910,7 +47963,7 @@
       </c>
       <c r="C29" s="27">
         <f>C26-C28</f>
-        <v>3.4899999999999994E-2</v>
+        <v>4.8500000000000001E-2</v>
       </c>
     </row>
   </sheetData>
@@ -48066,7 +48119,7 @@
         <v>1120</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -48083,7 +48136,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -48100,7 +48153,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -48117,7 +48170,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -48134,7 +48187,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -48151,7 +48204,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -48168,7 +48221,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -48185,7 +48238,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -48202,7 +48255,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -48219,7 +48272,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -48236,7 +48289,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -48253,7 +48306,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -48270,7 +48323,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -48287,7 +48340,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -48304,7 +48357,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -48321,7 +48374,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -48338,7 +48391,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -48355,7 +48408,7 @@
         <v>2</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -48372,7 +48425,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -48389,7 +48442,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -48406,7 +48459,7 @@
         <v>88</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -48423,7 +48476,7 @@
         <v>2</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -48440,7 +48493,7 @@
         <v>2</v>
       </c>
       <c r="E23" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -48457,7 +48510,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -48474,7 +48527,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -48491,7 +48544,7 @@
         <v>2</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -48508,7 +48561,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -48525,7 +48578,7 @@
         <v>2</v>
       </c>
       <c r="E28" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -48542,7 +48595,7 @@
         <v>2</v>
       </c>
       <c r="E29" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -48559,7 +48612,7 @@
         <v>2</v>
       </c>
       <c r="E30" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -48576,7 +48629,7 @@
         <v>2</v>
       </c>
       <c r="E31" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -48593,7 +48646,7 @@
         <v>2</v>
       </c>
       <c r="E32" s="32" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -48610,7 +48663,7 @@
         <v>2</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -48627,7 +48680,7 @@
         <v>2</v>
       </c>
       <c r="E34" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -48644,7 +48697,7 @@
         <v>2</v>
       </c>
       <c r="E35" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -48661,7 +48714,7 @@
         <v>2</v>
       </c>
       <c r="E36" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -48678,7 +48731,7 @@
         <v>2</v>
       </c>
       <c r="E37" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -48695,7 +48748,7 @@
         <v>2</v>
       </c>
       <c r="E38" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -48712,7 +48765,7 @@
         <v>2</v>
       </c>
       <c r="E39" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -48729,7 +48782,7 @@
         <v>2</v>
       </c>
       <c r="E40" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -48746,7 +48799,7 @@
         <v>2</v>
       </c>
       <c r="E41" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -48763,7 +48816,7 @@
         <v>2</v>
       </c>
       <c r="E42" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -48780,7 +48833,7 @@
         <v>2</v>
       </c>
       <c r="E43" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -48797,7 +48850,7 @@
         <v>2</v>
       </c>
       <c r="E44" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -48814,7 +48867,7 @@
         <v>2</v>
       </c>
       <c r="E45" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -48831,7 +48884,7 @@
         <v>88</v>
       </c>
       <c r="E46" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -48848,7 +48901,7 @@
         <v>2</v>
       </c>
       <c r="E47" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -48865,7 +48918,7 @@
         <v>88</v>
       </c>
       <c r="E48" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -48882,7 +48935,7 @@
         <v>2</v>
       </c>
       <c r="E49" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -48899,7 +48952,7 @@
         <v>2</v>
       </c>
       <c r="E50" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -48916,7 +48969,7 @@
         <v>2</v>
       </c>
       <c r="E51" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -48933,7 +48986,7 @@
         <v>88</v>
       </c>
       <c r="E52" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -48950,7 +49003,7 @@
         <v>88</v>
       </c>
       <c r="E53" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -48967,7 +49020,7 @@
         <v>2</v>
       </c>
       <c r="E54" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -48984,7 +49037,7 @@
         <v>2</v>
       </c>
       <c r="E55" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -49001,7 +49054,7 @@
         <v>2</v>
       </c>
       <c r="E56" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -49018,7 +49071,7 @@
         <v>2</v>
       </c>
       <c r="E57" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -49035,7 +49088,7 @@
         <v>88</v>
       </c>
       <c r="E58" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -49052,7 +49105,7 @@
         <v>2</v>
       </c>
       <c r="E59" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -49069,7 +49122,7 @@
         <v>88</v>
       </c>
       <c r="E60" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -49086,7 +49139,7 @@
         <v>88</v>
       </c>
       <c r="E61" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -49103,7 +49156,7 @@
         <v>2</v>
       </c>
       <c r="E62" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -49120,7 +49173,7 @@
         <v>2</v>
       </c>
       <c r="E63" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -49137,7 +49190,7 @@
         <v>2</v>
       </c>
       <c r="E64" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -49154,7 +49207,7 @@
         <v>2</v>
       </c>
       <c r="E65" s="32" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -49171,7 +49224,7 @@
         <v>2</v>
       </c>
       <c r="E66" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -49188,7 +49241,7 @@
         <v>2</v>
       </c>
       <c r="E67" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -49205,7 +49258,7 @@
         <v>88</v>
       </c>
       <c r="E68" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -49222,7 +49275,7 @@
         <v>2</v>
       </c>
       <c r="E69" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -49239,7 +49292,7 @@
         <v>2</v>
       </c>
       <c r="E70" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -49256,7 +49309,7 @@
         <v>88</v>
       </c>
       <c r="E71" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -49273,7 +49326,7 @@
         <v>2</v>
       </c>
       <c r="E72" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -49290,7 +49343,7 @@
         <v>2</v>
       </c>
       <c r="E73" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -49307,7 +49360,7 @@
         <v>2</v>
       </c>
       <c r="E74" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -49324,7 +49377,7 @@
         <v>2</v>
       </c>
       <c r="E75" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -49341,7 +49394,7 @@
         <v>2</v>
       </c>
       <c r="E76" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -49358,7 +49411,7 @@
         <v>2</v>
       </c>
       <c r="E77" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -49375,7 +49428,7 @@
         <v>2</v>
       </c>
       <c r="E78" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -49392,7 +49445,7 @@
         <v>2</v>
       </c>
       <c r="E79" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -49409,7 +49462,7 @@
         <v>2</v>
       </c>
       <c r="E80" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -49426,7 +49479,7 @@
         <v>2</v>
       </c>
       <c r="E81" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -49443,7 +49496,7 @@
         <v>2</v>
       </c>
       <c r="E82" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -49460,7 +49513,7 @@
         <v>2</v>
       </c>
       <c r="E83" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -49477,7 +49530,7 @@
         <v>2</v>
       </c>
       <c r="E84" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -49494,7 +49547,7 @@
         <v>2</v>
       </c>
       <c r="E85" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -49511,7 +49564,7 @@
         <v>2</v>
       </c>
       <c r="E86" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -49528,7 +49581,7 @@
         <v>2</v>
       </c>
       <c r="E87" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -49545,7 +49598,7 @@
         <v>88</v>
       </c>
       <c r="E88" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -49562,7 +49615,7 @@
         <v>88</v>
       </c>
       <c r="E89" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -49579,7 +49632,7 @@
         <v>2</v>
       </c>
       <c r="E90" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -49596,7 +49649,7 @@
         <v>2</v>
       </c>
       <c r="E91" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -49613,7 +49666,7 @@
         <v>2</v>
       </c>
       <c r="E92" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -49630,7 +49683,7 @@
         <v>88</v>
       </c>
       <c r="E93" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -49647,7 +49700,7 @@
         <v>88</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -49664,7 +49717,7 @@
         <v>88</v>
       </c>
       <c r="E95" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -49681,7 +49734,7 @@
         <v>2</v>
       </c>
       <c r="E96" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -49698,7 +49751,7 @@
         <v>2</v>
       </c>
       <c r="E97" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -49715,7 +49768,7 @@
         <v>2</v>
       </c>
       <c r="E98" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -49732,7 +49785,7 @@
         <v>2</v>
       </c>
       <c r="E99" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -49749,7 +49802,7 @@
         <v>2</v>
       </c>
       <c r="E100" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -49766,7 +49819,7 @@
         <v>2</v>
       </c>
       <c r="E101" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -49783,7 +49836,7 @@
         <v>2</v>
       </c>
       <c r="E102" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -49800,7 +49853,7 @@
         <v>2</v>
       </c>
       <c r="E103" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -49817,7 +49870,7 @@
         <v>88</v>
       </c>
       <c r="E104" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -49834,7 +49887,7 @@
         <v>2</v>
       </c>
       <c r="E105" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -49851,7 +49904,7 @@
         <v>2</v>
       </c>
       <c r="E106" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -49868,7 +49921,7 @@
         <v>2</v>
       </c>
       <c r="E107" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -49885,7 +49938,7 @@
         <v>2</v>
       </c>
       <c r="E108" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -49902,7 +49955,7 @@
         <v>2</v>
       </c>
       <c r="E109" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -49919,7 +49972,7 @@
         <v>2</v>
       </c>
       <c r="E110" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -49936,7 +49989,7 @@
         <v>2</v>
       </c>
       <c r="E111" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -49953,7 +50006,7 @@
         <v>2</v>
       </c>
       <c r="E112" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -49970,7 +50023,7 @@
         <v>2</v>
       </c>
       <c r="E113" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -49987,7 +50040,7 @@
         <v>2</v>
       </c>
       <c r="E114" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -50004,7 +50057,7 @@
         <v>2</v>
       </c>
       <c r="E115" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -50021,7 +50074,7 @@
         <v>2</v>
       </c>
       <c r="E116" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -50038,7 +50091,7 @@
         <v>2</v>
       </c>
       <c r="E117" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -50055,7 +50108,7 @@
         <v>2</v>
       </c>
       <c r="E118" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -50072,7 +50125,7 @@
         <v>2</v>
       </c>
       <c r="E119" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -50089,7 +50142,7 @@
         <v>2</v>
       </c>
       <c r="E120" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -50106,7 +50159,7 @@
         <v>2</v>
       </c>
       <c r="E121" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -50123,7 +50176,7 @@
         <v>2</v>
       </c>
       <c r="E122" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -50140,7 +50193,7 @@
         <v>2</v>
       </c>
       <c r="E123" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -50157,7 +50210,7 @@
         <v>2</v>
       </c>
       <c r="E124" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -50174,7 +50227,7 @@
         <v>2</v>
       </c>
       <c r="E125" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -50191,7 +50244,7 @@
         <v>2</v>
       </c>
       <c r="E126" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -50208,7 +50261,7 @@
         <v>2</v>
       </c>
       <c r="E127" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -50225,7 +50278,7 @@
         <v>2</v>
       </c>
       <c r="E128" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -50242,7 +50295,7 @@
         <v>2</v>
       </c>
       <c r="E129" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -50259,7 +50312,7 @@
         <v>2</v>
       </c>
       <c r="E130" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -50276,7 +50329,7 @@
         <v>2</v>
       </c>
       <c r="E131" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -50293,7 +50346,7 @@
         <v>2</v>
       </c>
       <c r="E132" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -50310,7 +50363,7 @@
         <v>2</v>
       </c>
       <c r="E133" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -50327,7 +50380,7 @@
         <v>2</v>
       </c>
       <c r="E134" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -50344,7 +50397,7 @@
         <v>2</v>
       </c>
       <c r="E135" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -50361,7 +50414,7 @@
         <v>2</v>
       </c>
       <c r="E136" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -50378,7 +50431,7 @@
         <v>2</v>
       </c>
       <c r="E137" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -50395,7 +50448,7 @@
         <v>2</v>
       </c>
       <c r="E138" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -50412,7 +50465,7 @@
         <v>2</v>
       </c>
       <c r="E139" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -50429,7 +50482,7 @@
         <v>2</v>
       </c>
       <c r="E140" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -50446,7 +50499,7 @@
         <v>2</v>
       </c>
       <c r="E141" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -50463,7 +50516,7 @@
         <v>2</v>
       </c>
       <c r="E142" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -50480,7 +50533,7 @@
         <v>2</v>
       </c>
       <c r="E143" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -50497,7 +50550,7 @@
         <v>2</v>
       </c>
       <c r="E144" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -50514,7 +50567,7 @@
         <v>2</v>
       </c>
       <c r="E145" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -50531,7 +50584,7 @@
         <v>2</v>
       </c>
       <c r="E146" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -50548,7 +50601,7 @@
         <v>2</v>
       </c>
       <c r="E147" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -50565,7 +50618,7 @@
         <v>2</v>
       </c>
       <c r="E148" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -50582,7 +50635,7 @@
         <v>2</v>
       </c>
       <c r="E149" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -50599,7 +50652,7 @@
         <v>2</v>
       </c>
       <c r="E150" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -50616,7 +50669,7 @@
         <v>2</v>
       </c>
       <c r="E151" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -50633,7 +50686,7 @@
         <v>2</v>
       </c>
       <c r="E152" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -50650,7 +50703,7 @@
         <v>2</v>
       </c>
       <c r="E153" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -50667,7 +50720,7 @@
         <v>2</v>
       </c>
       <c r="E154" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -50684,7 +50737,7 @@
         <v>2</v>
       </c>
       <c r="E155" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -50701,7 +50754,7 @@
         <v>2</v>
       </c>
       <c r="E156" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -50718,7 +50771,7 @@
         <v>2</v>
       </c>
       <c r="E157" s="32" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -50735,7 +50788,7 @@
         <v>2</v>
       </c>
       <c r="E158" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -50752,7 +50805,7 @@
         <v>2</v>
       </c>
       <c r="E159" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -50769,7 +50822,7 @@
         <v>2</v>
       </c>
       <c r="E160" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -50786,7 +50839,7 @@
         <v>2</v>
       </c>
       <c r="E161" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -50803,7 +50856,7 @@
         <v>2</v>
       </c>
       <c r="E162" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -50820,7 +50873,7 @@
         <v>2</v>
       </c>
       <c r="E163" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -50837,7 +50890,7 @@
         <v>2</v>
       </c>
       <c r="E164" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -50854,7 +50907,7 @@
         <v>2</v>
       </c>
       <c r="E165" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -50871,7 +50924,7 @@
         <v>2</v>
       </c>
       <c r="E166" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -50888,7 +50941,7 @@
         <v>2</v>
       </c>
       <c r="E167" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -50905,7 +50958,7 @@
         <v>2</v>
       </c>
       <c r="E168" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -50922,7 +50975,7 @@
         <v>2</v>
       </c>
       <c r="E169" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -50939,7 +50992,7 @@
         <v>2</v>
       </c>
       <c r="E170" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -50956,7 +51009,7 @@
         <v>2</v>
       </c>
       <c r="E171" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -50973,7 +51026,7 @@
         <v>2</v>
       </c>
       <c r="E172" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -50990,7 +51043,7 @@
         <v>2</v>
       </c>
       <c r="E173" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -51007,7 +51060,7 @@
         <v>2</v>
       </c>
       <c r="E174" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -51024,7 +51077,7 @@
         <v>2</v>
       </c>
       <c r="E175" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -51041,7 +51094,7 @@
         <v>2</v>
       </c>
       <c r="E176" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -51058,7 +51111,7 @@
         <v>2</v>
       </c>
       <c r="E177" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -51075,7 +51128,7 @@
         <v>2</v>
       </c>
       <c r="E178" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -51092,7 +51145,7 @@
         <v>2</v>
       </c>
       <c r="E179" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -51109,7 +51162,7 @@
         <v>2</v>
       </c>
       <c r="E180" s="32" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -51126,7 +51179,7 @@
         <v>2</v>
       </c>
       <c r="E181" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -51143,7 +51196,7 @@
         <v>2</v>
       </c>
       <c r="E182" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -51160,7 +51213,7 @@
         <v>2</v>
       </c>
       <c r="E183" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -51177,7 +51230,7 @@
         <v>2</v>
       </c>
       <c r="E184" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -51194,7 +51247,7 @@
         <v>2</v>
       </c>
       <c r="E185" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -51211,7 +51264,7 @@
         <v>2</v>
       </c>
       <c r="E186" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -51228,7 +51281,7 @@
         <v>2</v>
       </c>
       <c r="E187" s="32" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -51245,7 +51298,7 @@
         <v>2</v>
       </c>
       <c r="E188" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -51262,7 +51315,7 @@
         <v>2</v>
       </c>
       <c r="E189" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -51279,7 +51332,7 @@
         <v>2</v>
       </c>
       <c r="E190" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -51296,7 +51349,7 @@
         <v>2</v>
       </c>
       <c r="E191" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -51313,7 +51366,7 @@
         <v>88</v>
       </c>
       <c r="E192" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -51330,7 +51383,7 @@
         <v>2</v>
       </c>
       <c r="E193" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -51347,7 +51400,7 @@
         <v>2</v>
       </c>
       <c r="E194" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -51364,7 +51417,7 @@
         <v>2</v>
       </c>
       <c r="E195" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -51381,7 +51434,7 @@
         <v>2</v>
       </c>
       <c r="E196" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -51398,7 +51451,7 @@
         <v>2</v>
       </c>
       <c r="E197" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -51415,7 +51468,7 @@
         <v>2</v>
       </c>
       <c r="E198" s="32" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -51432,7 +51485,7 @@
         <v>2</v>
       </c>
       <c r="E199" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -51449,7 +51502,7 @@
         <v>2</v>
       </c>
       <c r="E200" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -51466,7 +51519,7 @@
         <v>2</v>
       </c>
       <c r="E201" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -51483,7 +51536,7 @@
         <v>2</v>
       </c>
       <c r="E202" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -51500,7 +51553,7 @@
         <v>2</v>
       </c>
       <c r="E203" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -51517,7 +51570,7 @@
         <v>2</v>
       </c>
       <c r="E204" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -51534,7 +51587,7 @@
         <v>2</v>
       </c>
       <c r="E205" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -51551,7 +51604,7 @@
         <v>2</v>
       </c>
       <c r="E206" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -51568,7 +51621,7 @@
         <v>2</v>
       </c>
       <c r="E207" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -51585,7 +51638,7 @@
         <v>2</v>
       </c>
       <c r="E208" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -51602,7 +51655,7 @@
         <v>2</v>
       </c>
       <c r="E209" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -51619,7 +51672,7 @@
         <v>2</v>
       </c>
       <c r="E210" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -51636,7 +51689,7 @@
         <v>2</v>
       </c>
       <c r="E211" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -51653,7 +51706,7 @@
         <v>2</v>
       </c>
       <c r="E212" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -51670,7 +51723,7 @@
         <v>2</v>
       </c>
       <c r="E213" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -51687,7 +51740,7 @@
         <v>2</v>
       </c>
       <c r="E214" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -51704,7 +51757,7 @@
         <v>2</v>
       </c>
       <c r="E215" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -51721,7 +51774,7 @@
         <v>2</v>
       </c>
       <c r="E216" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -51738,7 +51791,7 @@
         <v>2</v>
       </c>
       <c r="E217" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -51755,7 +51808,7 @@
         <v>2</v>
       </c>
       <c r="E218" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -51772,7 +51825,7 @@
         <v>2</v>
       </c>
       <c r="E219" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -51789,7 +51842,7 @@
         <v>2</v>
       </c>
       <c r="E220" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -51806,7 +51859,7 @@
         <v>88</v>
       </c>
       <c r="E221" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -51823,7 +51876,7 @@
         <v>2</v>
       </c>
       <c r="E222" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -51840,7 +51893,7 @@
         <v>2</v>
       </c>
       <c r="E223" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -51857,7 +51910,7 @@
         <v>2</v>
       </c>
       <c r="E224" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -51874,7 +51927,7 @@
         <v>2</v>
       </c>
       <c r="E225" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -51891,7 +51944,7 @@
         <v>2</v>
       </c>
       <c r="E226" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -51908,7 +51961,7 @@
         <v>2</v>
       </c>
       <c r="E227" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -51925,7 +51978,7 @@
         <v>2</v>
       </c>
       <c r="E228" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -51942,7 +51995,7 @@
         <v>2</v>
       </c>
       <c r="E229" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -51959,7 +52012,7 @@
         <v>2</v>
       </c>
       <c r="E230" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -51976,7 +52029,7 @@
         <v>2</v>
       </c>
       <c r="E231" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -51993,7 +52046,7 @@
         <v>2</v>
       </c>
       <c r="E232" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -52010,7 +52063,7 @@
         <v>2</v>
       </c>
       <c r="E233" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -52027,7 +52080,7 @@
         <v>2</v>
       </c>
       <c r="E234" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -52044,7 +52097,7 @@
         <v>2</v>
       </c>
       <c r="E235" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -52061,7 +52114,7 @@
         <v>2</v>
       </c>
       <c r="E236" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -52078,7 +52131,7 @@
         <v>2</v>
       </c>
       <c r="E237" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -52095,7 +52148,7 @@
         <v>88</v>
       </c>
       <c r="E238" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -52112,7 +52165,7 @@
         <v>2</v>
       </c>
       <c r="E239" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -52129,7 +52182,7 @@
         <v>2</v>
       </c>
       <c r="E240" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -52146,7 +52199,7 @@
         <v>2</v>
       </c>
       <c r="E241" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -52163,7 +52216,7 @@
         <v>2</v>
       </c>
       <c r="E242" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -52180,7 +52233,7 @@
         <v>2</v>
       </c>
       <c r="E243" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -52197,7 +52250,7 @@
         <v>2</v>
       </c>
       <c r="E244" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -52214,7 +52267,7 @@
         <v>2</v>
       </c>
       <c r="E245" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -52231,7 +52284,7 @@
         <v>2</v>
       </c>
       <c r="E246" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -52248,7 +52301,7 @@
         <v>88</v>
       </c>
       <c r="E247" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -52265,7 +52318,7 @@
         <v>2</v>
       </c>
       <c r="E248" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -52282,7 +52335,7 @@
         <v>2</v>
       </c>
       <c r="E249" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -52299,7 +52352,7 @@
         <v>2</v>
       </c>
       <c r="E250" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -52316,7 +52369,7 @@
         <v>2</v>
       </c>
       <c r="E251" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -52333,7 +52386,7 @@
         <v>2</v>
       </c>
       <c r="E252" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -52350,7 +52403,7 @@
         <v>2</v>
       </c>
       <c r="E253" s="32" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -52367,7 +52420,7 @@
         <v>2</v>
       </c>
       <c r="E254" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -52384,7 +52437,7 @@
         <v>2</v>
       </c>
       <c r="E255" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -52401,7 +52454,7 @@
         <v>2</v>
       </c>
       <c r="E256" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -52418,7 +52471,7 @@
         <v>88</v>
       </c>
       <c r="E257" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -52435,7 +52488,7 @@
         <v>2</v>
       </c>
       <c r="E258" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -52452,7 +52505,7 @@
         <v>2</v>
       </c>
       <c r="E259" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -52469,7 +52522,7 @@
         <v>2</v>
       </c>
       <c r="E260" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -52486,7 +52539,7 @@
         <v>2</v>
       </c>
       <c r="E261" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -52503,7 +52556,7 @@
         <v>2</v>
       </c>
       <c r="E262" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -52520,7 +52573,7 @@
         <v>2</v>
       </c>
       <c r="E263" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -52537,7 +52590,7 @@
         <v>2</v>
       </c>
       <c r="E264" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -52554,7 +52607,7 @@
         <v>2</v>
       </c>
       <c r="E265" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -52571,7 +52624,7 @@
         <v>2</v>
       </c>
       <c r="E266" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -52588,7 +52641,7 @@
         <v>2</v>
       </c>
       <c r="E267" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -52596,16 +52649,16 @@
         <v>57468</v>
       </c>
       <c r="B268" s="32" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C268" s="32" t="s">
         <v>1668</v>
       </c>
-      <c r="C268" s="32" t="s">
-        <v>1669</v>
-      </c>
       <c r="D268" s="31" t="s">
         <v>2</v>
       </c>
       <c r="E268" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -52622,7 +52675,7 @@
         <v>2</v>
       </c>
       <c r="E269" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -52639,7 +52692,7 @@
         <v>2</v>
       </c>
       <c r="E270" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -52656,7 +52709,7 @@
         <v>88</v>
       </c>
       <c r="E271" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -52673,7 +52726,7 @@
         <v>2</v>
       </c>
       <c r="E272" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -52690,7 +52743,7 @@
         <v>2</v>
       </c>
       <c r="E273" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -52707,7 +52760,7 @@
         <v>2</v>
       </c>
       <c r="E274" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -52724,7 +52777,7 @@
         <v>2</v>
       </c>
       <c r="E275" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -52741,7 +52794,7 @@
         <v>2</v>
       </c>
       <c r="E276" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -52758,7 +52811,7 @@
         <v>2</v>
       </c>
       <c r="E277" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -52775,7 +52828,7 @@
         <v>2</v>
       </c>
       <c r="E278" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -52792,7 +52845,7 @@
         <v>2</v>
       </c>
       <c r="E279" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -52809,7 +52862,7 @@
         <v>2</v>
       </c>
       <c r="E280" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -52826,7 +52879,7 @@
         <v>2</v>
       </c>
       <c r="E281" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -52843,7 +52896,7 @@
         <v>2</v>
       </c>
       <c r="E282" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -52860,7 +52913,7 @@
         <v>2</v>
       </c>
       <c r="E283" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -52877,7 +52930,7 @@
         <v>2</v>
       </c>
       <c r="E284" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -52894,7 +52947,7 @@
         <v>2</v>
       </c>
       <c r="E285" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -52911,7 +52964,7 @@
         <v>88</v>
       </c>
       <c r="E286" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -52928,7 +52981,7 @@
         <v>2</v>
       </c>
       <c r="E287" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -52945,7 +52998,7 @@
         <v>88</v>
       </c>
       <c r="E288" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -52962,7 +53015,7 @@
         <v>2</v>
       </c>
       <c r="E289" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -52979,7 +53032,7 @@
         <v>88</v>
       </c>
       <c r="E290" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -52996,7 +53049,7 @@
         <v>2</v>
       </c>
       <c r="E291" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -53013,7 +53066,7 @@
         <v>2</v>
       </c>
       <c r="E292" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -53030,7 +53083,7 @@
         <v>2</v>
       </c>
       <c r="E293" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -53047,7 +53100,7 @@
         <v>2</v>
       </c>
       <c r="E294" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -53064,7 +53117,7 @@
         <v>2</v>
       </c>
       <c r="E295" s="32" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -53081,7 +53134,7 @@
         <v>2</v>
       </c>
       <c r="E296" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -53098,7 +53151,7 @@
         <v>88</v>
       </c>
       <c r="E297" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -53115,7 +53168,7 @@
         <v>2</v>
       </c>
       <c r="E298" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -53132,7 +53185,7 @@
         <v>2</v>
       </c>
       <c r="E299" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -53149,7 +53202,7 @@
         <v>2</v>
       </c>
       <c r="E300" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -53166,7 +53219,7 @@
         <v>2</v>
       </c>
       <c r="E301" s="32" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -53183,7 +53236,7 @@
         <v>2</v>
       </c>
       <c r="E302" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -53200,7 +53253,7 @@
         <v>2</v>
       </c>
       <c r="E303" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -53217,7 +53270,7 @@
         <v>2</v>
       </c>
       <c r="E304" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -53234,7 +53287,7 @@
         <v>88</v>
       </c>
       <c r="E305" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -53251,7 +53304,7 @@
         <v>2</v>
       </c>
       <c r="E306" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -53268,7 +53321,7 @@
         <v>2</v>
       </c>
       <c r="E307" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -53285,7 +53338,7 @@
         <v>2</v>
       </c>
       <c r="E308" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -53302,7 +53355,7 @@
         <v>2</v>
       </c>
       <c r="E309" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -53319,7 +53372,7 @@
         <v>2</v>
       </c>
       <c r="E310" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -53336,7 +53389,7 @@
         <v>2</v>
       </c>
       <c r="E311" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -53353,7 +53406,7 @@
         <v>2</v>
       </c>
       <c r="E312" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -53370,7 +53423,7 @@
         <v>88</v>
       </c>
       <c r="E313" s="32" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -53387,7 +53440,7 @@
         <v>88</v>
       </c>
       <c r="E314" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -53404,7 +53457,7 @@
         <v>2</v>
       </c>
       <c r="E315" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -53421,7 +53474,7 @@
         <v>2</v>
       </c>
       <c r="E316" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -53438,7 +53491,7 @@
         <v>2</v>
       </c>
       <c r="E317" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -53455,7 +53508,7 @@
         <v>2</v>
       </c>
       <c r="E318" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -53472,7 +53525,7 @@
         <v>2</v>
       </c>
       <c r="E319" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -53489,7 +53542,7 @@
         <v>88</v>
       </c>
       <c r="E320" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -53506,7 +53559,7 @@
         <v>88</v>
       </c>
       <c r="E321" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -53523,7 +53576,7 @@
         <v>88</v>
       </c>
       <c r="E322" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -53540,7 +53593,7 @@
         <v>88</v>
       </c>
       <c r="E323" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -53557,7 +53610,7 @@
         <v>2</v>
       </c>
       <c r="E324" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -53574,7 +53627,7 @@
         <v>88</v>
       </c>
       <c r="E325" s="32" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -53591,7 +53644,7 @@
         <v>2</v>
       </c>
       <c r="E326" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -53608,7 +53661,7 @@
         <v>2</v>
       </c>
       <c r="E327" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -53625,7 +53678,7 @@
         <v>2</v>
       </c>
       <c r="E328" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -53642,7 +53695,7 @@
         <v>2</v>
       </c>
       <c r="E329" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -53659,7 +53712,7 @@
         <v>2</v>
       </c>
       <c r="E330" s="32" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -53676,7 +53729,7 @@
         <v>2</v>
       </c>
       <c r="E331" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -53693,7 +53746,7 @@
         <v>2</v>
       </c>
       <c r="E332" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -53710,7 +53763,7 @@
         <v>2</v>
       </c>
       <c r="E333" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -53727,7 +53780,7 @@
         <v>2</v>
       </c>
       <c r="E334" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -53744,7 +53797,7 @@
         <v>2</v>
       </c>
       <c r="E335" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -53761,7 +53814,7 @@
         <v>2</v>
       </c>
       <c r="E336" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -53778,7 +53831,7 @@
         <v>88</v>
       </c>
       <c r="E337" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -53795,7 +53848,7 @@
         <v>2</v>
       </c>
       <c r="E338" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -53812,7 +53865,7 @@
         <v>88</v>
       </c>
       <c r="E339" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -53829,7 +53882,7 @@
         <v>2</v>
       </c>
       <c r="E340" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -53846,7 +53899,7 @@
         <v>2</v>
       </c>
       <c r="E341" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -53863,7 +53916,7 @@
         <v>2</v>
       </c>
       <c r="E342" s="32" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -53880,7 +53933,7 @@
         <v>2</v>
       </c>
       <c r="E343" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -53897,7 +53950,7 @@
         <v>2</v>
       </c>
       <c r="E344" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -53914,7 +53967,7 @@
         <v>2</v>
       </c>
       <c r="E345" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -53931,7 +53984,7 @@
         <v>2</v>
       </c>
       <c r="E346" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -53948,7 +54001,7 @@
         <v>2</v>
       </c>
       <c r="E347" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -53965,7 +54018,7 @@
         <v>2</v>
       </c>
       <c r="E348" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -53982,7 +54035,7 @@
         <v>2</v>
       </c>
       <c r="E349" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -53999,7 +54052,7 @@
         <v>2</v>
       </c>
       <c r="E350" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -54016,7 +54069,7 @@
         <v>2</v>
       </c>
       <c r="E351" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -54033,7 +54086,7 @@
         <v>2</v>
       </c>
       <c r="E352" s="32" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -54050,7 +54103,7 @@
         <v>88</v>
       </c>
       <c r="E353" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -54067,7 +54120,7 @@
         <v>88</v>
       </c>
       <c r="E354" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -54084,7 +54137,7 @@
         <v>2</v>
       </c>
       <c r="E355" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -54101,7 +54154,7 @@
         <v>2</v>
       </c>
       <c r="E356" s="32" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -54118,7 +54171,7 @@
         <v>88</v>
       </c>
       <c r="E357" s="32" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -54135,7 +54188,7 @@
         <v>2</v>
       </c>
       <c r="E358" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -54152,7 +54205,7 @@
         <v>2</v>
       </c>
       <c r="E359" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -54169,7 +54222,7 @@
         <v>88</v>
       </c>
       <c r="E360" s="32" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -54186,7 +54239,7 @@
         <v>88</v>
       </c>
       <c r="E361" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -54203,7 +54256,7 @@
         <v>2</v>
       </c>
       <c r="E362" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -54220,7 +54273,7 @@
         <v>88</v>
       </c>
       <c r="E363" s="32" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -54237,7 +54290,7 @@
         <v>2</v>
       </c>
       <c r="E364" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -54254,7 +54307,7 @@
         <v>88</v>
       </c>
       <c r="E365" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -54271,7 +54324,7 @@
         <v>2</v>
       </c>
       <c r="E366" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -54288,7 +54341,7 @@
         <v>2</v>
       </c>
       <c r="E367" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -54305,7 +54358,7 @@
         <v>2</v>
       </c>
       <c r="E368" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -54322,7 +54375,7 @@
         <v>2</v>
       </c>
       <c r="E369" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -54339,7 +54392,7 @@
         <v>2</v>
       </c>
       <c r="E370" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -54356,7 +54409,7 @@
         <v>2</v>
       </c>
       <c r="E371" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -54373,7 +54426,7 @@
         <v>2</v>
       </c>
       <c r="E372" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -54390,7 +54443,7 @@
         <v>2</v>
       </c>
       <c r="E373" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -54407,7 +54460,7 @@
         <v>2</v>
       </c>
       <c r="E374" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -54424,7 +54477,7 @@
         <v>2</v>
       </c>
       <c r="E375" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -54441,7 +54494,7 @@
         <v>2</v>
       </c>
       <c r="E376" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -54458,7 +54511,7 @@
         <v>2</v>
       </c>
       <c r="E377" s="32" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -54475,7 +54528,7 @@
         <v>2</v>
       </c>
       <c r="E378" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -54492,7 +54545,7 @@
         <v>2</v>
       </c>
       <c r="E379" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -54509,7 +54562,7 @@
         <v>88</v>
       </c>
       <c r="E380" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -54526,7 +54579,7 @@
         <v>2</v>
       </c>
       <c r="E381" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -54543,7 +54596,7 @@
         <v>2</v>
       </c>
       <c r="E382" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -54560,7 +54613,7 @@
         <v>2</v>
       </c>
       <c r="E383" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -54577,7 +54630,7 @@
         <v>2</v>
       </c>
       <c r="E384" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -54594,7 +54647,7 @@
         <v>2</v>
       </c>
       <c r="E385" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -54611,7 +54664,7 @@
         <v>2</v>
       </c>
       <c r="E386" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -54628,7 +54681,7 @@
         <v>2</v>
       </c>
       <c r="E387" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -54645,7 +54698,7 @@
         <v>2</v>
       </c>
       <c r="E388" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -54662,7 +54715,7 @@
         <v>2</v>
       </c>
       <c r="E389" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -54679,7 +54732,7 @@
         <v>2</v>
       </c>
       <c r="E390" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -54696,7 +54749,7 @@
         <v>2</v>
       </c>
       <c r="E391" s="32" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -54713,7 +54766,7 @@
         <v>2</v>
       </c>
       <c r="E392" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -54730,7 +54783,7 @@
         <v>2</v>
       </c>
       <c r="E393" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -54747,7 +54800,7 @@
         <v>88</v>
       </c>
       <c r="E394" s="32" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -54764,7 +54817,7 @@
         <v>88</v>
       </c>
       <c r="E395" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -54781,7 +54834,7 @@
         <v>2</v>
       </c>
       <c r="E396" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -54798,7 +54851,7 @@
         <v>2</v>
       </c>
       <c r="E397" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -54815,7 +54868,7 @@
         <v>2</v>
       </c>
       <c r="E398" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -54832,7 +54885,7 @@
         <v>2</v>
       </c>
       <c r="E399" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -54849,7 +54902,7 @@
         <v>2</v>
       </c>
       <c r="E400" s="32" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -54866,7 +54919,7 @@
         <v>2</v>
       </c>
       <c r="E401" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -54883,7 +54936,7 @@
         <v>2</v>
       </c>
       <c r="E402" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -54900,7 +54953,7 @@
         <v>2</v>
       </c>
       <c r="E403" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -54917,7 +54970,7 @@
         <v>88</v>
       </c>
       <c r="E404" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -54934,7 +54987,7 @@
         <v>2</v>
       </c>
       <c r="E405" s="32" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -54951,7 +55004,7 @@
         <v>2</v>
       </c>
       <c r="E406" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -54968,7 +55021,7 @@
         <v>2</v>
       </c>
       <c r="E407" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -54985,7 +55038,7 @@
         <v>2</v>
       </c>
       <c r="E408" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -55002,7 +55055,7 @@
         <v>2</v>
       </c>
       <c r="E409" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -55019,7 +55072,7 @@
         <v>2</v>
       </c>
       <c r="E410" s="32" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -55036,7 +55089,7 @@
         <v>2</v>
       </c>
       <c r="E411" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -55053,7 +55106,7 @@
         <v>2</v>
       </c>
       <c r="E412" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -55070,7 +55123,7 @@
         <v>2</v>
       </c>
       <c r="E413" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -55087,7 +55140,7 @@
         <v>2</v>
       </c>
       <c r="E414" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -55104,7 +55157,7 @@
         <v>2</v>
       </c>
       <c r="E415" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -55121,7 +55174,7 @@
         <v>88</v>
       </c>
       <c r="E416" s="32" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -55138,7 +55191,7 @@
         <v>2</v>
       </c>
       <c r="E417" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -55155,7 +55208,7 @@
         <v>2</v>
       </c>
       <c r="E418" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -55172,7 +55225,7 @@
         <v>88</v>
       </c>
       <c r="E419" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -55189,7 +55242,7 @@
         <v>88</v>
       </c>
       <c r="E420" s="32" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -55206,7 +55259,7 @@
         <v>88</v>
       </c>
       <c r="E421" s="32" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -55223,7 +55276,7 @@
         <v>88</v>
       </c>
       <c r="E422" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -55240,7 +55293,7 @@
         <v>88</v>
       </c>
       <c r="E423" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -55257,7 +55310,7 @@
         <v>2</v>
       </c>
       <c r="E424" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -55274,7 +55327,7 @@
         <v>2</v>
       </c>
       <c r="E425" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -55291,7 +55344,7 @@
         <v>2</v>
       </c>
       <c r="E426" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -55308,7 +55361,7 @@
         <v>2</v>
       </c>
       <c r="E427" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -55325,7 +55378,7 @@
         <v>2</v>
       </c>
       <c r="E428" s="32" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -55342,7 +55395,7 @@
         <v>2</v>
       </c>
       <c r="E429" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -55359,7 +55412,7 @@
         <v>2</v>
       </c>
       <c r="E430" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -55376,7 +55429,7 @@
         <v>2</v>
       </c>
       <c r="E431" s="32" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -55393,7 +55446,7 @@
         <v>2</v>
       </c>
       <c r="E432" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -55410,7 +55463,7 @@
         <v>2</v>
       </c>
       <c r="E433" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -55427,7 +55480,7 @@
         <v>2</v>
       </c>
       <c r="E434" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -55444,7 +55497,7 @@
         <v>2</v>
       </c>
       <c r="E435" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -55461,7 +55514,7 @@
         <v>2</v>
       </c>
       <c r="E436" s="32" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -55478,7 +55531,7 @@
         <v>88</v>
       </c>
       <c r="E437" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -55495,7 +55548,7 @@
         <v>88</v>
       </c>
       <c r="E438" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -55512,7 +55565,7 @@
         <v>2</v>
       </c>
       <c r="E439" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -55529,7 +55582,7 @@
         <v>2</v>
       </c>
       <c r="E440" s="32" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -55546,7 +55599,7 @@
         <v>88</v>
       </c>
       <c r="E441" s="32" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -55563,7 +55616,7 @@
         <v>88</v>
       </c>
       <c r="E442" s="32" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -55580,7 +55633,7 @@
         <v>2</v>
       </c>
       <c r="E443" s="32" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -55597,7 +55650,7 @@
         <v>88</v>
       </c>
       <c r="E444" s="32" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -55614,7 +55667,7 @@
         <v>2</v>
       </c>
       <c r="E445" s="32" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -55631,7 +55684,7 @@
         <v>2</v>
       </c>
       <c r="E446" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -55648,7 +55701,7 @@
         <v>2</v>
       </c>
       <c r="E447" s="32" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -55665,7 +55718,7 @@
         <v>2</v>
       </c>
       <c r="E448" s="32" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -55682,7 +55735,7 @@
         <v>88</v>
       </c>
       <c r="E449" s="32" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
   </sheetData>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baray020\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9446018A-B090-4EEC-BDC5-1D91A3EEF867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B5AA6B-C3FA-4E3D-8741-81EF6F8689A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dotaci" sheetId="1" r:id="rId1"/>
@@ -5171,6 +5171,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="dd/mmm/yyyy"/>
+  </numFmts>
   <fonts count="10">
     <font>
       <sz val="11"/>
@@ -5417,7 +5420,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -5576,6 +5579,15 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -6044,7 +6056,7 @@
       <c r="M2" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="39">
+      <c r="N2" s="54">
         <v>25338</v>
       </c>
       <c r="O2" s="38">
@@ -6110,7 +6122,7 @@
       <c r="M3" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="44">
+      <c r="N3" s="55">
         <v>22455</v>
       </c>
       <c r="O3" s="43">
@@ -6176,7 +6188,7 @@
       <c r="M4" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="44">
+      <c r="N4" s="55">
         <v>22344</v>
       </c>
       <c r="O4" s="43">
@@ -6242,7 +6254,7 @@
       <c r="M5" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="55">
         <v>23037</v>
       </c>
       <c r="O5" s="43">
@@ -6308,7 +6320,7 @@
       <c r="M6" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="44">
+      <c r="N6" s="55">
         <v>25711</v>
       </c>
       <c r="O6" s="43">
@@ -6374,7 +6386,7 @@
       <c r="M7" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N7" s="44">
+      <c r="N7" s="55">
         <v>23650</v>
       </c>
       <c r="O7" s="43">
@@ -6440,7 +6452,7 @@
       <c r="M8" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="44">
+      <c r="N8" s="55">
         <v>24734</v>
       </c>
       <c r="O8" s="43">
@@ -6506,7 +6518,7 @@
       <c r="M9" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N9" s="44">
+      <c r="N9" s="55">
         <v>24962</v>
       </c>
       <c r="O9" s="43">
@@ -6572,7 +6584,7 @@
       <c r="M10" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N10" s="44">
+      <c r="N10" s="55">
         <v>24375</v>
       </c>
       <c r="O10" s="43">
@@ -6638,7 +6650,7 @@
       <c r="M11" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N11" s="44">
+      <c r="N11" s="55">
         <v>23403</v>
       </c>
       <c r="O11" s="43">
@@ -6704,7 +6716,7 @@
       <c r="M12" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N12" s="44">
+      <c r="N12" s="55">
         <v>23870</v>
       </c>
       <c r="O12" s="43">
@@ -6770,7 +6782,7 @@
       <c r="M13" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N13" s="44">
+      <c r="N13" s="55">
         <v>25084</v>
       </c>
       <c r="O13" s="43">
@@ -6836,7 +6848,7 @@
       <c r="M14" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N14" s="44">
+      <c r="N14" s="55">
         <v>24618</v>
       </c>
       <c r="O14" s="43">
@@ -6902,7 +6914,7 @@
       <c r="M15" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N15" s="44">
+      <c r="N15" s="55">
         <v>25597</v>
       </c>
       <c r="O15" s="43">
@@ -6968,7 +6980,7 @@
       <c r="M16" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="44">
+      <c r="N16" s="55">
         <v>25198</v>
       </c>
       <c r="O16" s="43">
@@ -7034,7 +7046,7 @@
       <c r="M17" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N17" s="44">
+      <c r="N17" s="55">
         <v>25317</v>
       </c>
       <c r="O17" s="43">
@@ -7100,7 +7112,7 @@
       <c r="M18" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N18" s="44">
+      <c r="N18" s="55">
         <v>24047</v>
       </c>
       <c r="O18" s="43">
@@ -7166,7 +7178,7 @@
       <c r="M19" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N19" s="44">
+      <c r="N19" s="55">
         <v>23901</v>
       </c>
       <c r="O19" s="43">
@@ -7232,7 +7244,7 @@
       <c r="M20" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N20" s="44">
+      <c r="N20" s="55">
         <v>25072</v>
       </c>
       <c r="O20" s="43">
@@ -7298,7 +7310,7 @@
       <c r="M21" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N21" s="44">
+      <c r="N21" s="55">
         <v>24100</v>
       </c>
       <c r="O21" s="43">
@@ -7364,7 +7376,7 @@
       <c r="M22" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N22" s="44">
+      <c r="N22" s="55">
         <v>24544</v>
       </c>
       <c r="O22" s="43">
@@ -7430,7 +7442,7 @@
       <c r="M23" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N23" s="44">
+      <c r="N23" s="55">
         <v>25818</v>
       </c>
       <c r="O23" s="43">
@@ -7496,7 +7508,7 @@
       <c r="M24" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N24" s="44">
+      <c r="N24" s="55">
         <v>25286</v>
       </c>
       <c r="O24" s="43">
@@ -7562,7 +7574,7 @@
       <c r="M25" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N25" s="44">
+      <c r="N25" s="55">
         <v>24587</v>
       </c>
       <c r="O25" s="43">
@@ -7628,7 +7640,7 @@
       <c r="M26" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N26" s="44">
+      <c r="N26" s="55">
         <v>25370</v>
       </c>
       <c r="O26" s="43">
@@ -7694,7 +7706,7 @@
       <c r="M27" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N27" s="44">
+      <c r="N27" s="55">
         <v>25053</v>
       </c>
       <c r="O27" s="43">
@@ -7760,7 +7772,7 @@
       <c r="M28" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N28" s="44">
+      <c r="N28" s="55">
         <v>24907</v>
       </c>
       <c r="O28" s="43">
@@ -7826,7 +7838,7 @@
       <c r="M29" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N29" s="44">
+      <c r="N29" s="55">
         <v>25224</v>
       </c>
       <c r="O29" s="43">
@@ -7892,7 +7904,7 @@
       <c r="M30" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N30" s="44">
+      <c r="N30" s="55">
         <v>25487</v>
       </c>
       <c r="O30" s="43">
@@ -7958,7 +7970,7 @@
       <c r="M31" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="44">
+      <c r="N31" s="55">
         <v>25489</v>
       </c>
       <c r="O31" s="43">
@@ -8024,7 +8036,7 @@
       <c r="M32" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N32" s="44">
+      <c r="N32" s="55">
         <v>25397</v>
       </c>
       <c r="O32" s="43">
@@ -8090,7 +8102,7 @@
       <c r="M33" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N33" s="44">
+      <c r="N33" s="55">
         <v>25565</v>
       </c>
       <c r="O33" s="43">
@@ -8156,7 +8168,7 @@
       <c r="M34" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N34" s="44">
+      <c r="N34" s="55">
         <v>26069</v>
       </c>
       <c r="O34" s="43">
@@ -8222,7 +8234,7 @@
       <c r="M35" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N35" s="44">
+      <c r="N35" s="55">
         <v>26156</v>
       </c>
       <c r="O35" s="43">
@@ -8288,7 +8300,7 @@
       <c r="M36" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N36" s="44">
+      <c r="N36" s="55">
         <v>26106</v>
       </c>
       <c r="O36" s="43">
@@ -8354,7 +8366,7 @@
       <c r="M37" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N37" s="44">
+      <c r="N37" s="55">
         <v>26449</v>
       </c>
       <c r="O37" s="43">
@@ -8420,7 +8432,7 @@
       <c r="M38" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N38" s="44">
+      <c r="N38" s="55">
         <v>26588</v>
       </c>
       <c r="O38" s="43">
@@ -8486,7 +8498,7 @@
       <c r="M39" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N39" s="44">
+      <c r="N39" s="55">
         <v>25154</v>
       </c>
       <c r="O39" s="43">
@@ -8552,7 +8564,7 @@
       <c r="M40" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N40" s="44">
+      <c r="N40" s="55">
         <v>25469</v>
       </c>
       <c r="O40" s="43">
@@ -8618,7 +8630,7 @@
       <c r="M41" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N41" s="44">
+      <c r="N41" s="55">
         <v>25104</v>
       </c>
       <c r="O41" s="43">
@@ -8684,7 +8696,7 @@
       <c r="M42" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N42" s="44">
+      <c r="N42" s="55">
         <v>25368</v>
       </c>
       <c r="O42" s="43">
@@ -8750,7 +8762,7 @@
       <c r="M43" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N43" s="44">
+      <c r="N43" s="55">
         <v>25780</v>
       </c>
       <c r="O43" s="43">
@@ -8816,7 +8828,7 @@
       <c r="M44" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N44" s="44">
+      <c r="N44" s="55">
         <v>26872</v>
       </c>
       <c r="O44" s="43">
@@ -8882,7 +8894,7 @@
       <c r="M45" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N45" s="44">
+      <c r="N45" s="55">
         <v>26528</v>
       </c>
       <c r="O45" s="43">
@@ -8948,7 +8960,7 @@
       <c r="M46" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N46" s="44">
+      <c r="N46" s="55">
         <v>26315</v>
       </c>
       <c r="O46" s="43">
@@ -9014,7 +9026,7 @@
       <c r="M47" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N47" s="44">
+      <c r="N47" s="55">
         <v>26625</v>
       </c>
       <c r="O47" s="43">
@@ -9080,7 +9092,7 @@
       <c r="M48" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N48" s="44">
+      <c r="N48" s="55">
         <v>26537</v>
       </c>
       <c r="O48" s="43">
@@ -9146,7 +9158,7 @@
       <c r="M49" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N49" s="44">
+      <c r="N49" s="55">
         <v>26442</v>
       </c>
       <c r="O49" s="43">
@@ -9212,7 +9224,7 @@
       <c r="M50" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N50" s="44">
+      <c r="N50" s="55">
         <v>26599</v>
       </c>
       <c r="O50" s="43">
@@ -9278,7 +9290,7 @@
       <c r="M51" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N51" s="44">
+      <c r="N51" s="55">
         <v>26950</v>
       </c>
       <c r="O51" s="43">
@@ -9344,7 +9356,7 @@
       <c r="M52" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N52" s="44">
+      <c r="N52" s="55">
         <v>26695</v>
       </c>
       <c r="O52" s="43">
@@ -9410,7 +9422,7 @@
       <c r="M53" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N53" s="44">
+      <c r="N53" s="55">
         <v>26760</v>
       </c>
       <c r="O53" s="43">
@@ -9476,7 +9488,7 @@
       <c r="M54" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N54" s="44">
+      <c r="N54" s="55">
         <v>26871</v>
       </c>
       <c r="O54" s="43">
@@ -9542,7 +9554,7 @@
       <c r="M55" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N55" s="44">
+      <c r="N55" s="55">
         <v>27322</v>
       </c>
       <c r="O55" s="43">
@@ -9608,7 +9620,7 @@
       <c r="M56" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N56" s="44">
+      <c r="N56" s="55">
         <v>27117</v>
       </c>
       <c r="O56" s="43">
@@ -9674,7 +9686,7 @@
       <c r="M57" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N57" s="44">
+      <c r="N57" s="55">
         <v>27668</v>
       </c>
       <c r="O57" s="43">
@@ -9740,7 +9752,7 @@
       <c r="M58" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N58" s="44">
+      <c r="N58" s="55">
         <v>27729</v>
       </c>
       <c r="O58" s="43">
@@ -9806,7 +9818,7 @@
       <c r="M59" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N59" s="44">
+      <c r="N59" s="55">
         <v>28089</v>
       </c>
       <c r="O59" s="43">
@@ -9872,7 +9884,7 @@
       <c r="M60" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N60" s="44">
+      <c r="N60" s="55">
         <v>28713</v>
       </c>
       <c r="O60" s="43">
@@ -9938,7 +9950,7 @@
       <c r="M61" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N61" s="44">
+      <c r="N61" s="55">
         <v>28719</v>
       </c>
       <c r="O61" s="43">
@@ -10004,7 +10016,7 @@
       <c r="M62" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N62" s="44">
+      <c r="N62" s="55">
         <v>28514</v>
       </c>
       <c r="O62" s="43">
@@ -10070,7 +10082,7 @@
       <c r="M63" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N63" s="44">
+      <c r="N63" s="55">
         <v>28521</v>
       </c>
       <c r="O63" s="43">
@@ -10136,7 +10148,7 @@
       <c r="M64" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N64" s="44">
+      <c r="N64" s="55">
         <v>29086</v>
       </c>
       <c r="O64" s="43">
@@ -10202,7 +10214,7 @@
       <c r="M65" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N65" s="44">
+      <c r="N65" s="55">
         <v>29321</v>
       </c>
       <c r="O65" s="43">
@@ -10268,7 +10280,7 @@
       <c r="M66" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N66" s="44">
+      <c r="N66" s="55">
         <v>29301</v>
       </c>
       <c r="O66" s="43">
@@ -10334,7 +10346,7 @@
       <c r="M67" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N67" s="44">
+      <c r="N67" s="55">
         <v>27178</v>
       </c>
       <c r="O67" s="43">
@@ -10400,7 +10412,7 @@
       <c r="M68" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N68" s="44">
+      <c r="N68" s="55">
         <v>25323</v>
       </c>
       <c r="O68" s="43">
@@ -10466,7 +10478,7 @@
       <c r="M69" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N69" s="44">
+      <c r="N69" s="55">
         <v>27211</v>
       </c>
       <c r="O69" s="43">
@@ -10532,7 +10544,7 @@
       <c r="M70" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="N70" s="44">
+      <c r="N70" s="55">
         <v>26769</v>
       </c>
       <c r="O70" s="43">
@@ -10598,7 +10610,7 @@
       <c r="M71" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N71" s="44">
+      <c r="N71" s="55">
         <v>26884</v>
       </c>
       <c r="O71" s="43">
@@ -10664,7 +10676,7 @@
       <c r="M72" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N72" s="44">
+      <c r="N72" s="55">
         <v>27510</v>
       </c>
       <c r="O72" s="43">
@@ -10730,7 +10742,7 @@
       <c r="M73" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N73" s="44">
+      <c r="N73" s="55">
         <v>30549</v>
       </c>
       <c r="O73" s="43">
@@ -10796,7 +10808,7 @@
       <c r="M74" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N74" s="44">
+      <c r="N74" s="55">
         <v>30782</v>
       </c>
       <c r="O74" s="43">
@@ -10862,7 +10874,7 @@
       <c r="M75" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N75" s="44">
+      <c r="N75" s="55">
         <v>31303</v>
       </c>
       <c r="O75" s="43">
@@ -10928,7 +10940,7 @@
       <c r="M76" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N76" s="44">
+      <c r="N76" s="55">
         <v>25382</v>
       </c>
       <c r="O76" s="43">
@@ -10994,7 +11006,7 @@
       <c r="M77" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N77" s="44">
+      <c r="N77" s="55">
         <v>22396</v>
       </c>
       <c r="O77" s="43">
@@ -11060,7 +11072,7 @@
       <c r="M78" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N78" s="44">
+      <c r="N78" s="55">
         <v>23925</v>
       </c>
       <c r="O78" s="43">
@@ -11126,7 +11138,7 @@
       <c r="M79" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N79" s="44">
+      <c r="N79" s="55">
         <v>22229</v>
       </c>
       <c r="O79" s="43">
@@ -11192,7 +11204,7 @@
       <c r="M80" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N80" s="44">
+      <c r="N80" s="55">
         <v>22999</v>
       </c>
       <c r="O80" s="43">
@@ -11258,7 +11270,7 @@
       <c r="M81" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N81" s="44">
+      <c r="N81" s="55">
         <v>22521</v>
       </c>
       <c r="O81" s="43">
@@ -11324,7 +11336,7 @@
       <c r="M82" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N82" s="44">
+      <c r="N82" s="55">
         <v>22379</v>
       </c>
       <c r="O82" s="43">
@@ -11390,7 +11402,7 @@
       <c r="M83" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N83" s="44">
+      <c r="N83" s="55">
         <v>28892</v>
       </c>
       <c r="O83" s="43">
@@ -11456,7 +11468,7 @@
       <c r="M84" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N84" s="44">
+      <c r="N84" s="55">
         <v>22630</v>
       </c>
       <c r="O84" s="43">
@@ -11522,7 +11534,7 @@
       <c r="M85" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N85" s="44">
+      <c r="N85" s="55">
         <v>24460</v>
       </c>
       <c r="O85" s="43">
@@ -11588,7 +11600,7 @@
       <c r="M86" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N86" s="44">
+      <c r="N86" s="55">
         <v>24349</v>
       </c>
       <c r="O86" s="43">
@@ -11654,7 +11666,7 @@
       <c r="M87" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N87" s="44">
+      <c r="N87" s="55">
         <v>30609</v>
       </c>
       <c r="O87" s="43">
@@ -11720,7 +11732,7 @@
       <c r="M88" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N88" s="44">
+      <c r="N88" s="55">
         <v>27971</v>
       </c>
       <c r="O88" s="43">
@@ -11786,7 +11798,7 @@
       <c r="M89" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N89" s="44">
+      <c r="N89" s="55">
         <v>28617</v>
       </c>
       <c r="O89" s="43">
@@ -11852,7 +11864,7 @@
       <c r="M90" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N90" s="44">
+      <c r="N90" s="55">
         <v>25892</v>
       </c>
       <c r="O90" s="43">
@@ -11918,7 +11930,7 @@
       <c r="M91" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N91" s="44">
+      <c r="N91" s="55">
         <v>30111</v>
       </c>
       <c r="O91" s="43">
@@ -11984,7 +11996,7 @@
       <c r="M92" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N92" s="44">
+      <c r="N92" s="55">
         <v>26221</v>
       </c>
       <c r="O92" s="43">
@@ -12050,7 +12062,7 @@
       <c r="M93" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N93" s="44">
+      <c r="N93" s="55">
         <v>29493</v>
       </c>
       <c r="O93" s="43">
@@ -12116,7 +12128,7 @@
       <c r="M94" s="42" t="s">
         <v>310</v>
       </c>
-      <c r="N94" s="44">
+      <c r="N94" s="55">
         <v>30100</v>
       </c>
       <c r="O94" s="43">
@@ -12182,7 +12194,7 @@
       <c r="M95" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N95" s="44">
+      <c r="N95" s="55">
         <v>27811</v>
       </c>
       <c r="O95" s="43">
@@ -12248,7 +12260,7 @@
       <c r="M96" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N96" s="44">
+      <c r="N96" s="55">
         <v>32435</v>
       </c>
       <c r="O96" s="43">
@@ -12314,7 +12326,7 @@
       <c r="M97" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N97" s="44">
+      <c r="N97" s="55">
         <v>29693</v>
       </c>
       <c r="O97" s="43">
@@ -12380,7 +12392,7 @@
       <c r="M98" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N98" s="44">
+      <c r="N98" s="55">
         <v>27813</v>
       </c>
       <c r="O98" s="43">
@@ -12446,7 +12458,7 @@
       <c r="M99" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N99" s="44">
+      <c r="N99" s="55">
         <v>30391</v>
       </c>
       <c r="O99" s="43">
@@ -12512,7 +12524,7 @@
       <c r="M100" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N100" s="44">
+      <c r="N100" s="55">
         <v>31061</v>
       </c>
       <c r="O100" s="43">
@@ -12578,7 +12590,7 @@
       <c r="M101" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N101" s="44">
+      <c r="N101" s="55">
         <v>31313</v>
       </c>
       <c r="O101" s="43">
@@ -12644,7 +12656,7 @@
       <c r="M102" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N102" s="44">
+      <c r="N102" s="55">
         <v>31295</v>
       </c>
       <c r="O102" s="43">
@@ -12710,7 +12722,7 @@
       <c r="M103" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N103" s="44">
+      <c r="N103" s="55">
         <v>31493</v>
       </c>
       <c r="O103" s="43">
@@ -12776,7 +12788,7 @@
       <c r="M104" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N104" s="44">
+      <c r="N104" s="55">
         <v>27192</v>
       </c>
       <c r="O104" s="43">
@@ -12842,7 +12854,7 @@
       <c r="M105" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N105" s="44">
+      <c r="N105" s="55">
         <v>27628</v>
       </c>
       <c r="O105" s="43">
@@ -12908,7 +12920,7 @@
       <c r="M106" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N106" s="44">
+      <c r="N106" s="55">
         <v>27264</v>
       </c>
       <c r="O106" s="43">
@@ -12974,7 +12986,7 @@
       <c r="M107" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N107" s="44">
+      <c r="N107" s="55">
         <v>27770</v>
       </c>
       <c r="O107" s="43">
@@ -13040,7 +13052,7 @@
       <c r="M108" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N108" s="44">
+      <c r="N108" s="55">
         <v>28014</v>
       </c>
       <c r="O108" s="43">
@@ -13106,7 +13118,7 @@
       <c r="M109" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N109" s="44">
+      <c r="N109" s="55">
         <v>28170</v>
       </c>
       <c r="O109" s="43">
@@ -13172,7 +13184,7 @@
       <c r="M110" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N110" s="44">
+      <c r="N110" s="55">
         <v>26412</v>
       </c>
       <c r="O110" s="43">
@@ -13238,7 +13250,7 @@
       <c r="M111" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N111" s="44">
+      <c r="N111" s="55">
         <v>24988</v>
       </c>
       <c r="O111" s="43">
@@ -13304,7 +13316,7 @@
       <c r="M112" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N112" s="44">
+      <c r="N112" s="55">
         <v>27404</v>
       </c>
       <c r="O112" s="43">
@@ -13370,7 +13382,7 @@
       <c r="M113" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N113" s="44">
+      <c r="N113" s="55">
         <v>25124</v>
       </c>
       <c r="O113" s="43">
@@ -13436,7 +13448,7 @@
       <c r="M114" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N114" s="44">
+      <c r="N114" s="55">
         <v>26464</v>
       </c>
       <c r="O114" s="43">
@@ -13502,7 +13514,7 @@
       <c r="M115" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N115" s="44">
+      <c r="N115" s="55">
         <v>28459</v>
       </c>
       <c r="O115" s="43">
@@ -13568,7 +13580,7 @@
       <c r="M116" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N116" s="44">
+      <c r="N116" s="55">
         <v>26789</v>
       </c>
       <c r="O116" s="43">
@@ -13634,7 +13646,7 @@
       <c r="M117" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N117" s="44">
+      <c r="N117" s="55">
         <v>26868</v>
       </c>
       <c r="O117" s="43">
@@ -13700,7 +13712,7 @@
       <c r="M118" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N118" s="44">
+      <c r="N118" s="55">
         <v>28020</v>
       </c>
       <c r="O118" s="43">
@@ -13766,7 +13778,7 @@
       <c r="M119" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N119" s="44">
+      <c r="N119" s="55">
         <v>22911</v>
       </c>
       <c r="O119" s="43">
@@ -13832,7 +13844,7 @@
       <c r="M120" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N120" s="44">
+      <c r="N120" s="55">
         <v>27844</v>
       </c>
       <c r="O120" s="43">
@@ -13898,7 +13910,7 @@
       <c r="M121" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N121" s="44">
+      <c r="N121" s="55">
         <v>27020</v>
       </c>
       <c r="O121" s="43">
@@ -13964,7 +13976,7 @@
       <c r="M122" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N122" s="44">
+      <c r="N122" s="55">
         <v>26591</v>
       </c>
       <c r="O122" s="43">
@@ -14030,7 +14042,7 @@
       <c r="M123" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N123" s="44">
+      <c r="N123" s="55">
         <v>28854</v>
       </c>
       <c r="O123" s="43">
@@ -14096,7 +14108,7 @@
       <c r="M124" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N124" s="44">
+      <c r="N124" s="55">
         <v>24495</v>
       </c>
       <c r="O124" s="43">
@@ -14162,7 +14174,7 @@
       <c r="M125" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N125" s="44">
+      <c r="N125" s="55">
         <v>29651</v>
       </c>
       <c r="O125" s="43">
@@ -14228,7 +14240,7 @@
       <c r="M126" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N126" s="44">
+      <c r="N126" s="55">
         <v>25393</v>
       </c>
       <c r="O126" s="43">
@@ -14294,7 +14306,7 @@
       <c r="M127" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N127" s="44">
+      <c r="N127" s="55">
         <v>26387</v>
       </c>
       <c r="O127" s="43">
@@ -14360,7 +14372,7 @@
       <c r="M128" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N128" s="44">
+      <c r="N128" s="55">
         <v>24247</v>
       </c>
       <c r="O128" s="43">
@@ -14426,7 +14438,7 @@
       <c r="M129" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N129" s="44">
+      <c r="N129" s="55">
         <v>28323</v>
       </c>
       <c r="O129" s="43">
@@ -14492,7 +14504,7 @@
       <c r="M130" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N130" s="44">
+      <c r="N130" s="55">
         <v>25528</v>
       </c>
       <c r="O130" s="43">
@@ -14558,7 +14570,7 @@
       <c r="M131" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N131" s="44">
+      <c r="N131" s="55">
         <v>25213</v>
       </c>
       <c r="O131" s="43">
@@ -14624,7 +14636,7 @@
       <c r="M132" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N132" s="44">
+      <c r="N132" s="55">
         <v>26615</v>
       </c>
       <c r="O132" s="43">
@@ -14690,7 +14702,7 @@
       <c r="M133" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N133" s="44">
+      <c r="N133" s="55">
         <v>27870</v>
       </c>
       <c r="O133" s="43">
@@ -14756,7 +14768,7 @@
       <c r="M134" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N134" s="44">
+      <c r="N134" s="55">
         <v>26598</v>
       </c>
       <c r="O134" s="43">
@@ -14822,7 +14834,7 @@
       <c r="M135" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N135" s="44">
+      <c r="N135" s="55">
         <v>26153</v>
       </c>
       <c r="O135" s="43">
@@ -14888,7 +14900,7 @@
       <c r="M136" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N136" s="44">
+      <c r="N136" s="55">
         <v>26437</v>
       </c>
       <c r="O136" s="43">
@@ -14954,7 +14966,7 @@
       <c r="M137" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N137" s="44">
+      <c r="N137" s="55">
         <v>27048</v>
       </c>
       <c r="O137" s="43">
@@ -15020,7 +15032,7 @@
       <c r="M138" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N138" s="44">
+      <c r="N138" s="55">
         <v>26759</v>
       </c>
       <c r="O138" s="43">
@@ -15086,7 +15098,7 @@
       <c r="M139" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N139" s="44">
+      <c r="N139" s="55">
         <v>28350</v>
       </c>
       <c r="O139" s="43">
@@ -15152,7 +15164,7 @@
       <c r="M140" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N140" s="44">
+      <c r="N140" s="55">
         <v>28106</v>
       </c>
       <c r="O140" s="43">
@@ -15218,7 +15230,7 @@
       <c r="M141" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N141" s="44">
+      <c r="N141" s="55">
         <v>26945</v>
       </c>
       <c r="O141" s="43">
@@ -15284,7 +15296,7 @@
       <c r="M142" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N142" s="44">
+      <c r="N142" s="55">
         <v>27498</v>
       </c>
       <c r="O142" s="43">
@@ -15350,7 +15362,7 @@
       <c r="M143" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N143" s="44">
+      <c r="N143" s="55">
         <v>26261</v>
       </c>
       <c r="O143" s="43">
@@ -15416,7 +15428,7 @@
       <c r="M144" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N144" s="44">
+      <c r="N144" s="55">
         <v>28267</v>
       </c>
       <c r="O144" s="43">
@@ -15482,7 +15494,7 @@
       <c r="M145" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N145" s="44">
+      <c r="N145" s="55">
         <v>27256</v>
       </c>
       <c r="O145" s="43">
@@ -15548,7 +15560,7 @@
       <c r="M146" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N146" s="44">
+      <c r="N146" s="55">
         <v>27382</v>
       </c>
       <c r="O146" s="43">
@@ -15614,7 +15626,7 @@
       <c r="M147" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N147" s="44">
+      <c r="N147" s="55">
         <v>26960</v>
       </c>
       <c r="O147" s="43">
@@ -15680,7 +15692,7 @@
       <c r="M148" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N148" s="44">
+      <c r="N148" s="55">
         <v>25799</v>
       </c>
       <c r="O148" s="43">
@@ -15746,7 +15758,7 @@
       <c r="M149" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N149" s="44">
+      <c r="N149" s="55">
         <v>27933</v>
       </c>
       <c r="O149" s="43">
@@ -15812,7 +15824,7 @@
       <c r="M150" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N150" s="44">
+      <c r="N150" s="55">
         <v>31840</v>
       </c>
       <c r="O150" s="43">
@@ -15878,7 +15890,7 @@
       <c r="M151" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N151" s="44">
+      <c r="N151" s="55">
         <v>27371</v>
       </c>
       <c r="O151" s="43">
@@ -15944,7 +15956,7 @@
       <c r="M152" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N152" s="44">
+      <c r="N152" s="55">
         <v>27777</v>
       </c>
       <c r="O152" s="43">
@@ -16010,7 +16022,7 @@
       <c r="M153" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N153" s="44">
+      <c r="N153" s="55">
         <v>29097</v>
       </c>
       <c r="O153" s="43">
@@ -16076,7 +16088,7 @@
       <c r="M154" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N154" s="44">
+      <c r="N154" s="55">
         <v>26390</v>
       </c>
       <c r="O154" s="43">
@@ -16142,7 +16154,7 @@
       <c r="M155" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N155" s="44">
+      <c r="N155" s="55">
         <v>28091</v>
       </c>
       <c r="O155" s="43">
@@ -16208,7 +16220,7 @@
       <c r="M156" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N156" s="44">
+      <c r="N156" s="55">
         <v>29715</v>
       </c>
       <c r="O156" s="43">
@@ -16274,7 +16286,7 @@
       <c r="M157" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N157" s="44">
+      <c r="N157" s="55">
         <v>26880</v>
       </c>
       <c r="O157" s="43">
@@ -16340,7 +16352,7 @@
       <c r="M158" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N158" s="44">
+      <c r="N158" s="55">
         <v>30362</v>
       </c>
       <c r="O158" s="43">
@@ -16406,7 +16418,7 @@
       <c r="M159" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N159" s="44">
+      <c r="N159" s="55">
         <v>26003</v>
       </c>
       <c r="O159" s="43">
@@ -16472,7 +16484,7 @@
       <c r="M160" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N160" s="44">
+      <c r="N160" s="55">
         <v>26517</v>
       </c>
       <c r="O160" s="43">
@@ -16538,7 +16550,7 @@
       <c r="M161" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N161" s="44">
+      <c r="N161" s="55">
         <v>29868</v>
       </c>
       <c r="O161" s="43">
@@ -16604,7 +16616,7 @@
       <c r="M162" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N162" s="44">
+      <c r="N162" s="55">
         <v>29844</v>
       </c>
       <c r="O162" s="43">
@@ -16670,7 +16682,7 @@
       <c r="M163" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N163" s="44">
+      <c r="N163" s="55">
         <v>31767</v>
       </c>
       <c r="O163" s="43">
@@ -16736,7 +16748,7 @@
       <c r="M164" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N164" s="44">
+      <c r="N164" s="55">
         <v>28371</v>
       </c>
       <c r="O164" s="43">
@@ -16802,7 +16814,7 @@
       <c r="M165" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N165" s="44">
+      <c r="N165" s="55">
         <v>24449</v>
       </c>
       <c r="O165" s="43">
@@ -16868,7 +16880,7 @@
       <c r="M166" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N166" s="44">
+      <c r="N166" s="55">
         <v>26164</v>
       </c>
       <c r="O166" s="43">
@@ -16934,7 +16946,7 @@
       <c r="M167" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N167" s="44">
+      <c r="N167" s="55">
         <v>29629</v>
       </c>
       <c r="O167" s="43">
@@ -17000,7 +17012,7 @@
       <c r="M168" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N168" s="44">
+      <c r="N168" s="55">
         <v>31548</v>
       </c>
       <c r="O168" s="43">
@@ -17066,7 +17078,7 @@
       <c r="M169" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N169" s="44">
+      <c r="N169" s="55">
         <v>23439</v>
       </c>
       <c r="O169" s="43">
@@ -17132,7 +17144,7 @@
       <c r="M170" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N170" s="44">
+      <c r="N170" s="55">
         <v>31785</v>
       </c>
       <c r="O170" s="43">
@@ -17198,7 +17210,7 @@
       <c r="M171" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N171" s="44">
+      <c r="N171" s="55">
         <v>29187</v>
       </c>
       <c r="O171" s="43">
@@ -17264,7 +17276,7 @@
       <c r="M172" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N172" s="44">
+      <c r="N172" s="55">
         <v>27175</v>
       </c>
       <c r="O172" s="43">
@@ -17330,7 +17342,7 @@
       <c r="M173" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N173" s="44">
+      <c r="N173" s="55">
         <v>25445</v>
       </c>
       <c r="O173" s="43">
@@ -17396,7 +17408,7 @@
       <c r="M174" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N174" s="44">
+      <c r="N174" s="55">
         <v>26899</v>
       </c>
       <c r="O174" s="43">
@@ -17462,7 +17474,7 @@
       <c r="M175" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N175" s="44">
+      <c r="N175" s="55">
         <v>28703</v>
       </c>
       <c r="O175" s="43">
@@ -17528,7 +17540,7 @@
       <c r="M176" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N176" s="44">
+      <c r="N176" s="55">
         <v>30401</v>
       </c>
       <c r="O176" s="43">
@@ -17594,7 +17606,7 @@
       <c r="M177" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N177" s="44">
+      <c r="N177" s="55">
         <v>27445</v>
       </c>
       <c r="O177" s="43">
@@ -17660,7 +17672,7 @@
       <c r="M178" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N178" s="44">
+      <c r="N178" s="55">
         <v>30367</v>
       </c>
       <c r="O178" s="43">
@@ -17726,7 +17738,7 @@
       <c r="M179" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N179" s="44">
+      <c r="N179" s="55">
         <v>28499</v>
       </c>
       <c r="O179" s="43">
@@ -17792,7 +17804,7 @@
       <c r="M180" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N180" s="44">
+      <c r="N180" s="55">
         <v>28982</v>
       </c>
       <c r="O180" s="43">
@@ -17858,7 +17870,7 @@
       <c r="M181" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N181" s="44">
+      <c r="N181" s="55">
         <v>24294</v>
       </c>
       <c r="O181" s="43">
@@ -17924,7 +17936,7 @@
       <c r="M182" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N182" s="44">
+      <c r="N182" s="55">
         <v>27729</v>
       </c>
       <c r="O182" s="43">
@@ -17990,7 +18002,7 @@
       <c r="M183" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N183" s="44">
+      <c r="N183" s="55">
         <v>26247</v>
       </c>
       <c r="O183" s="43">
@@ -18056,7 +18068,7 @@
       <c r="M184" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N184" s="44">
+      <c r="N184" s="55">
         <v>27349</v>
       </c>
       <c r="O184" s="43">
@@ -18122,7 +18134,7 @@
       <c r="M185" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N185" s="44">
+      <c r="N185" s="55">
         <v>29747</v>
       </c>
       <c r="O185" s="43">
@@ -18188,7 +18200,7 @@
       <c r="M186" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N186" s="44">
+      <c r="N186" s="55">
         <v>27920</v>
       </c>
       <c r="O186" s="43">
@@ -18254,7 +18266,7 @@
       <c r="M187" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N187" s="44">
+      <c r="N187" s="55">
         <v>29365</v>
       </c>
       <c r="O187" s="43">
@@ -18320,7 +18332,7 @@
       <c r="M188" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N188" s="44">
+      <c r="N188" s="55">
         <v>28199</v>
       </c>
       <c r="O188" s="43">
@@ -18386,7 +18398,7 @@
       <c r="M189" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N189" s="44">
+      <c r="N189" s="55">
         <v>26407</v>
       </c>
       <c r="O189" s="43">
@@ -18452,7 +18464,7 @@
       <c r="M190" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N190" s="44">
+      <c r="N190" s="55">
         <v>30770</v>
       </c>
       <c r="O190" s="43">
@@ -18518,7 +18530,7 @@
       <c r="M191" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N191" s="44">
+      <c r="N191" s="55">
         <v>29708</v>
       </c>
       <c r="O191" s="43">
@@ -18584,7 +18596,7 @@
       <c r="M192" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N192" s="44">
+      <c r="N192" s="55">
         <v>28226</v>
       </c>
       <c r="O192" s="43">
@@ -18650,7 +18662,7 @@
       <c r="M193" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N193" s="44">
+      <c r="N193" s="55">
         <v>28471</v>
       </c>
       <c r="O193" s="43">
@@ -18716,7 +18728,7 @@
       <c r="M194" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N194" s="44">
+      <c r="N194" s="55">
         <v>29353</v>
       </c>
       <c r="O194" s="43">
@@ -18782,7 +18794,7 @@
       <c r="M195" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N195" s="44">
+      <c r="N195" s="55">
         <v>27868</v>
       </c>
       <c r="O195" s="43">
@@ -18848,7 +18860,7 @@
       <c r="M196" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N196" s="44">
+      <c r="N196" s="55">
         <v>31432</v>
       </c>
       <c r="O196" s="43">
@@ -18914,7 +18926,7 @@
       <c r="M197" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N197" s="44">
+      <c r="N197" s="55">
         <v>29785</v>
       </c>
       <c r="O197" s="43">
@@ -18980,7 +18992,7 @@
       <c r="M198" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N198" s="44">
+      <c r="N198" s="55">
         <v>26659</v>
       </c>
       <c r="O198" s="43">
@@ -19046,7 +19058,7 @@
       <c r="M199" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N199" s="44">
+      <c r="N199" s="55">
         <v>30330</v>
       </c>
       <c r="O199" s="43">
@@ -19112,7 +19124,7 @@
       <c r="M200" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N200" s="44">
+      <c r="N200" s="55">
         <v>25605</v>
       </c>
       <c r="O200" s="43">
@@ -19178,7 +19190,7 @@
       <c r="M201" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N201" s="44">
+      <c r="N201" s="55">
         <v>29357</v>
       </c>
       <c r="O201" s="43">
@@ -19244,7 +19256,7 @@
       <c r="M202" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N202" s="44">
+      <c r="N202" s="55">
         <v>28350</v>
       </c>
       <c r="O202" s="43">
@@ -19310,7 +19322,7 @@
       <c r="M203" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N203" s="44">
+      <c r="N203" s="55">
         <v>31161</v>
       </c>
       <c r="O203" s="43">
@@ -19376,7 +19388,7 @@
       <c r="M204" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N204" s="44">
+      <c r="N204" s="55">
         <v>31251</v>
       </c>
       <c r="O204" s="43">
@@ -19442,7 +19454,7 @@
       <c r="M205" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N205" s="44">
+      <c r="N205" s="55">
         <v>25062</v>
       </c>
       <c r="O205" s="43">
@@ -19508,7 +19520,7 @@
       <c r="M206" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N206" s="44">
+      <c r="N206" s="55">
         <v>30274</v>
       </c>
       <c r="O206" s="43">
@@ -19574,7 +19586,7 @@
       <c r="M207" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N207" s="44">
+      <c r="N207" s="55">
         <v>25238</v>
       </c>
       <c r="O207" s="43">
@@ -19640,7 +19652,7 @@
       <c r="M208" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N208" s="44">
+      <c r="N208" s="55">
         <v>25123</v>
       </c>
       <c r="O208" s="43">
@@ -19706,7 +19718,7 @@
       <c r="M209" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N209" s="44">
+      <c r="N209" s="55">
         <v>30201</v>
       </c>
       <c r="O209" s="43">
@@ -19772,7 +19784,7 @@
       <c r="M210" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N210" s="44">
+      <c r="N210" s="55">
         <v>30428</v>
       </c>
       <c r="O210" s="43">
@@ -19838,7 +19850,7 @@
       <c r="M211" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N211" s="44">
+      <c r="N211" s="55">
         <v>23084</v>
       </c>
       <c r="O211" s="43">
@@ -19904,7 +19916,7 @@
       <c r="M212" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N212" s="44">
+      <c r="N212" s="55">
         <v>28422</v>
       </c>
       <c r="O212" s="43">
@@ -19970,7 +19982,7 @@
       <c r="M213" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N213" s="44">
+      <c r="N213" s="55">
         <v>30238</v>
       </c>
       <c r="O213" s="43">
@@ -20036,7 +20048,7 @@
       <c r="M214" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N214" s="44">
+      <c r="N214" s="55">
         <v>30120</v>
       </c>
       <c r="O214" s="43">
@@ -20102,7 +20114,7 @@
       <c r="M215" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N215" s="44">
+      <c r="N215" s="55">
         <v>29892</v>
       </c>
       <c r="O215" s="43">
@@ -20168,7 +20180,7 @@
       <c r="M216" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N216" s="44">
+      <c r="N216" s="55">
         <v>27689</v>
       </c>
       <c r="O216" s="43">
@@ -20234,7 +20246,7 @@
       <c r="M217" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N217" s="44">
+      <c r="N217" s="55">
         <v>26085</v>
       </c>
       <c r="O217" s="43">
@@ -20300,7 +20312,7 @@
       <c r="M218" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N218" s="44">
+      <c r="N218" s="55">
         <v>26995</v>
       </c>
       <c r="O218" s="43">
@@ -20366,7 +20378,7 @@
       <c r="M219" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N219" s="44">
+      <c r="N219" s="55">
         <v>29224</v>
       </c>
       <c r="O219" s="43">
@@ -20432,7 +20444,7 @@
       <c r="M220" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="N220" s="44">
+      <c r="N220" s="55">
         <v>29688</v>
       </c>
       <c r="O220" s="43">
@@ -20498,7 +20510,7 @@
       <c r="M221" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N221" s="44">
+      <c r="N221" s="55">
         <v>26839</v>
       </c>
       <c r="O221" s="43">
@@ -20564,7 +20576,7 @@
       <c r="M222" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N222" s="44">
+      <c r="N222" s="55">
         <v>31628</v>
       </c>
       <c r="O222" s="43">
@@ -20630,7 +20642,7 @@
       <c r="M223" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N223" s="44">
+      <c r="N223" s="55">
         <v>26331</v>
       </c>
       <c r="O223" s="43">
@@ -20696,7 +20708,7 @@
       <c r="M224" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N224" s="44">
+      <c r="N224" s="55">
         <v>32059</v>
       </c>
       <c r="O224" s="43">
@@ -20762,7 +20774,7 @@
       <c r="M225" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N225" s="44">
+      <c r="N225" s="55">
         <v>31539</v>
       </c>
       <c r="O225" s="43">
@@ -20828,7 +20840,7 @@
       <c r="M226" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N226" s="44">
+      <c r="N226" s="55">
         <v>25691</v>
       </c>
       <c r="O226" s="43">
@@ -20894,7 +20906,7 @@
       <c r="M227" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N227" s="44">
+      <c r="N227" s="55">
         <v>30939</v>
       </c>
       <c r="O227" s="43">
@@ -20960,7 +20972,7 @@
       <c r="M228" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N228" s="44">
+      <c r="N228" s="55">
         <v>26741</v>
       </c>
       <c r="O228" s="43">
@@ -21026,7 +21038,7 @@
       <c r="M229" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N229" s="44">
+      <c r="N229" s="55">
         <v>27502</v>
       </c>
       <c r="O229" s="43">
@@ -21092,7 +21104,7 @@
       <c r="M230" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N230" s="44">
+      <c r="N230" s="55">
         <v>28792</v>
       </c>
       <c r="O230" s="43">
@@ -21158,7 +21170,7 @@
       <c r="M231" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N231" s="44">
+      <c r="N231" s="55">
         <v>24387</v>
       </c>
       <c r="O231" s="43">
@@ -21224,7 +21236,7 @@
       <c r="M232" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N232" s="44">
+      <c r="N232" s="55">
         <v>24405</v>
       </c>
       <c r="O232" s="43">
@@ -21290,7 +21302,7 @@
       <c r="M233" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N233" s="44">
+      <c r="N233" s="55">
         <v>29203</v>
       </c>
       <c r="O233" s="43">
@@ -21356,7 +21368,7 @@
       <c r="M234" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N234" s="44">
+      <c r="N234" s="55">
         <v>31280</v>
       </c>
       <c r="O234" s="43">
@@ -21422,7 +21434,7 @@
       <c r="M235" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N235" s="44">
+      <c r="N235" s="55">
         <v>28346</v>
       </c>
       <c r="O235" s="43">
@@ -21488,7 +21500,7 @@
       <c r="M236" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N236" s="44">
+      <c r="N236" s="55">
         <v>28425</v>
       </c>
       <c r="O236" s="43">
@@ -21554,7 +21566,7 @@
       <c r="M237" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N237" s="44">
+      <c r="N237" s="55">
         <v>29384</v>
       </c>
       <c r="O237" s="43">
@@ -21620,7 +21632,7 @@
       <c r="M238" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N238" s="44">
+      <c r="N238" s="55">
         <v>25334</v>
       </c>
       <c r="O238" s="43">
@@ -21686,7 +21698,7 @@
       <c r="M239" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N239" s="44">
+      <c r="N239" s="55">
         <v>30239</v>
       </c>
       <c r="O239" s="43">
@@ -21752,7 +21764,7 @@
       <c r="M240" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N240" s="44">
+      <c r="N240" s="55">
         <v>24981</v>
       </c>
       <c r="O240" s="43">
@@ -21818,7 +21830,7 @@
       <c r="M241" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N241" s="44">
+      <c r="N241" s="55">
         <v>28461</v>
       </c>
       <c r="O241" s="43">
@@ -21884,7 +21896,7 @@
       <c r="M242" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N242" s="44">
+      <c r="N242" s="55">
         <v>29180</v>
       </c>
       <c r="O242" s="43">
@@ -21950,7 +21962,7 @@
       <c r="M243" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N243" s="44">
+      <c r="N243" s="55">
         <v>28891</v>
       </c>
       <c r="O243" s="43">
@@ -22016,7 +22028,7 @@
       <c r="M244" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N244" s="44">
+      <c r="N244" s="55">
         <v>30343</v>
       </c>
       <c r="O244" s="43">
@@ -22082,7 +22094,7 @@
       <c r="M245" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N245" s="44">
+      <c r="N245" s="55">
         <v>30260</v>
       </c>
       <c r="O245" s="43">
@@ -22148,7 +22160,7 @@
       <c r="M246" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N246" s="44">
+      <c r="N246" s="55">
         <v>27217</v>
       </c>
       <c r="O246" s="43">
@@ -22214,7 +22226,7 @@
       <c r="M247" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N247" s="44">
+      <c r="N247" s="55">
         <v>25850</v>
       </c>
       <c r="O247" s="43">
@@ -22280,7 +22292,7 @@
       <c r="M248" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N248" s="44">
+      <c r="N248" s="55">
         <v>28720</v>
       </c>
       <c r="O248" s="43">
@@ -22346,7 +22358,7 @@
       <c r="M249" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N249" s="44">
+      <c r="N249" s="55">
         <v>28476</v>
       </c>
       <c r="O249" s="43">
@@ -22412,7 +22424,7 @@
       <c r="M250" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N250" s="44">
+      <c r="N250" s="55">
         <v>30889</v>
       </c>
       <c r="O250" s="43">
@@ -22478,7 +22490,7 @@
       <c r="M251" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N251" s="44">
+      <c r="N251" s="55">
         <v>31231</v>
       </c>
       <c r="O251" s="43">
@@ -22544,7 +22556,7 @@
       <c r="M252" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N252" s="44">
+      <c r="N252" s="55">
         <v>26617</v>
       </c>
       <c r="O252" s="43">
@@ -22610,7 +22622,7 @@
       <c r="M253" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N253" s="44">
+      <c r="N253" s="55">
         <v>27109</v>
       </c>
       <c r="O253" s="43">
@@ -22676,7 +22688,7 @@
       <c r="M254" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N254" s="44">
+      <c r="N254" s="55">
         <v>26888</v>
       </c>
       <c r="O254" s="43">
@@ -22742,7 +22754,7 @@
       <c r="M255" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N255" s="44">
+      <c r="N255" s="55">
         <v>26066</v>
       </c>
       <c r="O255" s="43">
@@ -22808,7 +22820,7 @@
       <c r="M256" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N256" s="44">
+      <c r="N256" s="55">
         <v>31565</v>
       </c>
       <c r="O256" s="43">
@@ -22874,7 +22886,7 @@
       <c r="M257" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N257" s="44">
+      <c r="N257" s="55">
         <v>31220</v>
       </c>
       <c r="O257" s="43">
@@ -22940,7 +22952,7 @@
       <c r="M258" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N258" s="44">
+      <c r="N258" s="55">
         <v>25853</v>
       </c>
       <c r="O258" s="43">
@@ -23006,7 +23018,7 @@
       <c r="M259" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N259" s="44">
+      <c r="N259" s="55">
         <v>30546</v>
       </c>
       <c r="O259" s="43">
@@ -23072,7 +23084,7 @@
       <c r="M260" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N260" s="44">
+      <c r="N260" s="55">
         <v>30472</v>
       </c>
       <c r="O260" s="43">
@@ -23138,7 +23150,7 @@
       <c r="M261" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N261" s="44">
+      <c r="N261" s="55">
         <v>30654</v>
       </c>
       <c r="O261" s="43">
@@ -23204,7 +23216,7 @@
       <c r="M262" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N262" s="44">
+      <c r="N262" s="55">
         <v>28650</v>
       </c>
       <c r="O262" s="43">
@@ -23270,7 +23282,7 @@
       <c r="M263" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N263" s="44">
+      <c r="N263" s="55">
         <v>31241</v>
       </c>
       <c r="O263" s="43">
@@ -23336,7 +23348,7 @@
       <c r="M264" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N264" s="44">
+      <c r="N264" s="55">
         <v>31118</v>
       </c>
       <c r="O264" s="43">
@@ -23402,7 +23414,7 @@
       <c r="M265" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N265" s="44">
+      <c r="N265" s="55">
         <v>29131</v>
       </c>
       <c r="O265" s="43">
@@ -23468,7 +23480,7 @@
       <c r="M266" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N266" s="44">
+      <c r="N266" s="55">
         <v>33163</v>
       </c>
       <c r="O266" s="43">
@@ -23534,7 +23546,7 @@
       <c r="M267" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N267" s="44">
+      <c r="N267" s="55">
         <v>31879</v>
       </c>
       <c r="O267" s="43">
@@ -23600,7 +23612,7 @@
       <c r="M268" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N268" s="44">
+      <c r="N268" s="55">
         <v>30278</v>
       </c>
       <c r="O268" s="43">
@@ -23666,7 +23678,7 @@
       <c r="M269" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N269" s="44">
+      <c r="N269" s="55">
         <v>31225</v>
       </c>
       <c r="O269" s="43">
@@ -23732,7 +23744,7 @@
       <c r="M270" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N270" s="44">
+      <c r="N270" s="55">
         <v>30169</v>
       </c>
       <c r="O270" s="43">
@@ -23798,7 +23810,7 @@
       <c r="M271" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N271" s="44">
+      <c r="N271" s="55">
         <v>31862</v>
       </c>
       <c r="O271" s="43">
@@ -23864,7 +23876,7 @@
       <c r="M272" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N272" s="44">
+      <c r="N272" s="55">
         <v>31875</v>
       </c>
       <c r="O272" s="43">
@@ -23930,7 +23942,7 @@
       <c r="M273" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N273" s="44">
+      <c r="N273" s="55">
         <v>28713</v>
       </c>
       <c r="O273" s="43">
@@ -23996,7 +24008,7 @@
       <c r="M274" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N274" s="44">
+      <c r="N274" s="55">
         <v>32321</v>
       </c>
       <c r="O274" s="43">
@@ -24062,7 +24074,7 @@
       <c r="M275" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N275" s="44">
+      <c r="N275" s="55">
         <v>32964</v>
       </c>
       <c r="O275" s="43">
@@ -24128,7 +24140,7 @@
       <c r="M276" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N276" s="44">
+      <c r="N276" s="55">
         <v>31579</v>
       </c>
       <c r="O276" s="43">
@@ -24194,7 +24206,7 @@
       <c r="M277" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N277" s="44">
+      <c r="N277" s="55">
         <v>29151</v>
       </c>
       <c r="O277" s="43">
@@ -24260,7 +24272,7 @@
       <c r="M278" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N278" s="44">
+      <c r="N278" s="55">
         <v>29910</v>
       </c>
       <c r="O278" s="43">
@@ -24326,7 +24338,7 @@
       <c r="M279" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N279" s="44">
+      <c r="N279" s="55">
         <v>30749</v>
       </c>
       <c r="O279" s="43">
@@ -24392,7 +24404,7 @@
       <c r="M280" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N280" s="44">
+      <c r="N280" s="55">
         <v>28375</v>
       </c>
       <c r="O280" s="43">
@@ -24458,7 +24470,7 @@
       <c r="M281" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N281" s="44">
+      <c r="N281" s="55">
         <v>31563</v>
       </c>
       <c r="O281" s="43">
@@ -24524,7 +24536,7 @@
       <c r="M282" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N282" s="44">
+      <c r="N282" s="55">
         <v>31548</v>
       </c>
       <c r="O282" s="43">
@@ -24590,7 +24602,7 @@
       <c r="M283" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N283" s="44">
+      <c r="N283" s="55">
         <v>29917</v>
       </c>
       <c r="O283" s="43">
@@ -24656,7 +24668,7 @@
       <c r="M284" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N284" s="44">
+      <c r="N284" s="55">
         <v>31633</v>
       </c>
       <c r="O284" s="43">
@@ -24722,7 +24734,7 @@
       <c r="M285" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N285" s="44">
+      <c r="N285" s="55">
         <v>30315</v>
       </c>
       <c r="O285" s="43">
@@ -24788,7 +24800,7 @@
       <c r="M286" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N286" s="44">
+      <c r="N286" s="55">
         <v>33295</v>
       </c>
       <c r="O286" s="43">
@@ -24854,7 +24866,7 @@
       <c r="M287" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N287" s="44">
+      <c r="N287" s="55">
         <v>31709</v>
       </c>
       <c r="O287" s="43">
@@ -24920,7 +24932,7 @@
       <c r="M288" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N288" s="44">
+      <c r="N288" s="55">
         <v>32997</v>
       </c>
       <c r="O288" s="43">
@@ -24986,7 +24998,7 @@
       <c r="M289" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N289" s="44">
+      <c r="N289" s="55">
         <v>31676</v>
       </c>
       <c r="O289" s="43">
@@ -25052,7 +25064,7 @@
       <c r="M290" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N290" s="44">
+      <c r="N290" s="55">
         <v>31339</v>
       </c>
       <c r="O290" s="43">
@@ -25118,7 +25130,7 @@
       <c r="M291" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N291" s="44">
+      <c r="N291" s="55">
         <v>32777</v>
       </c>
       <c r="O291" s="43">
@@ -25184,7 +25196,7 @@
       <c r="M292" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N292" s="44">
+      <c r="N292" s="55">
         <v>31180</v>
       </c>
       <c r="O292" s="43">
@@ -25250,7 +25262,7 @@
       <c r="M293" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N293" s="44">
+      <c r="N293" s="55">
         <v>30374</v>
       </c>
       <c r="O293" s="43">
@@ -25316,7 +25328,7 @@
       <c r="M294" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N294" s="44">
+      <c r="N294" s="55">
         <v>30231</v>
       </c>
       <c r="O294" s="43">
@@ -25382,7 +25394,7 @@
       <c r="M295" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N295" s="44">
+      <c r="N295" s="55">
         <v>33173</v>
       </c>
       <c r="O295" s="43">
@@ -25448,7 +25460,7 @@
       <c r="M296" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N296" s="44">
+      <c r="N296" s="55">
         <v>31455</v>
       </c>
       <c r="O296" s="43">
@@ -25514,7 +25526,7 @@
       <c r="M297" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N297" s="44">
+      <c r="N297" s="55">
         <v>30207</v>
       </c>
       <c r="O297" s="43">
@@ -25580,7 +25592,7 @@
       <c r="M298" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N298" s="44">
+      <c r="N298" s="55">
         <v>32222</v>
       </c>
       <c r="O298" s="43">
@@ -25646,7 +25658,7 @@
       <c r="M299" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N299" s="44">
+      <c r="N299" s="55">
         <v>31854</v>
       </c>
       <c r="O299" s="43">
@@ -25712,7 +25724,7 @@
       <c r="M300" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N300" s="44">
+      <c r="N300" s="55">
         <v>32710</v>
       </c>
       <c r="O300" s="43">
@@ -25778,7 +25790,7 @@
       <c r="M301" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N301" s="44">
+      <c r="N301" s="55">
         <v>28096</v>
       </c>
       <c r="O301" s="43">
@@ -25844,7 +25856,7 @@
       <c r="M302" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N302" s="44">
+      <c r="N302" s="55">
         <v>33012</v>
       </c>
       <c r="O302" s="43">
@@ -25910,7 +25922,7 @@
       <c r="M303" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N303" s="44">
+      <c r="N303" s="55">
         <v>30046</v>
       </c>
       <c r="O303" s="43">
@@ -25976,7 +25988,7 @@
       <c r="M304" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N304" s="44">
+      <c r="N304" s="55">
         <v>31845</v>
       </c>
       <c r="O304" s="43">
@@ -26042,7 +26054,7 @@
       <c r="M305" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N305" s="44">
+      <c r="N305" s="55">
         <v>33758</v>
       </c>
       <c r="O305" s="43">
@@ -26108,7 +26120,7 @@
       <c r="M306" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N306" s="44">
+      <c r="N306" s="55">
         <v>32589</v>
       </c>
       <c r="O306" s="43">
@@ -26174,7 +26186,7 @@
       <c r="M307" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N307" s="44">
+      <c r="N307" s="55">
         <v>32267</v>
       </c>
       <c r="O307" s="43">
@@ -26240,7 +26252,7 @@
       <c r="M308" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N308" s="44">
+      <c r="N308" s="55">
         <v>32321</v>
       </c>
       <c r="O308" s="43">
@@ -26306,7 +26318,7 @@
       <c r="M309" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N309" s="44">
+      <c r="N309" s="55">
         <v>27484</v>
       </c>
       <c r="O309" s="43">
@@ -26372,7 +26384,7 @@
       <c r="M310" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N310" s="44">
+      <c r="N310" s="55">
         <v>32087</v>
       </c>
       <c r="O310" s="43">
@@ -26438,7 +26450,7 @@
       <c r="M311" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N311" s="44">
+      <c r="N311" s="55">
         <v>30603</v>
       </c>
       <c r="O311" s="43">
@@ -26504,7 +26516,7 @@
       <c r="M312" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N312" s="44">
+      <c r="N312" s="55">
         <v>28997</v>
       </c>
       <c r="O312" s="43">
@@ -26570,7 +26582,7 @@
       <c r="M313" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N313" s="44">
+      <c r="N313" s="55">
         <v>33479</v>
       </c>
       <c r="O313" s="43">
@@ -26636,7 +26648,7 @@
       <c r="M314" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N314" s="44">
+      <c r="N314" s="55">
         <v>33486</v>
       </c>
       <c r="O314" s="43">
@@ -26702,7 +26714,7 @@
       <c r="M315" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N315" s="44">
+      <c r="N315" s="55">
         <v>33129</v>
       </c>
       <c r="O315" s="43">
@@ -26768,7 +26780,7 @@
       <c r="M316" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N316" s="44">
+      <c r="N316" s="55">
         <v>33854</v>
       </c>
       <c r="O316" s="43">
@@ -26834,7 +26846,7 @@
       <c r="M317" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N317" s="44">
+      <c r="N317" s="55">
         <v>33571</v>
       </c>
       <c r="O317" s="43">
@@ -26900,7 +26912,7 @@
       <c r="M318" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="N318" s="44">
+      <c r="N318" s="55">
         <v>29762</v>
       </c>
       <c r="O318" s="43">
@@ -26966,7 +26978,7 @@
       <c r="M319" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="N319" s="44">
+      <c r="N319" s="55">
         <v>29258</v>
       </c>
       <c r="O319" s="43">
@@ -27032,7 +27044,7 @@
       <c r="M320" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N320" s="44">
+      <c r="N320" s="55">
         <v>31379</v>
       </c>
       <c r="O320" s="43">
@@ -27098,7 +27110,7 @@
       <c r="M321" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N321" s="44">
+      <c r="N321" s="55">
         <v>30688</v>
       </c>
       <c r="O321" s="43">
@@ -27164,7 +27176,7 @@
       <c r="M322" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N322" s="44">
+      <c r="N322" s="55">
         <v>32203</v>
       </c>
       <c r="O322" s="43">
@@ -27230,7 +27242,7 @@
       <c r="M323" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N323" s="44">
+      <c r="N323" s="55">
         <v>34741</v>
       </c>
       <c r="O323" s="43">
@@ -27296,7 +27308,7 @@
       <c r="M324" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N324" s="44">
+      <c r="N324" s="55">
         <v>33610</v>
       </c>
       <c r="O324" s="43">
@@ -27362,7 +27374,7 @@
       <c r="M325" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N325" s="44">
+      <c r="N325" s="55">
         <v>34739</v>
       </c>
       <c r="O325" s="43">
@@ -27428,7 +27440,7 @@
       <c r="M326" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N326" s="44">
+      <c r="N326" s="55">
         <v>32817</v>
       </c>
       <c r="O326" s="43">
@@ -27494,7 +27506,7 @@
       <c r="M327" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N327" s="44">
+      <c r="N327" s="55">
         <v>33812</v>
       </c>
       <c r="O327" s="43">
@@ -27560,7 +27572,7 @@
       <c r="M328" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N328" s="44">
+      <c r="N328" s="55">
         <v>33701</v>
       </c>
       <c r="O328" s="43">
@@ -27626,7 +27638,7 @@
       <c r="M329" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N329" s="44">
+      <c r="N329" s="55">
         <v>33251</v>
       </c>
       <c r="O329" s="43">
@@ -27692,7 +27704,7 @@
       <c r="M330" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N330" s="44">
+      <c r="N330" s="55">
         <v>33896</v>
       </c>
       <c r="O330" s="43">
@@ -27758,7 +27770,7 @@
       <c r="M331" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N331" s="44">
+      <c r="N331" s="55">
         <v>34307</v>
       </c>
       <c r="O331" s="43">
@@ -27824,7 +27836,7 @@
       <c r="M332" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N332" s="44">
+      <c r="N332" s="55">
         <v>34270</v>
       </c>
       <c r="O332" s="43">
@@ -27890,7 +27902,7 @@
       <c r="M333" s="42" t="s">
         <v>855</v>
       </c>
-      <c r="N333" s="44">
+      <c r="N333" s="55">
         <v>29301</v>
       </c>
       <c r="O333" s="43">
@@ -27956,7 +27968,7 @@
       <c r="M334" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N334" s="44">
+      <c r="N334" s="55">
         <v>34269</v>
       </c>
       <c r="O334" s="43">
@@ -28022,7 +28034,7 @@
       <c r="M335" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N335" s="44">
+      <c r="N335" s="55">
         <v>33229</v>
       </c>
       <c r="O335" s="43">
@@ -28088,7 +28100,7 @@
       <c r="M336" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N336" s="44">
+      <c r="N336" s="55">
         <v>32436</v>
       </c>
       <c r="O336" s="43">
@@ -28154,7 +28166,7 @@
       <c r="M337" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N337" s="44">
+      <c r="N337" s="55">
         <v>32289</v>
       </c>
       <c r="O337" s="43">
@@ -28220,7 +28232,7 @@
       <c r="M338" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N338" s="44">
+      <c r="N338" s="55">
         <v>33780</v>
       </c>
       <c r="O338" s="43">
@@ -28286,7 +28298,7 @@
       <c r="M339" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N339" s="44">
+      <c r="N339" s="55">
         <v>32880</v>
       </c>
       <c r="O339" s="43">
@@ -28352,7 +28364,7 @@
       <c r="M340" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N340" s="44">
+      <c r="N340" s="55">
         <v>33809</v>
       </c>
       <c r="O340" s="43">
@@ -28418,7 +28430,7 @@
       <c r="M341" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N341" s="44">
+      <c r="N341" s="55">
         <v>35512</v>
       </c>
       <c r="O341" s="43">
@@ -28484,7 +28496,7 @@
       <c r="M342" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N342" s="44">
+      <c r="N342" s="55">
         <v>32660</v>
       </c>
       <c r="O342" s="43">
@@ -28550,7 +28562,7 @@
       <c r="M343" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N343" s="44">
+      <c r="N343" s="55">
         <v>30817</v>
       </c>
       <c r="O343" s="43">
@@ -28616,7 +28628,7 @@
       <c r="M344" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N344" s="44">
+      <c r="N344" s="55">
         <v>31941</v>
       </c>
       <c r="O344" s="43">
@@ -28682,7 +28694,7 @@
       <c r="M345" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N345" s="44">
+      <c r="N345" s="55">
         <v>32658</v>
       </c>
       <c r="O345" s="43">
@@ -28748,7 +28760,7 @@
       <c r="M346" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N346" s="44">
+      <c r="N346" s="55">
         <v>34968</v>
       </c>
       <c r="O346" s="43">
@@ -28814,7 +28826,7 @@
       <c r="M347" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N347" s="44">
+      <c r="N347" s="55">
         <v>32002</v>
       </c>
       <c r="O347" s="43">
@@ -28880,7 +28892,7 @@
       <c r="M348" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N348" s="44">
+      <c r="N348" s="55">
         <v>33888</v>
       </c>
       <c r="O348" s="43">
@@ -28946,7 +28958,7 @@
       <c r="M349" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N349" s="44">
+      <c r="N349" s="55">
         <v>26760</v>
       </c>
       <c r="O349" s="43">
@@ -29012,7 +29024,7 @@
       <c r="M350" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N350" s="44">
+      <c r="N350" s="55">
         <v>29570</v>
       </c>
       <c r="O350" s="43">
@@ -29078,7 +29090,7 @@
       <c r="M351" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N351" s="44">
+      <c r="N351" s="55">
         <v>30159</v>
       </c>
       <c r="O351" s="43">
@@ -29144,7 +29156,7 @@
       <c r="M352" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N352" s="44">
+      <c r="N352" s="55">
         <v>34797</v>
       </c>
       <c r="O352" s="43">
@@ -29210,7 +29222,7 @@
       <c r="M353" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N353" s="44">
+      <c r="N353" s="55">
         <v>33578</v>
       </c>
       <c r="O353" s="43">
@@ -29276,7 +29288,7 @@
       <c r="M354" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N354" s="44">
+      <c r="N354" s="55">
         <v>34276</v>
       </c>
       <c r="O354" s="43">
@@ -29342,7 +29354,7 @@
       <c r="M355" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N355" s="44">
+      <c r="N355" s="55">
         <v>34472</v>
       </c>
       <c r="O355" s="43">
@@ -29408,7 +29420,7 @@
       <c r="M356" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N356" s="44">
+      <c r="N356" s="55">
         <v>35132</v>
       </c>
       <c r="O356" s="43">
@@ -29474,7 +29486,7 @@
       <c r="M357" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N357" s="44">
+      <c r="N357" s="55">
         <v>32493</v>
       </c>
       <c r="O357" s="43">
@@ -29540,7 +29552,7 @@
       <c r="M358" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N358" s="44">
+      <c r="N358" s="55">
         <v>34324</v>
       </c>
       <c r="O358" s="43">
@@ -29606,7 +29618,7 @@
       <c r="M359" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N359" s="44">
+      <c r="N359" s="55">
         <v>28780</v>
       </c>
       <c r="O359" s="43">
@@ -29672,7 +29684,7 @@
       <c r="M360" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N360" s="44">
+      <c r="N360" s="55">
         <v>34388</v>
       </c>
       <c r="O360" s="43">
@@ -29738,7 +29750,7 @@
       <c r="M361" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N361" s="44">
+      <c r="N361" s="55">
         <v>31289</v>
       </c>
       <c r="O361" s="43">
@@ -29804,7 +29816,7 @@
       <c r="M362" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N362" s="44">
+      <c r="N362" s="55">
         <v>31331</v>
       </c>
       <c r="O362" s="43">
@@ -29870,7 +29882,7 @@
       <c r="M363" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N363" s="44">
+      <c r="N363" s="55">
         <v>34607</v>
       </c>
       <c r="O363" s="43">
@@ -29936,7 +29948,7 @@
       <c r="M364" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N364" s="44">
+      <c r="N364" s="55">
         <v>34934</v>
       </c>
       <c r="O364" s="43">
@@ -30002,7 +30014,7 @@
       <c r="M365" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N365" s="44">
+      <c r="N365" s="55">
         <v>31926</v>
       </c>
       <c r="O365" s="43">
@@ -30068,7 +30080,7 @@
       <c r="M366" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N366" s="44">
+      <c r="N366" s="55">
         <v>32253</v>
       </c>
       <c r="O366" s="43">
@@ -30134,7 +30146,7 @@
       <c r="M367" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N367" s="44">
+      <c r="N367" s="55">
         <v>32074</v>
       </c>
       <c r="O367" s="43">
@@ -30200,7 +30212,7 @@
       <c r="M368" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N368" s="44">
+      <c r="N368" s="55">
         <v>30076</v>
       </c>
       <c r="O368" s="43">
@@ -30266,7 +30278,7 @@
       <c r="M369" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N369" s="44">
+      <c r="N369" s="55">
         <v>32409</v>
       </c>
       <c r="O369" s="43">
@@ -30332,7 +30344,7 @@
       <c r="M370" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N370" s="44">
+      <c r="N370" s="55">
         <v>35784</v>
       </c>
       <c r="O370" s="43">
@@ -30398,7 +30410,7 @@
       <c r="M371" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N371" s="44">
+      <c r="N371" s="55">
         <v>33190</v>
       </c>
       <c r="O371" s="43">
@@ -30464,7 +30476,7 @@
       <c r="M372" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N372" s="44">
+      <c r="N372" s="55">
         <v>32609</v>
       </c>
       <c r="O372" s="43">
@@ -30530,7 +30542,7 @@
       <c r="M373" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N373" s="44">
+      <c r="N373" s="55">
         <v>27199</v>
       </c>
       <c r="O373" s="43">
@@ -30596,7 +30608,7 @@
       <c r="M374" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N374" s="44">
+      <c r="N374" s="55">
         <v>27808</v>
       </c>
       <c r="O374" s="43">
@@ -30662,7 +30674,7 @@
       <c r="M375" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N375" s="44">
+      <c r="N375" s="55">
         <v>27925</v>
       </c>
       <c r="O375" s="43">
@@ -30728,7 +30740,7 @@
       <c r="M376" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N376" s="44">
+      <c r="N376" s="55">
         <v>33612</v>
       </c>
       <c r="O376" s="43">
@@ -30794,7 +30806,7 @@
       <c r="M377" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N377" s="44">
+      <c r="N377" s="55">
         <v>35096</v>
       </c>
       <c r="O377" s="43">
@@ -30860,7 +30872,7 @@
       <c r="M378" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N378" s="44">
+      <c r="N378" s="55">
         <v>34117</v>
       </c>
       <c r="O378" s="43">
@@ -30926,7 +30938,7 @@
       <c r="M379" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N379" s="44">
+      <c r="N379" s="55">
         <v>34702</v>
       </c>
       <c r="O379" s="43">
@@ -30992,7 +31004,7 @@
       <c r="M380" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N380" s="44">
+      <c r="N380" s="55">
         <v>34709</v>
       </c>
       <c r="O380" s="43">
@@ -31058,7 +31070,7 @@
       <c r="M381" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N381" s="44">
+      <c r="N381" s="55">
         <v>30386</v>
       </c>
       <c r="O381" s="43">
@@ -31124,7 +31136,7 @@
       <c r="M382" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N382" s="44">
+      <c r="N382" s="55">
         <v>30209</v>
       </c>
       <c r="O382" s="43">
@@ -31190,7 +31202,7 @@
       <c r="M383" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N383" s="44">
+      <c r="N383" s="55">
         <v>31988</v>
       </c>
       <c r="O383" s="43">
@@ -31256,7 +31268,7 @@
       <c r="M384" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N384" s="44">
+      <c r="N384" s="55">
         <v>35937</v>
       </c>
       <c r="O384" s="43">
@@ -31322,7 +31334,7 @@
       <c r="M385" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N385" s="44">
+      <c r="N385" s="55">
         <v>34544</v>
       </c>
       <c r="O385" s="43">
@@ -31388,7 +31400,7 @@
       <c r="M386" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N386" s="44">
+      <c r="N386" s="55">
         <v>33705</v>
       </c>
       <c r="O386" s="43">
@@ -31454,7 +31466,7 @@
       <c r="M387" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N387" s="44">
+      <c r="N387" s="55">
         <v>29578</v>
       </c>
       <c r="O387" s="43">
@@ -31520,7 +31532,7 @@
       <c r="M388" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N388" s="44">
+      <c r="N388" s="55">
         <v>34194</v>
       </c>
       <c r="O388" s="43">
@@ -31586,7 +31598,7 @@
       <c r="M389" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N389" s="44">
+      <c r="N389" s="55">
         <v>33806</v>
       </c>
       <c r="O389" s="43">
@@ -31652,7 +31664,7 @@
       <c r="M390" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N390" s="44">
+      <c r="N390" s="55">
         <v>34239</v>
       </c>
       <c r="O390" s="43">
@@ -31718,7 +31730,7 @@
       <c r="M391" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N391" s="44">
+      <c r="N391" s="55">
         <v>29987</v>
       </c>
       <c r="O391" s="43">
@@ -31784,7 +31796,7 @@
       <c r="M392" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N392" s="44">
+      <c r="N392" s="55">
         <v>29803</v>
       </c>
       <c r="O392" s="43">
@@ -31850,7 +31862,7 @@
       <c r="M393" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="N393" s="44">
+      <c r="N393" s="55">
         <v>32736</v>
       </c>
       <c r="O393" s="43">
@@ -31916,7 +31928,7 @@
       <c r="M394" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N394" s="44">
+      <c r="N394" s="55">
         <v>33425</v>
       </c>
       <c r="O394" s="43">
@@ -31982,7 +31994,7 @@
       <c r="M395" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N395" s="44">
+      <c r="N395" s="55">
         <v>32240</v>
       </c>
       <c r="O395" s="43">
@@ -32048,7 +32060,7 @@
       <c r="M396" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N396" s="44">
+      <c r="N396" s="55">
         <v>36640</v>
       </c>
       <c r="O396" s="43">
@@ -32114,7 +32126,7 @@
       <c r="M397" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N397" s="44">
+      <c r="N397" s="55">
         <v>34434</v>
       </c>
       <c r="O397" s="43">
@@ -32180,7 +32192,7 @@
       <c r="M398" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N398" s="44">
+      <c r="N398" s="55">
         <v>32696</v>
       </c>
       <c r="O398" s="43">
@@ -32246,7 +32258,7 @@
       <c r="M399" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N399" s="44">
+      <c r="N399" s="55">
         <v>33866</v>
       </c>
       <c r="O399" s="43">
@@ -32312,7 +32324,7 @@
       <c r="M400" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N400" s="44">
+      <c r="N400" s="55">
         <v>35055</v>
       </c>
       <c r="O400" s="43">
@@ -32378,7 +32390,7 @@
       <c r="M401" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="N401" s="44">
+      <c r="N401" s="55">
         <v>28073</v>
       </c>
       <c r="O401" s="43">
@@ -32444,7 +32456,7 @@
       <c r="M402" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N402" s="44">
+      <c r="N402" s="55">
         <v>33862</v>
       </c>
       <c r="O402" s="43">
@@ -32510,7 +32522,7 @@
       <c r="M403" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N403" s="44">
+      <c r="N403" s="55">
         <v>30238</v>
       </c>
       <c r="O403" s="43">
@@ -32576,7 +32588,7 @@
       <c r="M404" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N404" s="44">
+      <c r="N404" s="55">
         <v>29813</v>
       </c>
       <c r="O404" s="43">
@@ -32642,7 +32654,7 @@
       <c r="M405" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N405" s="44">
+      <c r="N405" s="55">
         <v>26994</v>
       </c>
       <c r="O405" s="43">
@@ -32708,7 +32720,7 @@
       <c r="M406" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N406" s="44">
+      <c r="N406" s="55">
         <v>34771</v>
       </c>
       <c r="O406" s="43">
@@ -32774,7 +32786,7 @@
       <c r="M407" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N407" s="44">
+      <c r="N407" s="55">
         <v>34336</v>
       </c>
       <c r="O407" s="43">
@@ -32840,7 +32852,7 @@
       <c r="M408" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N408" s="44">
+      <c r="N408" s="55">
         <v>35865</v>
       </c>
       <c r="O408" s="43">
@@ -32906,7 +32918,7 @@
       <c r="M409" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N409" s="44">
+      <c r="N409" s="55">
         <v>33143</v>
       </c>
       <c r="O409" s="43">
@@ -32972,7 +32984,7 @@
       <c r="M410" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N410" s="44">
+      <c r="N410" s="55">
         <v>31973</v>
       </c>
       <c r="O410" s="43">
@@ -33038,7 +33050,7 @@
       <c r="M411" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N411" s="44">
+      <c r="N411" s="55">
         <v>27704</v>
       </c>
       <c r="O411" s="43">
@@ -33104,7 +33116,7 @@
       <c r="M412" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N412" s="44">
+      <c r="N412" s="55">
         <v>28549</v>
       </c>
       <c r="O412" s="43">
@@ -33170,7 +33182,7 @@
       <c r="M413" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N413" s="44">
+      <c r="N413" s="55">
         <v>32815</v>
       </c>
       <c r="O413" s="43">
@@ -33236,7 +33248,7 @@
       <c r="M414" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N414" s="44">
+      <c r="N414" s="55">
         <v>30411</v>
       </c>
       <c r="O414" s="43">
@@ -33302,7 +33314,7 @@
       <c r="M415" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N415" s="44">
+      <c r="N415" s="55">
         <v>26997</v>
       </c>
       <c r="O415" s="43">
@@ -33368,7 +33380,7 @@
       <c r="M416" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N416" s="44">
+      <c r="N416" s="55">
         <v>32420</v>
       </c>
       <c r="O416" s="43">
@@ -33434,7 +33446,7 @@
       <c r="M417" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N417" s="44">
+      <c r="N417" s="55">
         <v>32856</v>
       </c>
       <c r="O417" s="43">
@@ -33500,7 +33512,7 @@
       <c r="M418" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N418" s="44">
+      <c r="N418" s="55">
         <v>36166</v>
       </c>
       <c r="O418" s="43">
@@ -33568,7 +33580,7 @@
       <c r="M419" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N419" s="44">
+      <c r="N419" s="55">
         <v>35781</v>
       </c>
       <c r="O419" s="43">
@@ -33634,7 +33646,7 @@
       <c r="M420" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N420" s="44">
+      <c r="N420" s="55">
         <v>28243</v>
       </c>
       <c r="O420" s="43">
@@ -33700,7 +33712,7 @@
       <c r="M421" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N421" s="44">
+      <c r="N421" s="55">
         <v>33560</v>
       </c>
       <c r="O421" s="43">
@@ -33766,7 +33778,7 @@
       <c r="M422" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N422" s="44">
+      <c r="N422" s="55">
         <v>36112</v>
       </c>
       <c r="O422" s="43">
@@ -33832,7 +33844,7 @@
       <c r="M423" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N423" s="44">
+      <c r="N423" s="55">
         <v>35178</v>
       </c>
       <c r="O423" s="43">
@@ -33898,7 +33910,7 @@
       <c r="M424" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N424" s="44">
+      <c r="N424" s="55">
         <v>35563</v>
       </c>
       <c r="O424" s="43">
@@ -33964,7 +33976,7 @@
       <c r="M425" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N425" s="44">
+      <c r="N425" s="55">
         <v>34085</v>
       </c>
       <c r="O425" s="43">
@@ -34030,7 +34042,7 @@
       <c r="M426" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N426" s="44">
+      <c r="N426" s="55">
         <v>34275</v>
       </c>
       <c r="O426" s="43">
@@ -34096,7 +34108,7 @@
       <c r="M427" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N427" s="44">
+      <c r="N427" s="55">
         <v>30256</v>
       </c>
       <c r="O427" s="43">
@@ -34162,7 +34174,7 @@
       <c r="M428" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N428" s="44">
+      <c r="N428" s="55">
         <v>28531</v>
       </c>
       <c r="O428" s="43">
@@ -34228,7 +34240,7 @@
       <c r="M429" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N429" s="44">
+      <c r="N429" s="55">
         <v>34307</v>
       </c>
       <c r="O429" s="43">
@@ -34294,7 +34306,7 @@
       <c r="M430" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="N430" s="44">
+      <c r="N430" s="55">
         <v>24782</v>
       </c>
       <c r="O430" s="43">
@@ -34360,7 +34372,7 @@
       <c r="M431" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N431" s="44">
+      <c r="N431" s="55">
         <v>35973</v>
       </c>
       <c r="O431" s="43">
@@ -34426,7 +34438,7 @@
       <c r="M432" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N432" s="44">
+      <c r="N432" s="55">
         <v>34323</v>
       </c>
       <c r="O432" s="43">
@@ -34494,7 +34506,7 @@
       <c r="M433" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N433" s="44">
+      <c r="N433" s="55">
         <v>37046</v>
       </c>
       <c r="O433" s="43">
@@ -34562,7 +34574,7 @@
       <c r="M434" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N434" s="44">
+      <c r="N434" s="55">
         <v>33361</v>
       </c>
       <c r="O434" s="43">
@@ -34630,7 +34642,7 @@
       <c r="M435" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N435" s="44">
+      <c r="N435" s="55">
         <v>35165</v>
       </c>
       <c r="O435" s="43">
@@ -34698,7 +34710,7 @@
       <c r="M436" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N436" s="44">
+      <c r="N436" s="55">
         <v>35308</v>
       </c>
       <c r="O436" s="43">
@@ -34766,7 +34778,7 @@
       <c r="M437" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N437" s="44">
+      <c r="N437" s="55">
         <v>34753</v>
       </c>
       <c r="O437" s="43">
@@ -34834,7 +34846,7 @@
       <c r="M438" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="N438" s="44">
+      <c r="N438" s="55">
         <v>34693</v>
       </c>
       <c r="O438" s="43">
@@ -34900,7 +34912,7 @@
       <c r="M439" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N439" s="44">
+      <c r="N439" s="55">
         <v>33097</v>
       </c>
       <c r="O439" s="43">
@@ -34966,7 +34978,7 @@
       <c r="M440" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N440" s="44">
+      <c r="N440" s="55">
         <v>33846</v>
       </c>
       <c r="O440" s="43">
@@ -35034,7 +35046,7 @@
       <c r="M441" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N441" s="44">
+      <c r="N441" s="55">
         <v>38113</v>
       </c>
       <c r="O441" s="43">
@@ -35102,7 +35114,7 @@
       <c r="M442" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N442" s="44">
+      <c r="N442" s="55">
         <v>36384</v>
       </c>
       <c r="O442" s="43">
@@ -35170,7 +35182,7 @@
       <c r="M443" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N443" s="44">
+      <c r="N443" s="55">
         <v>35738</v>
       </c>
       <c r="O443" s="43">
@@ -35238,7 +35250,7 @@
       <c r="M444" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N444" s="44">
+      <c r="N444" s="55">
         <v>29218</v>
       </c>
       <c r="O444" s="43">
@@ -35304,7 +35316,7 @@
       <c r="M445" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N445" s="44">
+      <c r="N445" s="55">
         <v>36692</v>
       </c>
       <c r="O445" s="43">
@@ -35372,7 +35384,7 @@
       <c r="M446" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N446" s="44">
+      <c r="N446" s="55">
         <v>37199</v>
       </c>
       <c r="O446" s="43">
@@ -35440,7 +35452,7 @@
       <c r="M447" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N447" s="44">
+      <c r="N447" s="55">
         <v>33432</v>
       </c>
       <c r="O447" s="43">
@@ -35508,7 +35520,7 @@
       <c r="M448" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N448" s="44">
+      <c r="N448" s="55">
         <v>31140</v>
       </c>
       <c r="O448" s="43">
@@ -35576,7 +35588,7 @@
       <c r="M449" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="N449" s="44">
+      <c r="N449" s="55">
         <v>33332</v>
       </c>
       <c r="O449" s="43">
@@ -35640,7 +35652,7 @@
       <c r="M450" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="N450" s="50">
+      <c r="N450" s="56">
         <v>30867</v>
       </c>
       <c r="O450" s="49">

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baray020\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B5AA6B-C3FA-4E3D-8741-81EF6F8689A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67735F2-6BA3-46CF-859D-C0391AA3B357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1890" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dotaci" sheetId="1" r:id="rId1"/>
@@ -5172,7 +5172,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mmm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="[$-340A]d&quot; de &quot;mmmm&quot; de &quot;yyyy;@"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -5581,13 +5581,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -5941,7 +5941,8 @@
     <col min="11" max="11" width="36.81640625" customWidth="1"/>
     <col min="12" max="12" width="41" customWidth="1"/>
     <col min="13" max="13" width="38" customWidth="1"/>
-    <col min="14" max="18" width="13.36328125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="22.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="13.36328125" style="2" customWidth="1"/>
     <col min="19" max="19" width="19" style="2" customWidth="1"/>
     <col min="20" max="20" width="13.36328125" style="2" customWidth="1"/>
     <col min="21" max="21" width="39.1796875" customWidth="1"/>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baray020\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67735F2-6BA3-46CF-859D-C0391AA3B357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE15B326-1E07-4907-B76F-7DDFEF8CDEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1890" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5172,7 +5172,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="[$-340A]d&quot; de &quot;mmmm&quot; de &quot;yyyy;@"/>
+    <numFmt numFmtId="167" formatCode="dd/mmm/yyyy;@"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -5581,13 +5581,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -5941,7 +5941,7 @@
     <col min="11" max="11" width="36.81640625" customWidth="1"/>
     <col min="12" max="12" width="41" customWidth="1"/>
     <col min="13" max="13" width="38" customWidth="1"/>
-    <col min="14" max="14" width="22.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="18" width="13.36328125" style="2" customWidth="1"/>
     <col min="19" max="19" width="19" style="2" customWidth="1"/>
     <col min="20" max="20" width="13.36328125" style="2" customWidth="1"/>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baray020\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE15B326-1E07-4907-B76F-7DDFEF8CDEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D52DA4-09D1-4AB9-9C5A-1DB00D848DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1890" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1890" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dotaci" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8425" uniqueCount="1708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8425" uniqueCount="1707">
   <si>
     <t>HENRIQUEZ POOL FELIPE ALBERTO</t>
   </si>
@@ -5069,9 +5069,6 @@
   </si>
   <si>
     <t>Concepción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CirugíaVascular Periférica </t>
   </si>
   <si>
     <t>CARVAJAL DIAZ ORIANA DEL CARME</t>
@@ -6064,7 +6061,7 @@
         <v>57</v>
       </c>
       <c r="P2" s="40" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q2" s="39">
         <v>45789</v>
@@ -6130,7 +6127,7 @@
         <v>65</v>
       </c>
       <c r="P3" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q3" s="44">
         <v>33119</v>
@@ -6196,7 +6193,7 @@
         <v>65</v>
       </c>
       <c r="P4" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q4" s="44">
         <v>43235</v>
@@ -6262,7 +6259,7 @@
         <v>63</v>
       </c>
       <c r="P5" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q5" s="44">
         <v>34731</v>
@@ -6328,7 +6325,7 @@
         <v>56</v>
       </c>
       <c r="P6" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q6" s="44">
         <v>36923</v>
@@ -6394,7 +6391,7 @@
         <v>61</v>
       </c>
       <c r="P7" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q7" s="44">
         <v>31199</v>
@@ -6460,7 +6457,7 @@
         <v>58</v>
       </c>
       <c r="P8" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q8" s="44">
         <v>32629</v>
@@ -6526,7 +6523,7 @@
         <v>58</v>
       </c>
       <c r="P9" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q9" s="44">
         <v>37501</v>
@@ -6592,7 +6589,7 @@
         <v>59</v>
       </c>
       <c r="P10" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q10" s="44">
         <v>33091</v>
@@ -6658,7 +6655,7 @@
         <v>62</v>
       </c>
       <c r="P11" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q11" s="44">
         <v>32752</v>
@@ -6724,7 +6721,7 @@
         <v>61</v>
       </c>
       <c r="P12" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q12" s="44">
         <v>30817</v>
@@ -6790,7 +6787,7 @@
         <v>57</v>
       </c>
       <c r="P13" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q13" s="44">
         <v>33091</v>
@@ -6856,7 +6853,7 @@
         <v>59</v>
       </c>
       <c r="P14" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q14" s="44">
         <v>32157</v>
@@ -6922,7 +6919,7 @@
         <v>56</v>
       </c>
       <c r="P15" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q15" s="44">
         <v>38462</v>
@@ -6988,7 +6985,7 @@
         <v>57</v>
       </c>
       <c r="P16" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q16" s="44">
         <v>32782</v>
@@ -7054,7 +7051,7 @@
         <v>57</v>
       </c>
       <c r="P17" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q17" s="44">
         <v>33939</v>
@@ -7120,7 +7117,7 @@
         <v>60</v>
       </c>
       <c r="P18" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q18" s="44">
         <v>32660</v>
@@ -7186,7 +7183,7 @@
         <v>61</v>
       </c>
       <c r="P19" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q19" s="44">
         <v>32157</v>
@@ -7252,7 +7249,7 @@
         <v>57</v>
       </c>
       <c r="P20" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q20" s="44">
         <v>32629</v>
@@ -7318,7 +7315,7 @@
         <v>60</v>
       </c>
       <c r="P21" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q21" s="44">
         <v>38078</v>
@@ -7384,7 +7381,7 @@
         <v>59</v>
       </c>
       <c r="P22" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q22" s="44">
         <v>33263</v>
@@ -7450,7 +7447,7 @@
         <v>55</v>
       </c>
       <c r="P23" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q23" s="44">
         <v>33091</v>
@@ -7516,7 +7513,7 @@
         <v>57</v>
       </c>
       <c r="P24" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q24" s="44">
         <v>37015</v>
@@ -7582,7 +7579,7 @@
         <v>59</v>
       </c>
       <c r="P25" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q25" s="44">
         <v>33378</v>
@@ -7648,7 +7645,7 @@
         <v>57</v>
       </c>
       <c r="P26" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q26" s="44">
         <v>33179</v>
@@ -7714,7 +7711,7 @@
         <v>58</v>
       </c>
       <c r="P27" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q27" s="44">
         <v>37501</v>
@@ -7780,7 +7777,7 @@
         <v>58</v>
       </c>
       <c r="P28" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q28" s="44">
         <v>38322</v>
@@ -7846,7 +7843,7 @@
         <v>57</v>
       </c>
       <c r="P29" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q29" s="44">
         <v>33939</v>
@@ -7912,7 +7909,7 @@
         <v>56</v>
       </c>
       <c r="P30" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q30" s="44">
         <v>32752</v>
@@ -7978,7 +7975,7 @@
         <v>56</v>
       </c>
       <c r="P31" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q31" s="44">
         <v>37501</v>
@@ -8044,7 +8041,7 @@
         <v>57</v>
       </c>
       <c r="P32" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q32" s="44">
         <v>33165</v>
@@ -8110,7 +8107,7 @@
         <v>56</v>
       </c>
       <c r="P33" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q33" s="44">
         <v>33170</v>
@@ -8176,7 +8173,7 @@
         <v>55</v>
       </c>
       <c r="P34" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q34" s="44">
         <v>37501</v>
@@ -8242,7 +8239,7 @@
         <v>54</v>
       </c>
       <c r="P35" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q35" s="44">
         <v>37012</v>
@@ -8308,7 +8305,7 @@
         <v>55</v>
       </c>
       <c r="P36" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q36" s="44">
         <v>38462</v>
@@ -8374,7 +8371,7 @@
         <v>54</v>
       </c>
       <c r="P37" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q37" s="44">
         <v>38322</v>
@@ -8440,7 +8437,7 @@
         <v>53</v>
       </c>
       <c r="P38" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q38" s="44">
         <v>37501</v>
@@ -8506,7 +8503,7 @@
         <v>57</v>
       </c>
       <c r="P39" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q39" s="44">
         <v>33165</v>
@@ -8572,7 +8569,7 @@
         <v>56</v>
       </c>
       <c r="P40" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q40" s="44">
         <v>33210</v>
@@ -8638,7 +8635,7 @@
         <v>57</v>
       </c>
       <c r="P41" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q41" s="44">
         <v>32752</v>
@@ -8704,7 +8701,7 @@
         <v>57</v>
       </c>
       <c r="P42" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q42" s="44">
         <v>33101</v>
@@ -8770,7 +8767,7 @@
         <v>56</v>
       </c>
       <c r="P43" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q43" s="44">
         <v>37501</v>
@@ -8836,7 +8833,7 @@
         <v>53</v>
       </c>
       <c r="P44" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q44" s="44">
         <v>38034</v>
@@ -8902,7 +8899,7 @@
         <v>53</v>
       </c>
       <c r="P45" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q45" s="44">
         <v>37012</v>
@@ -8968,7 +8965,7 @@
         <v>54</v>
       </c>
       <c r="P46" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q46" s="44">
         <v>37012</v>
@@ -9034,7 +9031,7 @@
         <v>53</v>
       </c>
       <c r="P47" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q47" s="44">
         <v>37501</v>
@@ -9100,7 +9097,7 @@
         <v>53</v>
       </c>
       <c r="P48" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q48" s="44">
         <v>37501</v>
@@ -9166,7 +9163,7 @@
         <v>54</v>
       </c>
       <c r="P49" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q49" s="44">
         <v>37625</v>
@@ -9232,7 +9229,7 @@
         <v>53</v>
       </c>
       <c r="P50" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q50" s="44">
         <v>33504</v>
@@ -9298,7 +9295,7 @@
         <v>52</v>
       </c>
       <c r="P51" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q51" s="44">
         <v>37935</v>
@@ -9364,7 +9361,7 @@
         <v>53</v>
       </c>
       <c r="P52" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q52" s="44">
         <v>37501</v>
@@ -9430,7 +9427,7 @@
         <v>53</v>
       </c>
       <c r="P53" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q53" s="44">
         <v>37501</v>
@@ -9496,7 +9493,7 @@
         <v>53</v>
       </c>
       <c r="P54" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q54" s="44">
         <v>37012</v>
@@ -9562,7 +9559,7 @@
         <v>51</v>
       </c>
       <c r="P55" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q55" s="44">
         <v>38005</v>
@@ -9628,7 +9625,7 @@
         <v>52</v>
       </c>
       <c r="P56" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q56" s="44">
         <v>37012</v>
@@ -9694,7 +9691,7 @@
         <v>50</v>
       </c>
       <c r="P57" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q57" s="44">
         <v>37021</v>
@@ -9760,7 +9757,7 @@
         <v>50</v>
       </c>
       <c r="P58" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q58" s="44">
         <v>37501</v>
@@ -9826,7 +9823,7 @@
         <v>49</v>
       </c>
       <c r="P59" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q59" s="44">
         <v>37502</v>
@@ -9892,7 +9889,7 @@
         <v>47</v>
       </c>
       <c r="P60" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q60" s="44">
         <v>37501</v>
@@ -9958,7 +9955,7 @@
         <v>47</v>
       </c>
       <c r="P61" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q61" s="44">
         <v>38173</v>
@@ -10024,7 +10021,7 @@
         <v>48</v>
       </c>
       <c r="P62" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q62" s="44">
         <v>37561</v>
@@ -10090,7 +10087,7 @@
         <v>48</v>
       </c>
       <c r="P63" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q63" s="44">
         <v>37501</v>
@@ -10156,7 +10153,7 @@
         <v>46</v>
       </c>
       <c r="P64" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q64" s="44">
         <v>37935</v>
@@ -10222,7 +10219,7 @@
         <v>46</v>
       </c>
       <c r="P65" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q65" s="44">
         <v>38261</v>
@@ -10288,7 +10285,7 @@
         <v>46</v>
       </c>
       <c r="P66" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q66" s="44">
         <v>37622</v>
@@ -10354,7 +10351,7 @@
         <v>52</v>
       </c>
       <c r="P67" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q67" s="44">
         <v>37165</v>
@@ -10420,7 +10417,7 @@
         <v>57</v>
       </c>
       <c r="P68" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q68" s="44">
         <v>37501</v>
@@ -10486,7 +10483,7 @@
         <v>52</v>
       </c>
       <c r="P69" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q69" s="44">
         <v>37469</v>
@@ -10552,7 +10549,7 @@
         <v>53</v>
       </c>
       <c r="P70" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q70" s="44">
         <v>38462</v>
@@ -10618,7 +10615,7 @@
         <v>52</v>
       </c>
       <c r="P71" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q71" s="44">
         <v>38231</v>
@@ -10684,7 +10681,7 @@
         <v>51</v>
       </c>
       <c r="P72" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q72" s="44">
         <v>37973</v>
@@ -10750,7 +10747,7 @@
         <v>42</v>
       </c>
       <c r="P73" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q73" s="44">
         <v>38231</v>
@@ -10816,7 +10813,7 @@
         <v>42</v>
       </c>
       <c r="P74" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q74" s="44">
         <v>38322</v>
@@ -10882,7 +10879,7 @@
         <v>40</v>
       </c>
       <c r="P75" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q75" s="44">
         <v>38322</v>
@@ -10948,7 +10945,7 @@
         <v>57</v>
       </c>
       <c r="P76" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q76" s="44">
         <v>37622</v>
@@ -11014,7 +11011,7 @@
         <v>65</v>
       </c>
       <c r="P77" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q77" s="44">
         <v>33057</v>
@@ -11080,7 +11077,7 @@
         <v>61</v>
       </c>
       <c r="P78" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q78" s="44">
         <v>32752</v>
@@ -11146,7 +11143,7 @@
         <v>65</v>
       </c>
       <c r="P79" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q79" s="44">
         <v>32629</v>
@@ -11212,7 +11209,7 @@
         <v>63</v>
       </c>
       <c r="P80" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q80" s="44">
         <v>33939</v>
@@ -11278,7 +11275,7 @@
         <v>64</v>
       </c>
       <c r="P81" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q81" s="44">
         <v>30834</v>
@@ -11344,7 +11341,7 @@
         <v>65</v>
       </c>
       <c r="P82" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q82" s="44">
         <v>31731</v>
@@ -11410,7 +11407,7 @@
         <v>47</v>
       </c>
       <c r="P83" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q83" s="44">
         <v>38443</v>
@@ -11476,7 +11473,7 @@
         <v>64</v>
       </c>
       <c r="P84" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q84" s="44">
         <v>38462</v>
@@ -11542,7 +11539,7 @@
         <v>59</v>
       </c>
       <c r="P85" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q85" s="44">
         <v>38322</v>
@@ -11608,7 +11605,7 @@
         <v>59</v>
       </c>
       <c r="P86" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q86" s="44">
         <v>33064</v>
@@ -11674,7 +11671,7 @@
         <v>42</v>
       </c>
       <c r="P87" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q87" s="44">
         <v>40910</v>
@@ -11740,7 +11737,7 @@
         <v>50</v>
       </c>
       <c r="P88" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q88" s="44">
         <v>39114</v>
@@ -11806,7 +11803,7 @@
         <v>48</v>
       </c>
       <c r="P89" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q89" s="44">
         <v>38839</v>
@@ -11872,7 +11869,7 @@
         <v>55</v>
       </c>
       <c r="P90" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q90" s="44">
         <v>39734</v>
@@ -11938,7 +11935,7 @@
         <v>44</v>
       </c>
       <c r="P91" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q91" s="44">
         <v>39694</v>
@@ -12004,7 +12001,7 @@
         <v>54</v>
       </c>
       <c r="P92" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q92" s="44">
         <v>39098</v>
@@ -12070,7 +12067,7 @@
         <v>45</v>
       </c>
       <c r="P93" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q93" s="44">
         <v>39097</v>
@@ -12136,7 +12133,7 @@
         <v>44</v>
       </c>
       <c r="P94" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q94" s="44">
         <v>40301</v>
@@ -12202,7 +12199,7 @@
         <v>50</v>
       </c>
       <c r="P95" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q95" s="44">
         <v>39083</v>
@@ -12268,7 +12265,7 @@
         <v>37</v>
       </c>
       <c r="P96" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q96" s="44">
         <v>39234</v>
@@ -12334,7 +12331,7 @@
         <v>45</v>
       </c>
       <c r="P97" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q97" s="44">
         <v>39234</v>
@@ -12400,7 +12397,7 @@
         <v>50</v>
       </c>
       <c r="P98" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q98" s="44">
         <v>39234</v>
@@ -12466,7 +12463,7 @@
         <v>43</v>
       </c>
       <c r="P99" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q99" s="44">
         <v>39234</v>
@@ -12532,7 +12529,7 @@
         <v>41</v>
       </c>
       <c r="P100" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q100" s="44">
         <v>39234</v>
@@ -12598,7 +12595,7 @@
         <v>40</v>
       </c>
       <c r="P101" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q101" s="44">
         <v>39234</v>
@@ -12664,7 +12661,7 @@
         <v>40</v>
       </c>
       <c r="P102" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q102" s="44">
         <v>39234</v>
@@ -12730,7 +12727,7 @@
         <v>40</v>
       </c>
       <c r="P103" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q103" s="44">
         <v>39234</v>
@@ -12796,7 +12793,7 @@
         <v>52</v>
       </c>
       <c r="P104" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q104" s="44">
         <v>42064</v>
@@ -12862,7 +12859,7 @@
         <v>50</v>
       </c>
       <c r="P105" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q105" s="44">
         <v>39340</v>
@@ -12928,7 +12925,7 @@
         <v>51</v>
       </c>
       <c r="P106" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q106" s="44">
         <v>39340</v>
@@ -12994,7 +12991,7 @@
         <v>50</v>
       </c>
       <c r="P107" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q107" s="44">
         <v>39340</v>
@@ -13060,7 +13057,7 @@
         <v>49</v>
       </c>
       <c r="P108" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q108" s="44">
         <v>39340</v>
@@ -13126,7 +13123,7 @@
         <v>49</v>
       </c>
       <c r="P109" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q109" s="44">
         <v>39340</v>
@@ -13192,7 +13189,7 @@
         <v>54</v>
       </c>
       <c r="P110" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q110" s="44">
         <v>39340</v>
@@ -13258,7 +13255,7 @@
         <v>58</v>
       </c>
       <c r="P111" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q111" s="44">
         <v>39340</v>
@@ -13324,7 +13321,7 @@
         <v>51</v>
       </c>
       <c r="P112" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q112" s="44">
         <v>39340</v>
@@ -13390,7 +13387,7 @@
         <v>57</v>
       </c>
       <c r="P113" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q113" s="44">
         <v>39340</v>
@@ -13456,7 +13453,7 @@
         <v>54</v>
       </c>
       <c r="P114" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q114" s="44">
         <v>39340</v>
@@ -13522,7 +13519,7 @@
         <v>48</v>
       </c>
       <c r="P115" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q115" s="44">
         <v>39340</v>
@@ -13588,7 +13585,7 @@
         <v>53</v>
       </c>
       <c r="P116" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q116" s="44">
         <v>39340</v>
@@ -13654,7 +13651,7 @@
         <v>53</v>
       </c>
       <c r="P117" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q117" s="44">
         <v>39340</v>
@@ -13720,7 +13717,7 @@
         <v>49</v>
       </c>
       <c r="P118" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q118" s="44">
         <v>39340</v>
@@ -13786,7 +13783,7 @@
         <v>63</v>
       </c>
       <c r="P119" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q119" s="44">
         <v>39340</v>
@@ -13852,7 +13849,7 @@
         <v>50</v>
       </c>
       <c r="P120" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q120" s="44">
         <v>39340</v>
@@ -13918,7 +13915,7 @@
         <v>52</v>
       </c>
       <c r="P121" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q121" s="44">
         <v>39340</v>
@@ -13984,7 +13981,7 @@
         <v>53</v>
       </c>
       <c r="P122" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q122" s="44">
         <v>39340</v>
@@ -14050,7 +14047,7 @@
         <v>47</v>
       </c>
       <c r="P123" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q123" s="44">
         <v>39340</v>
@@ -14116,7 +14113,7 @@
         <v>59</v>
       </c>
       <c r="P124" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q124" s="44">
         <v>39340</v>
@@ -14182,7 +14179,7 @@
         <v>45</v>
       </c>
       <c r="P125" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q125" s="44">
         <v>39340</v>
@@ -14248,7 +14245,7 @@
         <v>57</v>
       </c>
       <c r="P126" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q126" s="44">
         <v>39340</v>
@@ -14314,7 +14311,7 @@
         <v>54</v>
       </c>
       <c r="P127" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q127" s="44">
         <v>39340</v>
@@ -14380,7 +14377,7 @@
         <v>60</v>
       </c>
       <c r="P128" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q128" s="44">
         <v>39340</v>
@@ -14446,7 +14443,7 @@
         <v>49</v>
       </c>
       <c r="P129" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q129" s="44">
         <v>39340</v>
@@ -14512,7 +14509,7 @@
         <v>56</v>
       </c>
       <c r="P130" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q130" s="44">
         <v>39340</v>
@@ -14578,7 +14575,7 @@
         <v>57</v>
       </c>
       <c r="P131" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q131" s="44">
         <v>39340</v>
@@ -14644,7 +14641,7 @@
         <v>53</v>
       </c>
       <c r="P132" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q132" s="44">
         <v>39356</v>
@@ -14710,7 +14707,7 @@
         <v>50</v>
       </c>
       <c r="P133" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q133" s="44">
         <v>39356</v>
@@ -14776,7 +14773,7 @@
         <v>53</v>
       </c>
       <c r="P134" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q134" s="44">
         <v>39356</v>
@@ -14842,7 +14839,7 @@
         <v>54</v>
       </c>
       <c r="P135" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q135" s="44">
         <v>39356</v>
@@ -14908,7 +14905,7 @@
         <v>54</v>
       </c>
       <c r="P136" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q136" s="44">
         <v>39356</v>
@@ -14974,7 +14971,7 @@
         <v>52</v>
       </c>
       <c r="P137" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q137" s="44">
         <v>40049</v>
@@ -15040,7 +15037,7 @@
         <v>53</v>
       </c>
       <c r="P138" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q138" s="44">
         <v>39356</v>
@@ -15106,7 +15103,7 @@
         <v>48</v>
       </c>
       <c r="P139" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q139" s="44">
         <v>39356</v>
@@ -15172,7 +15169,7 @@
         <v>49</v>
       </c>
       <c r="P140" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q140" s="44">
         <v>39356</v>
@@ -15238,7 +15235,7 @@
         <v>52</v>
       </c>
       <c r="P141" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q141" s="44">
         <v>39356</v>
@@ -15304,7 +15301,7 @@
         <v>51</v>
       </c>
       <c r="P142" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q142" s="44">
         <v>39356</v>
@@ -15370,7 +15367,7 @@
         <v>54</v>
       </c>
       <c r="P143" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q143" s="44">
         <v>39356</v>
@@ -15436,7 +15433,7 @@
         <v>49</v>
       </c>
       <c r="P144" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q144" s="44">
         <v>39356</v>
@@ -15502,7 +15499,7 @@
         <v>51</v>
       </c>
       <c r="P145" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q145" s="44">
         <v>39356</v>
@@ -15568,7 +15565,7 @@
         <v>51</v>
       </c>
       <c r="P146" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q146" s="44">
         <v>39630</v>
@@ -15634,7 +15631,7 @@
         <v>52</v>
       </c>
       <c r="P147" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q147" s="44">
         <v>39356</v>
@@ -15700,7 +15697,7 @@
         <v>55</v>
       </c>
       <c r="P148" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q148" s="44">
         <v>39356</v>
@@ -15766,7 +15763,7 @@
         <v>50</v>
       </c>
       <c r="P149" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q149" s="44">
         <v>39356</v>
@@ -15832,7 +15829,7 @@
         <v>39</v>
       </c>
       <c r="P150" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q150" s="44">
         <v>39356</v>
@@ -15898,7 +15895,7 @@
         <v>51</v>
       </c>
       <c r="P151" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q151" s="44">
         <v>39356</v>
@@ -15964,7 +15961,7 @@
         <v>50</v>
       </c>
       <c r="P152" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q152" s="44">
         <v>39356</v>
@@ -16030,7 +16027,7 @@
         <v>46</v>
       </c>
       <c r="P153" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q153" s="44">
         <v>39356</v>
@@ -16096,7 +16093,7 @@
         <v>54</v>
       </c>
       <c r="P154" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q154" s="44">
         <v>39356</v>
@@ -16162,7 +16159,7 @@
         <v>49</v>
       </c>
       <c r="P155" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q155" s="44">
         <v>39370</v>
@@ -16228,7 +16225,7 @@
         <v>45</v>
       </c>
       <c r="P156" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q156" s="44">
         <v>39370</v>
@@ -16294,7 +16291,7 @@
         <v>53</v>
       </c>
       <c r="P157" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q157" s="44">
         <v>39370</v>
@@ -16360,7 +16357,7 @@
         <v>43</v>
       </c>
       <c r="P158" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q158" s="44">
         <v>39370</v>
@@ -16426,7 +16423,7 @@
         <v>55</v>
       </c>
       <c r="P159" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q159" s="44">
         <v>39370</v>
@@ -16492,7 +16489,7 @@
         <v>53</v>
       </c>
       <c r="P160" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q160" s="44">
         <v>39370</v>
@@ -16558,7 +16555,7 @@
         <v>44</v>
       </c>
       <c r="P161" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q161" s="44">
         <v>39479</v>
@@ -16624,7 +16621,7 @@
         <v>44</v>
       </c>
       <c r="P162" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q162" s="44">
         <v>39479</v>
@@ -16690,7 +16687,7 @@
         <v>39</v>
       </c>
       <c r="P163" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q163" s="44">
         <v>39479</v>
@@ -16756,7 +16753,7 @@
         <v>48</v>
       </c>
       <c r="P164" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q164" s="44">
         <v>39479</v>
@@ -16822,7 +16819,7 @@
         <v>59</v>
       </c>
       <c r="P165" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q165" s="44">
         <v>39479</v>
@@ -16888,7 +16885,7 @@
         <v>54</v>
       </c>
       <c r="P166" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q166" s="44">
         <v>39479</v>
@@ -16954,7 +16951,7 @@
         <v>45</v>
       </c>
       <c r="P167" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q167" s="44">
         <v>39479</v>
@@ -17020,7 +17017,7 @@
         <v>40</v>
       </c>
       <c r="P168" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q168" s="44">
         <v>39479</v>
@@ -17086,7 +17083,7 @@
         <v>62</v>
       </c>
       <c r="P169" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q169" s="44">
         <v>39479</v>
@@ -17152,7 +17149,7 @@
         <v>39</v>
       </c>
       <c r="P170" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q170" s="44">
         <v>39479</v>
@@ -17218,7 +17215,7 @@
         <v>46</v>
       </c>
       <c r="P171" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q171" s="44">
         <v>39479</v>
@@ -17284,7 +17281,7 @@
         <v>52</v>
       </c>
       <c r="P172" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q172" s="44">
         <v>39479</v>
@@ -17350,7 +17347,7 @@
         <v>56</v>
       </c>
       <c r="P173" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q173" s="44">
         <v>39479</v>
@@ -17416,7 +17413,7 @@
         <v>52</v>
       </c>
       <c r="P174" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q174" s="44">
         <v>39479</v>
@@ -17482,7 +17479,7 @@
         <v>48</v>
       </c>
       <c r="P175" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q175" s="44">
         <v>39479</v>
@@ -17548,7 +17545,7 @@
         <v>43</v>
       </c>
       <c r="P176" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q176" s="44">
         <v>39479</v>
@@ -17614,7 +17611,7 @@
         <v>51</v>
       </c>
       <c r="P177" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q177" s="44">
         <v>39479</v>
@@ -17680,7 +17677,7 @@
         <v>43</v>
       </c>
       <c r="P178" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q178" s="44">
         <v>39479</v>
@@ -17746,7 +17743,7 @@
         <v>48</v>
       </c>
       <c r="P179" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q179" s="44">
         <v>39479</v>
@@ -17812,7 +17809,7 @@
         <v>47</v>
       </c>
       <c r="P180" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q180" s="44">
         <v>39479</v>
@@ -17878,7 +17875,7 @@
         <v>60</v>
       </c>
       <c r="P181" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q181" s="44">
         <v>39479</v>
@@ -17944,7 +17941,7 @@
         <v>50</v>
       </c>
       <c r="P182" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q182" s="44">
         <v>39479</v>
@@ -18010,7 +18007,7 @@
         <v>54</v>
       </c>
       <c r="P183" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q183" s="44">
         <v>39479</v>
@@ -18076,7 +18073,7 @@
         <v>51</v>
       </c>
       <c r="P184" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q184" s="44">
         <v>39479</v>
@@ -18142,7 +18139,7 @@
         <v>45</v>
       </c>
       <c r="P185" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q185" s="44">
         <v>39479</v>
@@ -18208,7 +18205,7 @@
         <v>50</v>
       </c>
       <c r="P186" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q186" s="44">
         <v>39479</v>
@@ -18274,7 +18271,7 @@
         <v>46</v>
       </c>
       <c r="P187" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q187" s="44">
         <v>39479</v>
@@ -18340,7 +18337,7 @@
         <v>49</v>
       </c>
       <c r="P188" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q188" s="44">
         <v>39479</v>
@@ -18406,7 +18403,7 @@
         <v>54</v>
       </c>
       <c r="P189" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q189" s="44">
         <v>39479</v>
@@ -18472,7 +18469,7 @@
         <v>42</v>
       </c>
       <c r="P190" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q190" s="44">
         <v>39479</v>
@@ -18538,7 +18535,7 @@
         <v>45</v>
       </c>
       <c r="P191" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q191" s="44">
         <v>39479</v>
@@ -18604,7 +18601,7 @@
         <v>49</v>
       </c>
       <c r="P192" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q192" s="44">
         <v>39496</v>
@@ -18670,7 +18667,7 @@
         <v>48</v>
       </c>
       <c r="P193" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q193" s="44">
         <v>39693</v>
@@ -18736,7 +18733,7 @@
         <v>46</v>
       </c>
       <c r="P194" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q194" s="44">
         <v>39693</v>
@@ -18802,7 +18799,7 @@
         <v>50</v>
       </c>
       <c r="P195" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q195" s="44">
         <v>39693</v>
@@ -18868,7 +18865,7 @@
         <v>40</v>
       </c>
       <c r="P196" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q196" s="44">
         <v>39693</v>
@@ -18934,7 +18931,7 @@
         <v>45</v>
       </c>
       <c r="P197" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q197" s="44">
         <v>39723</v>
@@ -19000,7 +18997,7 @@
         <v>53</v>
       </c>
       <c r="P198" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q198" s="44">
         <v>39517</v>
@@ -19066,7 +19063,7 @@
         <v>43</v>
       </c>
       <c r="P199" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q199" s="44">
         <v>45200</v>
@@ -19132,7 +19129,7 @@
         <v>56</v>
       </c>
       <c r="P200" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q200" s="44">
         <v>39557</v>
@@ -19198,7 +19195,7 @@
         <v>46</v>
       </c>
       <c r="P201" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q201" s="44">
         <v>39557</v>
@@ -19264,7 +19261,7 @@
         <v>48</v>
       </c>
       <c r="P202" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q202" s="44">
         <v>39583</v>
@@ -19330,7 +19327,7 @@
         <v>41</v>
       </c>
       <c r="P203" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q203" s="44">
         <v>39583</v>
@@ -19396,7 +19393,7 @@
         <v>41</v>
       </c>
       <c r="P204" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q204" s="44">
         <v>39583</v>
@@ -19462,7 +19459,7 @@
         <v>57</v>
       </c>
       <c r="P205" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q205" s="44">
         <v>39583</v>
@@ -19528,7 +19525,7 @@
         <v>43</v>
       </c>
       <c r="P206" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q206" s="44">
         <v>39583</v>
@@ -19594,7 +19591,7 @@
         <v>57</v>
       </c>
       <c r="P207" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q207" s="44">
         <v>39583</v>
@@ -19660,7 +19657,7 @@
         <v>57</v>
       </c>
       <c r="P208" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q208" s="44">
         <v>39583</v>
@@ -19726,7 +19723,7 @@
         <v>43</v>
       </c>
       <c r="P209" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q209" s="44">
         <v>39583</v>
@@ -19792,7 +19789,7 @@
         <v>43</v>
       </c>
       <c r="P210" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q210" s="44">
         <v>39583</v>
@@ -19858,7 +19855,7 @@
         <v>63</v>
       </c>
       <c r="P211" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q211" s="44">
         <v>39590</v>
@@ -19924,7 +19921,7 @@
         <v>48</v>
       </c>
       <c r="P212" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q212" s="44">
         <v>39590</v>
@@ -19990,7 +19987,7 @@
         <v>43</v>
       </c>
       <c r="P213" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q213" s="44">
         <v>39590</v>
@@ -20056,7 +20053,7 @@
         <v>44</v>
       </c>
       <c r="P214" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q214" s="44">
         <v>39590</v>
@@ -20122,7 +20119,7 @@
         <v>44</v>
       </c>
       <c r="P215" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q215" s="44">
         <v>39590</v>
@@ -20188,7 +20185,7 @@
         <v>50</v>
       </c>
       <c r="P216" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q216" s="44">
         <v>39590</v>
@@ -20254,7 +20251,7 @@
         <v>55</v>
       </c>
       <c r="P217" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q217" s="44">
         <v>39609</v>
@@ -20320,7 +20317,7 @@
         <v>52</v>
       </c>
       <c r="P218" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q218" s="44">
         <v>39615</v>
@@ -20386,7 +20383,7 @@
         <v>46</v>
       </c>
       <c r="P219" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q219" s="44">
         <v>39722</v>
@@ -20452,7 +20449,7 @@
         <v>45</v>
       </c>
       <c r="P220" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q220" s="44">
         <v>39630</v>
@@ -20518,7 +20515,7 @@
         <v>53</v>
       </c>
       <c r="P221" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q221" s="44">
         <v>39722</v>
@@ -20584,7 +20581,7 @@
         <v>40</v>
       </c>
       <c r="P222" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q222" s="44">
         <v>39734</v>
@@ -20650,7 +20647,7 @@
         <v>54</v>
       </c>
       <c r="P223" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q223" s="44">
         <v>39734</v>
@@ -20716,7 +20713,7 @@
         <v>38</v>
       </c>
       <c r="P224" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q224" s="44">
         <v>39734</v>
@@ -20782,7 +20779,7 @@
         <v>40</v>
       </c>
       <c r="P225" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q225" s="44">
         <v>39734</v>
@@ -20848,7 +20845,7 @@
         <v>56</v>
       </c>
       <c r="P226" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q226" s="44">
         <v>39734</v>
@@ -20914,7 +20911,7 @@
         <v>41</v>
       </c>
       <c r="P227" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q227" s="44">
         <v>39734</v>
@@ -20980,7 +20977,7 @@
         <v>53</v>
       </c>
       <c r="P228" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q228" s="44">
         <v>39734</v>
@@ -21046,7 +21043,7 @@
         <v>51</v>
       </c>
       <c r="P229" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q229" s="44">
         <v>39734</v>
@@ -21112,7 +21109,7 @@
         <v>47</v>
       </c>
       <c r="P230" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q230" s="44">
         <v>39734</v>
@@ -21178,7 +21175,7 @@
         <v>59</v>
       </c>
       <c r="P231" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q231" s="44">
         <v>39734</v>
@@ -21244,7 +21241,7 @@
         <v>59</v>
       </c>
       <c r="P232" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q232" s="44">
         <v>39734</v>
@@ -21310,7 +21307,7 @@
         <v>46</v>
       </c>
       <c r="P233" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q233" s="44">
         <v>39734</v>
@@ -21376,7 +21373,7 @@
         <v>40</v>
       </c>
       <c r="P234" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q234" s="44">
         <v>39734</v>
@@ -21442,7 +21439,7 @@
         <v>48</v>
       </c>
       <c r="P235" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q235" s="44">
         <v>39734</v>
@@ -21508,7 +21505,7 @@
         <v>48</v>
       </c>
       <c r="P236" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q236" s="44">
         <v>39734</v>
@@ -21574,7 +21571,7 @@
         <v>46</v>
       </c>
       <c r="P237" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q237" s="44">
         <v>39753</v>
@@ -21640,7 +21637,7 @@
         <v>57</v>
       </c>
       <c r="P238" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q238" s="44">
         <v>39753</v>
@@ -21706,7 +21703,7 @@
         <v>43</v>
       </c>
       <c r="P239" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q239" s="44">
         <v>39753</v>
@@ -21772,7 +21769,7 @@
         <v>58</v>
       </c>
       <c r="P240" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q240" s="44">
         <v>39762</v>
@@ -21838,7 +21835,7 @@
         <v>48</v>
       </c>
       <c r="P241" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q241" s="44">
         <v>39763</v>
@@ -21904,7 +21901,7 @@
         <v>46</v>
       </c>
       <c r="P242" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q242" s="44">
         <v>39783</v>
@@ -21970,7 +21967,7 @@
         <v>47</v>
       </c>
       <c r="P243" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q243" s="44">
         <v>39805</v>
@@ -22036,7 +22033,7 @@
         <v>43</v>
       </c>
       <c r="P244" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q244" s="44">
         <v>39821</v>
@@ -22102,7 +22099,7 @@
         <v>43</v>
       </c>
       <c r="P245" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q245" s="44">
         <v>39881</v>
@@ -22168,7 +22165,7 @@
         <v>52</v>
       </c>
       <c r="P246" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q246" s="44">
         <v>40009</v>
@@ -22234,7 +22231,7 @@
         <v>55</v>
       </c>
       <c r="P247" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q247" s="44">
         <v>40026</v>
@@ -22300,7 +22297,7 @@
         <v>47</v>
       </c>
       <c r="P248" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q248" s="44">
         <v>40049</v>
@@ -22366,7 +22363,7 @@
         <v>48</v>
       </c>
       <c r="P249" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q249" s="44">
         <v>40049</v>
@@ -22432,7 +22429,7 @@
         <v>42</v>
       </c>
       <c r="P250" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q250" s="44">
         <v>40049</v>
@@ -22498,7 +22495,7 @@
         <v>41</v>
       </c>
       <c r="P251" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q251" s="44">
         <v>40049</v>
@@ -22564,7 +22561,7 @@
         <v>53</v>
       </c>
       <c r="P252" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q252" s="44">
         <v>40049</v>
@@ -22630,7 +22627,7 @@
         <v>52</v>
       </c>
       <c r="P253" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q253" s="44">
         <v>40049</v>
@@ -22696,7 +22693,7 @@
         <v>52</v>
       </c>
       <c r="P254" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q254" s="44">
         <v>40049</v>
@@ -22762,7 +22759,7 @@
         <v>55</v>
       </c>
       <c r="P255" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q255" s="44">
         <v>40108</v>
@@ -22828,7 +22825,7 @@
         <v>40</v>
       </c>
       <c r="P256" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q256" s="44">
         <v>40192</v>
@@ -22894,7 +22891,7 @@
         <v>41</v>
       </c>
       <c r="P257" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q257" s="44">
         <v>40192</v>
@@ -22960,7 +22957,7 @@
         <v>55</v>
       </c>
       <c r="P258" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q258" s="44">
         <v>40192</v>
@@ -23026,7 +23023,7 @@
         <v>42</v>
       </c>
       <c r="P259" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q259" s="44">
         <v>40192</v>
@@ -23092,7 +23089,7 @@
         <v>43</v>
       </c>
       <c r="P260" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q260" s="44">
         <v>40192</v>
@@ -23158,7 +23155,7 @@
         <v>42</v>
       </c>
       <c r="P261" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q261" s="44">
         <v>40192</v>
@@ -23224,7 +23221,7 @@
         <v>48</v>
       </c>
       <c r="P262" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q262" s="44">
         <v>40192</v>
@@ -23290,7 +23287,7 @@
         <v>41</v>
       </c>
       <c r="P263" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q263" s="44">
         <v>40817</v>
@@ -23356,7 +23353,7 @@
         <v>41</v>
       </c>
       <c r="P264" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q264" s="44">
         <v>40210</v>
@@ -23422,7 +23419,7 @@
         <v>46</v>
       </c>
       <c r="P265" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q265" s="44">
         <v>40269</v>
@@ -23488,7 +23485,7 @@
         <v>35</v>
       </c>
       <c r="P266" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q266" s="44">
         <v>40269</v>
@@ -23554,7 +23551,7 @@
         <v>39</v>
       </c>
       <c r="P267" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q267" s="44">
         <v>40771</v>
@@ -23620,7 +23617,7 @@
         <v>43</v>
       </c>
       <c r="P268" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q268" s="44">
         <v>40583</v>
@@ -23686,7 +23683,7 @@
         <v>41</v>
       </c>
       <c r="P269" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q269" s="44">
         <v>43952</v>
@@ -23752,7 +23749,7 @@
         <v>43</v>
       </c>
       <c r="P270" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q270" s="44">
         <v>40764</v>
@@ -23818,7 +23815,7 @@
         <v>39</v>
       </c>
       <c r="P271" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q271" s="44">
         <v>40583</v>
@@ -23884,7 +23881,7 @@
         <v>39</v>
       </c>
       <c r="P272" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q272" s="44">
         <v>40583</v>
@@ -23950,7 +23947,7 @@
         <v>47</v>
       </c>
       <c r="P273" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q273" s="44">
         <v>40583</v>
@@ -24016,7 +24013,7 @@
         <v>38</v>
       </c>
       <c r="P274" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q274" s="44">
         <v>40583</v>
@@ -24082,7 +24079,7 @@
         <v>36</v>
       </c>
       <c r="P275" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q275" s="44">
         <v>40764</v>
@@ -24148,7 +24145,7 @@
         <v>40</v>
       </c>
       <c r="P276" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q276" s="44">
         <v>40583</v>
@@ -24214,7 +24211,7 @@
         <v>46</v>
       </c>
       <c r="P277" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q277" s="44">
         <v>40595</v>
@@ -24280,7 +24277,7 @@
         <v>44</v>
       </c>
       <c r="P278" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q278" s="44">
         <v>40595</v>
@@ -24346,7 +24343,7 @@
         <v>42</v>
       </c>
       <c r="P279" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q279" s="44">
         <v>40595</v>
@@ -24412,7 +24409,7 @@
         <v>48</v>
       </c>
       <c r="P280" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q280" s="44">
         <v>40595</v>
@@ -24478,7 +24475,7 @@
         <v>40</v>
       </c>
       <c r="P281" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q281" s="44">
         <v>40595</v>
@@ -24544,7 +24541,7 @@
         <v>40</v>
       </c>
       <c r="P282" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q282" s="44">
         <v>40776</v>
@@ -24610,7 +24607,7 @@
         <v>44</v>
       </c>
       <c r="P283" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q283" s="44">
         <v>40595</v>
@@ -24676,7 +24673,7 @@
         <v>39</v>
       </c>
       <c r="P284" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q284" s="44">
         <v>40595</v>
@@ -24742,7 +24739,7 @@
         <v>43</v>
       </c>
       <c r="P285" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q285" s="44">
         <v>40595</v>
@@ -24808,7 +24805,7 @@
         <v>35</v>
       </c>
       <c r="P286" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q286" s="44">
         <v>40595</v>
@@ -24874,7 +24871,7 @@
         <v>39</v>
       </c>
       <c r="P287" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q287" s="44">
         <v>40595</v>
@@ -24940,7 +24937,7 @@
         <v>36</v>
       </c>
       <c r="P288" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q288" s="44">
         <v>40595</v>
@@ -25006,7 +25003,7 @@
         <v>39</v>
       </c>
       <c r="P289" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q289" s="44">
         <v>40603</v>
@@ -25072,7 +25069,7 @@
         <v>40</v>
       </c>
       <c r="P290" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q290" s="44">
         <v>40603</v>
@@ -25138,7 +25135,7 @@
         <v>36</v>
       </c>
       <c r="P291" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q291" s="44">
         <v>40603</v>
@@ -25204,7 +25201,7 @@
         <v>41</v>
       </c>
       <c r="P292" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q292" s="44">
         <v>40603</v>
@@ -25270,7 +25267,7 @@
         <v>43</v>
       </c>
       <c r="P293" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q293" s="44">
         <v>40603</v>
@@ -25336,7 +25333,7 @@
         <v>43</v>
       </c>
       <c r="P294" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q294" s="44">
         <v>40603</v>
@@ -25402,7 +25399,7 @@
         <v>35</v>
       </c>
       <c r="P295" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q295" s="44">
         <v>40603</v>
@@ -25468,7 +25465,7 @@
         <v>40</v>
       </c>
       <c r="P296" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q296" s="44">
         <v>40603</v>
@@ -25534,7 +25531,7 @@
         <v>43</v>
       </c>
       <c r="P297" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q297" s="44">
         <v>40623</v>
@@ -25600,7 +25597,7 @@
         <v>38</v>
       </c>
       <c r="P298" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q298" s="44">
         <v>40634</v>
@@ -25666,7 +25663,7 @@
         <v>39</v>
       </c>
       <c r="P299" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q299" s="44">
         <v>40634</v>
@@ -25732,7 +25729,7 @@
         <v>37</v>
       </c>
       <c r="P300" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q300" s="44">
         <v>40634</v>
@@ -25798,7 +25795,7 @@
         <v>49</v>
       </c>
       <c r="P301" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q301" s="44">
         <v>40634</v>
@@ -25864,7 +25861,7 @@
         <v>36</v>
       </c>
       <c r="P302" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q302" s="44">
         <v>40634</v>
@@ -25930,7 +25927,7 @@
         <v>44</v>
       </c>
       <c r="P303" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q303" s="44">
         <v>40725</v>
@@ -25996,7 +25993,7 @@
         <v>39</v>
       </c>
       <c r="P304" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q304" s="44">
         <v>40737</v>
@@ -26062,7 +26059,7 @@
         <v>34</v>
       </c>
       <c r="P305" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q305" s="44">
         <v>40737</v>
@@ -26128,7 +26125,7 @@
         <v>37</v>
       </c>
       <c r="P306" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q306" s="44">
         <v>40737</v>
@@ -26194,7 +26191,7 @@
         <v>38</v>
       </c>
       <c r="P307" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q307" s="44">
         <v>40737</v>
@@ -26260,7 +26257,7 @@
         <v>38</v>
       </c>
       <c r="P308" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q308" s="44">
         <v>40737</v>
@@ -26326,7 +26323,7 @@
         <v>51</v>
       </c>
       <c r="P309" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q309" s="44">
         <v>41671</v>
@@ -26392,7 +26389,7 @@
         <v>38</v>
       </c>
       <c r="P310" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q310" s="44">
         <v>41631</v>
@@ -26458,7 +26455,7 @@
         <v>42</v>
       </c>
       <c r="P311" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q311" s="44">
         <v>40896</v>
@@ -26524,7 +26521,7 @@
         <v>47</v>
       </c>
       <c r="P312" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q312" s="44">
         <v>40955</v>
@@ -26590,7 +26587,7 @@
         <v>34</v>
       </c>
       <c r="P313" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q313" s="44">
         <v>44333</v>
@@ -26656,7 +26653,7 @@
         <v>34</v>
       </c>
       <c r="P314" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q314" s="44">
         <v>41631</v>
@@ -26722,7 +26719,7 @@
         <v>35</v>
       </c>
       <c r="P315" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q315" s="44">
         <v>41631</v>
@@ -26788,7 +26785,7 @@
         <v>33</v>
       </c>
       <c r="P316" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q316" s="44">
         <v>41631</v>
@@ -26854,7 +26851,7 @@
         <v>34</v>
       </c>
       <c r="P317" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q317" s="44">
         <v>41631</v>
@@ -26920,7 +26917,7 @@
         <v>45</v>
       </c>
       <c r="P318" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q318" s="44">
         <v>41064</v>
@@ -26986,7 +26983,7 @@
         <v>46</v>
       </c>
       <c r="P319" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q319" s="44">
         <v>44060</v>
@@ -27052,7 +27049,7 @@
         <v>40</v>
       </c>
       <c r="P320" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q320" s="44">
         <v>41129</v>
@@ -27118,7 +27115,7 @@
         <v>42</v>
       </c>
       <c r="P321" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q321" s="44">
         <v>41204</v>
@@ -27184,7 +27181,7 @@
         <v>38</v>
       </c>
       <c r="P322" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q322" s="44">
         <v>41218</v>
@@ -27250,7 +27247,7 @@
         <v>31</v>
       </c>
       <c r="P323" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q323" s="44">
         <v>43191</v>
@@ -27316,7 +27313,7 @@
         <v>34</v>
       </c>
       <c r="P324" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q324" s="44">
         <v>43800</v>
@@ -27382,7 +27379,7 @@
         <v>31</v>
       </c>
       <c r="P325" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q325" s="44">
         <v>41982</v>
@@ -27448,7 +27445,7 @@
         <v>36</v>
       </c>
       <c r="P326" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q326" s="44">
         <v>41852</v>
@@ -27514,7 +27511,7 @@
         <v>34</v>
       </c>
       <c r="P327" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q327" s="44">
         <v>42590</v>
@@ -27580,7 +27577,7 @@
         <v>34</v>
       </c>
       <c r="P328" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q328" s="44">
         <v>42064</v>
@@ -27646,7 +27643,7 @@
         <v>35</v>
       </c>
       <c r="P329" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q329" s="44">
         <v>41982</v>
@@ -27712,7 +27709,7 @@
         <v>33</v>
       </c>
       <c r="P330" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q330" s="44">
         <v>41982</v>
@@ -27778,7 +27775,7 @@
         <v>32</v>
       </c>
       <c r="P331" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q331" s="44">
         <v>42675</v>
@@ -27844,7 +27841,7 @@
         <v>32</v>
       </c>
       <c r="P332" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q332" s="44">
         <v>42675</v>
@@ -27910,7 +27907,7 @@
         <v>46</v>
       </c>
       <c r="P333" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q333" s="44">
         <v>41617</v>
@@ -27976,7 +27973,7 @@
         <v>32</v>
       </c>
       <c r="P334" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q334" s="44">
         <v>44333</v>
@@ -28042,7 +28039,7 @@
         <v>35</v>
       </c>
       <c r="P335" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q335" s="44">
         <v>43040</v>
@@ -28108,7 +28105,7 @@
         <v>37</v>
       </c>
       <c r="P336" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q336" s="44">
         <v>44348</v>
@@ -28174,7 +28171,7 @@
         <v>38</v>
       </c>
       <c r="P337" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q337" s="44">
         <v>41883</v>
@@ -28240,7 +28237,7 @@
         <v>34</v>
       </c>
       <c r="P338" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q338" s="44">
         <v>44333</v>
@@ -28306,7 +28303,7 @@
         <v>36</v>
       </c>
       <c r="P339" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q339" s="44">
         <v>42738</v>
@@ -28372,7 +28369,7 @@
         <v>34</v>
       </c>
       <c r="P340" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q340" s="44">
         <v>42738</v>
@@ -28438,7 +28435,7 @@
         <v>29</v>
       </c>
       <c r="P341" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q341" s="44">
         <v>43206</v>
@@ -28504,7 +28501,7 @@
         <v>37</v>
       </c>
       <c r="P342" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q342" s="44">
         <v>45299</v>
@@ -28570,7 +28567,7 @@
         <v>42</v>
       </c>
       <c r="P343" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q343" s="44">
         <v>42370</v>
@@ -28636,7 +28633,7 @@
         <v>39</v>
       </c>
       <c r="P344" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q344" s="44">
         <v>42370</v>
@@ -28702,7 +28699,7 @@
         <v>37</v>
       </c>
       <c r="P345" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q345" s="44">
         <v>42370</v>
@@ -28768,7 +28765,7 @@
         <v>30</v>
       </c>
       <c r="P346" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q346" s="44">
         <v>44713</v>
@@ -28834,7 +28831,7 @@
         <v>38</v>
       </c>
       <c r="P347" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q347" s="44">
         <v>42493</v>
@@ -28900,7 +28897,7 @@
         <v>33</v>
       </c>
       <c r="P348" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q348" s="44">
         <v>44333</v>
@@ -28966,7 +28963,7 @@
         <v>53</v>
       </c>
       <c r="P349" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q349" s="44">
         <v>42738</v>
@@ -29032,7 +29029,7 @@
         <v>45</v>
       </c>
       <c r="P350" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q350" s="44">
         <v>42979</v>
@@ -29098,7 +29095,7 @@
         <v>44</v>
       </c>
       <c r="P351" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q351" s="44">
         <v>43089</v>
@@ -29164,7 +29161,7 @@
         <v>31</v>
       </c>
       <c r="P352" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q352" s="44">
         <v>43819</v>
@@ -29230,7 +29227,7 @@
         <v>34</v>
       </c>
       <c r="P353" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q353" s="44">
         <v>43472</v>
@@ -29296,7 +29293,7 @@
         <v>32</v>
       </c>
       <c r="P354" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q354" s="44">
         <v>43831</v>
@@ -29362,7 +29359,7 @@
         <v>32</v>
       </c>
       <c r="P355" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q355" s="44">
         <v>43089</v>
@@ -29428,7 +29425,7 @@
         <v>30</v>
       </c>
       <c r="P356" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q356" s="44">
         <v>43089</v>
@@ -29494,7 +29491,7 @@
         <v>37</v>
       </c>
       <c r="P357" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q357" s="44">
         <v>43089</v>
@@ -29560,7 +29557,7 @@
         <v>32</v>
       </c>
       <c r="P358" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q358" s="44">
         <v>43089</v>
@@ -29626,7 +29623,7 @@
         <v>47</v>
       </c>
       <c r="P359" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q359" s="44">
         <v>43089</v>
@@ -29692,7 +29689,7 @@
         <v>32</v>
       </c>
       <c r="P360" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q360" s="44">
         <v>43831</v>
@@ -29758,7 +29755,7 @@
         <v>40</v>
       </c>
       <c r="P361" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q361" s="44">
         <v>43191</v>
@@ -29824,7 +29821,7 @@
         <v>40</v>
       </c>
       <c r="P362" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q362" s="44">
         <v>43206</v>
@@ -29890,7 +29887,7 @@
         <v>31</v>
       </c>
       <c r="P363" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q363" s="44">
         <v>44348</v>
@@ -29956,7 +29953,7 @@
         <v>30</v>
       </c>
       <c r="P364" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q364" s="44">
         <v>44333</v>
@@ -30022,7 +30019,7 @@
         <v>39</v>
       </c>
       <c r="P365" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q365" s="44">
         <v>43472</v>
@@ -30088,7 +30085,7 @@
         <v>38</v>
       </c>
       <c r="P366" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q366" s="44">
         <v>43472</v>
@@ -30154,7 +30151,7 @@
         <v>38</v>
       </c>
       <c r="P367" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q367" s="44">
         <v>43472</v>
@@ -30220,7 +30217,7 @@
         <v>44</v>
       </c>
       <c r="P368" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q368" s="44">
         <v>43472</v>
@@ -30286,7 +30283,7 @@
         <v>37</v>
       </c>
       <c r="P369" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q369" s="44">
         <v>43472</v>
@@ -30352,7 +30349,7 @@
         <v>28</v>
       </c>
       <c r="P370" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q370" s="44">
         <v>43472</v>
@@ -30418,7 +30415,7 @@
         <v>35</v>
       </c>
       <c r="P371" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q371" s="44">
         <v>43472</v>
@@ -30484,7 +30481,7 @@
         <v>37</v>
       </c>
       <c r="P372" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q372" s="44">
         <v>43472</v>
@@ -30550,7 +30547,7 @@
         <v>52</v>
       </c>
       <c r="P373" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q373" s="44">
         <v>43472</v>
@@ -30616,7 +30613,7 @@
         <v>50</v>
       </c>
       <c r="P374" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q374" s="44">
         <v>43497</v>
@@ -30682,7 +30679,7 @@
         <v>50</v>
       </c>
       <c r="P375" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q375" s="44">
         <v>44214</v>
@@ -30748,7 +30745,7 @@
         <v>34</v>
       </c>
       <c r="P376" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q376" s="44">
         <v>43800</v>
@@ -30814,7 +30811,7 @@
         <v>30</v>
       </c>
       <c r="P377" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q377" s="44">
         <v>43819</v>
@@ -30838,10 +30835,10 @@
         <v>300795</v>
       </c>
       <c r="B378" s="42" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C378" s="42" t="s">
         <v>1696</v>
-      </c>
-      <c r="C378" s="42" t="s">
-        <v>1697</v>
       </c>
       <c r="D378" s="41" t="s">
         <v>88</v>
@@ -30880,7 +30877,7 @@
         <v>33</v>
       </c>
       <c r="P378" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q378" s="46">
         <v>44228</v>
@@ -30896,7 +30893,7 @@
         <v>1135</v>
       </c>
       <c r="V378" s="45" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="379" spans="1:22">
@@ -30946,7 +30943,7 @@
         <v>31</v>
       </c>
       <c r="P379" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q379" s="44">
         <v>44242</v>
@@ -31012,7 +31009,7 @@
         <v>31</v>
       </c>
       <c r="P380" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q380" s="44">
         <v>44242</v>
@@ -31078,7 +31075,7 @@
         <v>43</v>
       </c>
       <c r="P381" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q381" s="44">
         <v>44317</v>
@@ -31144,7 +31141,7 @@
         <v>43</v>
       </c>
       <c r="P382" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q382" s="44">
         <v>44333</v>
@@ -31210,7 +31207,7 @@
         <v>39</v>
       </c>
       <c r="P383" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q383" s="44">
         <v>44333</v>
@@ -31276,7 +31273,7 @@
         <v>28</v>
       </c>
       <c r="P384" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q384" s="44">
         <v>44333</v>
@@ -31342,7 +31339,7 @@
         <v>32</v>
       </c>
       <c r="P385" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q385" s="44">
         <v>44333</v>
@@ -31408,7 +31405,7 @@
         <v>34</v>
       </c>
       <c r="P386" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q386" s="44">
         <v>44333</v>
@@ -31474,7 +31471,7 @@
         <v>45</v>
       </c>
       <c r="P387" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q387" s="44">
         <v>44333</v>
@@ -31540,7 +31537,7 @@
         <v>32</v>
       </c>
       <c r="P388" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q388" s="44">
         <v>44333</v>
@@ -31606,7 +31603,7 @@
         <v>34</v>
       </c>
       <c r="P389" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q389" s="44">
         <v>44333</v>
@@ -31672,7 +31669,7 @@
         <v>32</v>
       </c>
       <c r="P390" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q390" s="44">
         <v>44333</v>
@@ -31738,7 +31735,7 @@
         <v>44</v>
       </c>
       <c r="P391" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q391" s="44">
         <v>44333</v>
@@ -31804,7 +31801,7 @@
         <v>44</v>
       </c>
       <c r="P392" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q392" s="44">
         <v>44348</v>
@@ -31870,7 +31867,7 @@
         <v>36</v>
       </c>
       <c r="P393" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q393" s="44">
         <v>44410</v>
@@ -31936,7 +31933,7 @@
         <v>35</v>
       </c>
       <c r="P394" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q394" s="44">
         <v>44431</v>
@@ -32002,7 +31999,7 @@
         <v>38</v>
       </c>
       <c r="P395" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q395" s="44">
         <v>44531</v>
@@ -32068,7 +32065,7 @@
         <v>26</v>
       </c>
       <c r="P396" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q396" s="44">
         <v>44531</v>
@@ -32134,7 +32131,7 @@
         <v>32</v>
       </c>
       <c r="P397" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q397" s="44">
         <v>44531</v>
@@ -32200,7 +32197,7 @@
         <v>37</v>
       </c>
       <c r="P398" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q398" s="44">
         <v>44562</v>
@@ -32266,7 +32263,7 @@
         <v>33</v>
       </c>
       <c r="P399" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q399" s="44">
         <v>44562</v>
@@ -32332,7 +32329,7 @@
         <v>30</v>
       </c>
       <c r="P400" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q400" s="44">
         <v>44562</v>
@@ -32398,7 +32395,7 @@
         <v>49</v>
       </c>
       <c r="P401" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q401" s="44">
         <v>44621</v>
@@ -32464,7 +32461,7 @@
         <v>33</v>
       </c>
       <c r="P402" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q402" s="44">
         <v>44634</v>
@@ -32530,7 +32527,7 @@
         <v>43</v>
       </c>
       <c r="P403" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q403" s="44">
         <v>44652</v>
@@ -32596,7 +32593,7 @@
         <v>44</v>
       </c>
       <c r="P404" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q404" s="44">
         <v>44652</v>
@@ -32662,7 +32659,7 @@
         <v>52</v>
       </c>
       <c r="P405" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q405" s="44">
         <v>44662</v>
@@ -32728,7 +32725,7 @@
         <v>31</v>
       </c>
       <c r="P406" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q406" s="44">
         <v>44662</v>
@@ -32794,7 +32791,7 @@
         <v>32</v>
       </c>
       <c r="P407" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q407" s="44">
         <v>44662</v>
@@ -32860,7 +32857,7 @@
         <v>28</v>
       </c>
       <c r="P408" s="45" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="Q408" s="44">
         <v>44662</v>
@@ -32926,7 +32923,7 @@
         <v>35</v>
       </c>
       <c r="P409" s="45" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="Q409" s="44">
         <v>44697</v>
@@ -32992,7 +32989,7 @@
         <v>39</v>
       </c>
       <c r="P410" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q410" s="44">
         <v>44713</v>
@@ -33058,7 +33055,7 @@
         <v>50</v>
       </c>
       <c r="P411" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q411" s="44">
         <v>44713</v>
@@ -33124,7 +33121,7 @@
         <v>48</v>
       </c>
       <c r="P412" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q412" s="44">
         <v>44713</v>
@@ -33190,7 +33187,7 @@
         <v>36</v>
       </c>
       <c r="P413" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q413" s="44">
         <v>44713</v>
@@ -33256,7 +33253,7 @@
         <v>43</v>
       </c>
       <c r="P414" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q414" s="44">
         <v>44713</v>
@@ -33322,7 +33319,7 @@
         <v>52</v>
       </c>
       <c r="P415" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q415" s="44">
         <v>44732</v>
@@ -33388,7 +33385,7 @@
         <v>37</v>
       </c>
       <c r="P416" s="45" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="Q416" s="44">
         <v>44732</v>
@@ -33454,7 +33451,7 @@
         <v>36</v>
       </c>
       <c r="P417" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q417" s="44">
         <v>44732</v>
@@ -33520,7 +33517,7 @@
         <v>27</v>
       </c>
       <c r="P418" s="45" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="Q418" s="44">
         <v>46006</v>
@@ -33588,7 +33585,7 @@
         <v>28</v>
       </c>
       <c r="P419" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q419" s="44">
         <v>45250</v>
@@ -33654,7 +33651,7 @@
         <v>49</v>
       </c>
       <c r="P420" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q420" s="44">
         <v>45352</v>
@@ -33720,7 +33717,7 @@
         <v>34</v>
       </c>
       <c r="P421" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q421" s="44">
         <v>45352</v>
@@ -33786,7 +33783,7 @@
         <v>27</v>
       </c>
       <c r="P422" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q422" s="44">
         <v>45352</v>
@@ -33852,7 +33849,7 @@
         <v>30</v>
       </c>
       <c r="P423" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q423" s="44">
         <v>45352</v>
@@ -33918,7 +33915,7 @@
         <v>29</v>
       </c>
       <c r="P424" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q424" s="44">
         <v>45352</v>
@@ -33984,7 +33981,7 @@
         <v>33</v>
       </c>
       <c r="P425" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q425" s="44">
         <v>45352</v>
@@ -34050,7 +34047,7 @@
         <v>32</v>
       </c>
       <c r="P426" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q426" s="44">
         <v>45352</v>
@@ -34116,7 +34113,7 @@
         <v>43</v>
       </c>
       <c r="P427" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q427" s="44">
         <v>45352</v>
@@ -34182,7 +34179,7 @@
         <v>48</v>
       </c>
       <c r="P428" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q428" s="44">
         <v>45352</v>
@@ -34248,7 +34245,7 @@
         <v>32</v>
       </c>
       <c r="P429" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q429" s="44">
         <v>45418</v>
@@ -34314,7 +34311,7 @@
         <v>58</v>
       </c>
       <c r="P430" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q430" s="44">
         <v>45474</v>
@@ -34380,7 +34377,7 @@
         <v>28</v>
       </c>
       <c r="P431" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q431" s="44">
         <v>45627</v>
@@ -34446,7 +34443,7 @@
         <v>32</v>
       </c>
       <c r="P432" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q432" s="44">
         <v>45717</v>
@@ -34514,7 +34511,7 @@
         <v>25</v>
       </c>
       <c r="P433" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q433" s="44">
         <v>45717</v>
@@ -34582,7 +34579,7 @@
         <v>35</v>
       </c>
       <c r="P434" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q434" s="44">
         <v>45717</v>
@@ -34650,7 +34647,7 @@
         <v>30</v>
       </c>
       <c r="P435" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q435" s="44">
         <v>45824</v>
@@ -34718,7 +34715,7 @@
         <v>29</v>
       </c>
       <c r="P436" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q436" s="44">
         <v>45824</v>
@@ -34786,7 +34783,7 @@
         <v>31</v>
       </c>
       <c r="P437" s="45" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="Q437" s="44">
         <v>45824</v>
@@ -34854,7 +34851,7 @@
         <v>31</v>
       </c>
       <c r="P438" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q438" s="44">
         <v>45859</v>
@@ -34920,7 +34917,7 @@
         <v>35</v>
       </c>
       <c r="P439" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q439" s="44">
         <v>45950</v>
@@ -34986,7 +34983,7 @@
         <v>33</v>
       </c>
       <c r="P440" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q440" s="44">
         <v>46006</v>
@@ -35054,7 +35051,7 @@
         <v>22</v>
       </c>
       <c r="P441" s="45" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="Q441" s="44">
         <v>46020</v>
@@ -35122,7 +35119,7 @@
         <v>26</v>
       </c>
       <c r="P442" s="45" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="Q442" s="44">
         <v>46041</v>
@@ -35190,7 +35187,7 @@
         <v>28</v>
       </c>
       <c r="P443" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q443" s="44">
         <v>46041</v>
@@ -35258,7 +35255,7 @@
         <v>46</v>
       </c>
       <c r="P444" s="45" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="Q444" s="44">
         <v>46054</v>
@@ -35324,7 +35321,7 @@
         <v>26</v>
       </c>
       <c r="P445" s="45" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="Q445" s="44">
         <v>46054</v>
@@ -35392,7 +35389,7 @@
         <v>24</v>
       </c>
       <c r="P446" s="45" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="Q446" s="44">
         <v>46054</v>
@@ -35460,7 +35457,7 @@
         <v>35</v>
       </c>
       <c r="P447" s="45" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q447" s="44">
         <v>46054</v>
@@ -35528,7 +35525,7 @@
         <v>41</v>
       </c>
       <c r="P448" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q448" s="44">
         <v>46143</v>
@@ -35596,7 +35593,7 @@
         <v>35</v>
       </c>
       <c r="P449" s="45" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="Q449" s="44">
         <v>46223</v>
@@ -35618,10 +35615,10 @@
         <v>306541</v>
       </c>
       <c r="B450" s="48" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C450" s="48" t="s">
         <v>1699</v>
-      </c>
-      <c r="C450" s="48" t="s">
-        <v>1700</v>
       </c>
       <c r="D450" s="47" t="s">
         <v>2</v>
@@ -35660,7 +35657,7 @@
         <v>42</v>
       </c>
       <c r="P450" s="51" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="Q450" s="50">
         <v>46235</v>
@@ -35674,7 +35671,7 @@
       <c r="T450" s="47"/>
       <c r="U450" s="51"/>
       <c r="V450" s="51" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="451" spans="1:22">
@@ -35942,7 +35939,7 @@
         <v>173</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>114</v>
@@ -35969,13 +35966,13 @@
         <v>30</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="O2" s="8">
         <v>30</v>
@@ -36022,13 +36019,13 @@
         <v>746</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>1594</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="O3" s="8">
         <v>359</v>
@@ -36075,13 +36072,13 @@
         <v>15</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>1676</v>
+        <v>1706</v>
       </c>
       <c r="O4" s="8">
         <v>30</v>
@@ -36101,7 +36098,7 @@
         <v>241</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>244</v>
@@ -36128,13 +36125,13 @@
         <v>15</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="O5" s="8">
         <v>33</v>
@@ -36181,13 +36178,13 @@
         <v>912</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>1594</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="O6" s="8">
         <v>360</v>
@@ -36234,13 +36231,13 @@
         <v>1175</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>1594</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="O7" s="8">
         <v>375</v>
@@ -36260,7 +36257,7 @@
         <v>477</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>73</v>
@@ -36287,13 +36284,13 @@
         <v>11</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="O8" s="8">
         <v>11</v>
@@ -36340,13 +36337,13 @@
         <v>30</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="O9" s="8">
         <v>30</v>
@@ -36393,13 +36390,13 @@
         <v>120</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M10" s="7" t="s">
         <v>1594</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="O10" s="8">
         <v>150</v>
@@ -36446,13 +36443,13 @@
         <v>11</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="O11" s="8">
         <v>11</v>
@@ -36499,13 +36496,13 @@
         <v>42</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>1594</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="O12" s="8">
         <v>42</v>
@@ -36552,13 +36549,13 @@
         <v>76</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M13" s="7" t="s">
         <v>1594</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="O13" s="8">
         <v>76</v>
@@ -36578,7 +36575,7 @@
         <v>873</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>39</v>
@@ -36605,13 +36602,13 @@
         <v>15</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="O14" s="8">
         <v>15</v>
@@ -36658,13 +36655,13 @@
         <v>105</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>1594</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="O15" s="8">
         <v>105</v>
@@ -36711,13 +36708,13 @@
         <v>150</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M16" s="7" t="s">
         <v>1594</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="O16" s="8">
         <v>150</v>
@@ -36764,13 +36761,13 @@
         <v>21</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="O17" s="8">
         <v>21</v>
@@ -43749,10 +43746,10 @@
         <v>300795</v>
       </c>
       <c r="B378" s="42" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C378" s="42" t="s">
         <v>1696</v>
-      </c>
-      <c r="C378" s="42" t="s">
-        <v>1697</v>
       </c>
       <c r="D378" s="41" t="s">
         <v>88</v>
@@ -44973,10 +44970,10 @@
         <v>306541</v>
       </c>
       <c r="B450" s="48" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C450" s="48" t="s">
         <v>1699</v>
-      </c>
-      <c r="C450" s="48" t="s">
-        <v>1700</v>
       </c>
       <c r="D450" s="47" t="s">
         <v>2</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baray020\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A649ED0-D4F3-4A77-8039-3723B09B9364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A786DD81-81C8-4EBF-9580-C54C81A9FD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1890" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1890" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dotaci" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="ausdeo" sheetId="3" r:id="rId3"/>
     <sheet name="discapacidad" sheetId="4" r:id="rId4"/>
     <sheet name="Comuna" sheetId="5" r:id="rId5"/>
+    <sheet name="jefatura" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dotaci!$A$1:$V$23</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8425" uniqueCount="1707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8427" uniqueCount="1709">
   <si>
     <t>HENRIQUEZ POOL FELIPE ALBERTO</t>
   </si>
@@ -5162,6 +5163,12 @@
   </si>
   <si>
     <t>Cirugía Vascular Periférica</t>
+  </si>
+  <si>
+    <t>SAP Trabajador</t>
+  </si>
+  <si>
+    <t>SAP Jefatura</t>
   </si>
 </sst>
 </file>
@@ -5171,7 +5178,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mmm/yyyy;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5240,8 +5247,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5274,6 +5289,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5417,7 +5438,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -5578,14 +5599,20 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -35953,10 +35980,10 @@
       <c r="G2" s="8">
         <v>2</v>
       </c>
-      <c r="H2" s="56">
+      <c r="H2" s="54">
         <v>46238</v>
       </c>
-      <c r="I2" s="56">
+      <c r="I2" s="54">
         <v>46267</v>
       </c>
       <c r="J2" s="5">
@@ -36006,10 +36033,10 @@
       <c r="G3" s="8">
         <v>4</v>
       </c>
-      <c r="H3" s="56">
+      <c r="H3" s="54">
         <v>46213</v>
       </c>
-      <c r="I3" s="56">
+      <c r="I3" s="54">
         <v>46242</v>
       </c>
       <c r="J3" s="5">
@@ -36059,10 +36086,10 @@
       <c r="G4" s="8">
         <v>2</v>
       </c>
-      <c r="H4" s="56">
+      <c r="H4" s="54">
         <v>46225</v>
       </c>
-      <c r="I4" s="56">
+      <c r="I4" s="54">
         <v>46239</v>
       </c>
       <c r="J4" s="5">
@@ -36112,10 +36139,10 @@
       <c r="G5" s="8" t="s">
         <v>1135</v>
       </c>
-      <c r="H5" s="56">
+      <c r="H5" s="54">
         <v>46223</v>
       </c>
-      <c r="I5" s="56">
+      <c r="I5" s="54">
         <v>46237</v>
       </c>
       <c r="J5" s="5">
@@ -36165,10 +36192,10 @@
       <c r="G6" s="8">
         <v>4</v>
       </c>
-      <c r="H6" s="56">
+      <c r="H6" s="54">
         <v>46220</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="54">
         <v>46249</v>
       </c>
       <c r="J6" s="5">
@@ -36218,10 +36245,10 @@
       <c r="G7" s="8">
         <v>2</v>
       </c>
-      <c r="H7" s="56">
+      <c r="H7" s="54">
         <v>46221</v>
       </c>
-      <c r="I7" s="56">
+      <c r="I7" s="54">
         <v>46250</v>
       </c>
       <c r="J7" s="5">
@@ -36271,10 +36298,10 @@
       <c r="G8" s="8">
         <v>3</v>
       </c>
-      <c r="H8" s="56">
+      <c r="H8" s="54">
         <v>46237</v>
       </c>
-      <c r="I8" s="56">
+      <c r="I8" s="54">
         <v>46247</v>
       </c>
       <c r="J8" s="5">
@@ -36324,10 +36351,10 @@
       <c r="G9" s="8">
         <v>2</v>
       </c>
-      <c r="H9" s="56">
+      <c r="H9" s="54">
         <v>46238</v>
       </c>
-      <c r="I9" s="56">
+      <c r="I9" s="54">
         <v>46267</v>
       </c>
       <c r="J9" s="5">
@@ -36377,10 +36404,10 @@
       <c r="G10" s="8">
         <v>2</v>
       </c>
-      <c r="H10" s="56">
+      <c r="H10" s="54">
         <v>46230</v>
       </c>
-      <c r="I10" s="56">
+      <c r="I10" s="54">
         <v>46259</v>
       </c>
       <c r="J10" s="5">
@@ -36430,10 +36457,10 @@
       <c r="G11" s="8">
         <v>2</v>
       </c>
-      <c r="H11" s="56">
+      <c r="H11" s="54">
         <v>46224</v>
       </c>
-      <c r="I11" s="56">
+      <c r="I11" s="54">
         <v>46234</v>
       </c>
       <c r="J11" s="5">
@@ -36483,10 +36510,10 @@
       <c r="G12" s="8">
         <v>2</v>
       </c>
-      <c r="H12" s="56">
+      <c r="H12" s="54">
         <v>46236</v>
       </c>
-      <c r="I12" s="56">
+      <c r="I12" s="54">
         <v>46256</v>
       </c>
       <c r="J12" s="5">
@@ -36536,10 +36563,10 @@
       <c r="G13" s="8">
         <v>3</v>
       </c>
-      <c r="H13" s="56">
+      <c r="H13" s="54">
         <v>46240</v>
       </c>
-      <c r="I13" s="56">
+      <c r="I13" s="54">
         <v>46264</v>
       </c>
       <c r="J13" s="5">
@@ -36589,10 +36616,10 @@
       <c r="G14" s="8">
         <v>2</v>
       </c>
-      <c r="H14" s="56">
+      <c r="H14" s="54">
         <v>46231</v>
       </c>
-      <c r="I14" s="56">
+      <c r="I14" s="54">
         <v>46245</v>
       </c>
       <c r="J14" s="5">
@@ -36642,10 +36669,10 @@
       <c r="G15" s="8">
         <v>2</v>
       </c>
-      <c r="H15" s="56">
+      <c r="H15" s="54">
         <v>46229</v>
       </c>
-      <c r="I15" s="56">
+      <c r="I15" s="54">
         <v>46258</v>
       </c>
       <c r="J15" s="5">
@@ -36695,10 +36722,10 @@
       <c r="G16" s="8">
         <v>2</v>
       </c>
-      <c r="H16" s="56">
+      <c r="H16" s="54">
         <v>46232</v>
       </c>
-      <c r="I16" s="56">
+      <c r="I16" s="54">
         <v>46261</v>
       </c>
       <c r="J16" s="5">
@@ -36748,10 +36775,10 @@
       <c r="G17" s="8" t="s">
         <v>1135</v>
       </c>
-      <c r="H17" s="56">
+      <c r="H17" s="54">
         <v>46226</v>
       </c>
-      <c r="I17" s="56">
+      <c r="I17" s="54">
         <v>46246</v>
       </c>
       <c r="J17" s="5">
@@ -36795,35 +36822,35 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" s="9"/>
-      <c r="C2" s="54">
+      <c r="C2" s="55">
         <v>2026</v>
       </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
     </row>
     <row r="3" spans="2:14" ht="15.5">
       <c r="B3" s="10"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
     </row>
     <row r="4" spans="2:14" ht="15.5">
       <c r="B4" s="11"/>
@@ -37214,14 +37241,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9">
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="56" t="s">
         <v>1633</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="E1" s="55" t="s">
+      <c r="C1" s="56"/>
+      <c r="E1" s="56" t="s">
         <v>1634</v>
       </c>
-      <c r="F1" s="55"/>
+      <c r="F1" s="56"/>
       <c r="H1" s="28" t="s">
         <v>1640</v>
       </c>
@@ -44989,4 +45016,3618 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3682272E-EE01-47AF-9D72-46EB4E0FBABC}">
+  <dimension ref="A1:B450"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="2" width="14.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="57" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B1" s="57" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="6">
+        <v>12831</v>
+      </c>
+      <c r="B2" s="6">
+        <v>56057</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="6">
+        <v>18380</v>
+      </c>
+      <c r="B3" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="6">
+        <v>18525</v>
+      </c>
+      <c r="B4" s="6">
+        <v>56057</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="6">
+        <v>25059</v>
+      </c>
+      <c r="B5" s="6">
+        <v>18380</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="6">
+        <v>31682</v>
+      </c>
+      <c r="B6" s="6">
+        <v>52883</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="6">
+        <v>39491</v>
+      </c>
+      <c r="B7" s="6">
+        <v>68849</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="6">
+        <v>39497</v>
+      </c>
+      <c r="B8" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="6">
+        <v>39500</v>
+      </c>
+      <c r="B9" s="6">
+        <v>31682</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="6">
+        <v>39503</v>
+      </c>
+      <c r="B10" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="6">
+        <v>39504</v>
+      </c>
+      <c r="B11" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="6">
+        <v>39512</v>
+      </c>
+      <c r="B12" s="6">
+        <v>54004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="6">
+        <v>39520</v>
+      </c>
+      <c r="B13" s="6">
+        <v>18525</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="6">
+        <v>39523</v>
+      </c>
+      <c r="B14" s="6">
+        <v>56057</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="6">
+        <v>39538</v>
+      </c>
+      <c r="B15" s="6">
+        <v>58520</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="6">
+        <v>39540</v>
+      </c>
+      <c r="B16" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="6">
+        <v>39546</v>
+      </c>
+      <c r="B17" s="6">
+        <v>68849</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="6">
+        <v>39550</v>
+      </c>
+      <c r="B18" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="6">
+        <v>39551</v>
+      </c>
+      <c r="B19" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="6">
+        <v>39559</v>
+      </c>
+      <c r="B20" s="6">
+        <v>51647</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="6">
+        <v>39560</v>
+      </c>
+      <c r="B21" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="6">
+        <v>39569</v>
+      </c>
+      <c r="B22" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="6">
+        <v>39579</v>
+      </c>
+      <c r="B23" s="6">
+        <v>54730</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="6">
+        <v>39590</v>
+      </c>
+      <c r="B24" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="6">
+        <v>39595</v>
+      </c>
+      <c r="B25" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="6">
+        <v>39600</v>
+      </c>
+      <c r="B26" s="6">
+        <v>41213</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="6">
+        <v>39601</v>
+      </c>
+      <c r="B27" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="6">
+        <v>39605</v>
+      </c>
+      <c r="B28" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="6">
+        <v>39606</v>
+      </c>
+      <c r="B29" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="6">
+        <v>39607</v>
+      </c>
+      <c r="B30" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="6">
+        <v>39608</v>
+      </c>
+      <c r="B31" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="6">
+        <v>39609</v>
+      </c>
+      <c r="B32" s="6">
+        <v>41213</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="6">
+        <v>39615</v>
+      </c>
+      <c r="B33" s="6">
+        <v>68849</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="6">
+        <v>39628</v>
+      </c>
+      <c r="B34" s="6">
+        <v>300900</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="6">
+        <v>39629</v>
+      </c>
+      <c r="B35" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="6">
+        <v>39630</v>
+      </c>
+      <c r="B36" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="58">
+        <v>39631</v>
+      </c>
+      <c r="B37" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="6">
+        <v>39632</v>
+      </c>
+      <c r="B38" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="6">
+        <v>39638</v>
+      </c>
+      <c r="B39" s="6">
+        <v>300900</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="6">
+        <v>39640</v>
+      </c>
+      <c r="B40" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="6">
+        <v>39642</v>
+      </c>
+      <c r="B41" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="6">
+        <v>39643</v>
+      </c>
+      <c r="B42" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="6">
+        <v>39644</v>
+      </c>
+      <c r="B43" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="6">
+        <v>39645</v>
+      </c>
+      <c r="B44" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="6">
+        <v>39646</v>
+      </c>
+      <c r="B45" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="6">
+        <v>39647</v>
+      </c>
+      <c r="B46" s="6">
+        <v>41213</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="6">
+        <v>39650</v>
+      </c>
+      <c r="B47" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="6">
+        <v>39652</v>
+      </c>
+      <c r="B48" s="6">
+        <v>54745</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="58">
+        <v>39653</v>
+      </c>
+      <c r="B49" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="6">
+        <v>39654</v>
+      </c>
+      <c r="B50" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="6">
+        <v>39655</v>
+      </c>
+      <c r="B51" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="6">
+        <v>39658</v>
+      </c>
+      <c r="B52" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="6">
+        <v>39659</v>
+      </c>
+      <c r="B53" s="6">
+        <v>40969</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="6">
+        <v>39661</v>
+      </c>
+      <c r="B54" s="6">
+        <v>54745</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="58">
+        <v>39662</v>
+      </c>
+      <c r="B55" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="6">
+        <v>39664</v>
+      </c>
+      <c r="B56" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="6">
+        <v>39666</v>
+      </c>
+      <c r="B57" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="6">
+        <v>39667</v>
+      </c>
+      <c r="B58" s="6">
+        <v>63374</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="6">
+        <v>39669</v>
+      </c>
+      <c r="B59" s="6">
+        <v>301960</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="6">
+        <v>39673</v>
+      </c>
+      <c r="B60" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="6">
+        <v>39674</v>
+      </c>
+      <c r="B61" s="6">
+        <v>59743</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="58">
+        <v>39675</v>
+      </c>
+      <c r="B62" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="6">
+        <v>39676</v>
+      </c>
+      <c r="B63" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="6">
+        <v>39678</v>
+      </c>
+      <c r="B64" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="6">
+        <v>39680</v>
+      </c>
+      <c r="B65" s="6">
+        <v>39520</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="6">
+        <v>39681</v>
+      </c>
+      <c r="B66" s="6">
+        <v>300900</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="6">
+        <v>39685</v>
+      </c>
+      <c r="B67" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="6">
+        <v>39686</v>
+      </c>
+      <c r="B68" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="6">
+        <v>39687</v>
+      </c>
+      <c r="B69" s="6">
+        <v>40969</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="6">
+        <v>39690</v>
+      </c>
+      <c r="B70" s="6">
+        <v>63047</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="6">
+        <v>39691</v>
+      </c>
+      <c r="B71" s="6">
+        <v>50730</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="6">
+        <v>39693</v>
+      </c>
+      <c r="B72" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="6">
+        <v>39696</v>
+      </c>
+      <c r="B73" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="6">
+        <v>39697</v>
+      </c>
+      <c r="B74" s="6">
+        <v>300900</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="6">
+        <v>39699</v>
+      </c>
+      <c r="B75" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="6">
+        <v>40242</v>
+      </c>
+      <c r="B76" s="6">
+        <v>52884</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="6">
+        <v>40359</v>
+      </c>
+      <c r="B77" s="6">
+        <v>54004</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="6">
+        <v>40363</v>
+      </c>
+      <c r="B78" s="6">
+        <v>68849</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="6">
+        <v>40371</v>
+      </c>
+      <c r="B79" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="6">
+        <v>40380</v>
+      </c>
+      <c r="B80" s="6">
+        <v>68849</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="6">
+        <v>40382</v>
+      </c>
+      <c r="B81" s="6">
+        <v>52884</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="6">
+        <v>40395</v>
+      </c>
+      <c r="B82" s="6">
+        <v>300900</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="6">
+        <v>40419</v>
+      </c>
+      <c r="B83" s="6">
+        <v>59698</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="6">
+        <v>40434</v>
+      </c>
+      <c r="B84" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="6">
+        <v>40443</v>
+      </c>
+      <c r="B85" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="6">
+        <v>40453</v>
+      </c>
+      <c r="B86" s="6">
+        <v>54854</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="6">
+        <v>40969</v>
+      </c>
+      <c r="B87" s="6">
+        <v>47208</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="6">
+        <v>41213</v>
+      </c>
+      <c r="B88" s="6">
+        <v>47208</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="6">
+        <v>47208</v>
+      </c>
+      <c r="B89" s="6">
+        <v>18380</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="6">
+        <v>48593</v>
+      </c>
+      <c r="B90" s="6">
+        <v>54004</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="6">
+        <v>49639</v>
+      </c>
+      <c r="B91" s="6">
+        <v>55012</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="6">
+        <v>49996</v>
+      </c>
+      <c r="B92" s="6">
+        <v>68849</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="6">
+        <v>50002</v>
+      </c>
+      <c r="B93" s="6">
+        <v>51846</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="6">
+        <v>50304</v>
+      </c>
+      <c r="B94" s="6">
+        <v>18380</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="6">
+        <v>50730</v>
+      </c>
+      <c r="B95" s="6">
+        <v>51846</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="6">
+        <v>51642</v>
+      </c>
+      <c r="B96" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="6">
+        <v>51644</v>
+      </c>
+      <c r="B97" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="6">
+        <v>51646</v>
+      </c>
+      <c r="B98" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="6">
+        <v>51647</v>
+      </c>
+      <c r="B99" s="6">
+        <v>18525</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="6">
+        <v>51649</v>
+      </c>
+      <c r="B100" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="6">
+        <v>51650</v>
+      </c>
+      <c r="B101" s="6">
+        <v>39520</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="58">
+        <v>51651</v>
+      </c>
+      <c r="B102" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="6">
+        <v>51652</v>
+      </c>
+      <c r="B103" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="6">
+        <v>51846</v>
+      </c>
+      <c r="B104" s="6">
+        <v>25059</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="6">
+        <v>51882</v>
+      </c>
+      <c r="B105" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="6">
+        <v>51883</v>
+      </c>
+      <c r="B106" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="6">
+        <v>51884</v>
+      </c>
+      <c r="B107" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="6">
+        <v>51889</v>
+      </c>
+      <c r="B108" s="6">
+        <v>68849</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="6">
+        <v>51890</v>
+      </c>
+      <c r="B109" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="6">
+        <v>51891</v>
+      </c>
+      <c r="B110" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="6">
+        <v>51893</v>
+      </c>
+      <c r="B111" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="6">
+        <v>51896</v>
+      </c>
+      <c r="B112" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="6">
+        <v>51897</v>
+      </c>
+      <c r="B113" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="6">
+        <v>51899</v>
+      </c>
+      <c r="B114" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="6">
+        <v>51900</v>
+      </c>
+      <c r="B115" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="6">
+        <v>51901</v>
+      </c>
+      <c r="B116" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="6">
+        <v>51902</v>
+      </c>
+      <c r="B117" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="6">
+        <v>51905</v>
+      </c>
+      <c r="B118" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="6">
+        <v>51906</v>
+      </c>
+      <c r="B119" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="6">
+        <v>51907</v>
+      </c>
+      <c r="B120" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="6">
+        <v>51908</v>
+      </c>
+      <c r="B121" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="6">
+        <v>51909</v>
+      </c>
+      <c r="B122" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="6">
+        <v>51910</v>
+      </c>
+      <c r="B123" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="6">
+        <v>51911</v>
+      </c>
+      <c r="B124" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="6">
+        <v>51913</v>
+      </c>
+      <c r="B125" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="6">
+        <v>51915</v>
+      </c>
+      <c r="B126" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="6">
+        <v>51916</v>
+      </c>
+      <c r="B127" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="6">
+        <v>51917</v>
+      </c>
+      <c r="B128" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="6">
+        <v>51918</v>
+      </c>
+      <c r="B129" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="6">
+        <v>51919</v>
+      </c>
+      <c r="B130" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="6">
+        <v>51920</v>
+      </c>
+      <c r="B131" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="6">
+        <v>51965</v>
+      </c>
+      <c r="B132" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="6">
+        <v>51966</v>
+      </c>
+      <c r="B133" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="6">
+        <v>51967</v>
+      </c>
+      <c r="B134" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="6">
+        <v>51968</v>
+      </c>
+      <c r="B135" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="6">
+        <v>51969</v>
+      </c>
+      <c r="B136" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="6">
+        <v>51973</v>
+      </c>
+      <c r="B137" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="6">
+        <v>51974</v>
+      </c>
+      <c r="B138" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="6">
+        <v>51976</v>
+      </c>
+      <c r="B139" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="6">
+        <v>51977</v>
+      </c>
+      <c r="B140" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="6">
+        <v>51978</v>
+      </c>
+      <c r="B141" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="6">
+        <v>51979</v>
+      </c>
+      <c r="B142" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="6">
+        <v>51980</v>
+      </c>
+      <c r="B143" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="6">
+        <v>51981</v>
+      </c>
+      <c r="B144" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="6">
+        <v>51982</v>
+      </c>
+      <c r="B145" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="6">
+        <v>51983</v>
+      </c>
+      <c r="B146" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="6">
+        <v>51985</v>
+      </c>
+      <c r="B147" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="6">
+        <v>51987</v>
+      </c>
+      <c r="B148" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="6">
+        <v>51989</v>
+      </c>
+      <c r="B149" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="6">
+        <v>51990</v>
+      </c>
+      <c r="B150" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="6">
+        <v>51991</v>
+      </c>
+      <c r="B151" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="6">
+        <v>51992</v>
+      </c>
+      <c r="B152" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="6">
+        <v>51993</v>
+      </c>
+      <c r="B153" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="6">
+        <v>52017</v>
+      </c>
+      <c r="B154" s="6">
+        <v>54004</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="6">
+        <v>52148</v>
+      </c>
+      <c r="B155" s="6">
+        <v>52858</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="6">
+        <v>52149</v>
+      </c>
+      <c r="B156" s="6">
+        <v>52858</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="6">
+        <v>52151</v>
+      </c>
+      <c r="B157" s="6">
+        <v>54004</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="6">
+        <v>52152</v>
+      </c>
+      <c r="B158" s="6">
+        <v>54004</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="6">
+        <v>52155</v>
+      </c>
+      <c r="B159" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="6">
+        <v>52156</v>
+      </c>
+      <c r="B160" s="6">
+        <v>54004</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="6">
+        <v>52855</v>
+      </c>
+      <c r="B161" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="6">
+        <v>52856</v>
+      </c>
+      <c r="B162" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="6">
+        <v>52857</v>
+      </c>
+      <c r="B163" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="6">
+        <v>52858</v>
+      </c>
+      <c r="B164" s="6">
+        <v>52883</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="58">
+        <v>52859</v>
+      </c>
+      <c r="B165" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="6">
+        <v>52861</v>
+      </c>
+      <c r="B166" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="6">
+        <v>52862</v>
+      </c>
+      <c r="B167" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="6">
+        <v>52863</v>
+      </c>
+      <c r="B168" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="6">
+        <v>52864</v>
+      </c>
+      <c r="B169" s="6">
+        <v>54004</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="6">
+        <v>52866</v>
+      </c>
+      <c r="B170" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="6">
+        <v>52869</v>
+      </c>
+      <c r="B171" s="6">
+        <v>51647</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="6">
+        <v>52870</v>
+      </c>
+      <c r="B172" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="6">
+        <v>52871</v>
+      </c>
+      <c r="B173" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="6">
+        <v>52872</v>
+      </c>
+      <c r="B174" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="6">
+        <v>52875</v>
+      </c>
+      <c r="B175" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="6">
+        <v>52876</v>
+      </c>
+      <c r="B176" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="6">
+        <v>52879</v>
+      </c>
+      <c r="B177" s="6">
+        <v>51647</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="6">
+        <v>52882</v>
+      </c>
+      <c r="B178" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="6">
+        <v>52883</v>
+      </c>
+      <c r="B179" s="6">
+        <v>18525</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="6">
+        <v>52884</v>
+      </c>
+      <c r="B180" s="6">
+        <v>52883</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="6">
+        <v>52885</v>
+      </c>
+      <c r="B181" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="6">
+        <v>52888</v>
+      </c>
+      <c r="B182" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="6">
+        <v>52889</v>
+      </c>
+      <c r="B183" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="6">
+        <v>52890</v>
+      </c>
+      <c r="B184" s="6">
+        <v>68849</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="6">
+        <v>52891</v>
+      </c>
+      <c r="B185" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="6">
+        <v>52892</v>
+      </c>
+      <c r="B186" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="6">
+        <v>52893</v>
+      </c>
+      <c r="B187" s="6">
+        <v>301961</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="6">
+        <v>52900</v>
+      </c>
+      <c r="B188" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="6">
+        <v>52901</v>
+      </c>
+      <c r="B189" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="6">
+        <v>52904</v>
+      </c>
+      <c r="B190" s="6">
+        <v>300900</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="6">
+        <v>52906</v>
+      </c>
+      <c r="B191" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="58">
+        <v>53439</v>
+      </c>
+      <c r="B192" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="6">
+        <v>53447</v>
+      </c>
+      <c r="B193" s="6">
+        <v>300900</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="6">
+        <v>53448</v>
+      </c>
+      <c r="B194" s="6">
+        <v>39520</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="6">
+        <v>53449</v>
+      </c>
+      <c r="B195" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="6">
+        <v>53450</v>
+      </c>
+      <c r="B196" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="6">
+        <v>53451</v>
+      </c>
+      <c r="B197" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="6">
+        <v>53472</v>
+      </c>
+      <c r="B198" s="6">
+        <v>39520</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="6">
+        <v>53638</v>
+      </c>
+      <c r="B199" s="6">
+        <v>63744</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="6">
+        <v>53661</v>
+      </c>
+      <c r="B200" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="6">
+        <v>53665</v>
+      </c>
+      <c r="B201" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="6">
+        <v>53785</v>
+      </c>
+      <c r="B202" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="6">
+        <v>53789</v>
+      </c>
+      <c r="B203" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="6">
+        <v>53795</v>
+      </c>
+      <c r="B204" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="6">
+        <v>53797</v>
+      </c>
+      <c r="B205" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="6">
+        <v>53798</v>
+      </c>
+      <c r="B206" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="6">
+        <v>53800</v>
+      </c>
+      <c r="B207" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="6">
+        <v>53801</v>
+      </c>
+      <c r="B208" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="6">
+        <v>53803</v>
+      </c>
+      <c r="B209" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="6">
+        <v>53806</v>
+      </c>
+      <c r="B210" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="6">
+        <v>53848</v>
+      </c>
+      <c r="B211" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="6">
+        <v>53849</v>
+      </c>
+      <c r="B212" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="6">
+        <v>53850</v>
+      </c>
+      <c r="B213" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="6">
+        <v>53851</v>
+      </c>
+      <c r="B214" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="6">
+        <v>53852</v>
+      </c>
+      <c r="B215" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="6">
+        <v>53853</v>
+      </c>
+      <c r="B216" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="6">
+        <v>53946</v>
+      </c>
+      <c r="B217" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="6">
+        <v>53999</v>
+      </c>
+      <c r="B218" s="6">
+        <v>41213</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="6">
+        <v>54004</v>
+      </c>
+      <c r="B219" s="6">
+        <v>68849</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="6">
+        <v>54025</v>
+      </c>
+      <c r="B220" s="6">
+        <v>58520</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="6">
+        <v>54643</v>
+      </c>
+      <c r="B221" s="6">
+        <v>63374</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="6">
+        <v>54713</v>
+      </c>
+      <c r="B222" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="6">
+        <v>54717</v>
+      </c>
+      <c r="B223" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="6">
+        <v>54722</v>
+      </c>
+      <c r="B224" s="6">
+        <v>51647</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="6">
+        <v>54728</v>
+      </c>
+      <c r="B225" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="6">
+        <v>54729</v>
+      </c>
+      <c r="B226" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="6">
+        <v>54730</v>
+      </c>
+      <c r="B227" s="6">
+        <v>301960</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="6">
+        <v>54731</v>
+      </c>
+      <c r="B228" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="6">
+        <v>54732</v>
+      </c>
+      <c r="B229" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="6">
+        <v>54733</v>
+      </c>
+      <c r="B230" s="6">
+        <v>68849</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="6">
+        <v>54734</v>
+      </c>
+      <c r="B231" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="6">
+        <v>54737</v>
+      </c>
+      <c r="B232" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="6">
+        <v>54738</v>
+      </c>
+      <c r="B233" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="6">
+        <v>54739</v>
+      </c>
+      <c r="B234" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="6">
+        <v>54745</v>
+      </c>
+      <c r="B235" s="6">
+        <v>54833</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="6">
+        <v>54747</v>
+      </c>
+      <c r="B236" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="6">
+        <v>54831</v>
+      </c>
+      <c r="B237" s="6">
+        <v>301961</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="58">
+        <v>54832</v>
+      </c>
+      <c r="B238" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="6">
+        <v>54833</v>
+      </c>
+      <c r="B239" s="6">
+        <v>301960</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="6">
+        <v>54837</v>
+      </c>
+      <c r="B240" s="6">
+        <v>300900</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="6">
+        <v>54854</v>
+      </c>
+      <c r="B241" s="6">
+        <v>54833</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="6">
+        <v>54936</v>
+      </c>
+      <c r="B242" s="6">
+        <v>59698</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="6">
+        <v>55012</v>
+      </c>
+      <c r="B243" s="6">
+        <v>25059</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="58">
+        <v>55213</v>
+      </c>
+      <c r="B244" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="6">
+        <v>56057</v>
+      </c>
+      <c r="B245" s="6">
+        <v>18380</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="6">
+        <v>56222</v>
+      </c>
+      <c r="B246" s="6">
+        <v>301961</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="6">
+        <v>56247</v>
+      </c>
+      <c r="B247" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="6">
+        <v>56280</v>
+      </c>
+      <c r="B248" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="6">
+        <v>56282</v>
+      </c>
+      <c r="B249" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="6">
+        <v>56285</v>
+      </c>
+      <c r="B250" s="6">
+        <v>68849</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="6">
+        <v>56287</v>
+      </c>
+      <c r="B251" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="6">
+        <v>56288</v>
+      </c>
+      <c r="B252" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="6">
+        <v>56289</v>
+      </c>
+      <c r="B253" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="6">
+        <v>56291</v>
+      </c>
+      <c r="B254" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="6">
+        <v>56392</v>
+      </c>
+      <c r="B255" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="6">
+        <v>56561</v>
+      </c>
+      <c r="B256" s="6">
+        <v>52883</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="6">
+        <v>56562</v>
+      </c>
+      <c r="B257" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="6">
+        <v>56563</v>
+      </c>
+      <c r="B258" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="6">
+        <v>56567</v>
+      </c>
+      <c r="B259" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="6">
+        <v>56568</v>
+      </c>
+      <c r="B260" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="6">
+        <v>56569</v>
+      </c>
+      <c r="B261" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="6">
+        <v>56571</v>
+      </c>
+      <c r="B262" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="6">
+        <v>57143</v>
+      </c>
+      <c r="B263" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="6">
+        <v>57145</v>
+      </c>
+      <c r="B264" s="6">
+        <v>59743</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="6">
+        <v>57292</v>
+      </c>
+      <c r="B265" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="6">
+        <v>57293</v>
+      </c>
+      <c r="B266" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="6">
+        <v>57570</v>
+      </c>
+      <c r="B267" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="6">
+        <v>57636</v>
+      </c>
+      <c r="B268" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="6">
+        <v>58520</v>
+      </c>
+      <c r="B269" s="6">
+        <v>51846</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="6">
+        <v>59381</v>
+      </c>
+      <c r="B270" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="6">
+        <v>59382</v>
+      </c>
+      <c r="B271" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="6">
+        <v>59383</v>
+      </c>
+      <c r="B272" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="6">
+        <v>59384</v>
+      </c>
+      <c r="B273" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="6">
+        <v>59385</v>
+      </c>
+      <c r="B274" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="6">
+        <v>59386</v>
+      </c>
+      <c r="B275" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="6">
+        <v>59387</v>
+      </c>
+      <c r="B276" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="6">
+        <v>59396</v>
+      </c>
+      <c r="B277" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="6">
+        <v>59398</v>
+      </c>
+      <c r="B278" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="6">
+        <v>59399</v>
+      </c>
+      <c r="B279" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="6">
+        <v>59401</v>
+      </c>
+      <c r="B280" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="6">
+        <v>59404</v>
+      </c>
+      <c r="B281" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="6">
+        <v>59408</v>
+      </c>
+      <c r="B282" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="6">
+        <v>59411</v>
+      </c>
+      <c r="B283" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="6">
+        <v>59413</v>
+      </c>
+      <c r="B284" s="6">
+        <v>301961</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="6">
+        <v>59417</v>
+      </c>
+      <c r="B285" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="6">
+        <v>59421</v>
+      </c>
+      <c r="B286" s="6">
+        <v>54004</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="6">
+        <v>59423</v>
+      </c>
+      <c r="B287" s="6">
+        <v>51647</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="6">
+        <v>59426</v>
+      </c>
+      <c r="B288" s="6">
+        <v>54854</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="6">
+        <v>59558</v>
+      </c>
+      <c r="B289" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="6">
+        <v>59559</v>
+      </c>
+      <c r="B290" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="6">
+        <v>59561</v>
+      </c>
+      <c r="B291" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="6">
+        <v>59562</v>
+      </c>
+      <c r="B292" s="6">
+        <v>54004</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="6">
+        <v>59563</v>
+      </c>
+      <c r="B293" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="6">
+        <v>59564</v>
+      </c>
+      <c r="B294" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="6">
+        <v>59567</v>
+      </c>
+      <c r="B295" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="6">
+        <v>59568</v>
+      </c>
+      <c r="B296" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="6">
+        <v>59698</v>
+      </c>
+      <c r="B297" s="6">
+        <v>74704</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="6">
+        <v>59743</v>
+      </c>
+      <c r="B298" s="6">
+        <v>52883</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="6">
+        <v>59745</v>
+      </c>
+      <c r="B299" s="6">
+        <v>52884</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="6">
+        <v>59746</v>
+      </c>
+      <c r="B300" s="6">
+        <v>31682</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="6">
+        <v>60168</v>
+      </c>
+      <c r="B301" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="6">
+        <v>60170</v>
+      </c>
+      <c r="B302" s="6">
+        <v>41213</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="6">
+        <v>60595</v>
+      </c>
+      <c r="B303" s="6">
+        <v>58520</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="6">
+        <v>60642</v>
+      </c>
+      <c r="B304" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="6">
+        <v>60643</v>
+      </c>
+      <c r="B305" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="6">
+        <v>60644</v>
+      </c>
+      <c r="B306" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="6">
+        <v>60645</v>
+      </c>
+      <c r="B307" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="6">
+        <v>60646</v>
+      </c>
+      <c r="B308" s="6">
+        <v>51647</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="6">
+        <v>61088</v>
+      </c>
+      <c r="B309" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="6">
+        <v>61112</v>
+      </c>
+      <c r="B310" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="6">
+        <v>61421</v>
+      </c>
+      <c r="B311" s="6">
+        <v>47208</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="6">
+        <v>62100</v>
+      </c>
+      <c r="B312" s="6">
+        <v>55012</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="6">
+        <v>62439</v>
+      </c>
+      <c r="B313" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="6">
+        <v>62441</v>
+      </c>
+      <c r="B314" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="6">
+        <v>62444</v>
+      </c>
+      <c r="B315" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="6">
+        <v>62446</v>
+      </c>
+      <c r="B316" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="6">
+        <v>62449</v>
+      </c>
+      <c r="B317" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="6">
+        <v>63047</v>
+      </c>
+      <c r="B318" s="6">
+        <v>18380</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="6">
+        <v>63353</v>
+      </c>
+      <c r="B319" s="6">
+        <v>63047</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="6">
+        <v>63374</v>
+      </c>
+      <c r="B320" s="6">
+        <v>47208</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="6">
+        <v>63744</v>
+      </c>
+      <c r="B321" s="6">
+        <v>47208</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="6">
+        <v>63797</v>
+      </c>
+      <c r="B322" s="6">
+        <v>65214</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="6">
+        <v>64899</v>
+      </c>
+      <c r="B323" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="6">
+        <v>64956</v>
+      </c>
+      <c r="B324" s="6">
+        <v>65214</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="6">
+        <v>64996</v>
+      </c>
+      <c r="B325" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="6">
+        <v>65214</v>
+      </c>
+      <c r="B326" s="6">
+        <v>18380</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="6">
+        <v>65913</v>
+      </c>
+      <c r="B327" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="6">
+        <v>65914</v>
+      </c>
+      <c r="B328" s="6">
+        <v>39520</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="6">
+        <v>65915</v>
+      </c>
+      <c r="B329" s="6">
+        <v>300900</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="6">
+        <v>65919</v>
+      </c>
+      <c r="B330" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="6">
+        <v>65920</v>
+      </c>
+      <c r="B331" s="6">
+        <v>304835</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="6">
+        <v>65921</v>
+      </c>
+      <c r="B332" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="6">
+        <v>66080</v>
+      </c>
+      <c r="B333" s="6">
+        <v>18380</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="6">
+        <v>66410</v>
+      </c>
+      <c r="B334" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="6">
+        <v>66455</v>
+      </c>
+      <c r="B335" s="6">
+        <v>47208</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="6">
+        <v>66642</v>
+      </c>
+      <c r="B336" s="6">
+        <v>65214</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="6">
+        <v>67706</v>
+      </c>
+      <c r="B337" s="6">
+        <v>301959</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="6">
+        <v>68064</v>
+      </c>
+      <c r="B338" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="6">
+        <v>68067</v>
+      </c>
+      <c r="B339" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="6">
+        <v>68084</v>
+      </c>
+      <c r="B340" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="6">
+        <v>68121</v>
+      </c>
+      <c r="B341" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="6">
+        <v>68849</v>
+      </c>
+      <c r="B342" s="6">
+        <v>65214</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="58">
+        <v>70535</v>
+      </c>
+      <c r="B343" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="6">
+        <v>70539</v>
+      </c>
+      <c r="B344" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="6">
+        <v>70540</v>
+      </c>
+      <c r="B345" s="6">
+        <v>39520</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="6">
+        <v>70660</v>
+      </c>
+      <c r="B346" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="6">
+        <v>71303</v>
+      </c>
+      <c r="B347" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="6">
+        <v>71980</v>
+      </c>
+      <c r="B348" s="6">
+        <v>39520</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="6">
+        <v>72542</v>
+      </c>
+      <c r="B349" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="6">
+        <v>73560</v>
+      </c>
+      <c r="B350" s="6">
+        <v>55012</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="6">
+        <v>74059</v>
+      </c>
+      <c r="B351" s="6">
+        <v>54730</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="6">
+        <v>74064</v>
+      </c>
+      <c r="B352" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="6">
+        <v>74079</v>
+      </c>
+      <c r="B353" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="6">
+        <v>74080</v>
+      </c>
+      <c r="B354" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="6">
+        <v>74082</v>
+      </c>
+      <c r="B355" s="6">
+        <v>65214</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="6">
+        <v>74083</v>
+      </c>
+      <c r="B356" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="6">
+        <v>74084</v>
+      </c>
+      <c r="B357" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="6">
+        <v>74085</v>
+      </c>
+      <c r="B358" s="6">
+        <v>68849</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="6">
+        <v>74086</v>
+      </c>
+      <c r="B359" s="6">
+        <v>54004</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="6">
+        <v>74704</v>
+      </c>
+      <c r="B360" s="6">
+        <v>56057</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="6">
+        <v>75195</v>
+      </c>
+      <c r="B361" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="6">
+        <v>75241</v>
+      </c>
+      <c r="B362" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="6">
+        <v>76108</v>
+      </c>
+      <c r="B363" s="6">
+        <v>54730</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="6">
+        <v>76111</v>
+      </c>
+      <c r="B364" s="6">
+        <v>39520</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="6">
+        <v>76175</v>
+      </c>
+      <c r="B365" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="6">
+        <v>76176</v>
+      </c>
+      <c r="B366" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="6">
+        <v>76177</v>
+      </c>
+      <c r="B367" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="6">
+        <v>76178</v>
+      </c>
+      <c r="B368" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="6">
+        <v>76183</v>
+      </c>
+      <c r="B369" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="6">
+        <v>76184</v>
+      </c>
+      <c r="B370" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="6">
+        <v>76188</v>
+      </c>
+      <c r="B371" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="6">
+        <v>76189</v>
+      </c>
+      <c r="B372" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="6">
+        <v>76190</v>
+      </c>
+      <c r="B373" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="6">
+        <v>76672</v>
+      </c>
+      <c r="B374" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="6">
+        <v>77402</v>
+      </c>
+      <c r="B375" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="6">
+        <v>77625</v>
+      </c>
+      <c r="B376" s="6">
+        <v>56057</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="6">
+        <v>77784</v>
+      </c>
+      <c r="B377" s="6">
+        <v>68849</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="6">
+        <v>300795</v>
+      </c>
+      <c r="B378" s="6">
+        <v>63744</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="6">
+        <v>300900</v>
+      </c>
+      <c r="B379" s="6">
+        <v>56057</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="6">
+        <v>300902</v>
+      </c>
+      <c r="B380" s="6">
+        <v>65214</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="6">
+        <v>301117</v>
+      </c>
+      <c r="B381" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="6">
+        <v>301159</v>
+      </c>
+      <c r="B382" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="6">
+        <v>301161</v>
+      </c>
+      <c r="B383" s="6">
+        <v>51647</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="6">
+        <v>301167</v>
+      </c>
+      <c r="B384" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="6">
+        <v>301169</v>
+      </c>
+      <c r="B385" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="6">
+        <v>301170</v>
+      </c>
+      <c r="B386" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="6">
+        <v>301172</v>
+      </c>
+      <c r="B387" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="6">
+        <v>301175</v>
+      </c>
+      <c r="B388" s="6">
+        <v>39520</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="6">
+        <v>301176</v>
+      </c>
+      <c r="B389" s="6">
+        <v>51647</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="6">
+        <v>301178</v>
+      </c>
+      <c r="B390" s="6">
+        <v>51647</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="6">
+        <v>301180</v>
+      </c>
+      <c r="B391" s="6">
+        <v>304835</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="6">
+        <v>301258</v>
+      </c>
+      <c r="B392" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="6">
+        <v>301457</v>
+      </c>
+      <c r="B393" s="6">
+        <v>63047</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="6">
+        <v>301544</v>
+      </c>
+      <c r="B394" s="6">
+        <v>40969</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="6">
+        <v>301861</v>
+      </c>
+      <c r="B395" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="6">
+        <v>301862</v>
+      </c>
+      <c r="B396" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="6">
+        <v>301864</v>
+      </c>
+      <c r="B397" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="6">
+        <v>301959</v>
+      </c>
+      <c r="B398" s="6">
+        <v>55012</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="6">
+        <v>301960</v>
+      </c>
+      <c r="B399" s="6">
+        <v>40969</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="6">
+        <v>301961</v>
+      </c>
+      <c r="B400" s="6">
+        <v>74704</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="6">
+        <v>302177</v>
+      </c>
+      <c r="B401" s="6">
+        <v>63047</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="6">
+        <v>302214</v>
+      </c>
+      <c r="B402" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="6">
+        <v>302246</v>
+      </c>
+      <c r="B403" s="6">
+        <v>56057</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="6">
+        <v>302254</v>
+      </c>
+      <c r="B404" s="6">
+        <v>59698</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="6">
+        <v>302286</v>
+      </c>
+      <c r="B405" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="6">
+        <v>302290</v>
+      </c>
+      <c r="B406" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="6">
+        <v>302291</v>
+      </c>
+      <c r="B407" s="6">
+        <v>306118</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="6">
+        <v>302292</v>
+      </c>
+      <c r="B408" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="6">
+        <v>302371</v>
+      </c>
+      <c r="B409" s="6">
+        <v>65214</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="6">
+        <v>302407</v>
+      </c>
+      <c r="B410" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="58">
+        <v>302408</v>
+      </c>
+      <c r="B411" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="58">
+        <v>302409</v>
+      </c>
+      <c r="B412" s="58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="6">
+        <v>302410</v>
+      </c>
+      <c r="B413" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="6">
+        <v>302411</v>
+      </c>
+      <c r="B414" s="6">
+        <v>39681</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="6">
+        <v>302438</v>
+      </c>
+      <c r="B415" s="6">
+        <v>63374</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="6">
+        <v>302440</v>
+      </c>
+      <c r="B416" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="6">
+        <v>302441</v>
+      </c>
+      <c r="B417" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="6">
+        <v>303103</v>
+      </c>
+      <c r="B418" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="6">
+        <v>303933</v>
+      </c>
+      <c r="B419" s="6">
+        <v>40969</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="6">
+        <v>304246</v>
+      </c>
+      <c r="B420" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="6">
+        <v>304250</v>
+      </c>
+      <c r="B421" s="6">
+        <v>54004</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="6">
+        <v>304251</v>
+      </c>
+      <c r="B422" s="6">
+        <v>54004</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="6">
+        <v>304252</v>
+      </c>
+      <c r="B423" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="6">
+        <v>304253</v>
+      </c>
+      <c r="B424" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="6">
+        <v>304254</v>
+      </c>
+      <c r="B425" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="6">
+        <v>304256</v>
+      </c>
+      <c r="B426" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="6">
+        <v>304257</v>
+      </c>
+      <c r="B427" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="6">
+        <v>304258</v>
+      </c>
+      <c r="B428" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="6">
+        <v>304372</v>
+      </c>
+      <c r="B429" s="6">
+        <v>54854</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="6">
+        <v>304454</v>
+      </c>
+      <c r="B430" s="6">
+        <v>73560</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="6">
+        <v>304835</v>
+      </c>
+      <c r="B431" s="6">
+        <v>74704</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="6">
+        <v>305221</v>
+      </c>
+      <c r="B432" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="6">
+        <v>305227</v>
+      </c>
+      <c r="B433" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="6">
+        <v>305228</v>
+      </c>
+      <c r="B434" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="6">
+        <v>305437</v>
+      </c>
+      <c r="B435" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="6">
+        <v>305438</v>
+      </c>
+      <c r="B436" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="6">
+        <v>305439</v>
+      </c>
+      <c r="B437" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="6">
+        <v>305500</v>
+      </c>
+      <c r="B438" s="6">
+        <v>301961</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="6">
+        <v>305691</v>
+      </c>
+      <c r="B439" s="6">
+        <v>66642</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="6">
+        <v>305907</v>
+      </c>
+      <c r="B440" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="6">
+        <v>306026</v>
+      </c>
+      <c r="B441" s="6">
+        <v>64956</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="6">
+        <v>306108</v>
+      </c>
+      <c r="B442" s="6">
+        <v>66642</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="6">
+        <v>306109</v>
+      </c>
+      <c r="B443" s="6">
+        <v>66642</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="6">
+        <v>306118</v>
+      </c>
+      <c r="B444" s="6">
+        <v>68849</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="6">
+        <v>306119</v>
+      </c>
+      <c r="B445" s="6">
+        <v>39491</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="6">
+        <v>306120</v>
+      </c>
+      <c r="B446" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="6">
+        <v>306121</v>
+      </c>
+      <c r="B447" s="6">
+        <v>56285</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="6">
+        <v>306340</v>
+      </c>
+      <c r="B448" s="6">
+        <v>39546</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="6">
+        <v>306530</v>
+      </c>
+      <c r="B449" s="6">
+        <v>63797</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="6">
+        <v>306541</v>
+      </c>
+      <c r="B450" s="6">
+        <v>39520</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>